--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -44,589 +44,589 @@
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614468574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01786661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690081596375</t>
+    <t xml:space="preserve">3.08614444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01786684989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690057754517</t>
   </si>
   <si>
     <t xml:space="preserve">2.98099732398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88131213188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003081321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80620670318604</t>
+    <t xml:space="preserve">2.88131189346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94003105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80620694160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.86082863807678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75841212272644</t>
+    <t xml:space="preserve">2.75841236114502</t>
   </si>
   <si>
     <t xml:space="preserve">2.73929476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69013476371765</t>
+    <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
     <t xml:space="preserve">2.71744608879089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.866290807724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76387453079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7447566986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7570469379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71061825752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110151290894</t>
+    <t xml:space="preserve">2.86629104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76387429237366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74475693702698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75704717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.710618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110127449036</t>
   </si>
   <si>
     <t xml:space="preserve">2.76114368438721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72563934326172</t>
+    <t xml:space="preserve">2.7256395816803</t>
   </si>
   <si>
     <t xml:space="preserve">2.69696283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290802001953</t>
+    <t xml:space="preserve">2.72290825843811</t>
   </si>
   <si>
     <t xml:space="preserve">2.62868499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935654640198</t>
+    <t xml:space="preserve">2.45935678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45799112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30095314979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50442004203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81713104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78162693977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8335177898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84717321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8840434551239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540863990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769816398621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85126996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685864448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94958972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05883312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164855003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124987602234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767855644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001072883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2226996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089289665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076685905457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22543048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587157249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463266372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732157707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608242988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3865659236908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833025932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375025749207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780530929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2636661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1918261051178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1562032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330288887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3229193687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856772422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3343186378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403791427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.476811170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833804130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116209983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844012260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796053886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8997175693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89686751365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495712280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938532829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671439170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500840187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96526408195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233746528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058043479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17045259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702063560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9196662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86551904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90399193763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83559584617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79854798316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442625999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771737575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88546824455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92109107971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94103980064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694407463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85839462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707191467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007509231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80567240715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75865006446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77859902381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68597912788391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62470746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54776120185852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605568885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463089942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333323478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5719850063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45086693763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44516730308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42379307746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44374203681946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41666841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941615104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900782585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61045837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54918622970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57910966873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5506112575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57340979576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69310355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64038157463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63895630836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898230552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63325691223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67172956466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727583885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67315483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7030782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71447706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65178060531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66887974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65748071670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486082077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498818397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41524362564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43234276771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43661737442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39387011528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39244484901428</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30095291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38971400260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50441980361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67511391639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7488534450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78162670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467259407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8621940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8335177898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88404297828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540863990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769864082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85126972198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94685840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9495894908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173289299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1790018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217421531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635506629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269940376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089289665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952723503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076685905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543025016785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2923424243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587228775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463290214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27732157707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559941291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656544685364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511591911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375001907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780507087708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26366686820984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182634353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15620303153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13482975959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291960716248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856724739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33431839942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31151986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419103622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403767585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406343460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108553886414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841460227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607542991638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796030044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89971780776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89686751365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938508987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671415328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500840187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96526384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9552891254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99233746528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058043479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1704523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13625454902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702111244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91966652870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86551928520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90399217605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84129524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83559584617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79854822158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73442649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77717399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88546824455261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87406873703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272050857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834334373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9410400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85839462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409425735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707191467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007485389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80567240715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289891242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75865006446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77859902381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68597912788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62470746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478402137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54776167869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610672950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5719850063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45086693763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44516682624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42379331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44374179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941615104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61045813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54918670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57910990715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5506112575531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52353763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69310355186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64038133621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63895630836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898182868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63325691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67172980308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67315483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7144775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735287666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65178084373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66887974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65748047828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498818397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41524386405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43234252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43661761283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39386987686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39244484901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45799160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3511221408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236804962158</t>
+    <t xml:space="preserve">2.35112237930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236828804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.53066253662109</t>
@@ -641,22 +641,22 @@
     <t xml:space="preserve">2.63468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69595336914062</t>
+    <t xml:space="preserve">2.6959536075592</t>
   </si>
   <si>
     <t xml:space="preserve">2.68027925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69167876243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69737839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297571182251</t>
+    <t xml:space="preserve">2.69167900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69737863540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297595024109</t>
   </si>
   <si>
     <t xml:space="preserve">2.72445201873779</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7558000087738</t>
+    <t xml:space="preserve">2.7287266254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152564048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75580024719238</t>
   </si>
   <si>
     <t xml:space="preserve">2.71162748336792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69025349617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65035581588745</t>
+    <t xml:space="preserve">2.69025373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65035557746887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60760831832886</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">2.55346131324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5206880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60618329048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54491114616394</t>
+    <t xml:space="preserve">2.52068781852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60618305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058573722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54491138458252</t>
   </si>
   <si>
     <t xml:space="preserve">2.54063701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501370429993</t>
+    <t xml:space="preserve">2.50501394271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.49788928031921</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">2.57625985145569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60048365592957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193396568298</t>
+    <t xml:space="preserve">2.60048341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193420410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.58195972442627</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">2.75722503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79712319374084</t>
+    <t xml:space="preserve">2.7714741230011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79712343215942</t>
   </si>
   <si>
     <t xml:space="preserve">2.78857350349426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79997253417969</t>
+    <t xml:space="preserve">2.79997277259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.83132100105286</t>
@@ -782,43 +782,43 @@
     <t xml:space="preserve">3.06215834617615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15477871894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727053642273</t>
+    <t xml:space="preserve">3.15477848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727077484131</t>
   </si>
   <si>
     <t xml:space="preserve">3.25737261772156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07783246040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1619029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16047787666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21889996528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2217493057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159689903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23172402381897</t>
+    <t xml:space="preserve">3.07783269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16760277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16190338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16047811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21889972686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174954414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589678764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23172426223755</t>
   </si>
   <si>
     <t xml:space="preserve">3.1291298866272</t>
@@ -830,40 +830,40 @@
     <t xml:space="preserve">3.10063147544861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19752645492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.238849401474</t>
+    <t xml:space="preserve">3.19752597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884868621826</t>
   </si>
   <si>
     <t xml:space="preserve">3.22602438926697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29157114028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32576942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302145004272</t>
+    <t xml:space="preserve">3.29157090187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32576966285706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302121162415</t>
   </si>
   <si>
     <t xml:space="preserve">3.31864428520203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34001851081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35569262504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457360267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27019762992859</t>
+    <t xml:space="preserve">3.3400182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559054374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3556923866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457407951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27019715309143</t>
   </si>
   <si>
     <t xml:space="preserve">3.08923196792603</t>
@@ -875,61 +875,61 @@
     <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11147856712341</t>
+    <t xml:space="preserve">3.09706664085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11147880554199</t>
   </si>
   <si>
     <t xml:space="preserve">3.13886070251465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14462494850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003708839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11868405342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07112598419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03797912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04806733131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00627326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97744989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91836261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8722448348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90395069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89098024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87512731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918642044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92700910568237</t>
+    <t xml:space="preserve">3.14462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1186842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07112574577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0379786491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04806756973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762606620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00627303123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97745013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9183623790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87224459648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90395045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89098000526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87512707710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918618202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92700886726379</t>
   </si>
   <si>
     <t xml:space="preserve">2.90683269500732</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85783338546753</t>
+    <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.8535099029541</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">2.82468628883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79298067092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76415729522705</t>
+    <t xml:space="preserve">2.79298043251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76415705680847</t>
   </si>
   <si>
     <t xml:space="preserve">2.81027483940125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80018639564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79153966903687</t>
+    <t xml:space="preserve">2.80018615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79153943061829</t>
   </si>
   <si>
     <t xml:space="preserve">2.72956943511963</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">2.75262808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75983381271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74686336517334</t>
+    <t xml:space="preserve">2.75983357429504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74686360359192</t>
   </si>
   <si>
     <t xml:space="preserve">2.95439124107361</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">2.92845034599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9255678653717</t>
+    <t xml:space="preserve">2.92556810379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189225196838</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">2.80450987815857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83045077323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82612752914429</t>
+    <t xml:space="preserve">2.83045101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82612776756287</t>
   </si>
   <si>
     <t xml:space="preserve">2.78865718841553</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80883359909058</t>
+    <t xml:space="preserve">2.808833360672</t>
   </si>
   <si>
     <t xml:space="preserve">2.84053897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85495090484619</t>
+    <t xml:space="preserve">2.85495066642761</t>
   </si>
   <si>
     <t xml:space="preserve">2.86503934860229</t>
@@ -1031,55 +1031,55 @@
     <t xml:space="preserve">2.90827393531799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83909821510315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73821663856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75551009178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76848101615906</t>
+    <t xml:space="preserve">2.83909797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73821640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7555103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7684805393219</t>
   </si>
   <si>
     <t xml:space="preserve">2.70218729972839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72668695449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71371650695801</t>
+    <t xml:space="preserve">2.72668719291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71371626853943</t>
   </si>
   <si>
     <t xml:space="preserve">2.7252459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68056988716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6748046875</t>
+    <t xml:space="preserve">2.6805694103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480492591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.67336392402649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65895247459412</t>
+    <t xml:space="preserve">2.65895223617554</t>
   </si>
   <si>
     <t xml:space="preserve">2.67624616622925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75406908988953</t>
+    <t xml:space="preserve">2.75406932830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79874515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74542212486267</t>
+    <t xml:space="preserve">2.79874563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74542188644409</t>
   </si>
   <si>
     <t xml:space="preserve">2.78577518463135</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">2.92268586158752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0250084400177</t>
+    <t xml:space="preserve">3.02500820159912</t>
   </si>
   <si>
     <t xml:space="preserve">3.02644968032837</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">3.10571384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12156653404236</t>
+    <t xml:space="preserve">3.12156629562378</t>
   </si>
   <si>
     <t xml:space="preserve">3.17056632041931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14174294471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597869873047</t>
+    <t xml:space="preserve">3.14174318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597846031189</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850811958313</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">3.08409667015076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07400822639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04086089134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05383157730103</t>
+    <t xml:space="preserve">3.07400798797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04086112976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0538318157196</t>
   </si>
   <si>
     <t xml:space="preserve">3.17921352386475</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">3.12589001655579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05527281761169</t>
+    <t xml:space="preserve">3.05527257919312</t>
   </si>
   <si>
     <t xml:space="preserve">3.07977294921875</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.16191935539246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14750790596008</t>
+    <t xml:space="preserve">3.1475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">3.09994912147522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13453674316406</t>
+    <t xml:space="preserve">3.13453698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.15903687477112</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">3.15471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12877225875854</t>
+    <t xml:space="preserve">3.12877249717712</t>
   </si>
   <si>
     <t xml:space="preserve">3.11580181121826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10427284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815529823303</t>
+    <t xml:space="preserve">3.10427260398865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815505981445</t>
   </si>
   <si>
     <t xml:space="preserve">3.00483226776123</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.86792135238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89674472808838</t>
+    <t xml:space="preserve">2.8967444896698</t>
   </si>
   <si>
     <t xml:space="preserve">2.88233304023743</t>
@@ -1208,34 +1208,34 @@
     <t xml:space="preserve">2.8290102481842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70362830162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72236371040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70506978034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71227550506592</t>
+    <t xml:space="preserve">2.82324528694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70362854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72236394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70506930351257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71227502822876</t>
   </si>
   <si>
     <t xml:space="preserve">2.65606999397278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69858431816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76703929901123</t>
+    <t xml:space="preserve">2.69858407974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76703953742981</t>
   </si>
   <si>
     <t xml:space="preserve">2.78505420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72740745544434</t>
+    <t xml:space="preserve">2.72740769386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.69498157501221</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">2.7057900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73101043701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72020220756531</t>
+    <t xml:space="preserve">2.7310106754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72020173072815</t>
   </si>
   <si>
     <t xml:space="preserve">2.79225993156433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84630370140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77424550056458</t>
+    <t xml:space="preserve">2.84630393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77424573898315</t>
   </si>
   <si>
     <t xml:space="preserve">2.77064275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70939326286316</t>
+    <t xml:space="preserve">2.709392786026</t>
   </si>
   <si>
     <t xml:space="preserve">2.74181938171387</t>
@@ -1280,67 +1280,67 @@
     <t xml:space="preserve">2.62652587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64093780517578</t>
+    <t xml:space="preserve">2.64093732833862</t>
   </si>
   <si>
     <t xml:space="preserve">2.65534925460815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64814352989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58689379692078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5724823474884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57968831062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55807042121887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56167364120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086493492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5688796043396</t>
+    <t xml:space="preserve">2.64814329147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5868935585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57968783378601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55807065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56167340278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086445808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56887936592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.43557143211365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37432169914246</t>
+    <t xml:space="preserve">2.37432193756104</t>
   </si>
   <si>
     <t xml:space="preserve">2.30946922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39593935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41755652427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3599100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4499831199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35270428657532</t>
+    <t xml:space="preserve">2.39593958854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41755676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41395354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36351323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35991048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505777359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44998288154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3527045249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.52204132080078</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">2.44638013839722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4211597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59409976005554</t>
+    <t xml:space="preserve">2.42115998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50762963294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59409999847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527638435364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63012909889221</t>
+    <t xml:space="preserve">2.63012886047363</t>
   </si>
   <si>
     <t xml:space="preserve">2.65174651145935</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60851144790649</t>
+    <t xml:space="preserve">2.60851120948792</t>
   </si>
   <si>
     <t xml:space="preserve">2.6373348236084</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">2.69137835502625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67696690559387</t>
+    <t xml:space="preserve">2.67696666717529</t>
   </si>
   <si>
     <t xml:space="preserve">2.73281216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172222137451</t>
+    <t xml:space="preserve">2.62172174453735</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48841404914856</t>
+    <t xml:space="preserve">2.48841428756714</t>
   </si>
   <si>
     <t xml:space="preserve">2.40324521064758</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.45879006385803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39213609695435</t>
+    <t xml:space="preserve">2.39213633537292</t>
   </si>
   <si>
     <t xml:space="preserve">2.40694832801819</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.36991810798645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29956150054932</t>
+    <t xml:space="preserve">2.29956126213074</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068906784058</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">2.38843297958374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4291660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805696487427</t>
+    <t xml:space="preserve">2.42916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805720329285</t>
   </si>
   <si>
     <t xml:space="preserve">2.46989917755127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5032262802124</t>
+    <t xml:space="preserve">2.50322604179382</t>
   </si>
   <si>
     <t xml:space="preserve">2.52174115180969</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">2.45508694648743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58098912239075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395914077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47360229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44768095016479</t>
+    <t xml:space="preserve">2.58098888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395890235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4736020565033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44768118858337</t>
   </si>
   <si>
     <t xml:space="preserve">2.53655314445496</t>
@@ -1487,58 +1487,58 @@
     <t xml:space="preserve">2.51433515548706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48100805282593</t>
+    <t xml:space="preserve">2.48100781440735</t>
   </si>
   <si>
     <t xml:space="preserve">2.46619606018066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39583897590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41065120697021</t>
+    <t xml:space="preserve">2.39583921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41065096855164</t>
   </si>
   <si>
     <t xml:space="preserve">2.35140299797058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36621499061584</t>
+    <t xml:space="preserve">2.36621522903442</t>
   </si>
   <si>
     <t xml:space="preserve">2.34399724006653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35880899429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35510611534119</t>
+    <t xml:space="preserve">2.35880923271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35510635375977</t>
   </si>
   <si>
     <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30696702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31066989898682</t>
+    <t xml:space="preserve">2.30696725845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39954209327698</t>
+    <t xml:space="preserve">2.39954233169556</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41435384750366</t>
+    <t xml:space="preserve">2.41435408592224</t>
   </si>
   <si>
     <t xml:space="preserve">2.37362122535706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31807613372803</t>
+    <t xml:space="preserve">2.31807637214661</t>
   </si>
   <si>
     <t xml:space="preserve">2.29585814476013</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">2.28104615211487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26993703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30326414108276</t>
+    <t xml:space="preserve">2.26993727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30326437950134</t>
   </si>
   <si>
     <t xml:space="preserve">2.32918524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27734303474426</t>
+    <t xml:space="preserve">2.27734327316284</t>
   </si>
   <si>
     <t xml:space="preserve">2.26623439788818</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">2.29215526580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27363991737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2884521484375</t>
+    <t xml:space="preserve">2.27364039421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28845191001892</t>
   </si>
   <si>
     <t xml:space="preserve">2.28474926948547</t>
@@ -1580,49 +1580,49 @@
     <t xml:space="preserve">2.20698618888855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24031329154968</t>
+    <t xml:space="preserve">2.24031352996826</t>
   </si>
   <si>
     <t xml:space="preserve">2.15514421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13292622566223</t>
+    <t xml:space="preserve">2.13292646408081</t>
   </si>
   <si>
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1033022403717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849048614502</t>
+    <t xml:space="preserve">2.10330247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959959983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849024772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10700535774231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06256937980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98850953578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147967338562</t>
+    <t xml:space="preserve">2.0625696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98850929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147955417633</t>
   </si>
   <si>
     <t xml:space="preserve">2.02553939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06627225875854</t>
+    <t xml:space="preserve">2.06627249717712</t>
   </si>
   <si>
     <t xml:space="preserve">2.04775738716125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06997537612915</t>
+    <t xml:space="preserve">2.06997561454773</t>
   </si>
   <si>
     <t xml:space="preserve">2.12922334671021</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">2.13662934303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18847107887268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439218521118</t>
+    <t xml:space="preserve">2.18847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439242362976</t>
   </si>
   <si>
     <t xml:space="preserve">2.23290753364563</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">2.1995804309845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811447143555</t>
+    <t xml:space="preserve">2.21809506416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811423301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.07367849349976</t>
@@ -1667,85 +1667,88 @@
     <t xml:space="preserve">2.24771928787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33659100532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51063203811646</t>
+    <t xml:space="preserve">2.3365912437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51063227653503</t>
   </si>
   <si>
     <t xml:space="preserve">2.65504908561707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68096995353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60320711135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62912797927856</t>
+    <t xml:space="preserve">2.68096971511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60320734977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62912821769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6661581993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.65875172615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65134620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62542486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71800017356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70318818092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72910904884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69207882881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71429705619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75502991676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80316877365112</t>
+    <t xml:space="preserve">2.65134596824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62542510032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71799993515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70318794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7291088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69207906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71429681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75502967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8031690120697</t>
   </si>
   <si>
     <t xml:space="preserve">2.81798100471497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84390187263489</t>
+    <t xml:space="preserve">2.84390163421631</t>
   </si>
   <si>
     <t xml:space="preserve">2.87352585792542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86241698265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88093209266663</t>
+    <t xml:space="preserve">2.86241674423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88093185424805</t>
   </si>
   <si>
     <t xml:space="preserve">2.76243615150452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76984190940857</t>
+    <t xml:space="preserve">2.76984214782715</t>
   </si>
   <si>
     <t xml:space="preserve">2.7994658946991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79206013679504</t>
+    <t xml:space="preserve">2.79205989837646</t>
   </si>
   <si>
     <t xml:space="preserve">2.81427788734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79576325416565</t>
+    <t xml:space="preserve">2.79576301574707</t>
   </si>
   <si>
     <t xml:space="preserve">2.75873303413391</t>
@@ -1769,13 +1772,13 @@
     <t xml:space="preserve">2.962397813797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98091268539429</t>
+    <t xml:space="preserve">2.98091292381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.91796183586121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758558273315</t>
+    <t xml:space="preserve">2.94758582115173</t>
   </si>
   <si>
     <t xml:space="preserve">2.95128846168518</t>
@@ -1784,7 +1787,7 @@
     <t xml:space="preserve">2.93647694587708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95499181747437</t>
+    <t xml:space="preserve">2.95499157905579</t>
   </si>
   <si>
     <t xml:space="preserve">2.93277382850647</t>
@@ -1799,34 +1802,34 @@
     <t xml:space="preserve">2.97720980644226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9401798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89944672584534</t>
+    <t xml:space="preserve">2.94018006324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89944696426392</t>
   </si>
   <si>
     <t xml:space="preserve">2.81057500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8661196231842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80687165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85501098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71059417724609</t>
+    <t xml:space="preserve">2.86611986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80687212944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279299736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85501074790955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71059393882751</t>
   </si>
   <si>
     <t xml:space="preserve">2.70689082145691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61061334609985</t>
+    <t xml:space="preserve">2.61061310768127</t>
   </si>
   <si>
     <t xml:space="preserve">2.6402370929718</t>
@@ -1835,58 +1838,55 @@
     <t xml:space="preserve">2.6365339756012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63283109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61801934242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69578194618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467307090759</t>
+    <t xml:space="preserve">2.63283085823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61801910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69578218460083</t>
   </si>
   <si>
     <t xml:space="preserve">2.6883761882782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61431622505188</t>
+    <t xml:space="preserve">2.6143159866333</t>
   </si>
   <si>
     <t xml:space="preserve">2.56988024711609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211740493774</t>
+    <t xml:space="preserve">2.49211716651917</t>
   </si>
   <si>
     <t xml:space="preserve">2.50692915916443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34770035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2366099357605</t>
+    <t xml:space="preserve">2.34770011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23661041259766</t>
   </si>
   <si>
     <t xml:space="preserve">2.18476843833923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587731361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.299480676651</t>
+    <t xml:space="preserve">2.19587755203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29948091506958</t>
   </si>
   <si>
     <t xml:space="preserve">2.21777319908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10883021354675</t>
+    <t xml:space="preserve">2.10883045196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.12439346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893759727478</t>
+    <t xml:space="preserve">2.08937573432922</t>
   </si>
   <si>
     <t xml:space="preserve">2.10104846954346</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326696395874</t>
+    <t xml:space="preserve">2.09326672554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.12050271034241</t>
@@ -1910,70 +1910,70 @@
     <t xml:space="preserve">2.07770371437073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05046796798706</t>
+    <t xml:space="preserve">2.0504674911499</t>
   </si>
   <si>
     <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03490447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03101348876953</t>
+    <t xml:space="preserve">2.03490424156189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435872077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03101372718811</t>
   </si>
   <si>
     <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0582492351532</t>
+    <t xml:space="preserve">2.05824947357178</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944593429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1866466999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96876037120819</t>
+    <t xml:space="preserve">2.22944569587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18664693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9687602519989</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92985200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02712249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94152438640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84425354003906</t>
+    <t xml:space="preserve">1.92985165119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02712273597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94152414798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84425377845764</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76643693447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8092360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7508739233017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74698269367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69251120090485</t>
+    <t xml:space="preserve">1.76643705368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80923628807068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75087368488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74698281288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69251132011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.78978192806244</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">1.7119654417038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71974694728851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7041836977005</t>
+    <t xml:space="preserve">1.71974718570709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70418393611908</t>
   </si>
   <si>
     <t xml:space="preserve">1.78589129447937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141944408417</t>
+    <t xml:space="preserve">1.73141956329346</t>
   </si>
   <si>
     <t xml:space="preserve">1.71585619449615</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">1.78200030326843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83258104324341</t>
+    <t xml:space="preserve">1.83258128166199</t>
   </si>
   <si>
     <t xml:space="preserve">1.80145454406738</t>
@@ -2024,43 +2024,43 @@
     <t xml:space="preserve">1.84036290645599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85592615604401</t>
+    <t xml:space="preserve">1.85592603683472</t>
   </si>
   <si>
     <t xml:space="preserve">1.83647203445435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87927114963531</t>
+    <t xml:space="preserve">1.87927103042603</t>
   </si>
   <si>
     <t xml:space="preserve">1.79756367206573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77032780647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869040966034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75476455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75865530967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254618167877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80534529685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81701791286469</t>
+    <t xml:space="preserve">1.77032792568207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869017124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75476467609406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75865542888641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254630088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80534517765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8170177936554</t>
   </si>
   <si>
     <t xml:space="preserve">1.82479953765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91428864002228</t>
+    <t xml:space="preserve">1.91428852081299</t>
   </si>
   <si>
     <t xml:space="preserve">1.93374276161194</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">1.89094376564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87538027763367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89483439922333</t>
+    <t xml:space="preserve">1.87538015842438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650689601898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89483463764191</t>
   </si>
   <si>
     <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92207038402557</t>
+    <t xml:space="preserve">1.92207050323486</t>
   </si>
   <si>
     <t xml:space="preserve">2.01155948638916</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">2.08159446716309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06214022636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13217496871948</t>
+    <t xml:space="preserve">2.06213998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13217544555664</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">2.15551996231079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19831919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1710832118988</t>
+    <t xml:space="preserve">2.19831943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17108345031738</t>
   </si>
   <si>
     <t xml:space="preserve">2.14384770393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11272072792053</t>
+    <t xml:space="preserve">2.11272096633911</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548521995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01545023918152</t>
+    <t xml:space="preserve">2.01545000076294</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821449279785</t>
@@ -2138,40 +2138,40 @@
     <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01934099197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87148940563202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91039764881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596113681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872539043427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9531968832016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99988687038422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95708787441254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96486961841583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72752857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862056732178</t>
+    <t xml:space="preserve">2.01934123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8714896440506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91039776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596089839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872527122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95319664478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99988698959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95708775520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96486937999725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210500717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72752869129181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862044811249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">1.48941004276276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45361435413361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33844578266144</t>
+    <t xml:space="preserve">1.45361423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33844566345215</t>
   </si>
   <si>
     <t xml:space="preserve">1.30420637130737</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">1.09098887443542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16102385520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08009457588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05986213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08476364612579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10188317298889</t>
+    <t xml:space="preserve">1.16102373600006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08009445667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05986225605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0847635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10188329219818</t>
   </si>
   <si>
     <t xml:space="preserve">1.22483336925507</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">1.31976974010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910752296448</t>
+    <t xml:space="preserve">1.32910776138306</t>
   </si>
   <si>
     <t xml:space="preserve">1.35400903224945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26685440540314</t>
+    <t xml:space="preserve">1.26685428619385</t>
   </si>
   <si>
     <t xml:space="preserve">1.27152335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32288241386414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28864312171936</t>
+    <t xml:space="preserve">1.32288253307343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28864300251007</t>
   </si>
   <si>
     <t xml:space="preserve">1.28397405147552</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">1.39291739463806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36179065704346</t>
+    <t xml:space="preserve">1.36179077625275</t>
   </si>
   <si>
     <t xml:space="preserve">1.26062905788422</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29953742027283</t>
+    <t xml:space="preserve">1.29953730106354</t>
   </si>
   <si>
     <t xml:space="preserve">1.31354439258575</t>
@@ -2276,25 +2276,25 @@
     <t xml:space="preserve">1.28241777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2295024394989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23884046077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24350941181183</t>
+    <t xml:space="preserve">1.22950255870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23884057998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24350953102112</t>
   </si>
   <si>
     <t xml:space="preserve">1.20927011966705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13300967216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10343956947327</t>
+    <t xml:space="preserve">1.17503082752228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13300979137421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10343945026398</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">1.06764376163483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12211561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10655224323273</t>
+    <t xml:space="preserve">1.12211549282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10655212402344</t>
   </si>
   <si>
     <t xml:space="preserve">1.14234793186188</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708672523499</t>
+    <t xml:space="preserve">1.28708684444427</t>
   </si>
   <si>
     <t xml:space="preserve">1.27930498123169</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">1.16413640975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23572778701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2061573266983</t>
+    <t xml:space="preserve">1.23572790622711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20615744590759</t>
   </si>
   <si>
     <t xml:space="preserve">1.20771384239197</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">1.15791118144989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14079141616821</t>
+    <t xml:space="preserve">1.1407915353775</t>
   </si>
   <si>
     <t xml:space="preserve">1.18436884880066</t>
@@ -2384,46 +2384,46 @@
     <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546048641205</t>
+    <t xml:space="preserve">1.14546060562134</t>
   </si>
   <si>
     <t xml:space="preserve">1.16724920272827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17347455024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15168583393097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17191815376282</t>
+    <t xml:space="preserve">1.1734744310379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15168571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17191827297211</t>
   </si>
   <si>
     <t xml:space="preserve">1.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15635478496552</t>
+    <t xml:space="preserve">1.15635466575623</t>
   </si>
   <si>
     <t xml:space="preserve">1.1252281665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09565782546997</t>
+    <t xml:space="preserve">1.09565794467926</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08320713043213</t>
+    <t xml:space="preserve">1.06608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08320724964142</t>
   </si>
   <si>
     <t xml:space="preserve">1.06297492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04896795749664</t>
+    <t xml:space="preserve">1.04896783828735</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410154819489</t>
@@ -2441,28 +2441,28 @@
     <t xml:space="preserve">1.05052423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585528373718</t>
+    <t xml:space="preserve">1.04585516452789</t>
   </si>
   <si>
     <t xml:space="preserve">1.03962993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04118633270264</t>
+    <t xml:space="preserve">1.04118621349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03496086597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0365172624588</t>
+    <t xml:space="preserve">1.03496098518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03651738166809</t>
   </si>
   <si>
     <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996052622795105</t>
+    <t xml:space="preserve">0.996052503585815</t>
   </si>
   <si>
     <t xml:space="preserve">1.01628482341766</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">1.00072157382965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991383731365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96648234128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96492600440979</t>
+    <t xml:space="preserve">0.991383612155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966482281684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964925825595856</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
@@ -2495,58 +2495,58 @@
     <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827215671539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969595015048981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949362695217133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968038558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957144320011139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99916535615921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05830597877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02406656742096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988270998001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985158324241638</t>
+    <t xml:space="preserve">0.989827275276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969594955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949362635612488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968038618564606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957144260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489313602448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999165296554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06453120708466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05830574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02406668663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988270938396454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985158383846283</t>
   </si>
   <si>
     <t xml:space="preserve">0.941581070423126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93379932641983</t>
+    <t xml:space="preserve">0.933799386024475</t>
   </si>
   <si>
     <t xml:space="preserve">0.904228985309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879327654838562</t>
+    <t xml:space="preserve">0.879327714443207</t>
   </si>
   <si>
     <t xml:space="preserve">0.887109339237213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888665616512299</t>
+    <t xml:space="preserve">0.888665556907654</t>
   </si>
   <si>
     <t xml:space="preserve">0.891778409481049</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.83575040102005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803067326545715</t>
+    <t xml:space="preserve">0.80306738615036</t>
   </si>
   <si>
     <t xml:space="preserve">0.787504076957703</t>
@@ -2564,61 +2564,61 @@
     <t xml:space="preserve">0.829525053501129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831081390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840419352054596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826412498950958</t>
+    <t xml:space="preserve">0.831081330776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840419471263885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826412379741669</t>
   </si>
   <si>
     <t xml:space="preserve">0.817074358463287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866877019405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896447241306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902672648429871</t>
+    <t xml:space="preserve">0.86687707901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896447360515594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902672588825226</t>
   </si>
   <si>
     <t xml:space="preserve">0.915123343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940024495124817</t>
+    <t xml:space="preserve">0.940024614334106</t>
   </si>
   <si>
     <t xml:space="preserve">0.977376639842987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963369607925415</t>
+    <t xml:space="preserve">0.963369727134705</t>
   </si>
   <si>
     <t xml:space="preserve">0.983601987361908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978932917118073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92913031578064</t>
+    <t xml:space="preserve">0.978932976722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929130256175995</t>
   </si>
   <si>
     <t xml:space="preserve">0.961813151836395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946249902248383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943137288093567</t>
+    <t xml:space="preserve">0.946250081062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943137407302856</t>
   </si>
   <si>
     <t xml:space="preserve">0.930686712265015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952475309371948</t>
+    <t xml:space="preserve">0.952475190162659</t>
   </si>
   <si>
     <t xml:space="preserve">0.927574038505554</t>
@@ -2627,34 +2627,34 @@
     <t xml:space="preserve">0.926017701625824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935355663299561</t>
+    <t xml:space="preserve">0.935355603694916</t>
   </si>
   <si>
     <t xml:space="preserve">0.971151292324066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792294502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913566946983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341599464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8995600938797</t>
+    <t xml:space="preserve">0.947806298732758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913567066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341659069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679680347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560034275055</t>
   </si>
   <si>
     <t xml:space="preserve">0.918236017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908897995948792</t>
+    <t xml:space="preserve">0.908898055553436</t>
   </si>
   <si>
     <t xml:space="preserve">0.894890964031219</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">0.910454332828522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944693684577942</t>
+    <t xml:space="preserve">0.944693624973297</t>
   </si>
   <si>
     <t xml:space="preserve">1.01784121990204</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12989735603333</t>
+    <t xml:space="preserve">1.12989723682404</t>
   </si>
   <si>
     <t xml:space="preserve">1.10032689571381</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">1.09877049922943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07231283187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12834084033966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12055909633636</t>
+    <t xml:space="preserve">1.07231295108795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12834095954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12055921554565</t>
   </si>
   <si>
     <t xml:space="preserve">1.11744654178619</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">1.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25751650333405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26841068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27307987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36023437976837</t>
+    <t xml:space="preserve">1.25751638412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26841080188751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27307975292206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36023426055908</t>
   </si>
   <si>
     <t xml:space="preserve">1.38513565063477</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">1.40069901943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381169319153</t>
+    <t xml:space="preserve">1.40381157398224</t>
   </si>
   <si>
     <t xml:space="preserve">1.37112867832184</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">1.39447367191315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38980460166931</t>
+    <t xml:space="preserve">1.3898047208786</t>
   </si>
   <si>
     <t xml:space="preserve">1.39758634567261</t>
@@ -2768,22 +2768,22 @@
     <t xml:space="preserve">1.40536797046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43805086612701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52053654193878</t>
+    <t xml:space="preserve">1.43805110454559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52053642272949</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022310256958</t>
+    <t xml:space="preserve">1.56022322177887</t>
   </si>
   <si>
     <t xml:space="preserve">1.58745884895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53765606880188</t>
+    <t xml:space="preserve">1.53765618801117</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431119441986</t>
@@ -2792,43 +2792,46 @@
     <t xml:space="preserve">1.50341689586639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497317314148</t>
+    <t xml:space="preserve">1.50497329235077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49096620082855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51798808574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871316432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45281779766083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46712338924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47348165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48619771003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48937666416168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49096632003784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51798808574677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871316432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45281779766083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46712338924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47348153591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48619771003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48937678337097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48142910003662</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.54818880558014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55454683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55613648891449</t>
+    <t xml:space="preserve">1.55454695224762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5561363697052</t>
   </si>
   <si>
     <t xml:space="preserve">1.57044196128845</t>
@@ -2840,10 +2843,10 @@
     <t xml:space="preserve">1.567263007164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53706216812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52752506732941</t>
+    <t xml:space="preserve">1.53706228733063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5275251865387</t>
   </si>
   <si>
     <t xml:space="preserve">1.47030258178711</t>
@@ -2855,13 +2858,13 @@
     <t xml:space="preserve">1.40672183036804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43374371528625</t>
+    <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
     <t xml:space="preserve">1.44487023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39241623878479</t>
+    <t xml:space="preserve">1.39241635799408</t>
   </si>
   <si>
     <t xml:space="preserve">1.35744690895081</t>
@@ -2876,10 +2879,10 @@
     <t xml:space="preserve">1.33201456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35585725307465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929838657379</t>
+    <t xml:space="preserve">1.35585737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929850578308</t>
   </si>
   <si>
     <t xml:space="preserve">1.31453001499176</t>
@@ -2888,25 +2891,25 @@
     <t xml:space="preserve">1.27638149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3018137216568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30499279499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31135094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30340337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22074854373932</t>
+    <t xml:space="preserve">1.30181384086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30499291419983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31135082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30340325832367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28432905673981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479207515717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22074842453003</t>
   </si>
   <si>
     <t xml:space="preserve">1.2223379611969</t>
@@ -2924,10 +2927,10 @@
     <t xml:space="preserve">1.28273963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2271066904068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2112113237381</t>
+    <t xml:space="preserve">1.22710657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21121144294739</t>
   </si>
   <si>
     <t xml:space="preserve">1.2732025384903</t>
@@ -2939,37 +2942,37 @@
     <t xml:space="preserve">1.37652099132538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36698400974274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35267841815948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37493169307709</t>
+    <t xml:space="preserve">1.36698389053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3526782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3749315738678</t>
   </si>
   <si>
     <t xml:space="preserve">1.37969994544983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38128972053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34314131736755</t>
+    <t xml:space="preserve">1.38128960132599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34314119815826</t>
   </si>
   <si>
     <t xml:space="preserve">1.33678317070007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221528053284</t>
+    <t xml:space="preserve">1.36221539974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.363804936409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39877438545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897510528564</t>
+    <t xml:space="preserve">1.39877426624298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897498607635</t>
   </si>
   <si>
     <t xml:space="preserve">1.40513241291046</t>
@@ -2981,7 +2984,7 @@
     <t xml:space="preserve">1.49732422828674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189211845398</t>
+    <t xml:space="preserve">1.47189199924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738556861877</t>
@@ -2990,7 +2993,7 @@
     <t xml:space="preserve">1.4146693944931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42420661449432</t>
+    <t xml:space="preserve">1.42420649528503</t>
   </si>
   <si>
     <t xml:space="preserve">1.45917594432831</t>
@@ -3029,7 +3032,7 @@
     <t xml:space="preserve">1.33837270736694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38287913799286</t>
+    <t xml:space="preserve">1.38287925720215</t>
   </si>
   <si>
     <t xml:space="preserve">1.50050342082977</t>
@@ -3050,7 +3053,7 @@
     <t xml:space="preserve">1.50209283828735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51321947574615</t>
+    <t xml:space="preserve">1.51321959495544</t>
   </si>
   <si>
     <t xml:space="preserve">1.47507095336914</t>
@@ -3071,7 +3074,7 @@
     <t xml:space="preserve">1.48301875591278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51004028320312</t>
+    <t xml:space="preserve">1.51004040241241</t>
   </si>
   <si>
     <t xml:space="preserve">1.56249439716339</t>
@@ -3086,7 +3089,7 @@
     <t xml:space="preserve">1.67693960666656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70078253746033</t>
+    <t xml:space="preserve">1.70078241825104</t>
   </si>
   <si>
     <t xml:space="preserve">1.65309679508209</t>
@@ -3098,13 +3101,13 @@
     <t xml:space="preserve">1.55772590637207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57362115383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43851220607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645977020264</t>
+    <t xml:space="preserve">1.57362103462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43851208686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645988941193</t>
   </si>
   <si>
     <t xml:space="preserve">1.45440745353699</t>
@@ -3116,7 +3119,7 @@
     <t xml:space="preserve">1.49414527416229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51639842987061</t>
+    <t xml:space="preserve">1.5163985490799</t>
   </si>
   <si>
     <t xml:space="preserve">1.61335909366608</t>
@@ -3134,7 +3137,7 @@
     <t xml:space="preserve">1.59349024295807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58792674541473</t>
+    <t xml:space="preserve">1.58792662620544</t>
   </si>
   <si>
     <t xml:space="preserve">1.60143780708313</t>
@@ -3143,31 +3146,31 @@
     <t xml:space="preserve">1.62925410270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5386518239975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183077812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52911472320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53070414066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434611320496</t>
+    <t xml:space="preserve">1.66104447841644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53865170478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51957738399506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183089733124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52911460399628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53070425987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434599399567</t>
   </si>
   <si>
     <t xml:space="preserve">1.43056464195251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37334203720093</t>
+    <t xml:space="preserve">1.37334215641022</t>
   </si>
   <si>
     <t xml:space="preserve">1.30817186832428</t>
@@ -3176,7 +3179,7 @@
     <t xml:space="preserve">1.30022442340851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22869598865509</t>
+    <t xml:space="preserve">1.22869610786438</t>
   </si>
   <si>
     <t xml:space="preserve">1.23346471786499</t>
@@ -3194,19 +3197,19 @@
     <t xml:space="preserve">1.59746372699738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7484678030014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423190116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76038908958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77231061458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025805950165</t>
+    <t xml:space="preserve">1.74846792221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423202037811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76038920879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77231073379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025817871094</t>
   </si>
   <si>
     <t xml:space="preserve">1.74449408054352</t>
@@ -3221,31 +3224,31 @@
     <t xml:space="preserve">1.83191752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82794368267059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178649425507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986520767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82396996021271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628433704376</t>
+    <t xml:space="preserve">1.8279435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178637504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589136600494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986508846283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.823970079422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628421783447</t>
   </si>
   <si>
     <t xml:space="preserve">1.79217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76833689212799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78820586204529</t>
+    <t xml:space="preserve">1.7683367729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788205742836</t>
   </si>
   <si>
     <t xml:space="preserve">1.7285989522934</t>
@@ -3257,13 +3260,13 @@
     <t xml:space="preserve">1.71667766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73654651641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641560554504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436305046082</t>
+    <t xml:space="preserve">1.73654639720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641548633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436293125153</t>
   </si>
   <si>
     <t xml:space="preserve">1.80410087108612</t>
@@ -3519,9 +3522,6 @@
   </si>
   <si>
     <t xml:space="preserve">1.39746820926666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
     <t xml:space="preserve">1.44929027557373</t>
@@ -24983,7 +24983,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="s">
-        <v>457</v>
+        <v>557</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25009,7 +25009,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25035,7 +25035,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25061,7 +25061,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25087,7 +25087,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25113,7 +25113,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25139,7 +25139,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25165,7 +25165,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25191,7 +25191,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25217,7 +25217,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25243,7 +25243,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25269,7 +25269,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25295,7 +25295,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25321,7 +25321,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25347,7 +25347,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25373,7 +25373,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25399,7 +25399,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25425,7 +25425,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25451,7 +25451,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25477,7 +25477,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G788" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25503,7 +25503,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25529,7 +25529,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25555,7 +25555,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G791" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25581,7 +25581,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G792" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25607,7 +25607,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25633,7 +25633,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G794" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25659,7 +25659,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25685,7 +25685,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25711,7 +25711,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25737,7 +25737,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25763,7 +25763,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25789,7 +25789,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G800" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25815,7 +25815,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G801" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25841,7 +25841,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25867,7 +25867,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25893,7 +25893,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25919,7 +25919,7 @@
         <v>4</v>
       </c>
       <c r="G805" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25945,7 +25945,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25971,7 +25971,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25997,7 +25997,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G808" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26023,7 +26023,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G809" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26049,7 +26049,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26075,7 +26075,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26101,7 +26101,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26127,7 +26127,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26153,7 +26153,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26179,7 +26179,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G815" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26205,7 +26205,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26231,7 +26231,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26257,7 +26257,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26283,7 +26283,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26309,7 +26309,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26335,7 +26335,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G821" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26361,7 +26361,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26387,7 +26387,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26413,7 +26413,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26439,7 +26439,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26465,7 +26465,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26491,7 +26491,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26517,7 +26517,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26543,7 +26543,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26569,7 +26569,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G830" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26595,7 +26595,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G831" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26621,7 +26621,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G832" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26647,7 +26647,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G833" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26673,7 +26673,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26725,7 +26725,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26751,7 +26751,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26803,7 +26803,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26829,7 +26829,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26855,7 +26855,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26907,7 +26907,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26933,7 +26933,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26959,7 +26959,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26985,7 +26985,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27011,7 +27011,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="s">
-        <v>610</v>
+        <v>43</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -40791,7 +40791,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1377" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -40843,7 +40843,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1379" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -40869,7 +40869,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1380" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -40895,7 +40895,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40921,7 +40921,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40947,7 +40947,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40973,7 +40973,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G1384" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40999,7 +40999,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -41025,7 +41025,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1386" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -41051,7 +41051,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1387" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -41077,7 +41077,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -41129,7 +41129,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1390" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -41155,7 +41155,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1391" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -41181,7 +41181,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1392" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -41207,7 +41207,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1393" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -41233,7 +41233,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -41259,7 +41259,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1395" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -41285,7 +41285,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1396" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -41311,7 +41311,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -41337,7 +41337,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -41363,7 +41363,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1399" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -41389,7 +41389,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -41415,7 +41415,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1401" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -41441,7 +41441,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -41467,7 +41467,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1403" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -41493,7 +41493,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1404" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41519,7 +41519,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41545,7 +41545,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1406" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41571,7 +41571,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -41597,7 +41597,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -41623,7 +41623,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1409" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -41649,7 +41649,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1410" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -41675,7 +41675,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1411" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -41701,7 +41701,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1412" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -41727,7 +41727,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1413" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -41753,7 +41753,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1414" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -41779,7 +41779,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1415" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41805,7 +41805,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1416" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41831,7 +41831,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1417" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41857,7 +41857,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1418" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41883,7 +41883,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1419" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41909,7 +41909,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1420" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41935,7 +41935,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1421" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41961,7 +41961,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41987,7 +41987,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1423" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -42013,7 +42013,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1424" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -42039,7 +42039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1425" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -42065,7 +42065,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1426" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -42091,7 +42091,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1427" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -42117,7 +42117,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1428" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -42143,7 +42143,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1429" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -42169,7 +42169,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1430" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -42195,7 +42195,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1431" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -42221,7 +42221,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1432" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -42247,7 +42247,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1433" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -42273,7 +42273,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1434" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -42299,7 +42299,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1435" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42325,7 +42325,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -42351,7 +42351,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1437" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -42377,7 +42377,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1438" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -42403,7 +42403,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1439" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -42429,7 +42429,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1440" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -42481,7 +42481,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1442" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -42507,7 +42507,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42559,7 +42559,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1445" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -42585,7 +42585,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1446" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -42611,7 +42611,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1447" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -42637,7 +42637,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1448" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -42663,7 +42663,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1449" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -42689,7 +42689,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1450" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -42715,7 +42715,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1451" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -42741,7 +42741,7 @@
         <v>1.75</v>
       </c>
       <c r="G1452" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -42767,7 +42767,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1453" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42793,7 +42793,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1454" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42819,7 +42819,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1455" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42845,7 +42845,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1456" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42871,7 +42871,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1457" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42897,7 +42897,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1458" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42923,7 +42923,7 @@
         <v>1.75</v>
       </c>
       <c r="G1459" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42949,7 +42949,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G1460" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42975,7 +42975,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1461" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -43001,7 +43001,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1462" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -43027,7 +43027,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1463" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -43053,7 +43053,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1464" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -43079,7 +43079,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1465" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -43105,7 +43105,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1466" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -43131,7 +43131,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1467" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -43157,7 +43157,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1468" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -43183,7 +43183,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1469" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -43209,7 +43209,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1470" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -43235,7 +43235,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1471" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -43261,7 +43261,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1472" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -43313,7 +43313,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1474" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -43339,7 +43339,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1475" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -43391,7 +43391,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1477" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -43417,7 +43417,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43443,7 +43443,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1479" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43469,7 +43469,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1480" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43495,7 +43495,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1481" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43521,7 +43521,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1482" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43547,7 +43547,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1483" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43573,7 +43573,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1484" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -43599,7 +43599,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1485" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43625,7 +43625,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1486" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43651,7 +43651,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1487" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43677,7 +43677,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1488" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -43703,7 +43703,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1489" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43729,7 +43729,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1490" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -43755,7 +43755,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1491" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43781,7 +43781,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1492" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43807,7 +43807,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1493" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43833,7 +43833,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1494" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43859,7 +43859,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1495" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43885,7 +43885,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1496" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43911,7 +43911,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1497" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43937,7 +43937,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43963,7 +43963,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1499" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43989,7 +43989,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -44015,7 +44015,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1501" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -44041,7 +44041,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1502" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -44093,7 +44093,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1504" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -44119,7 +44119,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1505" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -44197,7 +44197,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1508" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -44223,7 +44223,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1509" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -44249,7 +44249,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1510" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -44275,7 +44275,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1511" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -44301,7 +44301,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1512" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -44327,7 +44327,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1513" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -44353,7 +44353,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1514" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44379,7 +44379,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1515" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -44405,7 +44405,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1516" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44431,7 +44431,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1517" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -44457,7 +44457,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1518" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44483,7 +44483,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1519" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44535,7 +44535,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1521" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44561,7 +44561,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44587,7 +44587,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1523" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -44613,7 +44613,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1524" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -44639,7 +44639,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -44665,7 +44665,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -44691,7 +44691,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1527" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -44717,7 +44717,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1528" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -44743,7 +44743,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1529" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -44769,7 +44769,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44795,7 +44795,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44821,7 +44821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1532" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44847,7 +44847,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1533" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44873,7 +44873,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44899,7 +44899,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1535" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44925,7 +44925,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1536" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44951,7 +44951,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44977,7 +44977,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1538" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -45003,7 +45003,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1539" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -45029,7 +45029,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1540" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -45055,7 +45055,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1541" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -45081,7 +45081,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1542" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -45133,7 +45133,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1544" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -45159,7 +45159,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1545" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -45185,7 +45185,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1546" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -45211,7 +45211,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1547" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -45237,7 +45237,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1548" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -45263,7 +45263,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1549" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -45289,7 +45289,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1550" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -45315,7 +45315,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1551" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45341,7 +45341,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1552" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -45367,7 +45367,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1553" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -45393,7 +45393,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1554" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45419,7 +45419,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1555" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45445,7 +45445,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G1556" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45471,7 +45471,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1557" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45497,7 +45497,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45523,7 +45523,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1559" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45549,7 +45549,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1560" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45575,7 +45575,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1561" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45601,7 +45601,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1562" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45627,7 +45627,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1563" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45653,7 +45653,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1564" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45679,7 +45679,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45705,7 +45705,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1566" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45731,7 +45731,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1567" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45757,7 +45757,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1568" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45783,7 +45783,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1569" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45809,7 +45809,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45835,7 +45835,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G1571" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45861,7 +45861,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1572" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45887,7 +45887,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1573" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45913,7 +45913,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1574" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45939,7 +45939,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45965,7 +45965,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1576" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45991,7 +45991,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1577" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -46017,7 +46017,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1578" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -46043,7 +46043,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1579" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -46069,7 +46069,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -46095,7 +46095,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1581" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -46121,7 +46121,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1582" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -46147,7 +46147,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1583" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -46173,7 +46173,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1584" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -46199,7 +46199,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1585" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -46225,7 +46225,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1586" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -46251,7 +46251,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1587" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -46277,7 +46277,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1588" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -46303,7 +46303,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1589" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -46329,7 +46329,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46355,7 +46355,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -46381,7 +46381,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46407,7 +46407,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46433,7 +46433,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1594" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46459,7 +46459,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1595" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46485,7 +46485,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1596" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46511,7 +46511,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46537,7 +46537,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46563,7 +46563,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46589,7 +46589,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1600" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46615,7 +46615,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46641,7 +46641,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46667,7 +46667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46693,7 +46693,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46719,7 +46719,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46745,7 +46745,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46771,7 +46771,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46797,7 +46797,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1608" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46823,7 +46823,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46849,7 +46849,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46875,7 +46875,7 @@
         <v>2.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46901,7 +46901,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46927,7 +46927,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1613" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46953,7 +46953,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1614" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46979,7 +46979,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -47005,7 +47005,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1616" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -47031,7 +47031,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1617" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -47057,7 +47057,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -47083,7 +47083,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1619" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -47109,7 +47109,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1620" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -47135,7 +47135,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -47161,7 +47161,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -47187,7 +47187,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -47213,7 +47213,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1624" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -47239,7 +47239,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47265,7 +47265,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47291,7 +47291,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47317,7 +47317,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47343,7 +47343,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47369,7 +47369,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47395,7 +47395,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47421,7 +47421,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47447,7 +47447,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47473,7 +47473,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47499,7 +47499,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47525,7 +47525,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47551,7 +47551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G1637" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47577,7 +47577,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1638" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47603,7 +47603,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47629,7 +47629,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1640" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47655,7 +47655,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47681,7 +47681,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1642" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47707,7 +47707,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47733,7 +47733,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1644" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47759,7 +47759,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1645" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47785,7 +47785,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1646" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47811,7 +47811,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47837,7 +47837,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47863,7 +47863,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47889,7 +47889,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47915,7 +47915,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47941,7 +47941,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47967,7 +47967,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47993,7 +47993,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -48019,7 +48019,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -48045,7 +48045,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -48071,7 +48071,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1657" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -48097,7 +48097,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -48123,7 +48123,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1659" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -48149,7 +48149,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -48175,7 +48175,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -48201,7 +48201,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -48227,7 +48227,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1663" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48253,7 +48253,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48279,7 +48279,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1665" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48305,7 +48305,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48331,7 +48331,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48357,7 +48357,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48383,7 +48383,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48409,7 +48409,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48435,7 +48435,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48461,7 +48461,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1672" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48487,7 +48487,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48513,7 +48513,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48539,7 +48539,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48565,7 +48565,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1676" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48591,7 +48591,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1677" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48617,7 +48617,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1678" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48643,7 +48643,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48669,7 +48669,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48695,7 +48695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48721,7 +48721,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48747,7 +48747,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48773,7 +48773,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1684" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48799,7 +48799,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48825,7 +48825,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48851,7 +48851,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1687" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48877,7 +48877,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48903,7 +48903,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48929,7 +48929,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48955,7 +48955,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48981,7 +48981,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -49007,7 +49007,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -49033,7 +49033,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -49059,7 +49059,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -49085,7 +49085,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1696" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -49111,7 +49111,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -49137,7 +49137,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -49163,7 +49163,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -49189,7 +49189,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1700" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -49215,7 +49215,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49241,7 +49241,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49267,7 +49267,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49293,7 +49293,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49319,7 +49319,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49345,7 +49345,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49371,7 +49371,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49397,7 +49397,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49423,7 +49423,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1709" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49449,7 +49449,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49475,7 +49475,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49501,7 +49501,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49527,7 +49527,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49553,7 +49553,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49579,7 +49579,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1715" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49605,7 +49605,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49631,7 +49631,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49657,7 +49657,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49683,7 +49683,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49709,7 +49709,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49735,7 +49735,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1721" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49761,7 +49761,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49787,7 +49787,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49813,7 +49813,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49839,7 +49839,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49865,7 +49865,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49891,7 +49891,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49917,7 +49917,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49943,7 +49943,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49969,7 +49969,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49995,7 +49995,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -50021,7 +50021,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -50047,7 +50047,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -50073,7 +50073,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -50099,7 +50099,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="s">
-        <v>1169</v>
+        <v>948</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -50255,7 +50255,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50281,7 +50281,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50359,7 +50359,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50411,7 +50411,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50463,7 +50463,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1749" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50671,7 +50671,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1757" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50749,7 +50749,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50775,7 +50775,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50827,7 +50827,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50879,7 +50879,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1765" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50931,7 +50931,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -51009,7 +51009,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -51061,7 +51061,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -51269,7 +51269,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51399,7 +51399,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51503,7 +51503,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51529,7 +51529,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51581,7 +51581,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51633,7 +51633,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51711,7 +51711,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51737,7 +51737,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1798" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51763,7 +51763,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51867,7 +51867,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51919,7 +51919,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -52283,7 +52283,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52335,7 +52335,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1821" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52387,7 +52387,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52491,7 +52491,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1827" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52517,7 +52517,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52621,7 +52621,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52647,7 +52647,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52699,7 +52699,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52725,7 +52725,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52751,7 +52751,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52829,7 +52829,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52881,7 +52881,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -53063,7 +53063,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1849" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53245,7 +53245,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53505,7 +53505,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1866" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53765,7 +53765,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1876" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53895,7 +53895,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -69763,7 +69763,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494675926</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>171289</v>
@@ -69784,6 +69784,32 @@
         <v>1498</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.649537037</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>113651</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>2.82500004768372</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385444641113</t>
+    <t xml:space="preserve">3.07385468482971</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614468574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01786732673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690033912659</t>
+    <t xml:space="preserve">3.08614444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01786708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690081596375</t>
   </si>
   <si>
     <t xml:space="preserve">2.98099732398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88131189346313</t>
+    <t xml:space="preserve">2.88131165504456</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003057479858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620694160461</t>
+    <t xml:space="preserve">2.80620670318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.86082887649536</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">2.75841236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73929452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69013476371765</t>
+    <t xml:space="preserve">2.73929476737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
     <t xml:space="preserve">2.71744585037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86629104614258</t>
+    <t xml:space="preserve">2.86629056930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.76387476921082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7447566986084</t>
+    <t xml:space="preserve">2.74475693702698</t>
   </si>
   <si>
     <t xml:space="preserve">2.7570469379425</t>
@@ -98,1758 +98,1758 @@
     <t xml:space="preserve">2.73110127449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76114368438721</t>
+    <t xml:space="preserve">2.76114344596863</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563910484314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69696283340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72290825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62868499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935678482056</t>
+    <t xml:space="preserve">2.69696259498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72290802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62868523597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935654640198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45799112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30095267295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50442028045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67511391639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81713080406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78162693977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86219453811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8335177898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84717321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8840434551239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769864082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85126972198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685864448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9495894908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16125011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173289299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217397689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635530471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001072883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040964126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269988059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2308931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952795028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076685905457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22543048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732157707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704894065857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38656568527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330893516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3251166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780530929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366639137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182658195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1562032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1348295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330241203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208226203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32291913032532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856772422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3343186378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151986122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406319618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108601570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681069374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833827972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4084141254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844059944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714341163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607542991638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796030044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8997175693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89686727523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643319129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495736122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938532829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671439170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500840187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9652636051178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9552891254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058043479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17045211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625454902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91966652870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86551904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90399241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549328804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83559584617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79854798316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77717399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88546800613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87406873703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92109107971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94103980064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694407463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85839486122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409401893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707167625427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007509231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80567240715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289938926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75865006446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77859902381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68597912788391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62470769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478402137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54776120185852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480954170227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463042259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57198476791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45086669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44516682624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42379307746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44374227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41666841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900734901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61045837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54918646812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57910966873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55061101913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57340979576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69310355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64038133621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.628981590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63325667381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67172980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67315483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70307803153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7144775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65178084373474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66887974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65748071670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486058235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211260795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498818397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41524386405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43234276771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43661761283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39386987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39244508743286</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30095291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38971376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50442004203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74885368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78162670135498</t>
+    <t xml:space="preserve">2.3511221408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53066253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57768487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58908438682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63468170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69595313072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68027925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69167876243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69737839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012589454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297595024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72445178031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7230269908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7287266254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75580024719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7116277217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69025373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65035605430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760807991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5833842754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55346131324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52068781852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60618329048157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058549880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5449116230011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54063677787781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50501394271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49788951873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50643849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53351235389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57625985145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048365592957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193396568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58195948600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55916094779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58623433113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53636169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48506474494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54348683357239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6874041557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69452810287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75722503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77147459983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79712295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78857326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79997301101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83132076263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90541696548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03508496284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215786933899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477824211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727005958557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25737285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07783269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16760301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1619029045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16047835350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21890020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174954414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589726448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23172426223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900204658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12913036346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19610142707825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10063171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157137870789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32576942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302121162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864476203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3400182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35569262504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457407951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0892322063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06358337402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17488980293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0970664024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11147832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13886070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462542533875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11868405342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07112622261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0379786491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04806733131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762606620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00627326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97744965553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91836214065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8722448348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90395045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89098000526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87512707710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918618202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92700910568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90683269500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86936259269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87800931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85783338546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85350942611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87080359458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82468628883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79298043251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76415729522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81027483940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80018663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79153966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72956919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75262808799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75983381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74686360359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95439124107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92124462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92845034599304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92556810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83189249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342169761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83045125007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82612752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80739212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.808833360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84053921699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85495090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86503911018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87656855583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90827393531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83909821510315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73821640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7555103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76848077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70218753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72668695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71371626853943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72524571418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68056988716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480492591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336392402649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65895175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67624640464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406908988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79442191123962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79874539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74542212486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78577470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92268586158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02500796318054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02644944190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06968450546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10571360588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12156653404236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17056608200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14174318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09850788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05671405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07689046859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08409667015076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0740077495575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04086089134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05383133888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17921328544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12588977813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05527281761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07977318763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14894843101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16191911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14750742912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09994959831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15903663635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15471315383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1287727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11580204963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10427260398865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815553665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483202934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9716854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86792135238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89674472808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88233280181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85062718391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82901000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82324528694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70362830162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72236371040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71227526664734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65606999397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858431816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76703977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740769386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69498133659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73461365699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70579028129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7310106754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72020173072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79225993156433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84630370140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77424550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77064275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70939326286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74181938171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71299600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63373160362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6409375667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65534901618958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64814352989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689379692078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57968783378601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55807042121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56167364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086445808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56887912750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43557167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37432169914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30946922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39593935012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41755700111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41395378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36351299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35991024971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505777359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44998335838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35270428657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52204132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42836546897888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44638013839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4211597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50762963294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59409952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56527614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63012862205505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65174627304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62292289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60130524635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60851120948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63733458518982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68417263031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66615796089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69137811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67696690559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73281192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62172198295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49582004547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48841404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40324521064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43657207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45879006385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39213585853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40694832801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36991810798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29956150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21068930625916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32548213005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732434272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38843321800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805720329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46989917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52174115180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57728600502014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5254442691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45508742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58098888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395914077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4736020565033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44768095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53655290603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4773051738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51433515548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48100805282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46619629859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39583921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41065144538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35140347480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36621522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34399724006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35880899429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35510635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36251258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30696749687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31067037582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32177948951721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39954233169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102698326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41435408592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37362122535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31807637214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29585838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104615211487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26993727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30326414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32918524742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27734327316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26623439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29215502738953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27364015579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2884521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28474926948547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38473033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20698642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24031329154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15514445304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14773845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1033022403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959959983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10700535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0625696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98850929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147967338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06627225875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04775762557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922310829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14403533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13662934303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439218521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512552261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20328330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19958066940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21809530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811423301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070847511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24771928787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33659100532532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51063227653503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65504884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68096971511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60320711135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62912797927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65875196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65134596824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62542510032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71800017356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70318818092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72910904884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69207882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71429705619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75503015518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8031690120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81798100471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84390163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87352609634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86241698265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88093185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76243591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76984214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81427788734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79576301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75873279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85871386528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314984321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89574384689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90685296058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88833785057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96239805221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98091268539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91796207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758558273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95128893852234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9364767074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95499181747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93277382850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91055583953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96980381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720980644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94018006324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89944672584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81057500839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8661196231842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80687189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279299736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85501098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71059417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70689082145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61061310768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64023685455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6365339756012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63283085823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61801910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69578194618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.68467283248901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86219429969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83351755142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88404297828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769887924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85127019882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94685816764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94958972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124987602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767855644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1790018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635506629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21041011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269940376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2308931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952723503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076638221741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14896011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.225430727005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587157249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463242530823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27732157707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3865659236908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330965042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.325115442276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780459403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26366639137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097700119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1918261051178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15620303153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1348295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3229193687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856748580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33431816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31151986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419079780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403767585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981387138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406319618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108601570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681069374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833804130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714293479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796030044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89971733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89686727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1319797039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938532829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671439170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500840187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96526384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528936386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99233722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058019638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1704523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757701873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13625431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9495894908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91966652870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86551904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90399265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84129571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549328804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83559560775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79854798316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73442649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77717399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88546800613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87406849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9410400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85839438438416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409425735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707167625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007485389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80567264556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7586498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77859902381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68597888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62470698356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5477614402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480954170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610672950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5719850063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45086669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44516682624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42379331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44374203681946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941615104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61045813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54918670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57910943031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5506112575531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5235378742218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57341027259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69310355186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64038133621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63895678520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898230552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63325691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67172956466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67315459251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71447706222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65178084373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66887998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753151893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65748047828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486082077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211260795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498818397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41524362564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43234276771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43661713600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39386963844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39244532585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3511221408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53066205978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57768487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58908414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63468146324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6959536075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68027949333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69167876243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69737815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297571182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72445178031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72302675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434969902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152516365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75580024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71162748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65035581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760831832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5833842754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55346131324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5206880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60618352890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058573722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5449116230011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54063677787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50501394271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49788928031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50643849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53351235389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57625985145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58195972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5591607093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58623433113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53636193275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48506498336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54348683357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68740367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69452834129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75722503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79712271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78857350349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79997253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83132123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90541696548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03508496284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477824211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25737309455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07783269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16190314292908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16047787666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21889972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174978256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877188682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23172402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12913012504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19610142707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19752597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602438926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157090187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3257691860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864452362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34001874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3556923866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457384109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27019715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08923196792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06358361244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17489004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11147832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13886046409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462542533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1186842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07112574577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03797912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04806733131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00627326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97744989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9183623790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8722448348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90395045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8909797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87512707710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92700886726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9068329334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86936259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87800931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85783338546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8535099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87080359458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82468628883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79298067092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76415729522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81027483940125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80018639564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79153943061829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72956967353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75262808799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75983357429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74686360359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95439100265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92124485969543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92845010757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9255678653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83189225196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342169761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80450987815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83045101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82612752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80739212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80883359909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84053897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85495066642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86503911018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87656831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90827369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83909773826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73821640014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7555103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76848101615906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70218706130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72668719291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71371650695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72524571418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68056964874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65895223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406885147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7944221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79874539375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74542212486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78577494621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92268586158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0250084400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02644944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06968474388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1057140827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12156653404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17056608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14174270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09850835800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05671453475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08409643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07400798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04086112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0538318157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17921352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589001655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05527281761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07977294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14894866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16191911697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1475076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09994912147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15903687477112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15471339225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12877225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11580204963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10427260398865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168564796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82180380821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86792159080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89674472808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88233327865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85062742233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82900977134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82324504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7036280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72236371040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70506978034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71227502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6560697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858431816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76703953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740793228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69498133659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7346134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7057900428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7310106754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72020173072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79226016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84630393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.774245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77064251899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70939302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74181938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71299624443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63373184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6409375667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65534925460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64814329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58689379692078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5724823474884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57968783378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55807065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56167340278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086445808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56887912750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43557143211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37432193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30946898460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39593911170959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41755700111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41395354270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36351323127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991024971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4499831199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3527045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52204132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42836546897888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44638013839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4211597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50762987136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59409976005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56527614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63012909889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65174651145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62292313575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60130548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60851120948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6373348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6841721534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66615796089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69137835502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67696690559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73281192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62172174453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49582004547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48841404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.403244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43657207489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45878982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39213585853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40694832801819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991810798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29956126213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21068906784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32548236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732410430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38843321800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42916631698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805720329285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46989917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5032262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52174115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53284978866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57728600502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5254442691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45508718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58098888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395914077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4736020565033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44768142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53655290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4773051738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51433515548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48100805282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46619606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39583897590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41065120697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35140299797058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.366215467453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34399724006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35880923271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35510635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3625123500824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30696725845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31066989898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32177901268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39954209327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102698326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41435408592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37362098693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31807637214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29585838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104615211487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26993727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30326414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32918500900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27734327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26623439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29215526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27364015579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28845238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28474926948547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38473033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20698642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24031329154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15514445304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14773845672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1033022403717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849024772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10700559616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0625696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9885094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147931575775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553915977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0662727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04775738716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922334671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14403533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13662958145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847107887268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439218521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23290705680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512528419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20328330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1995804309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21809530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811423301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367825508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24771952629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3365912437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51063203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65504908561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68096971511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60320687294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62912797927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65875196456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65134596824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62542510032654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71799993515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70318818092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72910904884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69207882881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71429681777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75502991676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8031690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81798100471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84390187263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87352585792542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86241698265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88093185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76243591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76984190940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7994658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81427788734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79576301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75873255729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85871362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314984321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89574384689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90685272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88833808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.962397813797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98091268539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91796159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758582115173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95128870010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9364767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95499181747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93277406692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91055583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96980404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720980644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94017958641052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89944672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81057500839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86611986160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80687189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279299736023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85501074790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71059393882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70689105987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61061310768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6402370929718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6365339756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63283085823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69578194618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467307090759</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.68837594985962</t>
   </si>
   <si>
@@ -1859,28 +1859,28 @@
     <t xml:space="preserve">2.56988024711609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50692915916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34770035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23661017417908</t>
+    <t xml:space="preserve">2.49211716651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50692939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34770011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2366099357605</t>
   </si>
   <si>
     <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587731361389</t>
+    <t xml:space="preserve">2.19587707519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21777319908142</t>
+    <t xml:space="preserve">2.2177734375</t>
   </si>
   <si>
     <t xml:space="preserve">2.10882997512817</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">2.12439346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08937573432922</t>
+    <t xml:space="preserve">2.0893759727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.10104846954346</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">2.12050247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13995671272278</t>
+    <t xml:space="preserve">2.13995695114136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12828421592712</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">2.07770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0504674911499</t>
+    <t xml:space="preserve">2.05046772956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.04657673835754</t>
@@ -1922,16 +1922,16 @@
     <t xml:space="preserve">2.03490424156189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03101325035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02323198318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0582492351532</t>
+    <t xml:space="preserve">2.05435872077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03101348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02323174476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05824947357178</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
@@ -1940,64 +1940,64 @@
     <t xml:space="preserve">2.22944593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18664646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96876001358032</t>
+    <t xml:space="preserve">2.1866466999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9687602519989</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92985200881958</t>
+    <t xml:space="preserve">1.92985188961029</t>
   </si>
   <si>
     <t xml:space="preserve">2.02712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94152438640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84425354003906</t>
+    <t xml:space="preserve">1.94152414798737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84425365924835</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76643681526184</t>
+    <t xml:space="preserve">1.76643705368042</t>
   </si>
   <si>
     <t xml:space="preserve">1.8092360496521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75087368488312</t>
+    <t xml:space="preserve">1.75087380409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.74698269367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69251108169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78978192806244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82090842723846</t>
+    <t xml:space="preserve">1.69251132011414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78978180885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82090866565704</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74309194087982</t>
+    <t xml:space="preserve">1.74309206008911</t>
   </si>
   <si>
     <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196532249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7197470664978</t>
+    <t xml:space="preserve">1.71196556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71974718570709</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">1.73141944408417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71585607528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73531031608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78200030326843</t>
+    <t xml:space="preserve">1.71585619449615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353104352951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78200042247772</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
@@ -2024,31 +2024,31 @@
     <t xml:space="preserve">1.80145454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8403627872467</t>
+    <t xml:space="preserve">1.84036302566528</t>
   </si>
   <si>
     <t xml:space="preserve">1.85592615604401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83647191524506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87927103042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79756355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032780647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869017124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75476455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75865530967712</t>
+    <t xml:space="preserve">1.83647203445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87927114963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79756367206573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032792568207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869029045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75476479530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75865542888641</t>
   </si>
   <si>
     <t xml:space="preserve">1.76254630088806</t>
@@ -2057,31 +2057,31 @@
     <t xml:space="preserve">1.80534529685974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81701767444611</t>
+    <t xml:space="preserve">1.81701791286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.82479953765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91428852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93374264240265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89094364643097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538027763367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650689601898</t>
+    <t xml:space="preserve">1.91428875923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93374240398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89094352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538039684296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650701522827</t>
   </si>
   <si>
     <t xml:space="preserve">1.89483428001404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85981702804565</t>
+    <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
     <t xml:space="preserve">1.92207038402557</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217496871948</t>
+    <t xml:space="preserve">2.13217520713806</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19053769111633</t>
+    <t xml:space="preserve">2.19053745269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.15551996231079</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">2.17108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14384770393372</t>
+    <t xml:space="preserve">2.14384794235229</t>
   </si>
   <si>
     <t xml:space="preserve">2.11272072792053</t>
@@ -2132,43 +2132,43 @@
     <t xml:space="preserve">2.01545023918152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821437358856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15941095352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13606572151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01934123039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87148928642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91039764881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596101760864</t>
+    <t xml:space="preserve">1.98821473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15941119194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13606595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01934099197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87148940563202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91039776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596113681793</t>
   </si>
   <si>
     <t xml:space="preserve">1.89872527122498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95319676399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99988687038422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95708763599396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96486926078796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210512638092</t>
+    <t xml:space="preserve">1.9531968832016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99988698959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95708787441254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210524559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.72752869129181</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">1.68862056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62636697292328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59524047374725</t>
+    <t xml:space="preserve">1.62636709213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59524035453796</t>
   </si>
   <si>
     <t xml:space="preserve">1.54232513904572</t>
@@ -2189,37 +2189,37 @@
     <t xml:space="preserve">1.48941004276276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45361423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33844578266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30420649051666</t>
+    <t xml:space="preserve">1.45361435413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33844566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30420637130737</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619242668152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09098887443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16102373600006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08009445667267</t>
+    <t xml:space="preserve">1.09098875522614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16102385520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08009457588196</t>
   </si>
   <si>
     <t xml:space="preserve">1.05986225605011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0847635269165</t>
+    <t xml:space="preserve">1.08476364612579</t>
   </si>
   <si>
     <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22483348846436</t>
+    <t xml:space="preserve">1.22483336925507</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
@@ -2240,28 +2240,28 @@
     <t xml:space="preserve">1.32288241386414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28864312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28397405147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29331207275391</t>
+    <t xml:space="preserve">1.28864300251007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28397417068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29331195354462</t>
   </si>
   <si>
     <t xml:space="preserve">1.39291739463806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36179065704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062905788422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29642462730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29798102378845</t>
+    <t xml:space="preserve">1.36179077625275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062893867493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29642474651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29798114299774</t>
   </si>
   <si>
     <t xml:space="preserve">1.33688938617706</t>
@@ -2270,16 +2270,16 @@
     <t xml:space="preserve">1.29953730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31354415416718</t>
+    <t xml:space="preserve">1.31354427337646</t>
   </si>
   <si>
     <t xml:space="preserve">1.29175567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28241765499115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2295024394989</t>
+    <t xml:space="preserve">1.28241777420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22950255870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.23884046077728</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">1.17503070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1330099105835</t>
+    <t xml:space="preserve">1.13300967216492</t>
   </si>
   <si>
     <t xml:space="preserve">1.10343956947327</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">1.05674958229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06764388084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12211561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10655212402344</t>
+    <t xml:space="preserve">1.06764400005341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12211549282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
     <t xml:space="preserve">1.14234793186188</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">1.15012955665588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13923525810242</t>
+    <t xml:space="preserve">1.13923513889313</t>
   </si>
   <si>
     <t xml:space="preserve">1.19837582111359</t>
@@ -2339,16 +2339,16 @@
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708684444427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27930510044098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17969977855682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1641366481781</t>
+    <t xml:space="preserve">1.28708672523499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27930498123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17969989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16413640975952</t>
   </si>
   <si>
     <t xml:space="preserve">1.23572778701782</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">1.18748152256012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21082651615143</t>
+    <t xml:space="preserve">1.21082639694214</t>
   </si>
   <si>
     <t xml:space="preserve">1.17814350128174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18592524528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612246513367</t>
+    <t xml:space="preserve">1.18592512607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612258434296</t>
   </si>
   <si>
     <t xml:space="preserve">1.1579110622406</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18436884880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17036175727844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14546036720276</t>
+    <t xml:space="preserve">1.18436872959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17036187648773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14546048641205</t>
   </si>
   <si>
     <t xml:space="preserve">1.16724920272827</t>
@@ -2399,25 +2399,25 @@
     <t xml:space="preserve">1.15168583393097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17191827297211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16569268703461</t>
+    <t xml:space="preserve">1.17191815376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1656928062439</t>
   </si>
   <si>
     <t xml:space="preserve">1.1563549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12522828578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.12522804737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608748435974</t>
+    <t xml:space="preserve">1.06608760356903</t>
   </si>
   <si>
     <t xml:space="preserve">1.08320713043213</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">1.06297492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04896783828735</t>
+    <t xml:space="preserve">1.04896795749664</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410154819489</t>
@@ -2444,49 +2444,49 @@
     <t xml:space="preserve">1.05052423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585516452789</t>
+    <t xml:space="preserve">1.04585528373718</t>
   </si>
   <si>
     <t xml:space="preserve">1.03962993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04118621349335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03340470790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03496086597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0365172624588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02251029014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99605256319046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01628506183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00850343704224</t>
+    <t xml:space="preserve">1.04118633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03340458869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03496098518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03651714324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02251017093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996052622795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01628494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00850331783295</t>
   </si>
   <si>
     <t xml:space="preserve">1.01005959510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00072157382965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991383731365204</t>
+    <t xml:space="preserve">1.00072169303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991383671760559</t>
   </si>
   <si>
     <t xml:space="preserve">0.966482281684875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96492600440979</t>
+    <t xml:space="preserve">0.964925944805145</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.975820243358612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827156066895</t>
+    <t xml:space="preserve">0.989827334880829</t>
   </si>
   <si>
     <t xml:space="preserve">0.969595015048981</t>
@@ -2510,136 +2510,136 @@
     <t xml:space="preserve">0.968038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957144260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489134788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99916535615921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06453120708466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05830585956573</t>
+    <t xml:space="preserve">0.957144379615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489313602448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999165296554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06453132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05830597877502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02406656742096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988270938396454</t>
+    <t xml:space="preserve">0.988270878791809</t>
   </si>
   <si>
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941580951213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933799266815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904228925704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879327654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887109279632568</t>
+    <t xml:space="preserve">0.941581010818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93379932641983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904228985309601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879327714443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887109398841858</t>
   </si>
   <si>
     <t xml:space="preserve">0.888665616512299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891778349876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83575040102005</t>
+    <t xml:space="preserve">0.891778409481049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835750341415405</t>
   </si>
   <si>
     <t xml:space="preserve">0.80306738615036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787504136562347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829525113105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831081330776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840419471263885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826412379741669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817074418067932</t>
+    <t xml:space="preserve">0.787504076957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829525053501129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831081390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840419411659241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826412439346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817074358463287</t>
   </si>
   <si>
     <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89644730091095</t>
+    <t xml:space="preserve">0.896447241306305</t>
   </si>
   <si>
     <t xml:space="preserve">0.902672648429871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915123343467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940024614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977376639842987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96336966753006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983601987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978933036327362</t>
+    <t xml:space="preserve">0.915123283863068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940024554729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977376699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963369607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983602106571198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978932917118073</t>
   </si>
   <si>
     <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961813271045685</t>
+    <t xml:space="preserve">0.961813151836395</t>
   </si>
   <si>
     <t xml:space="preserve">0.946249961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943137347698212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952475368976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927573978900909</t>
+    <t xml:space="preserve">0.943137288093567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930686771869659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952475190162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927573919296265</t>
   </si>
   <si>
     <t xml:space="preserve">0.926017701625824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935355722904205</t>
+    <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
     <t xml:space="preserve">0.971151351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947806477546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792354106903</t>
+    <t xml:space="preserve">0.947806417942047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792413711548</t>
   </si>
   <si>
     <t xml:space="preserve">0.913567006587982</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">0.907341718673706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.916679620742798</t>
+    <t xml:space="preserve">0.916679680347443</t>
   </si>
   <si>
     <t xml:space="preserve">0.8995600938797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918235957622528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908897995948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894890964031219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910454213619232</t>
+    <t xml:space="preserve">0.918236017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908897936344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894890904426575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910454332828522</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
@@ -2675,16 +2675,16 @@
     <t xml:space="preserve">1.05363690853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13767886161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15946757793427</t>
+    <t xml:space="preserve">1.13767898082733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
     <t xml:space="preserve">1.12989723682404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10032689571381</t>
+    <t xml:space="preserve">1.10032677650452</t>
   </si>
   <si>
     <t xml:space="preserve">1.09877049922943</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">1.07231283187866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12834084033966</t>
+    <t xml:space="preserve">1.12834095954895</t>
   </si>
   <si>
     <t xml:space="preserve">1.12055921554565</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">1.15479850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31198811531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907278060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24662208557129</t>
+    <t xml:space="preserve">1.31198799610138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24662220478058</t>
   </si>
   <si>
     <t xml:space="preserve">1.25284743309021</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">1.22638976573944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23105871677399</t>
+    <t xml:space="preserve">1.23105883598328</t>
   </si>
   <si>
     <t xml:space="preserve">1.2699670791626</t>
@@ -2735,25 +2735,25 @@
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36023426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38513553142548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40069901943207</t>
+    <t xml:space="preserve">1.27307975292206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36023437976837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38513565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40069913864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112867832184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3991425037384</t>
+    <t xml:space="preserve">1.37112855911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914262294769</t>
   </si>
   <si>
     <t xml:space="preserve">1.39447367191315</t>
@@ -2765,43 +2765,43 @@
     <t xml:space="preserve">1.39758634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39136099815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4053680896759</t>
+    <t xml:space="preserve">1.3913608789444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40536797046661</t>
   </si>
   <si>
     <t xml:space="preserve">1.4380509853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52053654193878</t>
+    <t xml:space="preserve">1.52053666114807</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022322177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58745884895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53765606880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51431119441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50341689586639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497329235077</t>
+    <t xml:space="preserve">1.56022310256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58745872974396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53765618801117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51431131362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50341701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497317314148</t>
   </si>
   <si>
     <t xml:space="preserve">1.49096620082855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51798808574677</t>
+    <t xml:space="preserve">1.51798796653748</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871304512024</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937678337097</t>
+    <t xml:space="preserve">1.48937666416168</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54818868637085</t>
+    <t xml:space="preserve">1.54818880558014</t>
   </si>
   <si>
     <t xml:space="preserve">1.55454683303833</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">1.57044196128845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56567347049713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56726312637329</t>
+    <t xml:space="preserve">1.56567358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.567263007164</t>
   </si>
   <si>
     <t xml:space="preserve">1.53706228733063</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">1.44328081607819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40672183036804</t>
+    <t xml:space="preserve">1.40672194957733</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374371528625</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">1.39241623878479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744678974152</t>
+    <t xml:space="preserve">1.35744690895081</t>
   </si>
   <si>
     <t xml:space="preserve">1.34949922561646</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">1.35585737228394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31929838657379</t>
+    <t xml:space="preserve">1.31929850578308</t>
   </si>
   <si>
     <t xml:space="preserve">1.31453001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27638161182404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3018137216568</t>
+    <t xml:space="preserve">1.27638149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30181384086609</t>
   </si>
   <si>
     <t xml:space="preserve">1.30499279499054</t>
@@ -2900,25 +2900,25 @@
     <t xml:space="preserve">1.31135094165802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30340337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479195594788</t>
+    <t xml:space="preserve">1.30340325832367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28432929515839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479207515717</t>
   </si>
   <si>
     <t xml:space="preserve">1.22074854373932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22233784198761</t>
+    <t xml:space="preserve">1.2223379611969</t>
   </si>
   <si>
     <t xml:space="preserve">1.2557178735733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24935984611511</t>
+    <t xml:space="preserve">1.24935972690582</t>
   </si>
   <si>
     <t xml:space="preserve">1.25412821769714</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">1.37652099132538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36698400974274</t>
+    <t xml:space="preserve">1.36698389053345</t>
   </si>
   <si>
     <t xml:space="preserve">1.35267841815948</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">1.3749315738678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37970006465912</t>
+    <t xml:space="preserve">1.37970018386841</t>
   </si>
   <si>
     <t xml:space="preserve">1.38128960132599</t>
@@ -2972,19 +2972,19 @@
     <t xml:space="preserve">1.39877426624298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42897498607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40513241291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5338830947876</t>
+    <t xml:space="preserve">1.42897510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40513229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53388321399689</t>
   </si>
   <si>
     <t xml:space="preserve">1.49732434749603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189211845398</t>
+    <t xml:space="preserve">1.47189199924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738556861877</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">1.45917594432831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46076536178589</t>
+    <t xml:space="preserve">1.46076548099518</t>
   </si>
   <si>
     <t xml:space="preserve">1.41943800449371</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">1.33996224403381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3415515422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351936340332</t>
+    <t xml:space="preserve">1.34155166149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33519351482391</t>
   </si>
   <si>
     <t xml:space="preserve">1.37811064720154</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">1.38287913799286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50050342082977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116715908051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49573469161987</t>
+    <t xml:space="preserve">1.50050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116703987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49573481082916</t>
   </si>
   <si>
     <t xml:space="preserve">1.50845086574554</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">1.51321947574615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47507107257843</t>
+    <t xml:space="preserve">1.47507119178772</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010174274445</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">1.47983968257904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45599687099457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301875591278</t>
+    <t xml:space="preserve">1.45599699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301863670349</t>
   </si>
   <si>
     <t xml:space="preserve">1.51004040241241</t>
@@ -3080,19 +3080,19 @@
     <t xml:space="preserve">1.56249439716339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63720178604126</t>
+    <t xml:space="preserve">1.63720166683197</t>
   </si>
   <si>
     <t xml:space="preserve">1.66501832008362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67693960666656</t>
+    <t xml:space="preserve">1.67693948745728</t>
   </si>
   <si>
     <t xml:space="preserve">1.70078253746033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65309679508209</t>
+    <t xml:space="preserve">1.65309691429138</t>
   </si>
   <si>
     <t xml:space="preserve">1.60541141033173</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">1.57362115383148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43851208686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645977020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440745353699</t>
+    <t xml:space="preserve">1.43851220607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645988941193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4544073343277</t>
   </si>
   <si>
     <t xml:space="preserve">1.45122838020325</t>
@@ -3119,22 +3119,22 @@
     <t xml:space="preserve">1.49414527416229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51639842987061</t>
+    <t xml:space="preserve">1.5163985490799</t>
   </si>
   <si>
     <t xml:space="preserve">1.61335897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733281612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322806358337</t>
+    <t xml:space="preserve">1.61733293533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322794437408</t>
   </si>
   <si>
     <t xml:space="preserve">1.62130653858185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349024295807</t>
+    <t xml:space="preserve">1.59349012374878</t>
   </si>
   <si>
     <t xml:space="preserve">1.58792674541473</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">1.62925410270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104435920715</t>
+    <t xml:space="preserve">1.66104447841644</t>
   </si>
   <si>
     <t xml:space="preserve">1.53865170478821</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">1.52434611320496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43056464195251</t>
+    <t xml:space="preserve">1.43056452274323</t>
   </si>
   <si>
     <t xml:space="preserve">1.37334203720093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30817198753357</t>
+    <t xml:space="preserve">1.30817186832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.30022442340851</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">1.59746384620667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7484678030014</t>
+    <t xml:space="preserve">1.74846792221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.78423178195953</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">1.77231049537659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78025805950165</t>
+    <t xml:space="preserve">1.78025817871094</t>
   </si>
   <si>
     <t xml:space="preserve">1.74449396133423</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">1.64514923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71667766571045</t>
+    <t xml:space="preserve">1.71667754650116</t>
   </si>
   <si>
     <t xml:space="preserve">1.73654639720917</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">1.76195001602173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75763154029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490556240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7533130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603892326355</t>
+    <t xml:space="preserve">1.75763165950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75331294536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603904247284</t>
   </si>
   <si>
     <t xml:space="preserve">1.67730736732483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.644486784935</t>
+    <t xml:space="preserve">1.64448666572571</t>
   </si>
   <si>
     <t xml:space="preserve">1.55811655521393</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">1.50456702709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50283980369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865617275238</t>
+    <t xml:space="preserve">1.50283968448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865605354309</t>
   </si>
   <si>
     <t xml:space="preserve">1.51665902137756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48038339614868</t>
+    <t xml:space="preserve">1.48038351535797</t>
   </si>
   <si>
     <t xml:space="preserve">1.4890204668045</t>
@@ -3344,16 +3344,16 @@
     <t xml:space="preserve">1.3819215297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40092289447784</t>
+    <t xml:space="preserve">1.40092301368713</t>
   </si>
   <si>
     <t xml:space="preserve">1.43028879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4061051607132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501204013824</t>
+    <t xml:space="preserve">1.40610527992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501192092896</t>
   </si>
   <si>
     <t xml:space="preserve">1.37328457832336</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">1.34737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52875065803528</t>
+    <t xml:space="preserve">1.52875077724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.59957420825958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54775214195251</t>
+    <t xml:space="preserve">1.5477522611618</t>
   </si>
   <si>
     <t xml:space="preserve">1.55293428897858</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">1.55466175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60648393630981</t>
+    <t xml:space="preserve">1.60648381710052</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475647449493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58230018615723</t>
+    <t xml:space="preserve">1.58230030536652</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057284355164</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">1.4665641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45447242259979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510652542114</t>
+    <t xml:space="preserve">1.45447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510664463043</t>
   </si>
   <si>
     <t xml:space="preserve">1.43547093868256</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">1.33009946346283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3801943063736</t>
+    <t xml:space="preserve">1.38019418716431</t>
   </si>
   <si>
     <t xml:space="preserve">1.35082840919495</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">1.2005443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22300064563751</t>
+    <t xml:space="preserve">1.22300052642822</t>
   </si>
   <si>
     <t xml:space="preserve">1.1884526014328</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">1.35773801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39574074745178</t>
+    <t xml:space="preserve">1.39574086666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.39746820926666</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44929027557373</t>
+    <t xml:space="preserve">1.44929015636444</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992437839508</t>
+    <t xml:space="preserve">1.41992449760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301488876343</t>
+    <t xml:space="preserve">1.41301476955414</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464762687683</t>
+    <t xml:space="preserve">1.38710379600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464750766754</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33182692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591595172882</t>
+    <t xml:space="preserve">1.331827044487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591583251953</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564614295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937075614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136790752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345954418182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655017375946</t>
+    <t xml:space="preserve">1.34564602375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937063694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827751636505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136778831482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345966339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655005455017</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036927223206</t>
+    <t xml:space="preserve">1.29036915302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910094738007</t>
+    <t xml:space="preserve">1.34910106658936</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938476085663</t>
+    <t xml:space="preserve">1.49938488006592</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838624477386</t>
+    <t xml:space="preserve">1.51838636398315</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974929332733</t>
+    <t xml:space="preserve">1.50974941253662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41819703578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729312419891</t>
+    <t xml:space="preserve">1.4181969165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729300498962</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302889347076</t>
+    <t xml:space="preserve">1.60302901268005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62894010543823</t>
+    <t xml:space="preserve">1.62893998622894</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63239479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093725681305</t>
+    <t xml:space="preserve">1.6323949098587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093713760376</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3737,10 +3737,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548530101776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5719358921051</t>
+    <t xml:space="preserve">1.62548518180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57193577289581</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -8632,7 +8632,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G140" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8658,7 +8658,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8684,7 +8684,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8710,7 +8710,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8736,7 +8736,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8788,7 +8788,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8814,7 +8814,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8840,7 +8840,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8866,7 +8866,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8892,7 +8892,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8918,7 +8918,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8944,7 +8944,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8970,7 +8970,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -8996,7 +8996,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9022,7 +9022,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9048,7 +9048,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9074,7 +9074,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9100,7 +9100,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9126,7 +9126,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9152,7 +9152,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9178,7 +9178,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9204,7 +9204,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9282,7 +9282,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9308,7 +9308,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9386,7 +9386,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9412,7 +9412,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9464,7 +9464,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9490,7 +9490,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9516,7 +9516,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9542,7 +9542,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9568,7 +9568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9594,7 +9594,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9620,7 +9620,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9646,7 +9646,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9672,7 +9672,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9698,7 +9698,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9724,7 +9724,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9750,7 +9750,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9776,7 +9776,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9802,7 +9802,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9828,7 +9828,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9854,7 +9854,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9880,7 +9880,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9906,7 +9906,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9932,7 +9932,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9958,7 +9958,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9984,7 +9984,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10010,7 +10010,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10036,7 +10036,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10062,7 +10062,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10088,7 +10088,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10114,7 +10114,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10140,7 +10140,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10166,7 +10166,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10192,7 +10192,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10218,7 +10218,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10244,7 +10244,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10270,7 +10270,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10296,7 +10296,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10322,7 +10322,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10348,7 +10348,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10374,7 +10374,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10400,7 +10400,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10426,7 +10426,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10452,7 +10452,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10478,7 +10478,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10504,7 +10504,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10530,7 +10530,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10556,7 +10556,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10582,7 +10582,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10608,7 +10608,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10634,7 +10634,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G217" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10660,7 +10660,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10686,7 +10686,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10712,7 +10712,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10738,7 +10738,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10764,7 +10764,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10790,7 +10790,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10816,7 +10816,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10842,7 +10842,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10868,7 +10868,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10894,7 +10894,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10920,7 +10920,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10946,7 +10946,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10972,7 +10972,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10998,7 +10998,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11024,7 +11024,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11050,7 +11050,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11076,7 +11076,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11102,7 +11102,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11128,7 +11128,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11154,7 +11154,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11258,7 +11258,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11336,7 +11336,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11362,7 +11362,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11414,7 +11414,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11440,7 +11440,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11466,7 +11466,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11492,7 +11492,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11570,7 +11570,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11648,7 +11648,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11674,7 +11674,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11830,7 +11830,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11856,7 +11856,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G264" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11882,7 +11882,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11934,7 +11934,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12168,7 +12168,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12246,7 +12246,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12740,7 +12740,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12870,7 +12870,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13130,7 +13130,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -69922,7 +69922,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6911226852</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>47801</v>
@@ -69943,6 +69943,32 @@
         <v>1502</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6912384259</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>144691</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>2.85500001907349</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>2.84999990463257</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">3.08614468574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01786684989929</t>
+    <t xml:space="preserve">3.01786708831787</t>
   </si>
   <si>
     <t xml:space="preserve">2.97690057754517</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">2.94003105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86082887649536</t>
+    <t xml:space="preserve">2.80620718002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86082863807678</t>
   </si>
   <si>
     <t xml:space="preserve">2.75841236114502</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">2.866290807724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76387500762939</t>
+    <t xml:space="preserve">2.76387453079224</t>
   </si>
   <si>
     <t xml:space="preserve">2.74475693702698</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">2.72563934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69696259498596</t>
+    <t xml:space="preserve">2.69696283340454</t>
   </si>
   <si>
     <t xml:space="preserve">2.72290802001953</t>
@@ -119,292 +119,295 @@
     <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30095291137695</t>
+    <t xml:space="preserve">2.30095314979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.38971376419067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53992462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50441980361938</t>
+    <t xml:space="preserve">2.53992438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50442004203796</t>
   </si>
   <si>
     <t xml:space="preserve">2.67511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7488534450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78162670135498</t>
+    <t xml:space="preserve">2.81713128089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74885368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78162693977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.68467259407043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86219429969788</t>
+    <t xml:space="preserve">2.86219453811646</t>
   </si>
   <si>
     <t xml:space="preserve">2.8335177898407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88404297828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540840148926</t>
+    <t xml:space="preserve">2.84717345237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88404321670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540863990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.89769840240479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85126972198486</t>
+    <t xml:space="preserve">2.85126996040344</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685864448547</t>
   </si>
   <si>
+    <t xml:space="preserve">2.94958972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164926528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173336982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1790018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040987968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2226996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089289665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076685905457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225430727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732157707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38656568527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833025932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375025749207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780507087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1918261051178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1562032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1490786075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32291960716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856796264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3343186378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981434822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406367301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.476811170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4383385181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39843988418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714293479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796030044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8997175693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8968677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495712280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195418357849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938532829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500840187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96526408195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528936386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058019638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1704523563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757725715637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625454902649</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.9495894908905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164926528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124987602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173336982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635530471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269988059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089241981506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952723503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895963668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543120384216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234290122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463290214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2773220539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559941291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704846382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330988883972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511591911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2978048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2636661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1918261051178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1348295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1490786075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3229193687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33431816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31151986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419079780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981434822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406319618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108601570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833780288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841507911682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714269638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607542991638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796030044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89971733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89686727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938508987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671439170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500864028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96526384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9552891254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99233722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17045283317566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757725715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13625478744507</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.83702063560486</t>
   </si>
   <si>
     <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86551904678345</t>
+    <t xml:space="preserve">2.86551880836487</t>
   </si>
   <si>
     <t xml:space="preserve">2.90399241447449</t>
@@ -416,16 +419,16 @@
     <t xml:space="preserve">2.87549352645874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83559584617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79854822158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73442602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7771737575531</t>
+    <t xml:space="preserve">2.83559560775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79854798316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442625999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77717399597168</t>
   </si>
   <si>
     <t xml:space="preserve">2.88546824455261</t>
@@ -434,13 +437,13 @@
     <t xml:space="preserve">2.87406849861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84272050857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834334373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821574211121</t>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821598052979</t>
   </si>
   <si>
     <t xml:space="preserve">2.92109131813049</t>
@@ -449,43 +452,43 @@
     <t xml:space="preserve">2.9410400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86694431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85839486122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409425735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707191467285</t>
+    <t xml:space="preserve">2.86694407463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85839509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409449577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707167625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.76007485389709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80567240715027</t>
+    <t xml:space="preserve">2.80567264556885</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289915084839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75865006446838</t>
+    <t xml:space="preserve">2.7586498260498</t>
   </si>
   <si>
     <t xml:space="preserve">2.77859902381897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68597912788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62470746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5477614402771</t>
+    <t xml:space="preserve">2.68597888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62470722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478402137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54776167869568</t>
   </si>
   <si>
     <t xml:space="preserve">2.58480930328369</t>
@@ -494,13 +497,13 @@
     <t xml:space="preserve">2.65605545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610672950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333347320557</t>
+    <t xml:space="preserve">2.65463089942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333371162415</t>
   </si>
   <si>
     <t xml:space="preserve">2.57198524475098</t>
@@ -512,13 +515,13 @@
     <t xml:space="preserve">2.44516706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42379307746887</t>
+    <t xml:space="preserve">2.42379331588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.44374227523804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41666865348816</t>
+    <t xml:space="preserve">2.41666841506958</t>
   </si>
   <si>
     <t xml:space="preserve">2.45941615104675</t>
@@ -530,49 +533,49 @@
     <t xml:space="preserve">2.61045813560486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54918646812439</t>
+    <t xml:space="preserve">2.54918622970581</t>
   </si>
   <si>
     <t xml:space="preserve">2.57910966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5506112575531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5235378742218</t>
+    <t xml:space="preserve">2.55061149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52353763580322</t>
   </si>
   <si>
     <t xml:space="preserve">2.57341003417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465594291687</t>
+    <t xml:space="preserve">2.64465618133545</t>
   </si>
   <si>
     <t xml:space="preserve">2.69310355186462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64038157463074</t>
+    <t xml:space="preserve">2.64038181304932</t>
   </si>
   <si>
     <t xml:space="preserve">2.63895630836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62898230552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63325715065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67172956466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867582321167</t>
+    <t xml:space="preserve">2.62898182868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63325691223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67172980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867558479309</t>
   </si>
   <si>
     <t xml:space="preserve">2.73727607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6731550693512</t>
+    <t xml:space="preserve">2.67315483093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.70307803153992</t>
@@ -581,10 +584,10 @@
     <t xml:space="preserve">2.71447730064392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70735263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65178084373474</t>
+    <t xml:space="preserve">2.70735287666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65178108215332</t>
   </si>
   <si>
     <t xml:space="preserve">2.66887998580933</t>
@@ -593,10 +596,10 @@
     <t xml:space="preserve">2.63753151893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65748023986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486058235168</t>
+    <t xml:space="preserve">2.65748047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486082077026</t>
   </si>
   <si>
     <t xml:space="preserve">2.52211260795593</t>
@@ -605,7 +608,7 @@
     <t xml:space="preserve">2.5149884223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41524386405945</t>
+    <t xml:space="preserve">2.41524362564087</t>
   </si>
   <si>
     <t xml:space="preserve">2.43234300613403</t>
@@ -614,25 +617,22 @@
     <t xml:space="preserve">2.43661737442017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39386963844299</t>
+    <t xml:space="preserve">2.39386987686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.39244508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35112190246582</t>
+    <t xml:space="preserve">2.3511221408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236828804016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53066253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57768487930298</t>
+    <t xml:space="preserve">2.53066229820251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57768511772156</t>
   </si>
   <si>
     <t xml:space="preserve">2.58908438682556</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">2.63468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6959536075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68027925491333</t>
+    <t xml:space="preserve">2.69595336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68027949333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012589454651</t>
+    <t xml:space="preserve">2.69737839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012565612793</t>
   </si>
   <si>
     <t xml:space="preserve">2.74297571182251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72445154190063</t>
+    <t xml:space="preserve">2.72445178031921</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434993743896</t>
+    <t xml:space="preserve">2.7287266254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434969902039</t>
   </si>
   <si>
     <t xml:space="preserve">2.75152516365051</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">2.69025373458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760831832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58338475227356</t>
+    <t xml:space="preserve">2.65035605430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760807991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58338451385498</t>
   </si>
   <si>
     <t xml:space="preserve">2.5534610748291</t>
@@ -698,49 +698,49 @@
     <t xml:space="preserve">2.5206880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60618352890015</t>
+    <t xml:space="preserve">2.60618329048157</t>
   </si>
   <si>
     <t xml:space="preserve">2.56058597564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5449116230011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54063677787781</t>
+    <t xml:space="preserve">2.54491186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54063701629639</t>
   </si>
   <si>
     <t xml:space="preserve">2.50501370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49788928031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50643849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53351187705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57625985145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193396568298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58195924758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55916047096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58623433113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53636193275452</t>
+    <t xml:space="preserve">2.49788951873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50643873214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53351211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57625961303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048365592957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58195948600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5591607093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58623456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5363621711731</t>
   </si>
   <si>
     <t xml:space="preserve">2.48506474494934</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">2.54348659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68740391731262</t>
+    <t xml:space="preserve">2.68740367889404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69452834129333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75722479820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77147459983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79712295532227</t>
+    <t xml:space="preserve">2.75722503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7714741230011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79712271690369</t>
   </si>
   <si>
     <t xml:space="preserve">2.78857350349426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79997253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83132123947144</t>
+    <t xml:space="preserve">2.79997229576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83132100105286</t>
   </si>
   <si>
     <t xml:space="preserve">2.90541696548462</t>
@@ -779,49 +779,49 @@
     <t xml:space="preserve">3.03508520126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06215834617615</t>
+    <t xml:space="preserve">3.06215858459473</t>
   </si>
   <si>
     <t xml:space="preserve">3.15477848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29727077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25737333297729</t>
+    <t xml:space="preserve">3.29727029800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25737309455872</t>
   </si>
   <si>
     <t xml:space="preserve">3.07783269882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16190338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16047787666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21890020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174954414368</t>
+    <t xml:space="preserve">3.16760277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16190314292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16047835350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21889972686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174978256226</t>
   </si>
   <si>
     <t xml:space="preserve">3.27589678764343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28159618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877188682556</t>
+    <t xml:space="preserve">3.28159666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">3.23172378540039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12912964820862</t>
+    <t xml:space="preserve">3.1291298866272</t>
   </si>
   <si>
     <t xml:space="preserve">3.19610118865967</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">3.1975257396698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23884892463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602438926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157114028931</t>
+    <t xml:space="preserve">3.23884844779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157066345215</t>
   </si>
   <si>
     <t xml:space="preserve">3.32576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2830216884613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864428520203</t>
+    <t xml:space="preserve">3.28302145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864404678345</t>
   </si>
   <si>
     <t xml:space="preserve">3.34001898765564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39559030532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3556923866272</t>
+    <t xml:space="preserve">3.39559054374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35569262504578</t>
   </si>
   <si>
     <t xml:space="preserve">3.23457431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27019762992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08923196792603</t>
+    <t xml:space="preserve">3.27019715309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0892322063446</t>
   </si>
   <si>
     <t xml:space="preserve">3.06358313560486</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706664085388</t>
+    <t xml:space="preserve">3.09706711769104</t>
   </si>
   <si>
     <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13886070251465</t>
+    <t xml:space="preserve">3.13886046409607</t>
   </si>
   <si>
     <t xml:space="preserve">3.14462518692017</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">3.11003756523132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11868453025818</t>
+    <t xml:space="preserve">3.11868476867676</t>
   </si>
   <si>
     <t xml:space="preserve">3.07112598419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03797888755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04806709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762630462646</t>
+    <t xml:space="preserve">3.03797912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04806685447693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762606620789</t>
   </si>
   <si>
     <t xml:space="preserve">3.0062735080719</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">2.90395069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89098000526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87512731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918642044067</t>
+    <t xml:space="preserve">2.89098024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87512707710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918594360352</t>
   </si>
   <si>
     <t xml:space="preserve">2.92700886726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90683269500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86936259269714</t>
+    <t xml:space="preserve">2.9068329334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86936283111572</t>
   </si>
   <si>
     <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85783338546753</t>
+    <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.85350966453552</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">2.8246865272522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79298067092896</t>
+    <t xml:space="preserve">2.79298090934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.76415705680847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81027460098267</t>
+    <t xml:space="preserve">2.81027483940125</t>
   </si>
   <si>
     <t xml:space="preserve">2.80018639564514</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">2.72956919670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75262832641602</t>
+    <t xml:space="preserve">2.75262784957886</t>
   </si>
   <si>
     <t xml:space="preserve">2.75983381271362</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">2.74686336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95439100265503</t>
+    <t xml:space="preserve">2.95439124107361</t>
   </si>
   <si>
     <t xml:space="preserve">2.92124462127686</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">2.92845058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92556810379028</t>
+    <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189225196838</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">2.83045125007629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82612752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80739235877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80883359909058</t>
+    <t xml:space="preserve">2.82612729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80739212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80883383750916</t>
   </si>
   <si>
     <t xml:space="preserve">2.84053921699524</t>
@@ -1025,28 +1025,28 @@
     <t xml:space="preserve">2.86503911018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87656831741333</t>
+    <t xml:space="preserve">2.87656855583191</t>
   </si>
   <si>
     <t xml:space="preserve">2.90827393531799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83909797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73821616172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7555103302002</t>
+    <t xml:space="preserve">2.83909773826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73821640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75551056861877</t>
   </si>
   <si>
     <t xml:space="preserve">2.76848101615906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218706130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72668695449829</t>
+    <t xml:space="preserve">2.70218729972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72668671607971</t>
   </si>
   <si>
     <t xml:space="preserve">2.71371650695801</t>
@@ -1055,25 +1055,25 @@
     <t xml:space="preserve">2.72524571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68057012557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336392402649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65895247459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406908988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7944221496582</t>
+    <t xml:space="preserve">2.68056988716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65895223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67624592781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406885147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79442191123962</t>
   </si>
   <si>
     <t xml:space="preserve">2.79874539375305</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">2.74542212486267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78577494621277</t>
+    <t xml:space="preserve">2.78577470779419</t>
   </si>
   <si>
     <t xml:space="preserve">2.92268586158752</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">3.0250084400177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02644944190979</t>
+    <t xml:space="preserve">3.02644920349121</t>
   </si>
   <si>
     <t xml:space="preserve">3.0696849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10571384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12156653404236</t>
+    <t xml:space="preserve">3.1057140827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12156629562378</t>
   </si>
   <si>
     <t xml:space="preserve">3.17056632041931</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.14174294471741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13597846031189</t>
+    <t xml:space="preserve">3.13597822189331</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850788116455</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">3.07689023017883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08409667015076</t>
+    <t xml:space="preserve">3.08409643173218</t>
   </si>
   <si>
     <t xml:space="preserve">3.07400798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04086112976074</t>
+    <t xml:space="preserve">3.04086089134216</t>
   </si>
   <si>
     <t xml:space="preserve">3.05383157730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17921304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12588977813721</t>
+    <t xml:space="preserve">3.17921328544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589001655579</t>
   </si>
   <si>
     <t xml:space="preserve">3.05527305603027</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">3.14894866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16191935539246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14750790596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0999493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1590371131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15471339225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12877249717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11580157279968</t>
+    <t xml:space="preserve">3.16191911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14750742912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09994912147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15903687477112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15471315383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12877225875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11580181121826</t>
   </si>
   <si>
     <t xml:space="preserve">3.10427284240723</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">3.12012529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05815529823303</t>
+    <t xml:space="preserve">3.05815505981445</t>
   </si>
   <si>
     <t xml:space="preserve">3.00483226776123</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">2.7843337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82180404663086</t>
+    <t xml:space="preserve">2.82180380821228</t>
   </si>
   <si>
     <t xml:space="preserve">2.86792159080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89674472808838</t>
+    <t xml:space="preserve">2.89674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.88233304023743</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.82900977134705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70362854003906</t>
+    <t xml:space="preserve">2.82324528694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
     <t xml:space="preserve">2.72236371040344</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">2.70506954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71227550506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65606999397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858431816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76703977584839</t>
+    <t xml:space="preserve">2.71227526664734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65607023239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858407974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76703953742981</t>
   </si>
   <si>
     <t xml:space="preserve">2.78505420684814</t>
@@ -1244,31 +1244,31 @@
     <t xml:space="preserve">2.7346134185791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70579051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7310106754303</t>
+    <t xml:space="preserve">2.70579028129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73101043701172</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020173072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79225993156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84630393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.774245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77064251899719</t>
+    <t xml:space="preserve">2.79226040840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84630417823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77424573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77064228057861</t>
   </si>
   <si>
     <t xml:space="preserve">2.70939302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74181962013245</t>
+    <t xml:space="preserve">2.74181938171387</t>
   </si>
   <si>
     <t xml:space="preserve">2.71299600601196</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">2.63373184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62652564048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64093732833862</t>
+    <t xml:space="preserve">2.62652587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6409375667572</t>
   </si>
   <si>
     <t xml:space="preserve">2.65534925460815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64814329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58689379692078</t>
+    <t xml:space="preserve">2.64814305305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689403533936</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248210906982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57968783378601</t>
+    <t xml:space="preserve">2.57968807220459</t>
   </si>
   <si>
     <t xml:space="preserve">2.55807042121887</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.56887936592102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43557143211365</t>
+    <t xml:space="preserve">2.43557119369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.37432217597961</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">2.36351299285889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35991024971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44998288154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35270428657532</t>
+    <t xml:space="preserve">2.3599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4499831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3527045249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.52204155921936</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">2.4211597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50762987136841</t>
+    <t xml:space="preserve">2.50762963294983</t>
   </si>
   <si>
     <t xml:space="preserve">2.59409976005554</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">2.56527638435364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63012909889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65174603462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62292313575745</t>
+    <t xml:space="preserve">2.63012886047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65174627304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62292289733887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60130548477173</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.73281192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172174453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49582004547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48841428756714</t>
+    <t xml:space="preserve">2.62172198295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49582028388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48841404914856</t>
   </si>
   <si>
     <t xml:space="preserve">2.40324521064758</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">2.40694832801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36991786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29956126213074</t>
+    <t xml:space="preserve">2.36991810798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29956150054932</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068930625916</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">2.32548213005066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37732410430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38843321800232</t>
+    <t xml:space="preserve">2.37732434272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3884334564209</t>
   </si>
   <si>
     <t xml:space="preserve">2.4291660785675</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">2.52174115180969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53284978866577</t>
+    <t xml:space="preserve">2.53285002708435</t>
   </si>
   <si>
     <t xml:space="preserve">2.57728600502014</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">2.5254442691803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45508718490601</t>
+    <t xml:space="preserve">2.45508742332458</t>
   </si>
   <si>
     <t xml:space="preserve">2.58098888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395890235901</t>
+    <t xml:space="preserve">2.54395914077759</t>
   </si>
   <si>
     <t xml:space="preserve">2.47360229492188</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">2.44768118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53655290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47730541229248</t>
+    <t xml:space="preserve">2.5365526676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4773051738739</t>
   </si>
   <si>
     <t xml:space="preserve">2.51433515548706</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">2.48100829124451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46619606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39583897590637</t>
+    <t xml:space="preserve">2.46619629859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39583921432495</t>
   </si>
   <si>
     <t xml:space="preserve">2.41065144538879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35140323638916</t>
+    <t xml:space="preserve">2.35140299797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.36621522903442</t>
@@ -1508,31 +1508,31 @@
     <t xml:space="preserve">2.34399724006653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35880947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35510635375977</t>
+    <t xml:space="preserve">2.35880923271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35510611534119</t>
   </si>
   <si>
     <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30696725845337</t>
+    <t xml:space="preserve">2.30696749687195</t>
   </si>
   <si>
     <t xml:space="preserve">2.31067037582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32177925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39954233169556</t>
+    <t xml:space="preserve">2.32177901268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39954209327698</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102698326111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41435408592224</t>
+    <t xml:space="preserve">2.41435432434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.37362098693848</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">2.27734327316284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2662341594696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29215526580811</t>
+    <t xml:space="preserve">2.26623439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29215550422668</t>
   </si>
   <si>
     <t xml:space="preserve">2.27364039421082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2884521484375</t>
+    <t xml:space="preserve">2.28845238685608</t>
   </si>
   <si>
     <t xml:space="preserve">2.28474926948547</t>
@@ -1577,313 +1577,313 @@
     <t xml:space="preserve">2.38473033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24031329154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15514445304871</t>
+    <t xml:space="preserve">2.20698618888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24031352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15514421463013</t>
   </si>
   <si>
     <t xml:space="preserve">2.13292646408081</t>
   </si>
   <si>
+    <t xml:space="preserve">2.1477382183075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10330247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959959983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10700559616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0625696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9885094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147943496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06627249717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04775738716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14403510093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13662934303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23290705680847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512528419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20328330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1995804309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21809530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070871353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24771952629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3365912437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65504908561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68097019195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60320734977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62912797927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65875196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65134596824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62542486190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71799993515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70318794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7291088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69207906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71429681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75502991676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8031690120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81798100471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84390187263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87352585792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86241698265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88093185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76243567466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76984214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79946613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81427788734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79576325416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75873279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85871386528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314984321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89574384689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90685296058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88833808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96239757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98091292381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91796159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758582115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95128870010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9364767074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95499181747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93277382850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91055583953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96980381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97721004486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94017958641052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89944672584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81057500839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86611986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80687189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85501098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71059393882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70689105987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61061334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6402370929718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6365339756012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63283109664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61801910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69578194618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68837594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61431622505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56988024711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49211740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50692892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34770011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23661017417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18476819992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19587731361389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29948091506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2177734375</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1033022403717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849024772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10700559616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0625696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9885094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147943496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0662727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04775738716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997561454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922334671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14403533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13662934303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23290729522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2032835483551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19958066940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21809530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070847511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24771928787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3365912437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51063203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65504908561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68096995353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60320734977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62912797927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66615772247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65875172615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65134596824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62542486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71799993515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70318818092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72910904884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69207906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71429681777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75503015518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80316877365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81798100471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84390187263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87352585792542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86241674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88093209266663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76243591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76984214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7994658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81427788734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79576301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75873279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85871386528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314984321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89574408531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90685296058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88833808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96239757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98091292381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91796159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758558273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95128846168518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9364767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95499157905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93277382850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91055607795715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96980404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720980644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94017958641052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89944696426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81057500839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8661196231842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80687189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85501098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71059393882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70689105987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61061334609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64023733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6365339756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63283109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69578218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68837594985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61431622505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56988024711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49211716651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50692892074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34770035743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23661017417908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18476843833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19587755203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29948091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21777319908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10883045196533</t>
+    <t xml:space="preserve">2.10883021354675</t>
   </si>
   <si>
     <t xml:space="preserve">2.12439346313477</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">2.09326696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12050271034241</t>
+    <t xml:space="preserve">2.12050247192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.13995671272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12828397750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770347595215</t>
+    <t xml:space="preserve">2.12828421592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770323753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.0504674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657697677612</t>
+    <t xml:space="preserve">2.04657673835754</t>
   </si>
   <si>
     <t xml:space="preserve">2.03490447998047</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">2.03101348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02323174476624</t>
+    <t xml:space="preserve">2.02323198318481</t>
   </si>
   <si>
     <t xml:space="preserve">2.0582492351532</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944593429565</t>
+    <t xml:space="preserve">2.22944617271423</t>
   </si>
   <si>
     <t xml:space="preserve">2.1866466999054</t>
@@ -1946,22 +1946,22 @@
     <t xml:space="preserve">1.9687602519989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00377774238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.929851770401</t>
+    <t xml:space="preserve">2.00377798080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92985200881958</t>
   </si>
   <si>
     <t xml:space="preserve">2.02712273597717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94152414798737</t>
+    <t xml:space="preserve">1.94152438640594</t>
   </si>
   <si>
     <t xml:space="preserve">1.84425365924835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79367291927338</t>
+    <t xml:space="preserve">1.79367303848267</t>
   </si>
   <si>
     <t xml:space="preserve">1.76643693447113</t>
@@ -1973,19 +1973,19 @@
     <t xml:space="preserve">1.75087368488312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74698293209076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69251132011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78978192806244</t>
+    <t xml:space="preserve">1.74698281288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69251120090485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78978204727173</t>
   </si>
   <si>
     <t xml:space="preserve">1.82090854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73920106887817</t>
+    <t xml:space="preserve">1.73920118808746</t>
   </si>
   <si>
     <t xml:space="preserve">1.74309206008911</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">1.7197470664978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70418393611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78589141368866</t>
+    <t xml:space="preserve">1.7041836977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78589129447937</t>
   </si>
   <si>
     <t xml:space="preserve">1.73141956329346</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">1.71585607528687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73531055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78200030326843</t>
+    <t xml:space="preserve">1.7353104352951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78200042247772</t>
   </si>
   <si>
     <t xml:space="preserve">1.83258128166199</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">1.87927114963531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79756379127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032780647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869029045105</t>
+    <t xml:space="preserve">1.79756367206573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032792568207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869052886963</t>
   </si>
   <si>
     <t xml:space="preserve">1.75476455688477</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">1.76254630088806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80534517765045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8170177936554</t>
+    <t xml:space="preserve">1.80534541606903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81701803207397</t>
   </si>
   <si>
     <t xml:space="preserve">1.82479953765869</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">1.91428852081299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93374276161194</t>
+    <t xml:space="preserve">1.93374264240265</t>
   </si>
   <si>
     <t xml:space="preserve">1.89094376564026</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">1.90650689601898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89483451843262</t>
+    <t xml:space="preserve">1.89483428001404</t>
   </si>
   <si>
     <t xml:space="preserve">1.85981702804565</t>
@@ -2090,34 +2090,34 @@
     <t xml:space="preserve">2.01155948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16719245910645</t>
+    <t xml:space="preserve">2.16719269752502</t>
   </si>
   <si>
     <t xml:space="preserve">2.16330170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08159422874451</t>
+    <t xml:space="preserve">2.08159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217544555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2099916934967</t>
+    <t xml:space="preserve">2.13217520713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20999193191528</t>
   </si>
   <si>
     <t xml:space="preserve">2.19053769111633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15551996231079</t>
+    <t xml:space="preserve">2.15552020072937</t>
   </si>
   <si>
     <t xml:space="preserve">2.19831943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17108345031738</t>
+    <t xml:space="preserve">2.1710832118988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14384770393372</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.98821461200714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15941119194031</t>
+    <t xml:space="preserve">2.15941095352173</t>
   </si>
   <si>
     <t xml:space="preserve">2.13606595993042</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">2.01934123039246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87148940563202</t>
+    <t xml:space="preserve">1.87148928642273</t>
   </si>
   <si>
     <t xml:space="preserve">1.91039776802063</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">1.89872539043427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95319676399231</t>
+    <t xml:space="preserve">1.95319700241089</t>
   </si>
   <si>
     <t xml:space="preserve">1.99988687038422</t>
@@ -2168,16 +2168,16 @@
     <t xml:space="preserve">1.96486949920654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99210512638092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72752869129181</t>
+    <t xml:space="preserve">1.9921053647995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7275288105011</t>
   </si>
   <si>
     <t xml:space="preserve">1.68862044811249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62636709213257</t>
+    <t xml:space="preserve">1.62636697292328</t>
   </si>
   <si>
     <t xml:space="preserve">1.59524047374725</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">1.48941004276276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45361423492432</t>
+    <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
     <t xml:space="preserve">1.33844566345215</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">1.16102373600006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08009457588196</t>
+    <t xml:space="preserve">1.08009469509125</t>
   </si>
   <si>
     <t xml:space="preserve">1.05986213684082</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">1.0847635269165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10188317298889</t>
+    <t xml:space="preserve">1.1018830537796</t>
   </si>
   <si>
     <t xml:space="preserve">1.22483336925507</t>
@@ -2228,22 +2228,22 @@
     <t xml:space="preserve">1.32910776138306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35400915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26685428619385</t>
+    <t xml:space="preserve">1.35400903224945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26685440540314</t>
   </si>
   <si>
     <t xml:space="preserve">1.27152323722839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32288241386414</t>
+    <t xml:space="preserve">1.32288229465485</t>
   </si>
   <si>
     <t xml:space="preserve">1.28864300251007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28397393226624</t>
+    <t xml:space="preserve">1.28397405147552</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331195354462</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">1.36179065704346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26062917709351</t>
+    <t xml:space="preserve">1.26062905788422</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">1.28241789340973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2295024394989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23884046077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24350953102112</t>
+    <t xml:space="preserve">1.22950232028961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23884034156799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24350941181183</t>
   </si>
   <si>
     <t xml:space="preserve">1.20927011966705</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">1.10343956947327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10499584674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08631992340088</t>
+    <t xml:space="preserve">1.10499596595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08631980419159</t>
   </si>
   <si>
     <t xml:space="preserve">1.05674970149994</t>
@@ -2312,19 +2312,19 @@
     <t xml:space="preserve">1.06764388084412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12211549282074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10655212402344</t>
+    <t xml:space="preserve">1.12211561203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
     <t xml:space="preserve">1.14234793186188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15012955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13923513889313</t>
+    <t xml:space="preserve">1.15012943744659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13923525810242</t>
   </si>
   <si>
     <t xml:space="preserve">1.19837582111359</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">1.27930510044098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17969989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16413640975952</t>
+    <t xml:space="preserve">1.17969977855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16413652896881</t>
   </si>
   <si>
     <t xml:space="preserve">1.23572790622711</t>
@@ -2387,16 +2387,16 @@
     <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546048641205</t>
+    <t xml:space="preserve">1.14546036720276</t>
   </si>
   <si>
     <t xml:space="preserve">1.16724920272827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1734744310379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15168583393097</t>
+    <t xml:space="preserve">1.17347455024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15168595314026</t>
   </si>
   <si>
     <t xml:space="preserve">1.17191827297211</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">1.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15635478496552</t>
+    <t xml:space="preserve">1.1563549041748</t>
   </si>
   <si>
     <t xml:space="preserve">1.1252281665802</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08320724964142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06297492980957</t>
+    <t xml:space="preserve">1.06608760356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08320713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06297504901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.04896795749664</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">1.05052423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585516452789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03962993621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04118621349335</t>
+    <t xml:space="preserve">1.04585528373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03962981700897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04118633270264</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03496098518372</t>
+    <t xml:space="preserve">1.03496086597443</t>
   </si>
   <si>
     <t xml:space="preserve">1.0365172624588</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99605256319046</t>
+    <t xml:space="preserve">0.99605268239975</t>
   </si>
   <si>
     <t xml:space="preserve">1.01628494262695</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">0.966482281684875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9649258852005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958700656890869</t>
+    <t xml:space="preserve">0.96492600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958700597286224</t>
   </si>
   <si>
     <t xml:space="preserve">0.954031646251678</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827275276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969594895839691</t>
+    <t xml:space="preserve">0.989827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969595015048981</t>
   </si>
   <si>
     <t xml:space="preserve">0.949362695217133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968038618564606</t>
+    <t xml:space="preserve">0.968038558959961</t>
   </si>
   <si>
     <t xml:space="preserve">0.957144260406494</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">1.06453120708466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05830585956573</t>
+    <t xml:space="preserve">1.05830597877502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02406668663025</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">0.988270938396454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985158324241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941581070423126</t>
+    <t xml:space="preserve">0.985158205032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941580951213837</t>
   </si>
   <si>
     <t xml:space="preserve">0.93379932641983</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">0.887109339237213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888665616512299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891778409481049</t>
+    <t xml:space="preserve">0.888665676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891778290271759</t>
   </si>
   <si>
     <t xml:space="preserve">0.83575040102005</t>
@@ -2561,16 +2561,16 @@
     <t xml:space="preserve">0.803067326545715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787504136562347</t>
+    <t xml:space="preserve">0.787504076957703</t>
   </si>
   <si>
     <t xml:space="preserve">0.829525113105774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831081330776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840419471263885</t>
+    <t xml:space="preserve">0.831081390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840419411659241</t>
   </si>
   <si>
     <t xml:space="preserve">0.826412379741669</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896447360515594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902672588825226</t>
+    <t xml:space="preserve">0.89644730091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902672708034515</t>
   </si>
   <si>
     <t xml:space="preserve">0.915123343467712</t>
@@ -2603,40 +2603,40 @@
     <t xml:space="preserve">0.983601987361908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978932917118073</t>
+    <t xml:space="preserve">0.978933036327362</t>
   </si>
   <si>
     <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96181321144104</t>
+    <t xml:space="preserve">0.96181333065033</t>
   </si>
   <si>
     <t xml:space="preserve">0.946249961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943137347698212</t>
+    <t xml:space="preserve">0.943137228488922</t>
   </si>
   <si>
     <t xml:space="preserve">0.930686712265015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952475249767303</t>
+    <t xml:space="preserve">0.952475368976593</t>
   </si>
   <si>
     <t xml:space="preserve">0.927573978900909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926017761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935355663299561</t>
+    <t xml:space="preserve">0.926017642021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.935355722904205</t>
   </si>
   <si>
     <t xml:space="preserve">0.971151351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947806298732758</t>
+    <t xml:space="preserve">0.947806417942047</t>
   </si>
   <si>
     <t xml:space="preserve">0.919792413711548</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">0.916679620742798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899560034275055</t>
+    <t xml:space="preserve">0.89955997467041</t>
   </si>
   <si>
     <t xml:space="preserve">0.918236017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908897995948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894890964031219</t>
+    <t xml:space="preserve">0.908897876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894891023635864</t>
   </si>
   <si>
     <t xml:space="preserve">0.910454273223877</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">1.12989723682404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1003270149231</t>
+    <t xml:space="preserve">1.10032689571381</t>
   </si>
   <si>
     <t xml:space="preserve">1.09877049922943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07231283187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12834095954895</t>
+    <t xml:space="preserve">1.07231295108795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12834084033966</t>
   </si>
   <si>
     <t xml:space="preserve">1.12055921554565</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">1.23105883598328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26996719837189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25751638412476</t>
+    <t xml:space="preserve">1.2699670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25751650333405</t>
   </si>
   <si>
     <t xml:space="preserve">1.26841080188751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36023426055908</t>
+    <t xml:space="preserve">1.27307975292206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36023437976837</t>
   </si>
   <si>
     <t xml:space="preserve">1.38513553142548</t>
@@ -2750,13 +2750,13 @@
     <t xml:space="preserve">1.40381157398224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112867832184</t>
+    <t xml:space="preserve">1.37112855911255</t>
   </si>
   <si>
     <t xml:space="preserve">1.3991425037384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39447355270386</t>
+    <t xml:space="preserve">1.39447367191315</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980460166931</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">1.39758634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39136099815369</t>
+    <t xml:space="preserve">1.39136111736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.4053680896759</t>
@@ -2774,19 +2774,19 @@
     <t xml:space="preserve">1.43805110454559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52053642272949</t>
+    <t xml:space="preserve">1.52053654193878</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022322177887</t>
+    <t xml:space="preserve">1.56022310256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.58745884895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53765606880188</t>
+    <t xml:space="preserve">1.53765618801117</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431119441986</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">1.5561363697052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57044196128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56567347049713</t>
+    <t xml:space="preserve">1.57044208049774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56567358970642</t>
   </si>
   <si>
     <t xml:space="preserve">1.567263007164</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">1.4432806968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40672183036804</t>
+    <t xml:space="preserve">1.40672194957733</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374359607697</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">1.44487023353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39241635799408</t>
+    <t xml:space="preserve">1.39241623878479</t>
   </si>
   <si>
     <t xml:space="preserve">1.35744690895081</t>
@@ -2891,22 +2891,22 @@
     <t xml:space="preserve">1.31453001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27638149261475</t>
+    <t xml:space="preserve">1.27638161182404</t>
   </si>
   <si>
     <t xml:space="preserve">1.30181384086609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30499291419983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31135082244873</t>
+    <t xml:space="preserve">1.30499279499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31135094165802</t>
   </si>
   <si>
     <t xml:space="preserve">1.30340325832367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28432905673981</t>
+    <t xml:space="preserve">1.2843291759491</t>
   </si>
   <si>
     <t xml:space="preserve">1.27479207515717</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">1.2223379611969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2557178735733</t>
+    <t xml:space="preserve">1.25571775436401</t>
   </si>
   <si>
     <t xml:space="preserve">1.24935984611511</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">1.3749315738678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37969994544983</t>
+    <t xml:space="preserve">1.37970006465912</t>
   </si>
   <si>
     <t xml:space="preserve">1.38128960132599</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">1.40513241291046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5338830947876</t>
+    <t xml:space="preserve">1.53388321399689</t>
   </si>
   <si>
     <t xml:space="preserve">1.49732422828674</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">1.4146693944931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42420649528503</t>
+    <t xml:space="preserve">1.42420661449432</t>
   </si>
   <si>
     <t xml:space="preserve">1.45917594432831</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">1.33837270736694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38287925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050342082977</t>
+    <t xml:space="preserve">1.38287913799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050330162048</t>
   </si>
   <si>
     <t xml:space="preserve">1.52116715908051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49573481082916</t>
+    <t xml:space="preserve">1.49573469161987</t>
   </si>
   <si>
     <t xml:space="preserve">1.50845098495483</t>
@@ -3053,16 +3053,16 @@
     <t xml:space="preserve">1.51162993907928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50209283828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51321959495544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47507095336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010174274445</t>
+    <t xml:space="preserve">1.50209295749664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51321947574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47507107257843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010186195374</t>
   </si>
   <si>
     <t xml:space="preserve">1.4877872467041</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">1.47983956336975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45599687099457</t>
+    <t xml:space="preserve">1.45599699020386</t>
   </si>
   <si>
     <t xml:space="preserve">1.48301875591278</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">1.66501832008362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67693960666656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70078241825104</t>
+    <t xml:space="preserve">1.67693948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70078253746033</t>
   </si>
   <si>
     <t xml:space="preserve">1.65309679508209</t>
@@ -3107,16 +3107,16 @@
     <t xml:space="preserve">1.57362103462219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43851208686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645988941193</t>
+    <t xml:space="preserve">1.43851220607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645977020264</t>
   </si>
   <si>
     <t xml:space="preserve">1.45440745353699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45122838020325</t>
+    <t xml:space="preserve">1.45122826099396</t>
   </si>
   <si>
     <t xml:space="preserve">1.49414527416229</t>
@@ -3125,22 +3125,22 @@
     <t xml:space="preserve">1.5163985490799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61335909366608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733281612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322794437408</t>
+    <t xml:space="preserve">1.61335897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733293533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322806358337</t>
   </si>
   <si>
     <t xml:space="preserve">1.62130653858185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349024295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58792662620544</t>
+    <t xml:space="preserve">1.59349012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58792674541473</t>
   </si>
   <si>
     <t xml:space="preserve">1.60143780708313</t>
@@ -3149,22 +3149,22 @@
     <t xml:space="preserve">1.62925410270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104447841644</t>
+    <t xml:space="preserve">1.66104435920715</t>
   </si>
   <si>
     <t xml:space="preserve">1.53865170478821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51957738399506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183089733124</t>
+    <t xml:space="preserve">1.51957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183077812195</t>
   </si>
   <si>
     <t xml:space="preserve">1.52911460399628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53070425987244</t>
+    <t xml:space="preserve">1.53070414066315</t>
   </si>
   <si>
     <t xml:space="preserve">1.52434599399567</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">1.30817186832428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30022442340851</t>
+    <t xml:space="preserve">1.30022430419922</t>
   </si>
   <si>
     <t xml:space="preserve">1.22869610786438</t>
@@ -3191,25 +3191,25 @@
     <t xml:space="preserve">1.36539447307587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36062598228455</t>
+    <t xml:space="preserve">1.36062586307526</t>
   </si>
   <si>
     <t xml:space="preserve">1.40831136703491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59746372699738</t>
+    <t xml:space="preserve">1.59746384620667</t>
   </si>
   <si>
     <t xml:space="preserve">1.74846792221069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423202037811</t>
+    <t xml:space="preserve">1.78423190116882</t>
   </si>
   <si>
     <t xml:space="preserve">1.76038920879364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77231073379517</t>
+    <t xml:space="preserve">1.77231061458588</t>
   </si>
   <si>
     <t xml:space="preserve">1.78025817871094</t>
@@ -3218,31 +3218,31 @@
     <t xml:space="preserve">1.74449408054352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81999599933624</t>
+    <t xml:space="preserve">1.81999611854553</t>
   </si>
   <si>
     <t xml:space="preserve">1.81204855442047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83191752433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8279435634613</t>
+    <t xml:space="preserve">1.83191764354706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82794368267059</t>
   </si>
   <si>
     <t xml:space="preserve">1.85178637504578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83589136600494</t>
+    <t xml:space="preserve">1.83589124679565</t>
   </si>
   <si>
     <t xml:space="preserve">1.83986508846283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.823970079422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628421783447</t>
+    <t xml:space="preserve">1.82396996021271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628433704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.79217958450317</t>
@@ -3254,13 +3254,13 @@
     <t xml:space="preserve">1.788205742836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7285989522934</t>
+    <t xml:space="preserve">1.72859883308411</t>
   </si>
   <si>
     <t xml:space="preserve">1.64514923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71667766571045</t>
+    <t xml:space="preserve">1.71667754650116</t>
   </si>
   <si>
     <t xml:space="preserve">1.73654639720917</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">1.75641548633575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76436293125153</t>
+    <t xml:space="preserve">1.76436305046082</t>
   </si>
   <si>
     <t xml:space="preserve">1.80410087108612</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">1.76195001602173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75763154029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490556240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7533130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603892326355</t>
+    <t xml:space="preserve">1.75763165950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75331294536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603904247284</t>
   </si>
   <si>
     <t xml:space="preserve">1.67730736732483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.644486784935</t>
+    <t xml:space="preserve">1.64448666572571</t>
   </si>
   <si>
     <t xml:space="preserve">1.55811655521393</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">1.50456702709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50283980369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865617275238</t>
+    <t xml:space="preserve">1.50283968448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865605354309</t>
   </si>
   <si>
     <t xml:space="preserve">1.51665902137756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48038339614868</t>
+    <t xml:space="preserve">1.48038351535797</t>
   </si>
   <si>
     <t xml:space="preserve">1.4890204668045</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">1.3819215297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40092289447784</t>
+    <t xml:space="preserve">1.40092301368713</t>
   </si>
   <si>
     <t xml:space="preserve">1.43028879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4061051607132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501204013824</t>
+    <t xml:space="preserve">1.40610527992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501192092896</t>
   </si>
   <si>
     <t xml:space="preserve">1.37328457832336</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">1.34737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52875065803528</t>
+    <t xml:space="preserve">1.52875077724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.59957420825958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54775214195251</t>
+    <t xml:space="preserve">1.5477522611618</t>
   </si>
   <si>
     <t xml:space="preserve">1.55293428897858</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">1.55466175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60648393630981</t>
+    <t xml:space="preserve">1.60648381710052</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475647449493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58230018615723</t>
+    <t xml:space="preserve">1.58230030536652</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057284355164</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">1.4665641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45447242259979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510652542114</t>
+    <t xml:space="preserve">1.45447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510664463043</t>
   </si>
   <si>
     <t xml:space="preserve">1.43547093868256</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">1.33009946346283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3801943063736</t>
+    <t xml:space="preserve">1.38019418716431</t>
   </si>
   <si>
     <t xml:space="preserve">1.35082840919495</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">1.2005443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22300064563751</t>
+    <t xml:space="preserve">1.22300052642822</t>
   </si>
   <si>
     <t xml:space="preserve">1.1884526014328</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">1.35773801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39574074745178</t>
+    <t xml:space="preserve">1.39574086666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.39746820926666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44929027557373</t>
+    <t xml:space="preserve">1.44929015636444</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992437839508</t>
+    <t xml:space="preserve">1.41992449760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301488876343</t>
+    <t xml:space="preserve">1.41301476955414</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464762687683</t>
+    <t xml:space="preserve">1.38710379600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464750766754</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33182692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591595172882</t>
+    <t xml:space="preserve">1.331827044487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591583251953</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564614295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937075614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136790752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345954418182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655017375946</t>
+    <t xml:space="preserve">1.34564602375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937063694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827751636505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136778831482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345966339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655005455017</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036927223206</t>
+    <t xml:space="preserve">1.29036915302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910094738007</t>
+    <t xml:space="preserve">1.34910106658936</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938476085663</t>
+    <t xml:space="preserve">1.49938488006592</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838624477386</t>
+    <t xml:space="preserve">1.51838636398315</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974929332733</t>
+    <t xml:space="preserve">1.50974941253662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41819703578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729312419891</t>
+    <t xml:space="preserve">1.4181969165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729300498962</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302889347076</t>
+    <t xml:space="preserve">1.60302901268005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62894010543823</t>
+    <t xml:space="preserve">1.62893998622894</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63239479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093725681305</t>
+    <t xml:space="preserve">1.6323949098587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093713760376</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3737,10 +3737,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548530101776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5719358921051</t>
+    <t xml:space="preserve">1.62548518180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57193577289581</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -8632,7 +8632,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G140" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8658,7 +8658,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8684,7 +8684,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8710,7 +8710,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8736,7 +8736,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8788,7 +8788,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8814,7 +8814,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8840,7 +8840,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8866,7 +8866,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8892,7 +8892,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8918,7 +8918,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8944,7 +8944,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8970,7 +8970,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G153" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -8996,7 +8996,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9022,7 +9022,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9048,7 +9048,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9074,7 +9074,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9100,7 +9100,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9126,7 +9126,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9152,7 +9152,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9178,7 +9178,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9204,7 +9204,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9282,7 +9282,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9308,7 +9308,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9386,7 +9386,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9412,7 +9412,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9464,7 +9464,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9490,7 +9490,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9516,7 +9516,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9542,7 +9542,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9568,7 +9568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9594,7 +9594,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9620,7 +9620,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9646,7 +9646,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9672,7 +9672,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9698,7 +9698,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9724,7 +9724,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9750,7 +9750,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9776,7 +9776,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9802,7 +9802,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9828,7 +9828,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9854,7 +9854,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9880,7 +9880,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9906,7 +9906,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9932,7 +9932,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9958,7 +9958,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9984,7 +9984,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10010,7 +10010,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10036,7 +10036,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10062,7 +10062,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10088,7 +10088,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10114,7 +10114,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10140,7 +10140,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10166,7 +10166,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10192,7 +10192,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10218,7 +10218,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10244,7 +10244,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10270,7 +10270,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10296,7 +10296,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10322,7 +10322,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10348,7 +10348,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10374,7 +10374,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10400,7 +10400,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10426,7 +10426,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10452,7 +10452,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10478,7 +10478,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10504,7 +10504,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10530,7 +10530,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10556,7 +10556,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10582,7 +10582,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10608,7 +10608,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10634,7 +10634,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G217" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10660,7 +10660,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10686,7 +10686,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10712,7 +10712,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10738,7 +10738,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10764,7 +10764,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10790,7 +10790,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10816,7 +10816,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10842,7 +10842,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10868,7 +10868,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10894,7 +10894,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10920,7 +10920,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10946,7 +10946,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10972,7 +10972,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10998,7 +10998,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11024,7 +11024,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11050,7 +11050,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11076,7 +11076,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11102,7 +11102,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11128,7 +11128,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11154,7 +11154,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11258,7 +11258,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11336,7 +11336,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11362,7 +11362,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11414,7 +11414,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11440,7 +11440,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11466,7 +11466,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11492,7 +11492,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11570,7 +11570,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11648,7 +11648,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11674,7 +11674,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11830,7 +11830,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11856,7 +11856,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G264" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11882,7 +11882,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11934,7 +11934,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12168,7 +12168,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12246,7 +12246,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12740,7 +12740,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12870,7 +12870,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13130,7 +13130,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -24986,7 +24986,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="s">
-        <v>557</v>
+        <v>457</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25012,7 +25012,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25038,7 +25038,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25064,7 +25064,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25090,7 +25090,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25116,7 +25116,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25142,7 +25142,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25168,7 +25168,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25194,7 +25194,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25220,7 +25220,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25246,7 +25246,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25272,7 +25272,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25298,7 +25298,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25324,7 +25324,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25350,7 +25350,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25376,7 +25376,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25402,7 +25402,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25428,7 +25428,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25454,7 +25454,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25480,7 +25480,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G788" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25506,7 +25506,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25532,7 +25532,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25558,7 +25558,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G791" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25584,7 +25584,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G792" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25610,7 +25610,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25636,7 +25636,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G794" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25662,7 +25662,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25688,7 +25688,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25714,7 +25714,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25740,7 +25740,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25766,7 +25766,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25792,7 +25792,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G800" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25818,7 +25818,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G801" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25844,7 +25844,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25870,7 +25870,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25896,7 +25896,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25922,7 +25922,7 @@
         <v>4</v>
       </c>
       <c r="G805" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25948,7 +25948,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25974,7 +25974,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26000,7 +26000,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G808" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26026,7 +26026,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G809" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26052,7 +26052,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26078,7 +26078,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26104,7 +26104,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26130,7 +26130,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26156,7 +26156,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26182,7 +26182,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G815" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26208,7 +26208,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26234,7 +26234,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26260,7 +26260,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26286,7 +26286,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26312,7 +26312,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26338,7 +26338,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G821" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26364,7 +26364,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26390,7 +26390,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26416,7 +26416,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26442,7 +26442,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26468,7 +26468,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26494,7 +26494,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26520,7 +26520,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26546,7 +26546,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26572,7 +26572,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G830" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26598,7 +26598,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G831" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26624,7 +26624,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G832" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26650,7 +26650,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G833" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26676,7 +26676,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26754,7 +26754,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26806,7 +26806,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26832,7 +26832,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26858,7 +26858,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26910,7 +26910,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26936,7 +26936,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26962,7 +26962,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26988,7 +26988,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27014,7 +27014,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27040,7 +27040,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27066,7 +27066,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27118,7 +27118,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G851" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27144,7 +27144,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27170,7 +27170,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27196,7 +27196,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27300,7 +27300,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G858" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27352,7 +27352,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27378,7 +27378,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G861" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27430,7 +27430,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G863" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27456,7 +27456,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G864" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27482,7 +27482,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="s">
-        <v>525</v>
+        <v>622</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27742,7 +27742,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="s">
-        <v>525</v>
+        <v>622</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28392,7 +28392,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="s">
-        <v>525</v>
+        <v>622</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -31096,7 +31096,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1004" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31356,7 +31356,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="s">
-        <v>525</v>
+        <v>622</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -70000,13 +70000,13 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911226852</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>316122</v>
       </c>
       <c r="C2501" t="n">
-        <v>2.90000009536743</v>
+        <v>2.90499997138977</v>
       </c>
       <c r="D2501" t="n">
         <v>2.81500005722046</v>
@@ -70021,6 +70021,32 @@
         <v>1486</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911921296</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>207392</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>2.9449999332428</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1503</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614468574524</t>
+    <t xml:space="preserve">3.08614444732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.01786732673645</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">2.98099732398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88131165504456</t>
+    <t xml:space="preserve">2.88131213188171</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003081321716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620670318604</t>
+    <t xml:space="preserve">2.80620694160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.86082887649536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7584125995636</t>
+    <t xml:space="preserve">2.75841212272644</t>
   </si>
   <si>
     <t xml:space="preserve">2.73929476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69013524055481</t>
+    <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
     <t xml:space="preserve">2.71744585037231</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">2.74475693702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75704717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71061825752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110151290894</t>
+    <t xml:space="preserve">2.7570469379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.710618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110127449036</t>
   </si>
   <si>
     <t xml:space="preserve">2.76114368438721</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">2.69696283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62868499755859</t>
+    <t xml:space="preserve">2.72290825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62868475914001</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935678482056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30095267295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38971376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992438316345</t>
+    <t xml:space="preserve">2.45799136161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30095291137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992414474487</t>
   </si>
   <si>
     <t xml:space="preserve">2.50442004203796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81713080406189</t>
+    <t xml:space="preserve">2.67511391639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81713128089905</t>
   </si>
   <si>
     <t xml:space="preserve">2.74885368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7816264629364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467259407043</t>
+    <t xml:space="preserve">2.78162670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467283248901</t>
   </si>
   <si>
     <t xml:space="preserve">2.8621940612793</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">2.8335177898407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84717297554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8840434551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540816307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769864082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85126972198486</t>
+    <t xml:space="preserve">2.84717321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88404297828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85126996040344</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685840606689</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">2.9495894908905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05883407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16125011444092</t>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164926528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124987602234</t>
   </si>
   <si>
     <t xml:space="preserve">3.18173289299011</t>
@@ -188,52 +188,52 @@
     <t xml:space="preserve">3.20767831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217397689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635530471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001072883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040964126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2226996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089289665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952795028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14896011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2923424243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587157249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27732133865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559893608093</t>
+    <t xml:space="preserve">3.1790018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217421531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269988059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2308931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076662063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225430727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463266372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732157707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559917449951</t>
   </si>
   <si>
     <t xml:space="preserve">3.36608266830444</t>
@@ -242,118 +242,118 @@
     <t xml:space="preserve">3.40704894065857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38656568527222</t>
+    <t xml:space="preserve">3.38656544685364</t>
   </si>
   <si>
     <t xml:space="preserve">3.33330917358398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780530929565</t>
+    <t xml:space="preserve">3.3483304977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511591911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375025749207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780507087708</t>
   </si>
   <si>
     <t xml:space="preserve">3.26366662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29097747802734</t>
+    <t xml:space="preserve">3.29097723960876</t>
   </si>
   <si>
     <t xml:space="preserve">3.26022267341614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19182658195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13482975959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1733021736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907932281494</t>
+    <t xml:space="preserve">3.19182634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15620303153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1348295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330288887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208226203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
   </si>
   <si>
     <t xml:space="preserve">3.3229193687439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34856772422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33431839942932</t>
+    <t xml:space="preserve">3.34856796264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3343186378479</t>
   </si>
   <si>
     <t xml:space="preserve">3.31151986122131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38419079780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403743743896</t>
+    <t xml:space="preserve">3.38419127464294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403767585754</t>
   </si>
   <si>
     <t xml:space="preserve">3.41981410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43406343460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108601570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.476811170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4383385181427</t>
+    <t xml:space="preserve">3.43406319618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833827972412</t>
   </si>
   <si>
     <t xml:space="preserve">3.45116233825684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4084141254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714293479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607542991638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796053886414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246506690979</t>
+    <t xml:space="preserve">3.40841507911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844012260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796030044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246530532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.8997175693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89686727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495736122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197946548462</t>
+    <t xml:space="preserve">2.89686751365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643342971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495712280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
   </si>
   <si>
     <t xml:space="preserve">3.14195418357849</t>
@@ -365,43 +365,43 @@
     <t xml:space="preserve">2.84984517097473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95671439170837</t>
+    <t xml:space="preserve">2.95671415328979</t>
   </si>
   <si>
     <t xml:space="preserve">3.06500840187073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96526408195496</t>
+    <t xml:space="preserve">3.16332769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96526384353638</t>
   </si>
   <si>
     <t xml:space="preserve">2.9552891254425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9923369884491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058067321777</t>
+    <t xml:space="preserve">2.99233722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058019638062</t>
   </si>
   <si>
     <t xml:space="preserve">3.1704523563385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23599910736084</t>
+    <t xml:space="preserve">3.23599886894226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17757725715637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13625454902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702063560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91966652870178</t>
+    <t xml:space="preserve">3.13625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
     <t xml:space="preserve">2.86551904678345</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">2.84129548072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87549352645874</t>
+    <t xml:space="preserve">2.87549328804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.83559584617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854798316956</t>
+    <t xml:space="preserve">2.79854774475098</t>
   </si>
   <si>
     <t xml:space="preserve">2.73442625999451</t>
@@ -428,43 +428,43 @@
     <t xml:space="preserve">2.77717399597168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88546800613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87406873703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272050857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834405899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94103980064392</t>
+    <t xml:space="preserve">2.88546824455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92109084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9410400390625</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85839486122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409401893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707191467285</t>
+    <t xml:space="preserve">2.85839462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409449577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707215309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.76007509231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80567216873169</t>
+    <t xml:space="preserve">2.80567240715027</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289915084839</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">2.7586498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77859902381897</t>
+    <t xml:space="preserve">2.77859854698181</t>
   </si>
   <si>
     <t xml:space="preserve">2.68597888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62470746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478402137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54776120185852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480930328369</t>
+    <t xml:space="preserve">2.62470698356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5477614402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480978012085</t>
   </si>
   <si>
     <t xml:space="preserve">2.65605545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65463089942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610696792603</t>
+    <t xml:space="preserve">2.65463042259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
   </si>
   <si>
     <t xml:space="preserve">2.60333347320557</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">2.5719850063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45086669921875</t>
+    <t xml:space="preserve">2.45086693763733</t>
   </si>
   <si>
     <t xml:space="preserve">2.44516706466675</t>
@@ -515,64 +515,64 @@
     <t xml:space="preserve">2.42379331588745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44374227523804</t>
+    <t xml:space="preserve">2.44374179840088</t>
   </si>
   <si>
     <t xml:space="preserve">2.41666841506958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45941615104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900734901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61045837402344</t>
+    <t xml:space="preserve">2.45941638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900782585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61045789718628</t>
   </si>
   <si>
     <t xml:space="preserve">2.54918646812439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57910966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55061101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52353811264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57340979576111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69310355186462</t>
+    <t xml:space="preserve">2.57910943031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55061149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6931037902832</t>
   </si>
   <si>
     <t xml:space="preserve">2.64038157463074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63895630836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898206710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63325691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67172956466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67315483093262</t>
+    <t xml:space="preserve">2.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898230552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63325667381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67172980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727631568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67315459251404</t>
   </si>
   <si>
     <t xml:space="preserve">2.70307779312134</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">2.71447730064392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70735287666321</t>
+    <t xml:space="preserve">2.70735263824463</t>
   </si>
   <si>
     <t xml:space="preserve">2.65178084373474</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">2.63753151893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6574809551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486058235168</t>
+    <t xml:space="preserve">2.65748071670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486082077026</t>
   </si>
   <si>
     <t xml:space="preserve">2.52211284637451</t>
@@ -605,37 +605,34 @@
     <t xml:space="preserve">2.51498818397522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41524386405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43234276771545</t>
+    <t xml:space="preserve">2.41524410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43234252929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.43661761283875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39386963844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39244484901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45799136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3511221408844</t>
+    <t xml:space="preserve">2.39386987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39244508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35112237930298</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236828804016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53066253662109</t>
+    <t xml:space="preserve">2.53066229820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.57768487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58908462524414</t>
+    <t xml:space="preserve">2.5890839099884</t>
   </si>
   <si>
     <t xml:space="preserve">2.63468170166016</t>
@@ -650,7 +647,7 @@
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737815856934</t>
+    <t xml:space="preserve">2.69737839698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.74012589454651</t>
@@ -659,28 +656,28 @@
     <t xml:space="preserve">2.74297595024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72445178031921</t>
+    <t xml:space="preserve">2.72445154190063</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72872638702393</t>
+    <t xml:space="preserve">2.7287266254425</t>
   </si>
   <si>
     <t xml:space="preserve">2.76434969902039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75152540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75580024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71162748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025373458862</t>
+    <t xml:space="preserve">2.75152516365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7558000087738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71162796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6902539730072</t>
   </si>
   <si>
     <t xml:space="preserve">2.65035581588745</t>
@@ -689,7 +686,7 @@
     <t xml:space="preserve">2.60760831832886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58338451385498</t>
+    <t xml:space="preserve">2.5833842754364</t>
   </si>
   <si>
     <t xml:space="preserve">2.55346131324768</t>
@@ -698,7 +695,7 @@
     <t xml:space="preserve">2.5206880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60618329048157</t>
+    <t xml:space="preserve">2.60618305206299</t>
   </si>
   <si>
     <t xml:space="preserve">2.56058573722839</t>
@@ -710,49 +707,49 @@
     <t xml:space="preserve">2.54063677787781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501370429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49788951873779</t>
+    <t xml:space="preserve">2.50501418113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49788880348206</t>
   </si>
   <si>
     <t xml:space="preserve">2.50643849372864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53351259231567</t>
+    <t xml:space="preserve">2.53351211547852</t>
   </si>
   <si>
     <t xml:space="preserve">2.57625985145569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60048389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58195924758911</t>
+    <t xml:space="preserve">2.60048341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193396568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58195972442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.55916094779968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58623433113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53636193275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48506474494934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54348683357239</t>
+    <t xml:space="preserve">2.58623456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5363621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4850652217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54348635673523</t>
   </si>
   <si>
     <t xml:space="preserve">2.68740391731262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69452834129333</t>
+    <t xml:space="preserve">2.69452857971191</t>
   </si>
   <si>
     <t xml:space="preserve">2.75722503662109</t>
@@ -764,7 +761,7 @@
     <t xml:space="preserve">2.79712295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78857350349426</t>
+    <t xml:space="preserve">2.78857326507568</t>
   </si>
   <si>
     <t xml:space="preserve">2.79997277259827</t>
@@ -779,22 +776,22 @@
     <t xml:space="preserve">3.03508496284485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06215810775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477848052979</t>
+    <t xml:space="preserve">3.06215834617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477824211121</t>
   </si>
   <si>
     <t xml:space="preserve">3.29727029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25737309455872</t>
+    <t xml:space="preserve">3.25737285614014</t>
   </si>
   <si>
     <t xml:space="preserve">3.07783269882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16760301589966</t>
+    <t xml:space="preserve">3.16760325431824</t>
   </si>
   <si>
     <t xml:space="preserve">3.16190314292908</t>
@@ -803,46 +800,46 @@
     <t xml:space="preserve">3.16047811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21890020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174954414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589726448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159618377686</t>
+    <t xml:space="preserve">3.21889996528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589702606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159666061401</t>
   </si>
   <si>
     <t xml:space="preserve">3.26877188682556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23172402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12913012504578</t>
+    <t xml:space="preserve">3.23172354698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1291298866272</t>
   </si>
   <si>
     <t xml:space="preserve">3.19610142707825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19752550125122</t>
+    <t xml:space="preserve">3.10063147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752597808838</t>
   </si>
   <si>
     <t xml:space="preserve">3.23884916305542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22602438926697</t>
+    <t xml:space="preserve">3.22602462768555</t>
   </si>
   <si>
     <t xml:space="preserve">3.29157114028931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32576966285706</t>
+    <t xml:space="preserve">3.32576942443848</t>
   </si>
   <si>
     <t xml:space="preserve">3.28302121162415</t>
@@ -851,40 +848,40 @@
     <t xml:space="preserve">3.31864476203918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3400182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35569214820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27019739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0892322063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06358361244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17488956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706664085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11147856712341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13886046409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462542533875</t>
+    <t xml:space="preserve">3.34001898765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559030532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3556923866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27019715309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08923196792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06358337402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17488980293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09706687927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11147809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13886070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">3.11003708839417</t>
@@ -893,22 +890,22 @@
     <t xml:space="preserve">3.1186842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07112598419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0379786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04806733131409</t>
+    <t xml:space="preserve">3.07112622261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03797936439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04806709289551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99762606620789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00627303123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97744965553284</t>
+    <t xml:space="preserve">3.00627326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97744989395142</t>
   </si>
   <si>
     <t xml:space="preserve">2.9183623790741</t>
@@ -917,49 +914,49 @@
     <t xml:space="preserve">2.8722448348999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90395045280457</t>
+    <t xml:space="preserve">2.90395069122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.89098000526428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87512731552124</t>
+    <t xml:space="preserve">2.87512707710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.84918618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92700910568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90683269500732</t>
+    <t xml:space="preserve">2.92700886726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9068329334259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86936259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87800931930542</t>
+    <t xml:space="preserve">2.878009557724</t>
   </si>
   <si>
     <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85350942611694</t>
+    <t xml:space="preserve">2.85350966453552</t>
   </si>
   <si>
     <t xml:space="preserve">2.87080359458923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8246865272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79298043251038</t>
+    <t xml:space="preserve">2.82468628883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79298067092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.76415729522705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81027483940125</t>
+    <t xml:space="preserve">2.81027460098267</t>
   </si>
   <si>
     <t xml:space="preserve">2.80018639564514</t>
@@ -968,7 +965,7 @@
     <t xml:space="preserve">2.79153966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72956919670105</t>
+    <t xml:space="preserve">2.72956943511963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75262808799744</t>
@@ -977,19 +974,19 @@
     <t xml:space="preserve">2.75983357429504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7468638420105</t>
+    <t xml:space="preserve">2.74686336517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.95439100265503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92124485969543</t>
+    <t xml:space="preserve">2.92124438285828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92845034599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92556810379028</t>
+    <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189225196838</t>
@@ -998,37 +995,37 @@
     <t xml:space="preserve">2.843421459198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80451011657715</t>
+    <t xml:space="preserve">2.80450987815857</t>
   </si>
   <si>
     <t xml:space="preserve">2.83045101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82612729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865694999695</t>
+    <t xml:space="preserve">2.82612752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865718841553</t>
   </si>
   <si>
     <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.808833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84053897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85495090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86503911018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87656879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90827417373657</t>
+    <t xml:space="preserve">2.80883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84053921699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85495066642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86503934860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87656855583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90827393531799</t>
   </si>
   <si>
     <t xml:space="preserve">2.83909821510315</t>
@@ -1037,13 +1034,13 @@
     <t xml:space="preserve">2.73821640014648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7555103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76848077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70218729972839</t>
+    <t xml:space="preserve">2.75551009178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76848101615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72668719291687</t>
@@ -1052,22 +1049,22 @@
     <t xml:space="preserve">2.71371650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72524571418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68056988716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65895199775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67624640464783</t>
+    <t xml:space="preserve">2.7252459526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68056964874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336392402649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65895247459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67624616622925</t>
   </si>
   <si>
     <t xml:space="preserve">2.75406932830811</t>
@@ -1076,76 +1073,76 @@
     <t xml:space="preserve">2.79442191123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79874563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74542188644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78577470779419</t>
+    <t xml:space="preserve">2.79874539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74542212486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78577494621277</t>
   </si>
   <si>
     <t xml:space="preserve">2.92268562316895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02500820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02644944190979</t>
+    <t xml:space="preserve">3.02500867843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02644968032837</t>
   </si>
   <si>
     <t xml:space="preserve">3.06968474388123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10571360588074</t>
+    <t xml:space="preserve">3.10571384429932</t>
   </si>
   <si>
     <t xml:space="preserve">3.12156653404236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17056632041931</t>
+    <t xml:space="preserve">3.17056655883789</t>
   </si>
   <si>
     <t xml:space="preserve">3.14174294471741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13597846031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09850788116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08409667015076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07400798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04086089134216</t>
+    <t xml:space="preserve">3.13597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09850811958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05671429634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07689023017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08409643173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07400822639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04086112976074</t>
   </si>
   <si>
     <t xml:space="preserve">3.05383157730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17921352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589001655579</t>
+    <t xml:space="preserve">3.17921328544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12588977813721</t>
   </si>
   <si>
     <t xml:space="preserve">3.05527281761169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07977318763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14894843101501</t>
+    <t xml:space="preserve">3.07977294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14894866943359</t>
   </si>
   <si>
     <t xml:space="preserve">3.16191911697388</t>
@@ -1154,10 +1151,10 @@
     <t xml:space="preserve">3.1475076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09994959831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453698158264</t>
+    <t xml:space="preserve">3.09994888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1345374584198</t>
   </si>
   <si>
     <t xml:space="preserve">3.15903663635254</t>
@@ -1169,19 +1166,19 @@
     <t xml:space="preserve">3.12877249717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11580181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10427284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815505981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483202934265</t>
+    <t xml:space="preserve">3.11580204963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10427260398865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815529823303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483226776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.9716854095459</t>
@@ -1193,7 +1190,7 @@
     <t xml:space="preserve">2.82180380821228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86792159080505</t>
+    <t xml:space="preserve">2.8679211139679</t>
   </si>
   <si>
     <t xml:space="preserve">2.89674472808838</t>
@@ -1214,25 +1211,25 @@
     <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72236347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71227526664734</t>
+    <t xml:space="preserve">2.72236371040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70506978034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71227550506592</t>
   </si>
   <si>
     <t xml:space="preserve">2.65606999397278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69858431816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76704001426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505420684814</t>
+    <t xml:space="preserve">2.69858455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76703953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505444526672</t>
   </si>
   <si>
     <t xml:space="preserve">2.72740745544434</t>
@@ -1241,13 +1238,13 @@
     <t xml:space="preserve">2.69498133659363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73461365699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70579051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73101043701172</t>
+    <t xml:space="preserve">2.7346134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70579028129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7310106754303</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020173072815</t>
@@ -1256,25 +1253,25 @@
     <t xml:space="preserve">2.79226016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84630370140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.774245262146</t>
+    <t xml:space="preserve">2.84630393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77424550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.77064251899719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.709392786026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74181938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71299576759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63373160362244</t>
+    <t xml:space="preserve">2.70939302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74181914329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71299600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63373184204102</t>
   </si>
   <si>
     <t xml:space="preserve">2.62652587890625</t>
@@ -1283,28 +1280,28 @@
     <t xml:space="preserve">2.64093780517578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65534901618958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64814352989197</t>
+    <t xml:space="preserve">2.65534925460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64814329147339</t>
   </si>
   <si>
     <t xml:space="preserve">2.58689379692078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5724823474884</t>
+    <t xml:space="preserve">2.57248187065125</t>
   </si>
   <si>
     <t xml:space="preserve">2.57968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55807042121887</t>
+    <t xml:space="preserve">2.55807065963745</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167364120483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55086445808411</t>
+    <t xml:space="preserve">2.55086469650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.56887936592102</t>
@@ -1319,28 +1316,28 @@
     <t xml:space="preserve">2.30946922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39593935012817</t>
+    <t xml:space="preserve">2.39593958854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.41755676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991024971008</t>
+    <t xml:space="preserve">2.41395354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36351323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3599100112915</t>
   </si>
   <si>
     <t xml:space="preserve">2.29505753517151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44998335838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3527045249939</t>
+    <t xml:space="preserve">2.4499831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
     <t xml:space="preserve">2.52204155921936</t>
@@ -1352,37 +1349,37 @@
     <t xml:space="preserve">2.44638013839722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42115950584412</t>
+    <t xml:space="preserve">2.4211597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.50762963294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59409952163696</t>
+    <t xml:space="preserve">2.59409999847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63012909889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65174627304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62292313575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60130524635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60851120948792</t>
+    <t xml:space="preserve">2.63012886047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65174651145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62292289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60130548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60851144790649</t>
   </si>
   <si>
     <t xml:space="preserve">2.6373348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68417239189148</t>
+    <t xml:space="preserve">2.68417263031006</t>
   </si>
   <si>
     <t xml:space="preserve">2.66615796089172</t>
@@ -1397,7 +1394,7 @@
     <t xml:space="preserve">2.73281216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172198295593</t>
+    <t xml:space="preserve">2.62172174453735</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1406,94 +1403,94 @@
     <t xml:space="preserve">2.48841404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40324473381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43657207489014</t>
+    <t xml:space="preserve">2.403244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43657231330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.45879006385803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39213585853577</t>
+    <t xml:space="preserve">2.39213609695435</t>
   </si>
   <si>
     <t xml:space="preserve">2.40694832801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36991810798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29956126213074</t>
+    <t xml:space="preserve">2.36991834640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29956150054932</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068930625916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32548213005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732434272766</t>
+    <t xml:space="preserve">2.32548236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732410430908</t>
   </si>
   <si>
     <t xml:space="preserve">2.38843321800232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4291660785675</t>
+    <t xml:space="preserve">2.42916631698608</t>
   </si>
   <si>
     <t xml:space="preserve">2.41805720329285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5032262802124</t>
+    <t xml:space="preserve">2.46989893913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50322651863098</t>
   </si>
   <si>
     <t xml:space="preserve">2.52174115180969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53285002708435</t>
+    <t xml:space="preserve">2.53284978866577</t>
   </si>
   <si>
     <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52544403076172</t>
+    <t xml:space="preserve">2.5254442691803</t>
   </si>
   <si>
     <t xml:space="preserve">2.45508718490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58098888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395890235901</t>
+    <t xml:space="preserve">2.58098912239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395914077759</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44768095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53655314445496</t>
+    <t xml:space="preserve">2.44768118858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53655290603638</t>
   </si>
   <si>
     <t xml:space="preserve">2.4773051738739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51433491706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48100805282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46619606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39583921432495</t>
+    <t xml:space="preserve">2.51433515548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48100781440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46619582176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39583897590637</t>
   </si>
   <si>
     <t xml:space="preserve">2.41065120697021</t>
@@ -1502,7 +1499,7 @@
     <t xml:space="preserve">2.35140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36621522903442</t>
+    <t xml:space="preserve">2.366215467453</t>
   </si>
   <si>
     <t xml:space="preserve">2.34399724006653</t>
@@ -1511,7 +1508,7 @@
     <t xml:space="preserve">2.35880899429321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35510635375977</t>
+    <t xml:space="preserve">2.35510611534119</t>
   </si>
   <si>
     <t xml:space="preserve">2.3625123500824</t>
@@ -1520,16 +1517,16 @@
     <t xml:space="preserve">2.30696725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31067037582397</t>
+    <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39954233169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102698326111</t>
+    <t xml:space="preserve">2.3995418548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102722167969</t>
   </si>
   <si>
     <t xml:space="preserve">2.41435408592224</t>
@@ -1538,28 +1535,28 @@
     <t xml:space="preserve">2.37362122535706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31807637214661</t>
+    <t xml:space="preserve">2.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">2.29585814476013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26993703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30326414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32918548583984</t>
+    <t xml:space="preserve">2.28104639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26993727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30326437950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32918500900269</t>
   </si>
   <si>
     <t xml:space="preserve">2.27734327316284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26623439788818</t>
+    <t xml:space="preserve">2.2662341594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.29215526580811</t>
@@ -1571,46 +1568,46 @@
     <t xml:space="preserve">2.2884521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28474926948547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38473010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20698642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24031329154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15514445304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292670249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1477382183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1033022403717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959959983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10700535774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06256937980652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98850929737091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147943496704</t>
+    <t xml:space="preserve">2.28474950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38473033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20698618888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24031352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15514421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14773869514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10330247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849024772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10700559616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0625696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98850953578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147955417633</t>
   </si>
   <si>
     <t xml:space="preserve">2.02553939819336</t>
@@ -1619,49 +1616,49 @@
     <t xml:space="preserve">2.06627249717712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922310829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14403557777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13662934303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847155570984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439218521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23290753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512552261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20328307151794</t>
+    <t xml:space="preserve">2.04775738716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997561454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14403533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13662958145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23290729522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512528419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20328330993652</t>
   </si>
   <si>
     <t xml:space="preserve">2.1995804309845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809506416321</t>
+    <t xml:space="preserve">2.21809554100037</t>
   </si>
   <si>
     <t xml:space="preserve">2.11811423301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07367825508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070823669434</t>
+    <t xml:space="preserve">2.07367849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070847511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.24771928787231</t>
@@ -1673,7 +1670,7 @@
     <t xml:space="preserve">2.51063227653503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65504884719849</t>
+    <t xml:space="preserve">2.65504908561707</t>
   </si>
   <si>
     <t xml:space="preserve">2.68096995353699</t>
@@ -1685,25 +1682,28 @@
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
+    <t xml:space="preserve">2.6661581993103</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.65875196456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65134596824646</t>
+    <t xml:space="preserve">2.65134620666504</t>
   </si>
   <si>
     <t xml:space="preserve">2.62542510032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71799993515015</t>
+    <t xml:space="preserve">2.71800017356873</t>
   </si>
   <si>
     <t xml:space="preserve">2.70318794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7291088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69207882881165</t>
+    <t xml:space="preserve">2.72910904884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69207906723022</t>
   </si>
   <si>
     <t xml:space="preserve">2.71429705619812</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">2.8031690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81798100471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84390163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87352609634399</t>
+    <t xml:space="preserve">2.81798076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84390187263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87352585792542</t>
   </si>
   <si>
     <t xml:space="preserve">2.86241674423218</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">2.76984190940857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7994658946991</t>
+    <t xml:space="preserve">2.79946613311768</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81427764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79576277732849</t>
+    <t xml:space="preserve">2.81427788734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79576301574707</t>
   </si>
   <si>
     <t xml:space="preserve">2.75873279571533</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">2.90314984321594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89574384689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90685296058655</t>
+    <t xml:space="preserve">2.89574408531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90685272216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.88833785057068</t>
@@ -1769,37 +1769,37 @@
     <t xml:space="preserve">2.962397813797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98091268539429</t>
+    <t xml:space="preserve">2.98091292381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.91796183586121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758582115173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95128893852234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93647646903992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95499157905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93277382850647</t>
+    <t xml:space="preserve">2.94758558273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95128870010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93647694587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95499181747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93277406692505</t>
   </si>
   <si>
     <t xml:space="preserve">2.91055583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96980404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720980644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94018006324768</t>
+    <t xml:space="preserve">2.96980381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97721004486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9401798248291</t>
   </si>
   <si>
     <t xml:space="preserve">2.89944672584534</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">2.81057500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8661196231842</t>
+    <t xml:space="preserve">2.86611986160278</t>
   </si>
   <si>
     <t xml:space="preserve">2.80687189102173</t>
@@ -1823,46 +1823,43 @@
     <t xml:space="preserve">2.71059393882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70689105987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6106128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6402370929718</t>
+    <t xml:space="preserve">2.70689082145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61061310768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64023685455322</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63283085823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69578218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467283248901</t>
+    <t xml:space="preserve">2.63283109664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61801886558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69578194618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.68837594985962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6143159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56988000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49211716651917</t>
+    <t xml:space="preserve">2.61431574821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56988024711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49211692810059</t>
   </si>
   <si>
     <t xml:space="preserve">2.50692915916443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34770011901855</t>
+    <t xml:space="preserve">2.34770035743713</t>
   </si>
   <si>
     <t xml:space="preserve">2.23661017417908</t>
@@ -1880,10 +1877,13 @@
     <t xml:space="preserve">2.2177734375</t>
   </si>
   <si>
+    <t xml:space="preserve">2.14773845672607</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.10882997512817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12439322471619</t>
+    <t xml:space="preserve">2.12439346313477</t>
   </si>
   <si>
     <t xml:space="preserve">2.0893759727478</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326672554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12050223350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13995671272278</t>
+    <t xml:space="preserve">2.09326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12050247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13995695114136</t>
   </si>
   <si>
     <t xml:space="preserve">2.12828421592712</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">2.07770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0504674911499</t>
+    <t xml:space="preserve">2.05046772956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.04657673835754</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">2.03490424156189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03101325035095</t>
+    <t xml:space="preserve">2.05435872077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03101348876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0582492351532</t>
+    <t xml:space="preserve">2.05824947357178</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.1866466999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96876001358032</t>
+    <t xml:space="preserve">1.9687602519989</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">1.94152414798737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84425354003906</t>
+    <t xml:space="preserve">1.84425365924835</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">1.8092360496521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75087368488312</t>
+    <t xml:space="preserve">1.75087380409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.74698269367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69251108169556</t>
+    <t xml:space="preserve">1.69251132011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.78978180885315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82090842723846</t>
+    <t xml:space="preserve">1.82090866565704</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7119654417038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7197470664978</t>
+    <t xml:space="preserve">1.71196556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71974718570709</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">1.78589117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141932487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585607528687</t>
+    <t xml:space="preserve">1.73141944408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71585619449615</t>
   </si>
   <si>
     <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78200018405914</t>
+    <t xml:space="preserve">1.78200042247772</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">1.80145454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8403627872467</t>
+    <t xml:space="preserve">1.84036302566528</t>
   </si>
   <si>
     <t xml:space="preserve">1.85592615604401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83647191524506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87927091121674</t>
+    <t xml:space="preserve">1.83647203445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87927114963531</t>
   </si>
   <si>
     <t xml:space="preserve">1.79756367206573</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">1.82869029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75476455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75865519046783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254618167877</t>
+    <t xml:space="preserve">1.75476479530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75865542888641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254630088806</t>
   </si>
   <si>
     <t xml:space="preserve">1.80534529685974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81701767444611</t>
+    <t xml:space="preserve">1.81701791286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.82479953765869</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">1.87538039684296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90650677680969</t>
+    <t xml:space="preserve">1.90650701522827</t>
   </si>
   <si>
     <t xml:space="preserve">1.89483428001404</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92207026481628</t>
+    <t xml:space="preserve">1.92207038402557</t>
   </si>
   <si>
     <t xml:space="preserve">2.01155948638916</t>
@@ -2096,19 +2096,19 @@
     <t xml:space="preserve">2.08159422874451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06213998794556</t>
+    <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
     <t xml:space="preserve">2.13217520713806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20999145507812</t>
+    <t xml:space="preserve">2.2099916934967</t>
   </si>
   <si>
     <t xml:space="preserve">2.19053745269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15552020072937</t>
+    <t xml:space="preserve">2.15551996231079</t>
   </si>
   <si>
     <t xml:space="preserve">2.19831919670105</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">2.17108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14384770393372</t>
+    <t xml:space="preserve">2.14384794235229</t>
   </si>
   <si>
     <t xml:space="preserve">2.11272072792053</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">2.01545023918152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821449279785</t>
+    <t xml:space="preserve">1.98821473121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.15941119194031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13606572151184</t>
+    <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
     <t xml:space="preserve">2.01934099197388</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">1.87148940563202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91039752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596101760864</t>
+    <t xml:space="preserve">1.91039776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596113681793</t>
   </si>
   <si>
     <t xml:space="preserve">1.89872527122498</t>
@@ -2156,31 +2156,31 @@
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988675117493</t>
+    <t xml:space="preserve">1.99988698959351</t>
   </si>
   <si>
     <t xml:space="preserve">1.95708787441254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96486937999725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210500717163</t>
+    <t xml:space="preserve">1.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210524559021</t>
   </si>
   <si>
     <t xml:space="preserve">1.72752869129181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68862044811249</t>
+    <t xml:space="preserve">1.68862056732178</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59524047374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.542325258255</t>
+    <t xml:space="preserve">1.59524035453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54232513904572</t>
   </si>
   <si>
     <t xml:space="preserve">1.48941004276276</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">1.16102385520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08009445667267</t>
+    <t xml:space="preserve">1.08009457588196</t>
   </si>
   <si>
     <t xml:space="preserve">1.05986225605011</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">1.08476364612579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10188329219818</t>
+    <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
     <t xml:space="preserve">1.22483336925507</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">1.28864300251007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28397405147552</t>
+    <t xml:space="preserve">1.28397417068481</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331195354462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39291727542877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36179065704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062905788422</t>
+    <t xml:space="preserve">1.39291739463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36179077625275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062893867493</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">1.29175567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28241765499115</t>
+    <t xml:space="preserve">1.28241777420044</t>
   </si>
   <si>
     <t xml:space="preserve">1.22950255870819</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">1.17503070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13300979137421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10343968868256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10499572753906</t>
+    <t xml:space="preserve">1.13300967216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10343956947327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10499584674835</t>
   </si>
   <si>
     <t xml:space="preserve">1.08631992340088</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">1.05674958229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06764388084412</t>
+    <t xml:space="preserve">1.06764400005341</t>
   </si>
   <si>
     <t xml:space="preserve">1.12211549282074</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15012943744659</t>
+    <t xml:space="preserve">1.14234793186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15012955665588</t>
   </si>
   <si>
     <t xml:space="preserve">1.13923513889313</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708684444427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27930510044098</t>
+    <t xml:space="preserve">1.28708672523499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27930498123169</t>
   </si>
   <si>
     <t xml:space="preserve">1.17969989776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16413652896881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23572766780853</t>
+    <t xml:space="preserve">1.16413640975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23572778701782</t>
   </si>
   <si>
     <t xml:space="preserve">1.20615744590759</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">1.20771384239197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18748164176941</t>
+    <t xml:space="preserve">1.18748152256012</t>
   </si>
   <si>
     <t xml:space="preserve">1.21082639694214</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">1.18592512607574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612246513367</t>
+    <t xml:space="preserve">1.13612258434296</t>
   </si>
   <si>
     <t xml:space="preserve">1.1579110622406</t>
@@ -2384,19 +2384,19 @@
     <t xml:space="preserve">1.17036187648773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546060562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16724908351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1734744310379</t>
+    <t xml:space="preserve">1.14546048641205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16724920272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17347455024719</t>
   </si>
   <si>
     <t xml:space="preserve">1.15168583393097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17191827297211</t>
+    <t xml:space="preserve">1.17191815376282</t>
   </si>
   <si>
     <t xml:space="preserve">1.1656928062439</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">1.12522804737091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">1.03962993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04118621349335</t>
+    <t xml:space="preserve">1.04118633270264</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996052503585815</t>
+    <t xml:space="preserve">0.996052622795105</t>
   </si>
   <si>
     <t xml:space="preserve">1.01628494262695</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.975820243358612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827215671539</t>
+    <t xml:space="preserve">0.989827334880829</t>
   </si>
   <si>
     <t xml:space="preserve">0.969595015048981</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">0.999165296554565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06453120708466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05830585956573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02406668663025</t>
+    <t xml:space="preserve">1.06453132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05830597877502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02406656742096</t>
   </si>
   <si>
     <t xml:space="preserve">0.988270878791809</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941580951213837</t>
+    <t xml:space="preserve">0.941581010818481</t>
   </si>
   <si>
     <t xml:space="preserve">0.93379932641983</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">0.904228985309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879327595233917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887109279632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888665676116943</t>
+    <t xml:space="preserve">0.879327714443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887109398841858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888665616512299</t>
   </si>
   <si>
     <t xml:space="preserve">0.891778409481049</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">0.835750341415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803067445755005</t>
+    <t xml:space="preserve">0.80306738615036</t>
   </si>
   <si>
     <t xml:space="preserve">0.787504076957703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829525113105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831081330776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840419471263885</t>
+    <t xml:space="preserve">0.829525053501129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831081390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840419411659241</t>
   </si>
   <si>
     <t xml:space="preserve">0.826412439346313</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">0.902672648429871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915123403072357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940024673938751</t>
+    <t xml:space="preserve">0.915123283863068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940024554729462</t>
   </si>
   <si>
     <t xml:space="preserve">0.977376699447632</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">0.963369607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983601987361908</t>
+    <t xml:space="preserve">0.983602106571198</t>
   </si>
   <si>
     <t xml:space="preserve">0.978932917118073</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961813271045685</t>
+    <t xml:space="preserve">0.961813151836395</t>
   </si>
   <si>
     <t xml:space="preserve">0.946249961853027</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">0.927573919296265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926017582416534</t>
+    <t xml:space="preserve">0.926017701625824</t>
   </si>
   <si>
     <t xml:space="preserve">0.935355663299561</t>
@@ -2648,31 +2648,31 @@
     <t xml:space="preserve">0.916679680347443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89955997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918235957622528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908898055553436</t>
+    <t xml:space="preserve">0.8995600938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918236017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908897936344147</t>
   </si>
   <si>
     <t xml:space="preserve">0.894890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910454213619232</t>
+    <t xml:space="preserve">0.910454332828522</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01784133911133</t>
+    <t xml:space="preserve">1.01784121990204</t>
   </si>
   <si>
     <t xml:space="preserve">1.05363690853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13767886161804</t>
+    <t xml:space="preserve">1.13767898082733</t>
   </si>
   <si>
     <t xml:space="preserve">1.15946745872498</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">1.15479850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31198811531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907278060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24662208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25284731388092</t>
+    <t xml:space="preserve">1.31198799610138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24662220478058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25284743309021</t>
   </si>
   <si>
     <t xml:space="preserve">1.2544037103653</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307987213135</t>
+    <t xml:space="preserve">1.27307975292206</t>
   </si>
   <si>
     <t xml:space="preserve">1.36023437976837</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069901943207</t>
+    <t xml:space="preserve">1.40069913864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112867832184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3991425037384</t>
+    <t xml:space="preserve">1.37112855911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39914262294769</t>
   </si>
   <si>
     <t xml:space="preserve">1.39447367191315</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022322177887</t>
+    <t xml:space="preserve">1.56022310256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.58745872974396</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">1.53765618801117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51431119441986</t>
+    <t xml:space="preserve">1.51431131362915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50341701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497329235077</t>
+    <t xml:space="preserve">1.50497317314148</t>
   </si>
   <si>
     <t xml:space="preserve">1.49096620082855</t>
@@ -11151,7 +11151,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11177,7 +11177,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11203,7 +11203,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G239" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11229,7 +11229,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11281,7 +11281,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11307,7 +11307,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G243" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11385,7 +11385,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11515,7 +11515,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G251" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11541,7 +11541,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11593,7 +11593,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11619,7 +11619,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11697,7 +11697,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11723,7 +11723,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11749,7 +11749,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11775,7 +11775,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11801,7 +11801,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G262" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11905,7 +11905,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11957,7 +11957,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11983,7 +11983,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12009,7 +12009,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G270" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12035,7 +12035,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12061,7 +12061,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G272" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12087,7 +12087,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12113,7 +12113,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12139,7 +12139,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12191,7 +12191,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12217,7 +12217,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12269,7 +12269,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12295,7 +12295,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G281" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12321,7 +12321,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G282" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12347,7 +12347,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12373,7 +12373,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12399,7 +12399,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12425,7 +12425,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12451,7 +12451,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12477,7 +12477,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12503,7 +12503,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12529,7 +12529,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12555,7 +12555,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12581,7 +12581,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12607,7 +12607,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12633,7 +12633,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12659,7 +12659,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12685,7 +12685,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12711,7 +12711,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12763,7 +12763,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12789,7 +12789,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12815,7 +12815,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12841,7 +12841,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12893,7 +12893,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12919,7 +12919,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12945,7 +12945,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G306" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12971,7 +12971,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12997,7 +12997,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13023,7 +13023,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13049,7 +13049,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13075,7 +13075,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13101,7 +13101,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13153,7 +13153,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13179,7 +13179,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13205,7 +13205,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13231,7 +13231,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13257,7 +13257,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13335,7 +13335,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13361,7 +13361,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13387,7 +13387,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13413,7 +13413,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13439,7 +13439,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13465,7 +13465,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13491,7 +13491,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13517,7 +13517,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G328" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13543,7 +13543,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13569,7 +13569,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13621,7 +13621,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G332" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13647,7 +13647,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13699,7 +13699,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G335" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13725,7 +13725,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13777,7 +13777,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13803,7 +13803,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G339" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13855,7 +13855,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13881,7 +13881,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13907,7 +13907,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13933,7 +13933,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13959,7 +13959,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13985,7 +13985,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14011,7 +14011,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G347" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14037,7 +14037,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14063,7 +14063,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14089,7 +14089,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14141,7 +14141,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14167,7 +14167,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14193,7 +14193,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14219,7 +14219,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G355" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14245,7 +14245,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14271,7 +14271,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G357" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14297,7 +14297,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14323,7 +14323,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G359" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14349,7 +14349,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14375,7 +14375,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14401,7 +14401,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G362" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14427,7 +14427,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14453,7 +14453,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14479,7 +14479,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14505,7 +14505,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14531,7 +14531,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14557,7 +14557,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14583,7 +14583,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14609,7 +14609,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14635,7 +14635,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G371" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14661,7 +14661,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G372" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14687,7 +14687,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G373" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14713,7 +14713,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G374" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14739,7 +14739,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14765,7 +14765,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G376" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14791,7 +14791,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G377" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14817,7 +14817,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14843,7 +14843,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14869,7 +14869,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G380" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14895,7 +14895,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G381" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14921,7 +14921,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14947,7 +14947,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14973,7 +14973,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14999,7 +14999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G385" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15025,7 +15025,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15051,7 +15051,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15077,7 +15077,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G388" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15103,7 +15103,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15129,7 +15129,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G390" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15155,7 +15155,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G391" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15181,7 +15181,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15207,7 +15207,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G393" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15233,7 +15233,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G394" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15259,7 +15259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15285,7 +15285,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G396" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15311,7 +15311,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G397" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15337,7 +15337,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G398" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15363,7 +15363,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G399" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15389,7 +15389,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15415,7 +15415,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G401" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15441,7 +15441,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15467,7 +15467,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G403" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15493,7 +15493,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15519,7 +15519,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15545,7 +15545,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15571,7 +15571,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G407" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15597,7 +15597,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G408" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15623,7 +15623,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G409" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15649,7 +15649,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G410" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15675,7 +15675,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15701,7 +15701,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15727,7 +15727,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15753,7 +15753,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15779,7 +15779,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15805,7 +15805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15831,7 +15831,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15857,7 +15857,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15883,7 +15883,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15909,7 +15909,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G420" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15935,7 +15935,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15961,7 +15961,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15987,7 +15987,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G423" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16013,7 +16013,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G424" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16039,7 +16039,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G425" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16065,7 +16065,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G426" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16091,7 +16091,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G427" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16117,7 +16117,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G428" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16143,7 +16143,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16169,7 +16169,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16195,7 +16195,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G431" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16221,7 +16221,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16247,7 +16247,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16273,7 +16273,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16299,7 +16299,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16325,7 +16325,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16351,7 +16351,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G437" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16377,7 +16377,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G438" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16403,7 +16403,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16429,7 +16429,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G440" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16455,7 +16455,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16481,7 +16481,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16507,7 +16507,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16533,7 +16533,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16559,7 +16559,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16585,7 +16585,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16611,7 +16611,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16637,7 +16637,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16663,7 +16663,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16689,7 +16689,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16715,7 +16715,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16741,7 +16741,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16767,7 +16767,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16793,7 +16793,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16819,7 +16819,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16845,7 +16845,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G456" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16871,7 +16871,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16897,7 +16897,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G458" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16923,7 +16923,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G459" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16949,7 +16949,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16975,7 +16975,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17001,7 +17001,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G462" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17027,7 +17027,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17053,7 +17053,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17079,7 +17079,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G465" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17105,7 +17105,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17131,7 +17131,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17157,7 +17157,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17183,7 +17183,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17209,7 +17209,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17235,7 +17235,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17261,7 +17261,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17287,7 +17287,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17313,7 +17313,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G474" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17339,7 +17339,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17365,7 +17365,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17391,7 +17391,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17417,7 +17417,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17443,7 +17443,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17469,7 +17469,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17495,7 +17495,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17521,7 +17521,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G482" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17547,7 +17547,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17573,7 +17573,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17599,7 +17599,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G485" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17625,7 +17625,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17651,7 +17651,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G487" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17677,7 +17677,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17703,7 +17703,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17729,7 +17729,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G490" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17755,7 +17755,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17781,7 +17781,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17807,7 +17807,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17833,7 +17833,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G494" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17859,7 +17859,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G495" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17885,7 +17885,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G496" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17911,7 +17911,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G497" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17937,7 +17937,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17963,7 +17963,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17989,7 +17989,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18015,7 +18015,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18041,7 +18041,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18067,7 +18067,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18093,7 +18093,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18119,7 +18119,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18145,7 +18145,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18171,7 +18171,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18197,7 +18197,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18223,7 +18223,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18249,7 +18249,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18275,7 +18275,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G511" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18301,7 +18301,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G512" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18327,7 +18327,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18353,7 +18353,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18379,7 +18379,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18405,7 +18405,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18431,7 +18431,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18457,7 +18457,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18483,7 +18483,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18509,7 +18509,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18535,7 +18535,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18561,7 +18561,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18587,7 +18587,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18613,7 +18613,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18639,7 +18639,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18665,7 +18665,7 @@
         <v>3.875</v>
       </c>
       <c r="G526" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18691,7 +18691,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18717,7 +18717,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G528" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18743,7 +18743,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G529" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18769,7 +18769,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G530" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18795,7 +18795,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G531" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18821,7 +18821,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18847,7 +18847,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18873,7 +18873,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G534" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18899,7 +18899,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18925,7 +18925,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18951,7 +18951,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18977,7 +18977,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19003,7 +19003,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G539" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19029,7 +19029,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19055,7 +19055,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G541" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19081,7 +19081,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19107,7 +19107,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19133,7 +19133,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19159,7 +19159,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19185,7 +19185,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G546" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19211,7 +19211,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19237,7 +19237,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G548" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19263,7 +19263,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19289,7 +19289,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G550" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19315,7 +19315,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G551" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19341,7 +19341,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19367,7 +19367,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G553" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19393,7 +19393,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19419,7 +19419,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G555" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19445,7 +19445,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G556" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19471,7 +19471,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G557" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19497,7 +19497,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G558" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19523,7 +19523,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G559" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19549,7 +19549,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19575,7 +19575,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19601,7 +19601,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19627,7 +19627,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19653,7 +19653,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G564" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19679,7 +19679,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19705,7 +19705,7 @@
         <v>3.5</v>
       </c>
       <c r="G566" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19731,7 +19731,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19757,7 +19757,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19783,7 +19783,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19809,7 +19809,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19835,7 +19835,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19861,7 +19861,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19887,7 +19887,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19913,7 +19913,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19939,7 +19939,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19965,7 +19965,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G576" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19991,7 +19991,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20017,7 +20017,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20043,7 +20043,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G579" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20069,7 +20069,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20095,7 +20095,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20121,7 +20121,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20147,7 +20147,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20173,7 +20173,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20199,7 +20199,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20225,7 +20225,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20251,7 +20251,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20277,7 +20277,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20303,7 +20303,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G589" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20329,7 +20329,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20355,7 +20355,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20381,7 +20381,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20407,7 +20407,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G593" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20433,7 +20433,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20459,7 +20459,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20485,7 +20485,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20511,7 +20511,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20537,7 +20537,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20563,7 +20563,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20589,7 +20589,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20615,7 +20615,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20641,7 +20641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20667,7 +20667,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G603" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20693,7 +20693,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20719,7 +20719,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20745,7 +20745,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20771,7 +20771,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20797,7 +20797,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20823,7 +20823,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20849,7 +20849,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20875,7 +20875,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20901,7 +20901,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20927,7 +20927,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20953,7 +20953,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20979,7 +20979,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G615" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21005,7 +21005,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21031,7 +21031,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21057,7 +21057,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G618" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21083,7 +21083,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21109,7 +21109,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21135,7 +21135,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21161,7 +21161,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G622" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21187,7 +21187,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21213,7 +21213,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21239,7 +21239,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G625" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21265,7 +21265,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21291,7 +21291,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G627" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21317,7 +21317,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21343,7 +21343,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21369,7 +21369,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G630" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21395,7 +21395,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21421,7 +21421,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21447,7 +21447,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21473,7 +21473,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21499,7 +21499,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G635" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21525,7 +21525,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21551,7 +21551,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G637" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21577,7 +21577,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21603,7 +21603,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G639" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21629,7 +21629,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21655,7 +21655,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21681,7 +21681,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21707,7 +21707,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21733,7 +21733,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21759,7 +21759,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G645" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21785,7 +21785,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21811,7 +21811,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G647" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21837,7 +21837,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21863,7 +21863,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G649" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21889,7 +21889,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21915,7 +21915,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21941,7 +21941,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21967,7 +21967,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21993,7 +21993,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G654" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22019,7 +22019,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22045,7 +22045,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G656" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22071,7 +22071,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22097,7 +22097,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G658" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22123,7 +22123,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22149,7 +22149,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22175,7 +22175,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22201,7 +22201,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22227,7 +22227,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22253,7 +22253,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G664" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22279,7 +22279,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G665" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22305,7 +22305,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22331,7 +22331,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22357,7 +22357,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22383,7 +22383,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G669" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22409,7 +22409,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G670" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22435,7 +22435,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22461,7 +22461,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G672" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22487,7 +22487,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22513,7 +22513,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22539,7 +22539,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22565,7 +22565,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G676" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22591,7 +22591,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G677" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22617,7 +22617,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22643,7 +22643,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22669,7 +22669,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22695,7 +22695,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22721,7 +22721,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G682" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22747,7 +22747,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22773,7 +22773,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22799,7 +22799,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G685" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22825,7 +22825,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22851,7 +22851,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22877,7 +22877,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22903,7 +22903,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G689" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22929,7 +22929,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22955,7 +22955,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22981,7 +22981,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23007,7 +23007,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G693" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23033,7 +23033,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23059,7 +23059,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23085,7 +23085,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23111,7 +23111,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23137,7 +23137,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23163,7 +23163,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G699" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23189,7 +23189,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G700" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23215,7 +23215,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23241,7 +23241,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23267,7 +23267,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23293,7 +23293,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23319,7 +23319,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G705" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23345,7 +23345,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23371,7 +23371,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G707" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23397,7 +23397,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23423,7 +23423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23449,7 +23449,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23475,7 +23475,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23501,7 +23501,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G712" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23527,7 +23527,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23553,7 +23553,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23579,7 +23579,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G715" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23605,7 +23605,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23631,7 +23631,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23657,7 +23657,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23683,7 +23683,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23709,7 +23709,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23735,7 +23735,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23761,7 +23761,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23787,7 +23787,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23813,7 +23813,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23839,7 +23839,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23865,7 +23865,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23891,7 +23891,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23917,7 +23917,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23943,7 +23943,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23969,7 +23969,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23995,7 +23995,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24021,7 +24021,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G732" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24047,7 +24047,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G733" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24073,7 +24073,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24099,7 +24099,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G735" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24125,7 +24125,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24151,7 +24151,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G737" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24177,7 +24177,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24203,7 +24203,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24229,7 +24229,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24255,7 +24255,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24281,7 +24281,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G742" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24307,7 +24307,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G743" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24333,7 +24333,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G744" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24359,7 +24359,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G745" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24385,7 +24385,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24411,7 +24411,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24437,7 +24437,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24463,7 +24463,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24489,7 +24489,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24515,7 +24515,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24541,7 +24541,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G752" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24567,7 +24567,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G753" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24593,7 +24593,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24619,7 +24619,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G755" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24645,7 +24645,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24671,7 +24671,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G757" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24697,7 +24697,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24723,7 +24723,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24749,7 +24749,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24775,7 +24775,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24801,7 +24801,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24827,7 +24827,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G763" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24853,7 +24853,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24879,7 +24879,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24905,7 +24905,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G766" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24931,7 +24931,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G767" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24957,7 +24957,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G768" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24983,7 +24983,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="s">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -26699,7 +26699,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26777,7 +26777,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26881,7 +26881,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G842" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27011,7 +27011,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="s">
-        <v>610</v>
+        <v>43</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27037,7 +27037,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27063,7 +27063,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27089,7 +27089,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G850" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27115,7 +27115,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G851" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27141,7 +27141,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27167,7 +27167,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27193,7 +27193,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27219,7 +27219,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G855" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27245,7 +27245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27271,7 +27271,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27297,7 +27297,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G858" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27323,7 +27323,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27349,7 +27349,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27375,7 +27375,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G861" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27401,7 +27401,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27427,7 +27427,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G863" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27453,7 +27453,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G864" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27479,7 +27479,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="s">
-        <v>525</v>
+        <v>621</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27739,7 +27739,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="s">
-        <v>525</v>
+        <v>621</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28389,7 +28389,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="s">
-        <v>525</v>
+        <v>621</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -31093,7 +31093,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1004" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31353,7 +31353,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="s">
-        <v>525</v>
+        <v>621</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -70049,7 +70049,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911689815</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>109729</v>
@@ -70070,6 +70070,32 @@
         <v>1548</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6911111111</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>108672</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>2.86500000953674</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>2.82500004768372</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>2.86500000953674</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385492324829</t>
+    <t xml:space="preserve">3.07385468482971</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614444732666</t>
+    <t xml:space="preserve">3.08614468574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.01786708831787</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.98099732398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88131189346313</t>
+    <t xml:space="preserve">2.88131165504456</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003081321716</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">2.86082887649536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75841236114502</t>
+    <t xml:space="preserve">2.7584125995636</t>
   </si>
   <si>
     <t xml:space="preserve">2.73929476737976</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71744585037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86629128456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76387429237366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74475693702698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75704717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.710618019104</t>
+    <t xml:space="preserve">2.71744608879089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86629056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76387476921082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7447566986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7570469379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71061825752258</t>
   </si>
   <si>
     <t xml:space="preserve">2.73110151290894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76114344596863</t>
+    <t xml:space="preserve">2.76114368438721</t>
   </si>
   <si>
     <t xml:space="preserve">2.7256395816803</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">2.69696259498596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62868523597717</t>
+    <t xml:space="preserve">2.72290825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62868475914001</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935654640198</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30095291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38971352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992414474487</t>
+    <t xml:space="preserve">2.30095267295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992438316345</t>
   </si>
   <si>
     <t xml:space="preserve">2.50441980361938</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.68467259407043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8621940612793</t>
+    <t xml:space="preserve">2.86219382286072</t>
   </si>
   <si>
     <t xml:space="preserve">2.8335177898407</t>
@@ -155,16 +155,16 @@
     <t xml:space="preserve">2.84717345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88404297828674</t>
+    <t xml:space="preserve">2.88404321670532</t>
   </si>
   <si>
     <t xml:space="preserve">2.88540863990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89769911766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85126996040344</t>
+    <t xml:space="preserve">2.89769840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85126972198486</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685816764832</t>
@@ -173,64 +173,64 @@
     <t xml:space="preserve">2.9495894908905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05883383750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164878845215</t>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
   </si>
   <si>
     <t xml:space="preserve">3.16125011444092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18173313140869</t>
+    <t xml:space="preserve">3.18173289299011</t>
   </si>
   <si>
     <t xml:space="preserve">3.20767879486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900228500366</t>
+    <t xml:space="preserve">3.17900204658508</t>
   </si>
   <si>
     <t xml:space="preserve">3.17217421531677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23635530471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269988059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2308931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952771186829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895963668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463266372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2773220539093</t>
+    <t xml:space="preserve">3.23635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269940376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089289665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952723503113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076662063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14896011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225430727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587157249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732133865356</t>
   </si>
   <si>
     <t xml:space="preserve">3.34559965133667</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">3.36608242988586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40704870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3865659236908</t>
+    <t xml:space="preserve">3.40704894065857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38656568527222</t>
   </si>
   <si>
     <t xml:space="preserve">3.33330893516541</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">3.34833025932312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32511568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3237509727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780554771423</t>
+    <t xml:space="preserve">3.32511639595032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2978048324585</t>
   </si>
   <si>
     <t xml:space="preserve">3.26366662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29097676277161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2602231502533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182682037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15620279312134</t>
+    <t xml:space="preserve">3.29097747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022267341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182658195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15620350837708</t>
   </si>
   <si>
     <t xml:space="preserve">3.13482975959778</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">3.1733021736145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09208226203918</t>
+    <t xml:space="preserve">3.09208202362061</t>
   </si>
   <si>
     <t xml:space="preserve">3.14907884597778</t>
@@ -290,40 +290,40 @@
     <t xml:space="preserve">3.32291913032532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34856796264648</t>
+    <t xml:space="preserve">3.34856748580933</t>
   </si>
   <si>
     <t xml:space="preserve">3.33431839942932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31151986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419103622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403767585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981434822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406295776367</t>
+    <t xml:space="preserve">3.31152009963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419079780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403791427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981387138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406367301941</t>
   </si>
   <si>
     <t xml:space="preserve">3.48108601570129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47681093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4383385181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116257667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841507911682</t>
+    <t xml:space="preserve">3.47681140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833804130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841460227966</t>
   </si>
   <si>
     <t xml:space="preserve">3.39843988418579</t>
@@ -338,82 +338,82 @@
     <t xml:space="preserve">3.02796030044556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246482849121</t>
+    <t xml:space="preserve">2.94246530532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.8997175693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89686751365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495688438416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197946548462</t>
+    <t xml:space="preserve">2.89686727523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495736122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
   </si>
   <si>
     <t xml:space="preserve">3.14195394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02938485145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671439170837</t>
+    <t xml:space="preserve">3.02938532829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671415328979</t>
   </si>
   <si>
     <t xml:space="preserve">3.06500840187073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16332793235779</t>
+    <t xml:space="preserve">3.16332817077637</t>
   </si>
   <si>
     <t xml:space="preserve">2.96526408195496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9552891254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9923369884491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058019638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599910736084</t>
+    <t xml:space="preserve">2.95528888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058043479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17045211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17757725715637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13625431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702063560486</t>
+    <t xml:space="preserve">3.13625454902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702087402344</t>
   </si>
   <si>
     <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86551928520203</t>
+    <t xml:space="preserve">2.86551904678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.90399241447449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84129524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549328804016</t>
+    <t xml:space="preserve">2.84129548072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549352645874</t>
   </si>
   <si>
     <t xml:space="preserve">2.83559584617615</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">2.73442625999451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77717423439026</t>
+    <t xml:space="preserve">2.7771737575531</t>
   </si>
   <si>
     <t xml:space="preserve">2.88546824455261</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">2.87406873703003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84272050857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834358215332</t>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8783438205719</t>
   </si>
   <si>
     <t xml:space="preserve">2.92821574211121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94103956222534</t>
+    <t xml:space="preserve">2.92109084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94103980064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85839462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409401893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707167625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007533073425</t>
+    <t xml:space="preserve">2.85839486122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707191467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007485389709</t>
   </si>
   <si>
     <t xml:space="preserve">2.80567240715027</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">2.77289915084839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7586498260498</t>
+    <t xml:space="preserve">2.75865006446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.77859902381897</t>
@@ -482,49 +482,49 @@
     <t xml:space="preserve">2.62470722198486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59478378295898</t>
+    <t xml:space="preserve">2.59478402137756</t>
   </si>
   <si>
     <t xml:space="preserve">2.5477614402771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58480954170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5719850063324</t>
+    <t xml:space="preserve">2.58480930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605568885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463089942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333323478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57198524475098</t>
   </si>
   <si>
     <t xml:space="preserve">2.45086669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44516682624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42379331588745</t>
+    <t xml:space="preserve">2.44516706466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42379307746887</t>
   </si>
   <si>
     <t xml:space="preserve">2.44374203681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.416668176651</t>
+    <t xml:space="preserve">2.41666889190674</t>
   </si>
   <si>
     <t xml:space="preserve">2.45941615104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61900758743286</t>
+    <t xml:space="preserve">2.61900734901428</t>
   </si>
   <si>
     <t xml:space="preserve">2.61045813560486</t>
@@ -533,19 +533,19 @@
     <t xml:space="preserve">2.54918646812439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57910966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55061101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52353763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465594291687</t>
+    <t xml:space="preserve">2.57910990715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55061149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57340979576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465618133545</t>
   </si>
   <si>
     <t xml:space="preserve">2.69310355186462</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">2.64038157463074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898206710815</t>
+    <t xml:space="preserve">2.63895606994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898182868958</t>
   </si>
   <si>
     <t xml:space="preserve">2.63325691223145</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">2.67172980308533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74867558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727631568909</t>
+    <t xml:space="preserve">2.74867534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727607727051</t>
   </si>
   <si>
     <t xml:space="preserve">2.67315483093262</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">2.65748047828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56486082077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5149884223938</t>
+    <t xml:space="preserve">2.56486034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211260795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498794555664</t>
   </si>
   <si>
     <t xml:space="preserve">2.41524386405945</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">2.43234276771545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43661737442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39386963844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39244508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35112237930298</t>
+    <t xml:space="preserve">2.43661761283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39387011528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39244484901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511221408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236852645874</t>
@@ -632,46 +632,46 @@
     <t xml:space="preserve">2.5776846408844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58908414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69595336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68027901649475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69167852401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69737839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012613296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297595024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72445154190063</t>
+    <t xml:space="preserve">2.58908438682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63468194007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6959536075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68027925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69167876243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69737815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012589454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72445201873779</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7287266254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434969902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152564048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75580024719238</t>
+    <t xml:space="preserve">2.72872638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7558000087738</t>
   </si>
   <si>
     <t xml:space="preserve">2.71162748336792</t>
@@ -680,34 +680,34 @@
     <t xml:space="preserve">2.69025373458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035557746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760807991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58338451385498</t>
+    <t xml:space="preserve">2.65035581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760831832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5833842754364</t>
   </si>
   <si>
     <t xml:space="preserve">2.55346131324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5206880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60618329048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5449116230011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54063677787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50501394271851</t>
+    <t xml:space="preserve">2.52068829536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60618352890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058621406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54491138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54063701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50501346588135</t>
   </si>
   <si>
     <t xml:space="preserve">2.49788928031921</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">2.50643873214722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53351187705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193396568298</t>
+    <t xml:space="preserve">2.53351211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57625985145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193420410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.58195948600769</t>
@@ -734,31 +734,31 @@
     <t xml:space="preserve">2.55916094779968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58623433113098</t>
+    <t xml:space="preserve">2.58623480796814</t>
   </si>
   <si>
     <t xml:space="preserve">2.53636193275452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48506474494934</t>
+    <t xml:space="preserve">2.48506450653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.54348659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6874041557312</t>
+    <t xml:space="preserve">2.68740367889404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69452857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75722479820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79712271690369</t>
+    <t xml:space="preserve">2.75722503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77147459983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79712295532227</t>
   </si>
   <si>
     <t xml:space="preserve">2.78857326507568</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">2.79997277259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83132100105286</t>
+    <t xml:space="preserve">2.83132076263428</t>
   </si>
   <si>
     <t xml:space="preserve">2.90541696548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03508520126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215858459473</t>
+    <t xml:space="preserve">3.03508496284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215834617615</t>
   </si>
   <si>
     <t xml:space="preserve">3.15477848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29727005958557</t>
+    <t xml:space="preserve">3.29727029800415</t>
   </si>
   <si>
     <t xml:space="preserve">3.25737285614014</t>
@@ -794,64 +794,64 @@
     <t xml:space="preserve">3.16760301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16190314292908</t>
+    <t xml:space="preserve">3.1619029045105</t>
   </si>
   <si>
     <t xml:space="preserve">3.16047811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21889972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174954414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589702606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877188682556</t>
+    <t xml:space="preserve">3.21890020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22175002098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589678764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">3.23172402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12913012504578</t>
+    <t xml:space="preserve">3.12913036346436</t>
   </si>
   <si>
     <t xml:space="preserve">3.19610118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10063123703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1975257396698</t>
+    <t xml:space="preserve">3.10063147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752597808838</t>
   </si>
   <si>
     <t xml:space="preserve">3.23884892463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22602462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157114028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3257691860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864428520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34001874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559030532837</t>
+    <t xml:space="preserve">3.22602438926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157137870789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32576966285706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302121162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34001851081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559006690979</t>
   </si>
   <si>
     <t xml:space="preserve">3.3556923866272</t>
@@ -860,37 +860,37 @@
     <t xml:space="preserve">3.23457407951355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27019715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08923196792603</t>
+    <t xml:space="preserve">3.27019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0892322063446</t>
   </si>
   <si>
     <t xml:space="preserve">3.06358361244202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17489004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11147832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13886046409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462494850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1186842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07112598419189</t>
+    <t xml:space="preserve">3.17488980293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09706664085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11147856712341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13886070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462542533875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11868405342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07112574577332</t>
   </si>
   <si>
     <t xml:space="preserve">3.03797888755798</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">3.04806733131409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99762582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00627303123474</t>
+    <t xml:space="preserve">2.99762630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.97744989395142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91836214065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87224507331848</t>
+    <t xml:space="preserve">2.9183623790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8722448348999</t>
   </si>
   <si>
     <t xml:space="preserve">2.90395069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89098000526428</t>
+    <t xml:space="preserve">2.89098024368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.87512731552124</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">2.92700886726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90683269500732</t>
+    <t xml:space="preserve">2.9068329334259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86936259269714</t>
@@ -947,37 +947,37 @@
     <t xml:space="preserve">2.87080383300781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82468628883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79298043251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76415705680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81027460098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80018663406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79153990745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72956967353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75262784957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75983381271362</t>
+    <t xml:space="preserve">2.8246865272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79298067092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76415729522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81027483940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80018639564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79153943061829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72956943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75262808799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75983357429504</t>
   </si>
   <si>
     <t xml:space="preserve">2.74686360359192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95439147949219</t>
+    <t xml:space="preserve">2.95439124107361</t>
   </si>
   <si>
     <t xml:space="preserve">2.92124462127686</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">2.92845058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92556810379028</t>
+    <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189225196838</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.843421459198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80450987815857</t>
+    <t xml:space="preserve">2.80451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">2.83045101165771</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80739235877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80883359909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84053945541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85495066642761</t>
+    <t xml:space="preserve">2.78865718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80739212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.808833360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84053897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85495090484619</t>
   </si>
   <si>
     <t xml:space="preserve">2.86503911018372</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">2.87656855583191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90827369689941</t>
+    <t xml:space="preserve">2.90827393531799</t>
   </si>
   <si>
     <t xml:space="preserve">2.83909821510315</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">2.73821640014648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75551009178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76848077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70218753814697</t>
+    <t xml:space="preserve">2.7555103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76848101615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72668719291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71371650695801</t>
+    <t xml:space="preserve">2.71371626853943</t>
   </si>
   <si>
     <t xml:space="preserve">2.7252459526062</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">2.68056964874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6748046875</t>
+    <t xml:space="preserve">2.67480492591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.67336392402649</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">2.67624616622925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75406932830811</t>
+    <t xml:space="preserve">2.75406908988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">2.74542188644409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78577494621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92268562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02500867843628</t>
+    <t xml:space="preserve">2.78577470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92268586158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02500820159912</t>
   </si>
   <si>
     <t xml:space="preserve">3.02644944190979</t>
@@ -1097,49 +1097,49 @@
     <t xml:space="preserve">3.10571384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12156653404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17056655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14174318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597822189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09850835800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07689023017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07400822639465</t>
+    <t xml:space="preserve">3.1215660572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17056632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14174294471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09850811958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05671429634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07689046859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08409667015076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07400798797607</t>
   </si>
   <si>
     <t xml:space="preserve">3.04086089134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05383157730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17921352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589001655579</t>
+    <t xml:space="preserve">3.0538318157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17921376228333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589025497437</t>
   </si>
   <si>
     <t xml:space="preserve">3.05527281761169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07977271080017</t>
+    <t xml:space="preserve">3.07977318763733</t>
   </si>
   <si>
     <t xml:space="preserve">3.14894866943359</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">3.16191935539246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14750790596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09994912147522</t>
+    <t xml:space="preserve">3.1475076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0999493598938</t>
   </si>
   <si>
     <t xml:space="preserve">3.13453698158264</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">3.15903687477112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15471339225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12877249717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11580181121826</t>
+    <t xml:space="preserve">3.15471315383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12877225875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11580228805542</t>
   </si>
   <si>
     <t xml:space="preserve">3.10427284240723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12012529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483250617981</t>
+    <t xml:space="preserve">3.12012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815505981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483226776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.9716854095459</t>
@@ -1196,100 +1196,100 @@
     <t xml:space="preserve">2.89674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88233280181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85062766075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82900977134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82324528694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70362854003906</t>
+    <t xml:space="preserve">2.88233304023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85062742233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82901000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82324504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
     <t xml:space="preserve">2.72236371040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70506954193115</t>
+    <t xml:space="preserve">2.70506978034973</t>
   </si>
   <si>
     <t xml:space="preserve">2.71227550506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65606999397278</t>
+    <t xml:space="preserve">2.65607023239136</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858407974243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76703977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740769386292</t>
+    <t xml:space="preserve">2.76703953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505444526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740745544434</t>
   </si>
   <si>
     <t xml:space="preserve">2.69498133659363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73461389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70579028129578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73101043701172</t>
+    <t xml:space="preserve">2.73461365699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7057900428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73101019859314</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020196914673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79225993156433</t>
+    <t xml:space="preserve">2.79226040840149</t>
   </si>
   <si>
     <t xml:space="preserve">2.84630370140076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77424573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77064251899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70939326286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74181962013245</t>
+    <t xml:space="preserve">2.774245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77064275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70939302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74181914329529</t>
   </si>
   <si>
     <t xml:space="preserve">2.71299576759338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63373160362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65534949302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64814329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58689379692078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248210906982</t>
+    <t xml:space="preserve">2.63373184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6409375667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65534901618958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64814352989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689403533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5724823474884</t>
   </si>
   <si>
     <t xml:space="preserve">2.57968807220459</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">2.55807042121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56167364120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086469650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56887912750244</t>
+    <t xml:space="preserve">2.56167340278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086445808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56887936592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.43557167053223</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">2.39593958854675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41755700111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36351323127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991024971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505753517151</t>
+    <t xml:space="preserve">2.41755676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41395401954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36351299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505729675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.44998335838318</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52204132080078</t>
+    <t xml:space="preserve">2.5220410823822</t>
   </si>
   <si>
     <t xml:space="preserve">2.42836546897888</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">2.56527614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63012886047363</t>
+    <t xml:space="preserve">2.63012909889221</t>
   </si>
   <si>
     <t xml:space="preserve">2.65174627304077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62292337417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60130524635315</t>
+    <t xml:space="preserve">2.62292313575745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
     <t xml:space="preserve">2.60851144790649</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">2.66615796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69137811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67696690559387</t>
+    <t xml:space="preserve">2.69137835502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67696666717529</t>
   </si>
   <si>
     <t xml:space="preserve">2.73281216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172174453735</t>
+    <t xml:space="preserve">2.62172198295593</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.29956126213074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21068954467773</t>
+    <t xml:space="preserve">2.21068906784058</t>
   </si>
   <si>
     <t xml:space="preserve">2.32548236846924</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">2.37732434272766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38843321800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42916631698608</t>
+    <t xml:space="preserve">2.38843297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4291660785675</t>
   </si>
   <si>
     <t xml:space="preserve">2.41805720329285</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">2.46989917755127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5032262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52174091339111</t>
+    <t xml:space="preserve">2.50322604179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52174115180969</t>
   </si>
   <si>
     <t xml:space="preserve">2.53285002708435</t>
@@ -1466,28 +1466,28 @@
     <t xml:space="preserve">2.58098912239075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395914077759</t>
+    <t xml:space="preserve">2.54395890235901</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44768118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53655314445496</t>
+    <t xml:space="preserve">2.44768095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53655290603638</t>
   </si>
   <si>
     <t xml:space="preserve">2.4773051738739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51433515548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48100805282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46619582176208</t>
+    <t xml:space="preserve">2.51433491706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48100781440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46619606018066</t>
   </si>
   <si>
     <t xml:space="preserve">2.39583921432495</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">2.35140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36621499061584</t>
+    <t xml:space="preserve">2.36621475219727</t>
   </si>
   <si>
     <t xml:space="preserve">2.34399747848511</t>
@@ -1508,25 +1508,25 @@
     <t xml:space="preserve">2.35880899429321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35510635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36251258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31067037582397</t>
+    <t xml:space="preserve">2.35510611534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36251211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30696702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3995418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102698326111</t>
+    <t xml:space="preserve">2.39954209327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102722167969</t>
   </si>
   <si>
     <t xml:space="preserve">2.41435408592224</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.31807637214661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29585838317871</t>
+    <t xml:space="preserve">2.29585814476013</t>
   </si>
   <si>
     <t xml:space="preserve">2.28104615211487</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">2.26993727684021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30326414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32918548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27734351158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2662341594696</t>
+    <t xml:space="preserve">2.30326390266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32918524742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27734303474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26623439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.29215526580811</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">2.28474926948547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38473033905029</t>
+    <t xml:space="preserve">2.38473010063171</t>
   </si>
   <si>
     <t xml:space="preserve">2.20698618888855</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">2.24031329154968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15514445304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292646408081</t>
+    <t xml:space="preserve">2.15514421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292622566223</t>
   </si>
   <si>
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10330247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959959983826</t>
+    <t xml:space="preserve">2.1033022403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959936141968</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849048614502</t>
@@ -1604,43 +1604,43 @@
     <t xml:space="preserve">2.06256937980652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98850953578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147967338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553939819336</t>
+    <t xml:space="preserve">1.98850929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147943496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553963661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.06627225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997561454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922334671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14403557777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13662958145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847131729126</t>
+    <t xml:space="preserve">2.04775738716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922310829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14403533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13662934303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847107887268</t>
   </si>
   <si>
     <t xml:space="preserve">2.21439218521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23290729522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512528419495</t>
+    <t xml:space="preserve">2.23290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512552261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.20328330993652</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">2.1995804309845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811423301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070823669434</t>
+    <t xml:space="preserve">2.21809506416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367825508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070847511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.24771928787231</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">2.33659100532532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51063227653503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68096995353699</t>
+    <t xml:space="preserve">2.51063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65504908561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68096971511841</t>
   </si>
   <si>
     <t xml:space="preserve">2.60320711135864</t>
@@ -1682,19 +1682,19 @@
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65875196456909</t>
+    <t xml:space="preserve">2.65875172615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.65134596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62542486190796</t>
+    <t xml:space="preserve">2.62542510032654</t>
   </si>
   <si>
     <t xml:space="preserve">2.71800017356873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70318794250488</t>
+    <t xml:space="preserve">2.70318818092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.72910904884338</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.8031690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81798100471497</t>
+    <t xml:space="preserve">2.81798076629639</t>
   </si>
   <si>
     <t xml:space="preserve">2.84390187263489</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">2.87352585792542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86241674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88093185424805</t>
+    <t xml:space="preserve">2.86241698265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88093209266663</t>
   </si>
   <si>
     <t xml:space="preserve">2.76243591308594</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">2.76984190940857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7994658946991</t>
+    <t xml:space="preserve">2.79946613311768</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205989837646</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">2.75873279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85871362686157</t>
+    <t xml:space="preserve">2.85871386528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.90314984321594</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">2.98091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91796207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758558273315</t>
+    <t xml:space="preserve">2.91796183586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758582115173</t>
   </si>
   <si>
     <t xml:space="preserve">2.95128870010376</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">2.9364767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95499205589294</t>
+    <t xml:space="preserve">2.95499181747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.93277382850647</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">2.91055583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96980381011963</t>
+    <t xml:space="preserve">2.96980404853821</t>
   </si>
   <si>
     <t xml:space="preserve">2.97720980644226</t>
@@ -1799,34 +1799,34 @@
     <t xml:space="preserve">2.9401798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89944672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81057524681091</t>
+    <t xml:space="preserve">2.89944648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81057476997375</t>
   </si>
   <si>
     <t xml:space="preserve">2.8661196231842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80687165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279299736023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85501074790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71059417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70689058303833</t>
+    <t xml:space="preserve">2.80687189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85501098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71059393882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70689082145691</t>
   </si>
   <si>
     <t xml:space="preserve">2.61061310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64023685455322</t>
+    <t xml:space="preserve">2.6402370929718</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">2.61801910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69578218460083</t>
+    <t xml:space="preserve">2.69578194618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.68467307090759</t>
@@ -1847,43 +1847,43 @@
     <t xml:space="preserve">2.68837594985962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61431622505188</t>
+    <t xml:space="preserve">2.6143159866333</t>
   </si>
   <si>
     <t xml:space="preserve">2.56988024711609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211716651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50692915916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34770011901855</t>
+    <t xml:space="preserve">2.49211740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50692892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34770035743713</t>
   </si>
   <si>
     <t xml:space="preserve">2.23661017417908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18476819992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19587707519531</t>
+    <t xml:space="preserve">2.18476843833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19587731361389</t>
   </si>
   <si>
     <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21777319908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10882997512817</t>
+    <t xml:space="preserve">2.2177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10883021354675</t>
   </si>
   <si>
     <t xml:space="preserve">2.12439346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893759727478</t>
+    <t xml:space="preserve">2.08937573432922</t>
   </si>
   <si>
     <t xml:space="preserve">2.10104846954346</t>
@@ -1892,31 +1892,31 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326696395874</t>
+    <t xml:space="preserve">2.09326672554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.12050247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13995695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12828397750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770371437073</t>
+    <t xml:space="preserve">2.13995671272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12828421592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770347595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.05046772956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657673835754</t>
+    <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03490447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435872077942</t>
+    <t xml:space="preserve">2.05435848236084</t>
   </si>
   <si>
     <t xml:space="preserve">2.03101325035095</t>
@@ -1931,19 +1931,19 @@
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944593429565</t>
+    <t xml:space="preserve">2.22944569587708</t>
   </si>
   <si>
     <t xml:space="preserve">2.1866466999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9687602519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00377774238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92985188961029</t>
+    <t xml:space="preserve">1.96876013278961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00377750396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.929851770401</t>
   </si>
   <si>
     <t xml:space="preserve">2.02712249755859</t>
@@ -1952,43 +1952,43 @@
     <t xml:space="preserve">1.94152414798737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84425365924835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79367291927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76643705368042</t>
+    <t xml:space="preserve">1.84425354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79367303848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76643693447113</t>
   </si>
   <si>
     <t xml:space="preserve">1.8092360496521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75087380409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74698281288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69251120090485</t>
+    <t xml:space="preserve">1.75087368488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74698269367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69251108169556</t>
   </si>
   <si>
     <t xml:space="preserve">1.78978180885315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82090854644775</t>
+    <t xml:space="preserve">1.82090842723846</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7430921792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69640219211578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71196556091309</t>
+    <t xml:space="preserve">1.74309206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69640207290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7119654417038</t>
   </si>
   <si>
     <t xml:space="preserve">1.7197470664978</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">1.78589117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141956329346</t>
+    <t xml:space="preserve">1.73141932487488</t>
   </si>
   <si>
     <t xml:space="preserve">1.71585619449615</t>
@@ -2009,79 +2009,79 @@
     <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78200042247772</t>
+    <t xml:space="preserve">1.78200018405914</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80145466327667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84036290645599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85592591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83647203445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8792712688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79756379127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032780647278</t>
+    <t xml:space="preserve">1.80145454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403627872467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85592615604401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83647191524506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87927103042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79756367206573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032792568207</t>
   </si>
   <si>
     <t xml:space="preserve">1.82869029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75476467609406</t>
+    <t xml:space="preserve">1.75476455688477</t>
   </si>
   <si>
     <t xml:space="preserve">1.75865530967712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254630088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80534529685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81701791286469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8247994184494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91428875923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93374264240265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89094352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538015842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89483428001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85981714725494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92207038402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01155948638916</t>
+    <t xml:space="preserve">1.76254618167877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80534517765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81701767444611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82479953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91428864002228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93374252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89094376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538027763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650677680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89483439922333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85981702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92207026481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01155924797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.16719269752502</t>
@@ -2096,22 +2096,22 @@
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217496871948</t>
+    <t xml:space="preserve">2.13217520713806</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19053745269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15552020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17108345031738</t>
+    <t xml:space="preserve">2.19053769111633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15551996231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19831919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1710832118988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14384770393372</t>
@@ -2120,55 +2120,55 @@
     <t xml:space="preserve">2.11272072792053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08548521995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01545023918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15941119194031</t>
+    <t xml:space="preserve">2.08548498153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01545000076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821425437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15941095352173</t>
   </si>
   <si>
     <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01934123039246</t>
+    <t xml:space="preserve">2.01934099197388</t>
   </si>
   <si>
     <t xml:space="preserve">1.87148940563202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91039776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872527122498</t>
+    <t xml:space="preserve">1.91039741039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596089839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872539043427</t>
   </si>
   <si>
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988698959351</t>
+    <t xml:space="preserve">1.99988663196564</t>
   </si>
   <si>
     <t xml:space="preserve">1.95708787441254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96486973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72752869129181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862056732178</t>
+    <t xml:space="preserve">1.96486937999725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210500717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72752857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862044811249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
@@ -2186,34 +2186,34 @@
     <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33844566345215</t>
+    <t xml:space="preserve">1.33844578266144</t>
   </si>
   <si>
     <t xml:space="preserve">1.30420637130737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27619242668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09098887443542</t>
+    <t xml:space="preserve">1.27619230747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09098875522614</t>
   </si>
   <si>
     <t xml:space="preserve">1.16102385520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08009457588196</t>
+    <t xml:space="preserve">1.08009445667267</t>
   </si>
   <si>
     <t xml:space="preserve">1.05986213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0847635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10188317298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22483336925507</t>
+    <t xml:space="preserve">1.08476364612579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10188329219818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22483348846436</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
@@ -2225,46 +2225,46 @@
     <t xml:space="preserve">1.35400903224945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26685440540314</t>
+    <t xml:space="preserve">1.26685428619385</t>
   </si>
   <si>
     <t xml:space="preserve">1.27152335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32288253307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28864312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28397417068481</t>
+    <t xml:space="preserve">1.32288241386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28864300251007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28397393226624</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39291739463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36179065704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062893867493</t>
+    <t xml:space="preserve">1.39291727542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36179053783417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062917709351</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798102378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33688950538635</t>
+    <t xml:space="preserve">1.29798114299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31354427337646</t>
+    <t xml:space="preserve">1.31354439258575</t>
   </si>
   <si>
     <t xml:space="preserve">1.29175567626953</t>
@@ -2276,64 +2276,64 @@
     <t xml:space="preserve">1.22950255870819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23884034156799</t>
+    <t xml:space="preserve">1.23884046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.24350941181183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20927023887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17503070831299</t>
+    <t xml:space="preserve">1.20927011966705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17503082752228</t>
   </si>
   <si>
     <t xml:space="preserve">1.13300979137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10343945026398</t>
+    <t xml:space="preserve">1.10343956947327</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08631980419159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05674970149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06764388084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12211549282074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10655236244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14234793186188</t>
+    <t xml:space="preserve">1.08631992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05674958229065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06764376163483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12211561203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10655224323273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14234781265259</t>
   </si>
   <si>
     <t xml:space="preserve">1.15012955665588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13923513889313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19837582111359</t>
+    <t xml:space="preserve">1.13923525810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1983757019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.2450658082962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2372841835022</t>
+    <t xml:space="preserve">1.23728406429291</t>
   </si>
   <si>
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708672523499</t>
+    <t xml:space="preserve">1.28708684444427</t>
   </si>
   <si>
     <t xml:space="preserve">1.27930510044098</t>
@@ -2342,22 +2342,22 @@
     <t xml:space="preserve">1.17969989776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16413640975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23572790622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20615744590759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20771372318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18748152256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21082651615143</t>
+    <t xml:space="preserve">1.16413652896881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23572778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2061573266983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20771396160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18748164176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21082639694214</t>
   </si>
   <si>
     <t xml:space="preserve">1.17814350128174</t>
@@ -2366,55 +2366,55 @@
     <t xml:space="preserve">1.18592512607574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612258434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15791118144989</t>
+    <t xml:space="preserve">1.13612246513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1579110622406</t>
   </si>
   <si>
     <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18436884880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17036187648773</t>
+    <t xml:space="preserve">1.18436872959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
     <t xml:space="preserve">1.14546048641205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16724920272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17347455024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15168571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17191815376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16569292545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15635478496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1252281665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.16724908351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1734744310379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15168583393097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17191827297211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1656928062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1563549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12522804737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08320724964142</t>
+    <t xml:space="preserve">1.06608760356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08320713043213</t>
   </si>
   <si>
     <t xml:space="preserve">1.06297492980957</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">1.07075667381287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09721410274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0614185333252</t>
+    <t xml:space="preserve">1.09721422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06141865253448</t>
   </si>
   <si>
     <t xml:space="preserve">1.05052423477173</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">1.04118621349335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03340446949005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03496098518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03651714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02251017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996052622795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01628482341766</t>
+    <t xml:space="preserve">1.03340458869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03496086597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0365172624588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02251029014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996052503585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01628494262695</t>
   </si>
   <si>
     <t xml:space="preserve">1.00850331783295</t>
@@ -2471,25 +2471,25 @@
     <t xml:space="preserve">1.01005959510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00072169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991383671760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966482281684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964925944805145</t>
+    <t xml:space="preserve">1.00072157382965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991383612155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96648234128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9649258852005</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954031586647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975820243358612</t>
+    <t xml:space="preserve">0.954031646251678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
     <t xml:space="preserve">0.989827215671539</t>
@@ -2498,52 +2498,52 @@
     <t xml:space="preserve">0.969595015048981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949362635612488</t>
+    <t xml:space="preserve">0.949362695217133</t>
   </si>
   <si>
     <t xml:space="preserve">0.968038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957144379615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489194393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999165296554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06453132629395</t>
+    <t xml:space="preserve">0.957144320011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999165236949921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06453120708466</t>
   </si>
   <si>
     <t xml:space="preserve">1.05830585956573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02406656742096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988270878791809</t>
+    <t xml:space="preserve">1.02406668663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988270998001099</t>
   </si>
   <si>
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941581010818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93379944562912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904229044914246</t>
+    <t xml:space="preserve">0.941580951213837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93379932641983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904228985309601</t>
   </si>
   <si>
     <t xml:space="preserve">0.879327654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887109339237213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888665616512299</t>
+    <t xml:space="preserve">0.887109279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888665676116943</t>
   </si>
   <si>
     <t xml:space="preserve">0.891778409481049</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">0.835750341415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803067326545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787504076957703</t>
+    <t xml:space="preserve">0.80306738615036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787504136562347</t>
   </si>
   <si>
     <t xml:space="preserve">0.829525053501129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831081390380859</t>
+    <t xml:space="preserve">0.831081330776215</t>
   </si>
   <si>
     <t xml:space="preserve">0.840419411659241</t>
@@ -2573,82 +2573,82 @@
     <t xml:space="preserve">0.817074358463287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86687707901001</t>
+    <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
     <t xml:space="preserve">0.89644730091095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902672648429871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915123343467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940024554729462</t>
+    <t xml:space="preserve">0.902672588825226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915123403072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940024614334106</t>
   </si>
   <si>
     <t xml:space="preserve">0.977376699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983601987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978933036327362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92913031578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961813151836395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946249961853027</t>
+    <t xml:space="preserve">0.963369727134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983601927757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978932917118073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929130375385284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961813271045685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946250021457672</t>
   </si>
   <si>
     <t xml:space="preserve">0.943137288093567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930686771869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952475309371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927573919296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926017701625824</t>
+    <t xml:space="preserve">0.930686712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952475190162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927573978900909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926017582416534</t>
   </si>
   <si>
     <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971151351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947806417942047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913566946983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341659069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679620742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560034275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918236017227173</t>
+    <t xml:space="preserve">0.971151411533356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792354106903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913567006587982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341718673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679680347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89955997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918235957622528</t>
   </si>
   <si>
     <t xml:space="preserve">0.908898055553436</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">0.894890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910454273223877</t>
+    <t xml:space="preserve">0.910454213619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12989711761475</t>
+    <t xml:space="preserve">1.12989723682404</t>
   </si>
   <si>
     <t xml:space="preserve">1.10032689571381</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">1.07231283187866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12834095954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12055921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11744666099548</t>
+    <t xml:space="preserve">1.12834084033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12055909633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11744654178619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15479850769043</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">1.31198811531067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25907289981842</t>
+    <t xml:space="preserve">1.25907266139984</t>
   </si>
   <si>
     <t xml:space="preserve">1.24662208557129</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">1.22638976573944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23105883598328</t>
+    <t xml:space="preserve">1.23105871677399</t>
   </si>
   <si>
     <t xml:space="preserve">1.2699670791626</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307975292206</t>
+    <t xml:space="preserve">1.27307987213135</t>
   </si>
   <si>
     <t xml:space="preserve">1.36023437976837</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069901943207</t>
+    <t xml:space="preserve">1.40069890022278</t>
   </si>
   <si>
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112867832184</t>
+    <t xml:space="preserve">1.37112879753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">1.39447367191315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3898047208786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3975864648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3913608789444</t>
+    <t xml:space="preserve">1.38980460166931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39758634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39136099815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.40536797046661</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">1.4380509853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52053666114807</t>
+    <t xml:space="preserve">1.52053654193878</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
@@ -2780,19 +2780,19 @@
     <t xml:space="preserve">1.58745884895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53765618801117</t>
+    <t xml:space="preserve">1.53765606880188</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431119441986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497317314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49096632003784</t>
+    <t xml:space="preserve">1.50341689586639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497329235077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49096620082855</t>
   </si>
   <si>
     <t xml:space="preserve">1.51798808574677</t>
@@ -2813,16 +2813,16 @@
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937666416168</t>
+    <t xml:space="preserve">1.48937678337097</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54818880558014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55454695224762</t>
+    <t xml:space="preserve">1.54818868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55454683303833</t>
   </si>
   <si>
     <t xml:space="preserve">1.5561363697052</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">1.56567347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.567263007164</t>
+    <t xml:space="preserve">1.56726312637329</t>
   </si>
   <si>
     <t xml:space="preserve">1.53706228733063</t>
@@ -2846,682 +2846,682 @@
     <t xml:space="preserve">1.47030258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4432806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40672194957733</t>
+    <t xml:space="preserve">1.44328081607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40672183036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374371528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44487023353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39241623878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35744678974152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949922561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34790980815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33201467990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929838657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31453001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27638161182404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3018137216568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30499279499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31135094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30340337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2843291759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479195594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22074854373932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22233784198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2557178735733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935984611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25412821769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22710657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21121144294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2732025384903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26366543769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37652099132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36698400974274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35267841815948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3749315738678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37970006465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128960132599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34314131736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33678317070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221539974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.363804936409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39877426624298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897498607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40513241291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49732434749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189211845398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738556861877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4146693944931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42420661449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45917594432831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46076536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41943800449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39082670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33996224403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3415515422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37811064720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35426783561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33042514324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37175250053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33837270736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287913799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116715908051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49573469161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50845086574554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51162993907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50209283828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51321947574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47507107257843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010174274445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4877872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47983968257904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45599687099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301875591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51004040241241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249439716339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63720178604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66501832008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67693960666656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70078253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65309679508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60541141033173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55772590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57362115383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43851208686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645977020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440745353699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45122838020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49414527416229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51639842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61335897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733281612396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322806358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62130653858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349024295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58792674541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60143768787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62925410270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66104435920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53865170478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183077812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52911472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53070402145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43056464195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37334203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30817198753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30022442340851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22869610786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23346471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539447307587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36062598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40831136703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59746384620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7484678030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423178195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76038908958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77231049537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025805950165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74449396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81999599933624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81204843521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83191752433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8279435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178625583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589112758636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986508846283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76833665370941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788205742836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72859871387482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64514923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71667766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73654639720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641548633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436293125153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410075187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7403576374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76195001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75763154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490556240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7533130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67730736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.644486784935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55811655521393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4769287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46483683586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45792722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50456702709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50283980369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865617275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51665902137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48038339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4890204668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47001910209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41128730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3819215297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40092289447784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43028879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4061051607132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501204013824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37328457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34737348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52875065803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59957420825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54775214195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55293428897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466175079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60648393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60475647449493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58230018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58057284355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53047811985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5252959728241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51493144035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49420273303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49765753746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45447242259979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43547093868256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44756281375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4285614490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39228594303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35255575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33873653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3214625120163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32318985462189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31973516941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31628036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31282544136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33009946346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3801943063736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35082840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33355438709259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31800770759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555153846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26791310310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2368198633194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25754857063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2247279882431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23854720592499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2005443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22300064563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1884526014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21954572200775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2610034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28691446781158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32664465904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29382407665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2730952501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35773801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39574074745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39746820926666</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44487023353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39241623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35744690895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34790980815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33201456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585725307465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929850578308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31453001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27638149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30181384086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30499279499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31135094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30340337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479207515717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22074842453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22233808040619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2557178735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935984611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25412821769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28273963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2112113237381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2732025384903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26366543769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37652099132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36698389053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35267841815948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970006465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128972053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34314119815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33678317070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221539974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.363804936409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39877438545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40513241291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53388321399689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49732422828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189199924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738556861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4146693944931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42420661449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45917594432831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46076548099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41943800449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39082670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33996224403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34155166149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37811064720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35426783561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33042514324188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37175250053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33837270736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287913799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050342082977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116703987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49573481082916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50845098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51162981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50209283828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51321947574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47507107257843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010174274445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48778712749481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47983956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45599699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301875591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51004040241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249451637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63720166683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66501832008362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67693948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70078253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65309679508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60541141033173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55772590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57362115383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43851220607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645988941193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4544073343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45122826099396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49414539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61335897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733293533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62130665779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58792674541473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60143768787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62925410270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53865170478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183065891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52911460399628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53070414066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43056464195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37334203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30817174911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30022430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22869598865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23346471786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539447307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36062586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40831136703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59746384620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74846792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423190116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76038908958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77231061458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74449396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81999611854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81204855442047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83191764354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82794368267059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178649425507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589136600494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986520767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.823970079422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628433704376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217970371246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76833665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78820586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859883308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71667754650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436305046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410087108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7403576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71012794971466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76195001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75763165950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75331294536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603904247284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67730736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448666572571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55811655521393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46483683586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45792722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42337930202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50456702709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50283968448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865605354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51665902137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48038351535797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4890204668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48211085796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47001910209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41128730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3819215297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40092301368713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43028879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37328457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34737348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52875077724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59957420825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477522611618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55293428897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60648381710052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60475647449493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58230030536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58057284355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53047811985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5252959728241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51493144035339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49420273303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49765753746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510664463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43547093868256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44756281375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4285614490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39228594303131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35255575180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33873653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3214625120163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32318985462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31973516941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31628036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31282544136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33009946346283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38019418716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35082840919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33355438709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31800770759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555153846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26791310310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2368198633194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25754857063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247279882431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23854720592499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2005443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22300052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1884526014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21954572200775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2610034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28691446781158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30418848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32664465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29382407665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2730952501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35773801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39574086666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39746820926666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44929015636444</t>
+    <t xml:space="preserve">1.44929027557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992449760437</t>
+    <t xml:space="preserve">1.41992437839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301476955414</t>
+    <t xml:space="preserve">1.41301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464750766754</t>
+    <t xml:space="preserve">1.38710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464762687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.331827044487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591583251953</t>
+    <t xml:space="preserve">1.33182692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591595172882</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3569,22 +3569,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564602375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937063694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827751636505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136778831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655005455017</t>
+    <t xml:space="preserve">1.34564614295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136790752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655017375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036915302277</t>
+    <t xml:space="preserve">1.29036927223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910106658936</t>
+    <t xml:space="preserve">1.34910094738007</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938488006592</t>
+    <t xml:space="preserve">1.49938476085663</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838636398315</t>
+    <t xml:space="preserve">1.51838624477386</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974941253662</t>
+    <t xml:space="preserve">1.50974929332733</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4181969165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729300498962</t>
+    <t xml:space="preserve">1.41819703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729312419891</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302901268005</t>
+    <t xml:space="preserve">1.60302889347076</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62893998622894</t>
+    <t xml:space="preserve">1.62894010543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6323949098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093713760376</t>
+    <t xml:space="preserve">1.63239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093725681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548518180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57193577289581</t>
+    <t xml:space="preserve">1.62548530101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5719358921051</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -47239,7 +47239,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47265,7 +47265,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47291,7 +47291,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47317,7 +47317,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47343,7 +47343,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47369,7 +47369,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47395,7 +47395,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47421,7 +47421,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47447,7 +47447,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47473,7 +47473,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47499,7 +47499,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47525,7 +47525,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47551,7 +47551,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G1637" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47577,7 +47577,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1638" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47603,7 +47603,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47629,7 +47629,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1640" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47655,7 +47655,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47681,7 +47681,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1642" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47707,7 +47707,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47733,7 +47733,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1644" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47759,7 +47759,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1645" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47785,7 +47785,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1646" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47811,7 +47811,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47837,7 +47837,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47863,7 +47863,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47889,7 +47889,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47915,7 +47915,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47941,7 +47941,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47967,7 +47967,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47993,7 +47993,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -48019,7 +48019,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -48045,7 +48045,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -48071,7 +48071,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1657" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -48097,7 +48097,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -48123,7 +48123,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1659" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -48149,7 +48149,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -48175,7 +48175,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -48201,7 +48201,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -48227,7 +48227,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1663" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48253,7 +48253,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48279,7 +48279,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1665" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48305,7 +48305,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48331,7 +48331,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48357,7 +48357,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48383,7 +48383,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48409,7 +48409,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48435,7 +48435,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48461,7 +48461,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1672" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48487,7 +48487,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48513,7 +48513,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48539,7 +48539,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48565,7 +48565,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1676" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48591,7 +48591,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1677" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48617,7 +48617,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1678" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48643,7 +48643,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48669,7 +48669,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48695,7 +48695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48721,7 +48721,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48747,7 +48747,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48773,7 +48773,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1684" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48799,7 +48799,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48825,7 +48825,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48851,7 +48851,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1687" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48877,7 +48877,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48903,7 +48903,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48929,7 +48929,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48955,7 +48955,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48981,7 +48981,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -49007,7 +49007,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -49033,7 +49033,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -49059,7 +49059,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -49085,7 +49085,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1696" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -49111,7 +49111,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -49137,7 +49137,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -49163,7 +49163,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -49189,7 +49189,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1700" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -49215,7 +49215,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49241,7 +49241,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49267,7 +49267,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49293,7 +49293,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49319,7 +49319,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49345,7 +49345,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49371,7 +49371,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49397,7 +49397,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49423,7 +49423,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1709" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49449,7 +49449,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49475,7 +49475,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49501,7 +49501,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49527,7 +49527,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49553,7 +49553,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49579,7 +49579,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1715" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49605,7 +49605,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49631,7 +49631,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49657,7 +49657,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49683,7 +49683,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49709,7 +49709,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49735,7 +49735,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1721" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49761,7 +49761,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49787,7 +49787,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49813,7 +49813,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49839,7 +49839,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49865,7 +49865,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49891,7 +49891,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49917,7 +49917,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49943,7 +49943,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49969,7 +49969,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49995,7 +49995,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -50021,7 +50021,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -50047,7 +50047,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -50073,7 +50073,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -50099,7 +50099,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="s">
-        <v>946</v>
+        <v>1168</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -50255,7 +50255,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50281,7 +50281,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50359,7 +50359,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50411,7 +50411,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50463,7 +50463,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1749" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50671,7 +50671,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1757" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50749,7 +50749,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50775,7 +50775,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50827,7 +50827,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50879,7 +50879,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1765" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50931,7 +50931,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -51009,7 +51009,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -51061,7 +51061,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -51269,7 +51269,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51399,7 +51399,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51503,7 +51503,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51529,7 +51529,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51581,7 +51581,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51633,7 +51633,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51711,7 +51711,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51737,7 +51737,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1798" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51763,7 +51763,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51867,7 +51867,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51919,7 +51919,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -52283,7 +52283,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52335,7 +52335,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1821" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52387,7 +52387,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52491,7 +52491,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1827" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52517,7 +52517,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52621,7 +52621,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52647,7 +52647,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52699,7 +52699,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52725,7 +52725,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52751,7 +52751,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52829,7 +52829,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52881,7 +52881,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -53063,7 +53063,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1849" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53245,7 +53245,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53505,7 +53505,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1866" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53765,7 +53765,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1876" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53895,7 +53895,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -70283,7 +70283,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6912384259</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>674516</v>
@@ -70304,6 +70304,32 @@
         <v>1548</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6913194444</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>324334</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385444641113</t>
+    <t xml:space="preserve">3.07385468482971</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
@@ -50,55 +50,55 @@
     <t xml:space="preserve">3.01786732673645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97690105438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98099708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131165504456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003081321716</t>
+    <t xml:space="preserve">2.97690010070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98099756240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94003105163574</t>
   </si>
   <si>
     <t xml:space="preserve">2.80620694160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86082863807678</t>
+    <t xml:space="preserve">2.86082887649536</t>
   </si>
   <si>
     <t xml:space="preserve">2.7584125995636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73929500579834</t>
+    <t xml:space="preserve">2.73929476737976</t>
   </si>
   <si>
     <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71744608879089</t>
+    <t xml:space="preserve">2.71744632720947</t>
   </si>
   <si>
     <t xml:space="preserve">2.866290807724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76387476921082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7447566986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75704717636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71061825752258</t>
+    <t xml:space="preserve">2.76387500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74475693702698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7570469379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71061849594116</t>
   </si>
   <si>
     <t xml:space="preserve">2.73110127449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76114392280579</t>
+    <t xml:space="preserve">2.76114368438721</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563934326172</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">2.69696283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62868499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935678482056</t>
+    <t xml:space="preserve">2.72290825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62868523597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935702323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799136161804</t>
@@ -122,49 +122,49 @@
     <t xml:space="preserve">2.30095291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38971400260925</t>
+    <t xml:space="preserve">2.38971376419067</t>
   </si>
   <si>
     <t xml:space="preserve">2.53992438316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50441980361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67511415481567</t>
+    <t xml:space="preserve">2.50442004203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67511367797852</t>
   </si>
   <si>
     <t xml:space="preserve">2.81713104248047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74885368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7816264629364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467259407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86219453811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8335177898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88404321670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769840240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85126972198486</t>
+    <t xml:space="preserve">2.74885320663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78162670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86219429969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83351755142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84717345237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88404297828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540887832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769887924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85127019882202</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685840606689</t>
@@ -176,661 +176,664 @@
     <t xml:space="preserve">3.05883359909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12164926528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1612503528595</t>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124987602234</t>
   </si>
   <si>
     <t xml:space="preserve">3.18173313140869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20767855644226</t>
+    <t xml:space="preserve">3.20767903327942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900204658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217421531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635506629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001120567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269940376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089265823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952699661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076638221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895963668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225430727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732181549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559893608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608266830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38656568527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833025932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511591911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375073432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2978048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366639137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1562032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13482999801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330288887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208178520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32291960716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856772422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33431887626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151986122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419079780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.476811170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4383385181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116209983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796006202698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89971733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8968677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643319129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495759963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938532829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500816345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9552891254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1704523563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599863052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625454902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9196662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86551904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90399241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83559584617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79854774475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442625999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77717399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88546824455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87406897544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834334373474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92109131813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9410400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694407463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85839462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409449577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707191467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007485389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80567240715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75865006446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77859902381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68597865104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62470722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5477614402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605568885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57198476791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45086693763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44516706466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42379307746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44374227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41666841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941615104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61045813560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54918599128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57910966873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5506112575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69310355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64038157463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63895630836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898206710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63325715065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67172980308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67315459251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7030782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7144775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65178084373474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66887998580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65748047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486082077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498818397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41524386405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43234276771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43661761283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39386987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39244508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511221408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236828804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53066253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57768487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58908414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63468170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69595336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68027949333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69167876243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69737839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012589454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297595024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72445178031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72302722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72872638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75580024719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71162748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69025373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65035581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760855674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58338451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55346131324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5206880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60618305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058573722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54491186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54063701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50501370429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49788928031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50643849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53351235389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626008987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048365592957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193396568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58195972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5591607093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58623456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53636193275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48506474494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54348683357239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68740367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69452857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75722479820251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77147436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79712295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78857350349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79997277259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83132100105286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9054172039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03508520126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215834617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25737285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07783269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16760301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16190361976624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16047811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21889972686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174954414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589702606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23172378540039</t>
   </si>
   <si>
     <t xml:space="preserve">3.17900228500366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17217373847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635458946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269940376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2308931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952747344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076685905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587204933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463290214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27732157707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559893608093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330893516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375073432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780530929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2636661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2602231502533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182658195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13482975959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208226203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291913032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856772422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3343186378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31151986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419079780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981387138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406343460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108601570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4084141254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39843988418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714293479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796030044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8997175693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89686751365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938508987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671439170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500840187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96526384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9552891254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9923369884491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1704523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13625478744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9196662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86551904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90399241447449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84129548072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83559584617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79854774475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73442625999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7771737575531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88546848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87406873703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94103980064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85839486122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409425735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707191467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007509231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80567240715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7586498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77859926223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68597888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62470722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478402137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5477614402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480954170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605568885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463089942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610672950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333323478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5719850063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45086693763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44516706466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42379331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44374203681946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666865348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941615104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61045813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54918622970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57910966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5506112575531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52353763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69310355186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64038133621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898206710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63325691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67172980308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67315483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71447730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65178084373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66887974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65748047828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486058235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498818397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41524386405945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43234276771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43661761283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39386987686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39244484901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35112190246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53066277503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57768487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58908438682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69595336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68027925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69167876243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69737839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297571182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72445201873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7230269908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7287266254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434969902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7558000087738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71162748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65035581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760855674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5833842754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5534610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5206880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60618329048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54491138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54063701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50501346588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49788904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50643849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53351211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57625985145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193396568298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58195972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55916094779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58623456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53636193275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48506474494934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54348659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68740391731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69452881813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75722503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79712295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78857350349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79997301101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83132100105286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9054172039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03508543968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215810775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477871894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727053642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25737309455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07783269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1676025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16190338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16047787666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21889972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174978256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877164840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23172450065613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12912964820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19610142707825</t>
+    <t xml:space="preserve">3.12913012504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19610118865967</t>
   </si>
   <si>
     <t xml:space="preserve">3.10063147544861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19752621650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884868621826</t>
+    <t xml:space="preserve">3.1975257396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884892463684</t>
   </si>
   <si>
     <t xml:space="preserve">3.22602486610413</t>
@@ -842,22 +845,22 @@
     <t xml:space="preserve">3.3257691860199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864476203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34001874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559030532837</t>
+    <t xml:space="preserve">3.28302121162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864428520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34001898765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39558982849121</t>
   </si>
   <si>
     <t xml:space="preserve">3.35569262504578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23457360267639</t>
+    <t xml:space="preserve">3.23457431793213</t>
   </si>
   <si>
     <t xml:space="preserve">3.27019762992859</t>
@@ -866,43 +869,43 @@
     <t xml:space="preserve">3.0892322063446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06358337402344</t>
+    <t xml:space="preserve">3.06358361244202</t>
   </si>
   <si>
     <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0970664024353</t>
+    <t xml:space="preserve">3.09706664085388</t>
   </si>
   <si>
     <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13886070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462542533875</t>
+    <t xml:space="preserve">3.13886022567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">3.11003732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1186842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07112574577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03797888755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04806733131409</t>
+    <t xml:space="preserve">3.11868453025818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07112598419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03797912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04806709289551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99762606620789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00627303123474</t>
+    <t xml:space="preserve">3.0062735080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.97744989395142</t>
@@ -911,19 +914,19 @@
     <t xml:space="preserve">2.9183623790741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8722448348999</t>
+    <t xml:space="preserve">2.87224507331848</t>
   </si>
   <si>
     <t xml:space="preserve">2.90395069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89098024368286</t>
+    <t xml:space="preserve">2.8909797668457</t>
   </si>
   <si>
     <t xml:space="preserve">2.87512731552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84918665885925</t>
+    <t xml:space="preserve">2.84918618202209</t>
   </si>
   <si>
     <t xml:space="preserve">2.92700886726379</t>
@@ -932,22 +935,22 @@
     <t xml:space="preserve">2.90683317184448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86936259269714</t>
+    <t xml:space="preserve">2.86936283111572</t>
   </si>
   <si>
     <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85783290863037</t>
+    <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.85350966453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87080359458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8246865272522</t>
+    <t xml:space="preserve">2.87080383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82468628883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79298067092896</t>
@@ -956,7 +959,7 @@
     <t xml:space="preserve">2.76415753364563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81027483940125</t>
+    <t xml:space="preserve">2.81027460098267</t>
   </si>
   <si>
     <t xml:space="preserve">2.80018639564514</t>
@@ -965,16 +968,16 @@
     <t xml:space="preserve">2.79153966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72956919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75262808799744</t>
+    <t xml:space="preserve">2.72956943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75262784957886</t>
   </si>
   <si>
     <t xml:space="preserve">2.75983381271362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74686360359192</t>
+    <t xml:space="preserve">2.74686336517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.95439124107361</t>
@@ -986,7 +989,7 @@
     <t xml:space="preserve">2.92845034599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9255678653717</t>
+    <t xml:space="preserve">2.92556810379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189225196838</t>
@@ -1001,40 +1004,40 @@
     <t xml:space="preserve">2.83045101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82612729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865718841553</t>
+    <t xml:space="preserve">2.82612752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865694999695</t>
   </si>
   <si>
     <t xml:space="preserve">2.80739212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.808833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84053921699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85495090484619</t>
+    <t xml:space="preserve">2.80883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84053897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85495066642761</t>
   </si>
   <si>
     <t xml:space="preserve">2.86503911018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87656855583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90827417373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83909821510315</t>
+    <t xml:space="preserve">2.87656831741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90827393531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83909797668457</t>
   </si>
   <si>
     <t xml:space="preserve">2.73821640014648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75551009178162</t>
+    <t xml:space="preserve">2.7555103302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.76848077774048</t>
@@ -1043,40 +1046,40 @@
     <t xml:space="preserve">2.70218729972839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72668719291687</t>
+    <t xml:space="preserve">2.72668695449829</t>
   </si>
   <si>
     <t xml:space="preserve">2.71371650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7252459526062</t>
+    <t xml:space="preserve">2.72524571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.68056988716125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67480492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336392402649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65895199775696</t>
+    <t xml:space="preserve">2.67480516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65895223617554</t>
   </si>
   <si>
     <t xml:space="preserve">2.67624616622925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75406932830811</t>
+    <t xml:space="preserve">2.75406908988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79874539375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74542188644409</t>
+    <t xml:space="preserve">2.79874515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74542212486267</t>
   </si>
   <si>
     <t xml:space="preserve">2.78577494621277</t>
@@ -1091,31 +1094,31 @@
     <t xml:space="preserve">3.02644944190979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06968474388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10571360588074</t>
+    <t xml:space="preserve">3.0696849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10571384429932</t>
   </si>
   <si>
     <t xml:space="preserve">3.12156653404236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17056608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14174318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597869873047</t>
+    <t xml:space="preserve">3.17056655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14174270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597846031189</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850835800171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07689046859741</t>
+    <t xml:space="preserve">3.05671429634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07689023017883</t>
   </si>
   <si>
     <t xml:space="preserve">3.08409667015076</t>
@@ -1127,16 +1130,16 @@
     <t xml:space="preserve">3.04086112976074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05383133888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17921352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589025497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05527281761169</t>
+    <t xml:space="preserve">3.05383157730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17921328544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589001655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05527257919312</t>
   </si>
   <si>
     <t xml:space="preserve">3.07977294921875</t>
@@ -1145,64 +1148,64 @@
     <t xml:space="preserve">3.14894866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16191911697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14750742912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09994959831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15903687477112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15471291542053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12877249717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11580204963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10427284240723</t>
+    <t xml:space="preserve">3.16191935539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1475076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09994912147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1590371131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15471315383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12877225875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11580157279968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10427260398865</t>
   </si>
   <si>
     <t xml:space="preserve">3.12012577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05815505981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483202934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168564796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78433394432068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8679211139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89674472808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88233304023743</t>
+    <t xml:space="preserve">3.05815529823303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168517112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82180428504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86792159080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8967444896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88233280181885</t>
   </si>
   <si>
     <t xml:space="preserve">2.85062742233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82901000976562</t>
+    <t xml:space="preserve">2.82900977134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324528694153</t>
@@ -1220,7 +1223,7 @@
     <t xml:space="preserve">2.71227526664734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65607023239136</t>
+    <t xml:space="preserve">2.65606999397278</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">2.76703953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78505444526672</t>
+    <t xml:space="preserve">2.78505420684814</t>
   </si>
   <si>
     <t xml:space="preserve">2.72740769386292</t>
@@ -1238,28 +1241,28 @@
     <t xml:space="preserve">2.69498133659363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73461365699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70579028129578</t>
+    <t xml:space="preserve">2.7346134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7057900428772</t>
   </si>
   <si>
     <t xml:space="preserve">2.7310106754303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72020173072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79226040840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84630393981934</t>
+    <t xml:space="preserve">2.72020196914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79226016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84630370140076</t>
   </si>
   <si>
     <t xml:space="preserve">2.77424550056458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77064275741577</t>
+    <t xml:space="preserve">2.77064251899719</t>
   </si>
   <si>
     <t xml:space="preserve">2.70939302444458</t>
@@ -1268,13 +1271,13 @@
     <t xml:space="preserve">2.74181914329529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71299576759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63373184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652611732483</t>
+    <t xml:space="preserve">2.71299600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63373160362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652587890625</t>
   </si>
   <si>
     <t xml:space="preserve">2.6409375667572</t>
@@ -1283,25 +1286,25 @@
     <t xml:space="preserve">2.65534901618958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64814352989197</t>
+    <t xml:space="preserve">2.64814329147339</t>
   </si>
   <si>
     <t xml:space="preserve">2.58689379692078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5724823474884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57968807220459</t>
+    <t xml:space="preserve">2.57248210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57968783378601</t>
   </si>
   <si>
     <t xml:space="preserve">2.55807042121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56167340278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086445808411</t>
+    <t xml:space="preserve">2.56167364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086469650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.56887936592102</t>
@@ -1310,7 +1313,7 @@
     <t xml:space="preserve">2.43557143211365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37432169914246</t>
+    <t xml:space="preserve">2.37432193756104</t>
   </si>
   <si>
     <t xml:space="preserve">2.30946922302246</t>
@@ -1325,22 +1328,22 @@
     <t xml:space="preserve">2.41395378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36351323127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3599100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44998335838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35270404815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52204155921936</t>
+    <t xml:space="preserve">2.36351299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35991024971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4499831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35270428657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52204132080078</t>
   </si>
   <si>
     <t xml:space="preserve">2.42836546897888</t>
@@ -1355,7 +1358,7 @@
     <t xml:space="preserve">2.50762987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59409976005554</t>
+    <t xml:space="preserve">2.59409999847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527638435364</t>
@@ -1370,13 +1373,13 @@
     <t xml:space="preserve">2.62292313575745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60130524635315</t>
+    <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
     <t xml:space="preserve">2.60851120948792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6373348236084</t>
+    <t xml:space="preserve">2.63733458518982</t>
   </si>
   <si>
     <t xml:space="preserve">2.68417239189148</t>
@@ -1385,19 +1388,19 @@
     <t xml:space="preserve">2.66615796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69137835502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67696666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73281216621399</t>
+    <t xml:space="preserve">2.69137811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67696690559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73281192779541</t>
   </si>
   <si>
     <t xml:space="preserve">2.62172198295593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49582028388977</t>
+    <t xml:space="preserve">2.49582004547119</t>
   </si>
   <si>
     <t xml:space="preserve">2.48841404914856</t>
@@ -1415,7 +1418,7 @@
     <t xml:space="preserve">2.39213609695435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40694832801819</t>
+    <t xml:space="preserve">2.40694808959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.36991810798645</t>
@@ -1424,10 +1427,10 @@
     <t xml:space="preserve">2.29956126213074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21068906784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32548236846924</t>
+    <t xml:space="preserve">2.21068930625916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32548213005066</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732434272766</t>
@@ -1436,13 +1439,13 @@
     <t xml:space="preserve">2.38843321800232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4291660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46989941596985</t>
+    <t xml:space="preserve">2.42916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805720329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46989917755127</t>
   </si>
   <si>
     <t xml:space="preserve">2.5032262802124</t>
@@ -1454,13 +1457,13 @@
     <t xml:space="preserve">2.53285026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57728600502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45508694648743</t>
+    <t xml:space="preserve">2.57728624343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5254442691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45508718490601</t>
   </si>
   <si>
     <t xml:space="preserve">2.58098888397217</t>
@@ -1478,16 +1481,16 @@
     <t xml:space="preserve">2.53655314445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47730541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51433491706848</t>
+    <t xml:space="preserve">2.4773051738739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51433515548706</t>
   </si>
   <si>
     <t xml:space="preserve">2.48100805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46619606018066</t>
+    <t xml:space="preserve">2.46619582176208</t>
   </si>
   <si>
     <t xml:space="preserve">2.39583897590637</t>
@@ -1499,7 +1502,7 @@
     <t xml:space="preserve">2.35140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36621475219727</t>
+    <t xml:space="preserve">2.36621522903442</t>
   </si>
   <si>
     <t xml:space="preserve">2.34399724006653</t>
@@ -1511,37 +1514,37 @@
     <t xml:space="preserve">2.35510659217834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36251211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30696702003479</t>
+    <t xml:space="preserve">2.3625123500824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30696725845337</t>
   </si>
   <si>
     <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32177925109863</t>
+    <t xml:space="preserve">2.32177901268005</t>
   </si>
   <si>
     <t xml:space="preserve">2.39954233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38102746009827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41435432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37362146377563</t>
+    <t xml:space="preserve">2.38102722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41435408592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37362122535706</t>
   </si>
   <si>
     <t xml:space="preserve">2.31807661056519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29585814476013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104615211487</t>
+    <t xml:space="preserve">2.29585838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104639053345</t>
   </si>
   <si>
     <t xml:space="preserve">2.26993727684021</t>
@@ -1553,37 +1556,37 @@
     <t xml:space="preserve">2.32918524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27734303474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26623439788818</t>
+    <t xml:space="preserve">2.27734327316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2662341594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.29215550422668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27364015579224</t>
+    <t xml:space="preserve">2.27364039421082</t>
   </si>
   <si>
     <t xml:space="preserve">2.2884521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28474950790405</t>
+    <t xml:space="preserve">2.28474926948547</t>
   </si>
   <si>
     <t xml:space="preserve">2.38473010063171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698642730713</t>
+    <t xml:space="preserve">2.20698618888855</t>
   </si>
   <si>
     <t xml:space="preserve">2.24031352996826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15514421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292646408081</t>
+    <t xml:space="preserve">2.15514445304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292670249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.14773845672607</t>
@@ -1595,22 +1598,22 @@
     <t xml:space="preserve">2.09959959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08849024772644</t>
+    <t xml:space="preserve">2.08849048614502</t>
   </si>
   <si>
     <t xml:space="preserve">2.10700535774231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0625696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98850929737091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147943496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553963661194</t>
+    <t xml:space="preserve">2.06256985664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9885094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147931575775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553939819336</t>
   </si>
   <si>
     <t xml:space="preserve">2.06627225875854</t>
@@ -1622,25 +1625,25 @@
     <t xml:space="preserve">2.06997537612915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12922310829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14403557777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13662934303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847131729126</t>
+    <t xml:space="preserve">2.12922334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14403533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13662958145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847107887268</t>
   </si>
   <si>
     <t xml:space="preserve">2.21439242362976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23290753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512552261353</t>
+    <t xml:space="preserve">2.23290729522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512528419495</t>
   </si>
   <si>
     <t xml:space="preserve">2.2032835483551</t>
@@ -1649,10 +1652,10 @@
     <t xml:space="preserve">2.1995804309845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809506416321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811423301697</t>
+    <t xml:space="preserve">2.21809530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811399459839</t>
   </si>
   <si>
     <t xml:space="preserve">2.07367849349976</t>
@@ -1670,7 +1673,7 @@
     <t xml:space="preserve">2.51063227653503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65504908561707</t>
+    <t xml:space="preserve">2.65504932403564</t>
   </si>
   <si>
     <t xml:space="preserve">2.68096995353699</t>
@@ -1682,13 +1685,13 @@
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65875196456909</t>
+    <t xml:space="preserve">2.65875220298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.65134596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62542510032654</t>
+    <t xml:space="preserve">2.62542486190796</t>
   </si>
   <si>
     <t xml:space="preserve">2.71799993515015</t>
@@ -1697,25 +1700,25 @@
     <t xml:space="preserve">2.70318794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7291088104248</t>
+    <t xml:space="preserve">2.72910904884338</t>
   </si>
   <si>
     <t xml:space="preserve">2.69207906723022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71429705619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75502991676331</t>
+    <t xml:space="preserve">2.71429681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75503015518188</t>
   </si>
   <si>
     <t xml:space="preserve">2.8031690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81798100471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84390187263489</t>
+    <t xml:space="preserve">2.81798076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84390163421631</t>
   </si>
   <si>
     <t xml:space="preserve">2.87352609634399</t>
@@ -1733,19 +1736,19 @@
     <t xml:space="preserve">2.76984190940857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79946565628052</t>
+    <t xml:space="preserve">2.7994658946991</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81427788734436</t>
+    <t xml:space="preserve">2.81427812576294</t>
   </si>
   <si>
     <t xml:space="preserve">2.79576301574707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75873279571533</t>
+    <t xml:space="preserve">2.75873255729675</t>
   </si>
   <si>
     <t xml:space="preserve">2.85871362686157</t>
@@ -1757,22 +1760,22 @@
     <t xml:space="preserve">2.89574384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90685296058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88833785057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.962397813797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98091268539429</t>
+    <t xml:space="preserve">2.90685272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88833808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96239757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98091292381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.91796159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94758582115173</t>
+    <t xml:space="preserve">2.94758605957031</t>
   </si>
   <si>
     <t xml:space="preserve">2.95128870010376</t>
@@ -1781,13 +1784,13 @@
     <t xml:space="preserve">2.9364767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95499157905579</t>
+    <t xml:space="preserve">2.95499181747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.93277382850647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91055583953857</t>
+    <t xml:space="preserve">2.91055607795715</t>
   </si>
   <si>
     <t xml:space="preserve">2.96980404853821</t>
@@ -1796,7 +1799,7 @@
     <t xml:space="preserve">2.97720956802368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9401798248291</t>
+    <t xml:space="preserve">2.94017958641052</t>
   </si>
   <si>
     <t xml:space="preserve">2.89944672584534</t>
@@ -1814,10 +1817,10 @@
     <t xml:space="preserve">2.83279299736023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85501098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71059393882751</t>
+    <t xml:space="preserve">2.85501074790955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71059370040894</t>
   </si>
   <si>
     <t xml:space="preserve">2.70689105987549</t>
@@ -1835,25 +1838,22 @@
     <t xml:space="preserve">2.63283109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61801934242249</t>
+    <t xml:space="preserve">2.61801910400391</t>
   </si>
   <si>
     <t xml:space="preserve">2.69578194618225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68467283248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6883761882782</t>
+    <t xml:space="preserve">2.68837594985962</t>
   </si>
   <si>
     <t xml:space="preserve">2.6143159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56988000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49211716651917</t>
+    <t xml:space="preserve">2.56988024711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49211692810059</t>
   </si>
   <si>
     <t xml:space="preserve">2.50692915916443</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">2.34770011901855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23661041259766</t>
+    <t xml:space="preserve">2.23661017417908</t>
   </si>
   <si>
     <t xml:space="preserve">2.18476819992065</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">2.19587731361389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.299480676651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2177734375</t>
+    <t xml:space="preserve">2.29948091506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21777319908142</t>
   </si>
   <si>
     <t xml:space="preserve">2.10883021354675</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03490447998047</t>
+    <t xml:space="preserve">2.03490424156189</t>
   </si>
   <si>
     <t xml:space="preserve">2.05435848236084</t>
@@ -1931,34 +1931,34 @@
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944569587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1866466999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96876013278961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00377750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.929851770401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02712249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94152414798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84425354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79367303848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76643693447113</t>
+    <t xml:space="preserve">2.22944593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18664646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96876001358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00377774238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92985188961029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02712273597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94152426719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84425342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79367291927338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76643681526184</t>
   </si>
   <si>
     <t xml:space="preserve">1.8092360496521</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.69251108169556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78978180885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82090842723846</t>
+    <t xml:space="preserve">1.78978192806244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82090854644775</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">1.78589117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141932487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585619449615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7353104352951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78200018405914</t>
+    <t xml:space="preserve">1.73141944408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71585607528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73531031608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78200030326843</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
@@ -2018,25 +2018,25 @@
     <t xml:space="preserve">1.80145454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8403627872467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85592615604401</t>
+    <t xml:space="preserve">1.84036290645599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85592603683472</t>
   </si>
   <si>
     <t xml:space="preserve">1.83647191524506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87927103042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79756367206573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032792568207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869029045105</t>
+    <t xml:space="preserve">1.87927114963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79756355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032780647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869017124176</t>
   </si>
   <si>
     <t xml:space="preserve">1.75476455688477</t>
@@ -2048,43 +2048,43 @@
     <t xml:space="preserve">1.76254618167877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80534517765045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81701767444611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82479953765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91428864002228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93374252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89094376564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538027763367</t>
+    <t xml:space="preserve">1.80534529685974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8170177936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8247994184494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91428852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93374264240265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89094352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538039684296</t>
   </si>
   <si>
     <t xml:space="preserve">1.90650677680969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89483439922333</t>
+    <t xml:space="preserve">1.89483428001404</t>
   </si>
   <si>
     <t xml:space="preserve">1.85981702804565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92207026481628</t>
+    <t xml:space="preserve">1.92207038402557</t>
   </si>
   <si>
     <t xml:space="preserve">2.01155924797058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16719269752502</t>
+    <t xml:space="preserve">2.16719245910645</t>
   </si>
   <si>
     <t xml:space="preserve">2.16330170631409</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">2.14384770393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11272072792053</t>
+    <t xml:space="preserve">2.11272096633911</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548498153687</t>
@@ -2126,49 +2126,49 @@
     <t xml:space="preserve">2.01545000076294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821425437927</t>
+    <t xml:space="preserve">1.98821437358856</t>
   </si>
   <si>
     <t xml:space="preserve">2.15941095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13606595993042</t>
+    <t xml:space="preserve">2.13606572151184</t>
   </si>
   <si>
     <t xml:space="preserve">2.01934099197388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87148940563202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91039741039276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596089839935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872539043427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9531968832016</t>
+    <t xml:space="preserve">1.87148928642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91039752960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596113681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872527122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95319676399231</t>
   </si>
   <si>
     <t xml:space="preserve">1.99988663196564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95708787441254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96486937999725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210500717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72752857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862044811249</t>
+    <t xml:space="preserve">1.95708775520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210512638092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72752869129181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862056732178</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
@@ -2180,25 +2180,25 @@
     <t xml:space="preserve">1.542325258255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48941004276276</t>
+    <t xml:space="preserve">1.48940992355347</t>
   </si>
   <si>
     <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33844578266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30420637130737</t>
+    <t xml:space="preserve">1.33844566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30420649051666</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619230747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09098875522614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16102385520935</t>
+    <t xml:space="preserve">1.09098887443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16102373600006</t>
   </si>
   <si>
     <t xml:space="preserve">1.08009445667267</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">1.05986213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08476364612579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10188329219818</t>
+    <t xml:space="preserve">1.0847635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
     <t xml:space="preserve">1.22483348846436</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">1.31976974010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910764217377</t>
+    <t xml:space="preserve">1.32910776138306</t>
   </si>
   <si>
     <t xml:space="preserve">1.35400903224945</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">1.26685428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27152335643768</t>
+    <t xml:space="preserve">1.27152323722839</t>
   </si>
   <si>
     <t xml:space="preserve">1.32288241386414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28864300251007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28397393226624</t>
+    <t xml:space="preserve">1.28864312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28397405147552</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331207275391</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">1.39291727542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36179053783417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062917709351</t>
+    <t xml:space="preserve">1.36179065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062905788422</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798114299774</t>
+    <t xml:space="preserve">1.29798102378845</t>
   </si>
   <si>
     <t xml:space="preserve">1.33688938617706</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">1.29953730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31354439258575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29175567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28241765499115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22950255870819</t>
+    <t xml:space="preserve">1.31354427337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29175579547882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28241777420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2295024394989</t>
   </si>
   <si>
     <t xml:space="preserve">1.23884046077728</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">1.20927011966705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503082752228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13300979137421</t>
+    <t xml:space="preserve">1.17503070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1330099105835</t>
   </si>
   <si>
     <t xml:space="preserve">1.10343956947327</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">1.05674958229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06764376163483</t>
+    <t xml:space="preserve">1.06764388084412</t>
   </si>
   <si>
     <t xml:space="preserve">1.12211561203003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10655224323273</t>
+    <t xml:space="preserve">1.10655212402344</t>
   </si>
   <si>
     <t xml:space="preserve">1.14234781265259</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">1.13923525810242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1983757019043</t>
+    <t xml:space="preserve">1.19837582111359</t>
   </si>
   <si>
     <t xml:space="preserve">1.2450658082962</t>
@@ -2348,31 +2348,31 @@
     <t xml:space="preserve">1.23572778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2061573266983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20771396160126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18748164176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21082639694214</t>
+    <t xml:space="preserve">1.20615744590759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20771384239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18748152256012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21082651615143</t>
   </si>
   <si>
     <t xml:space="preserve">1.17814350128174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18592512607574</t>
+    <t xml:space="preserve">1.18592524528503</t>
   </si>
   <si>
     <t xml:space="preserve">1.13612246513367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1579110622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14079141616821</t>
+    <t xml:space="preserve">1.15791118144989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1407915353775</t>
   </si>
   <si>
     <t xml:space="preserve">1.18436872959137</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">1.14546048641205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16724908351898</t>
+    <t xml:space="preserve">1.16724920272827</t>
   </si>
   <si>
     <t xml:space="preserve">1.1734744310379</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">1.17191827297211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1656928062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1563549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12522804737091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565782546997</t>
+    <t xml:space="preserve">1.16569268703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15635478496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1252281665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565794467926</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">1.06608760356903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08320713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06297492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04896795749664</t>
+    <t xml:space="preserve">1.08320724964142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06297504901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04896783828735</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410154819489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07075667381287</t>
+    <t xml:space="preserve">1.07075655460358</t>
   </si>
   <si>
     <t xml:space="preserve">1.09721422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06141865253448</t>
+    <t xml:space="preserve">1.0614185333252</t>
   </si>
   <si>
     <t xml:space="preserve">1.05052423477173</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">1.03340458869934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03496086597443</t>
+    <t xml:space="preserve">1.03496098518372</t>
   </si>
   <si>
     <t xml:space="preserve">1.0365172624588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02251029014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996052503585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01628494262695</t>
+    <t xml:space="preserve">1.02251017093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99605256319046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01628506183624</t>
   </si>
   <si>
     <t xml:space="preserve">1.00850331783295</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">0.991383612155914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96648234128952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9649258852005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958700597286224</t>
+    <t xml:space="preserve">0.966482281684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964925944805145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958700656890869</t>
   </si>
   <si>
     <t xml:space="preserve">0.954031646251678</t>
@@ -2492,25 +2492,25 @@
     <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827215671539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969595015048981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949362695217133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968038558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957144320011139</t>
+    <t xml:space="preserve">0.989827275276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969594955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949362635612488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968038618564606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957144260406494</t>
   </si>
   <si>
     <t xml:space="preserve">0.980489253997803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999165236949921</t>
+    <t xml:space="preserve">0.99916535615921</t>
   </si>
   <si>
     <t xml:space="preserve">1.06453120708466</t>
@@ -2519,22 +2519,22 @@
     <t xml:space="preserve">1.05830585956573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02406668663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988270998001099</t>
+    <t xml:space="preserve">1.02406656742096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988270938396454</t>
   </si>
   <si>
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941580951213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93379932641983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904228985309601</t>
+    <t xml:space="preserve">0.941581070423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933799266815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904228925704956</t>
   </si>
   <si>
     <t xml:space="preserve">0.879327654838562</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">0.888665676116943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891778409481049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835750341415405</t>
+    <t xml:space="preserve">0.891778349876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83575040102005</t>
   </si>
   <si>
     <t xml:space="preserve">0.80306738615036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787504136562347</t>
+    <t xml:space="preserve">0.787504076957703</t>
   </si>
   <si>
     <t xml:space="preserve">0.829525053501129</t>
@@ -2567,61 +2567,61 @@
     <t xml:space="preserve">0.840419411659241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826412439346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817074358463287</t>
+    <t xml:space="preserve">0.826412379741669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817074418067932</t>
   </si>
   <si>
     <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89644730091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902672588825226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915123403072357</t>
+    <t xml:space="preserve">0.896447241306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902672648429871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915123283863068</t>
   </si>
   <si>
     <t xml:space="preserve">0.940024614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977376699447632</t>
+    <t xml:space="preserve">0.977376639842987</t>
   </si>
   <si>
     <t xml:space="preserve">0.963369727134705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983601927757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978932917118073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929130375385284</t>
+    <t xml:space="preserve">0.983601987361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978932976722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
     <t xml:space="preserve">0.961813271045685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946250021457672</t>
+    <t xml:space="preserve">0.946249961853027</t>
   </si>
   <si>
     <t xml:space="preserve">0.943137288093567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952475190162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927573978900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926017582416534</t>
+    <t xml:space="preserve">0.93068665266037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952475309371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927574038505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926017642021179</t>
   </si>
   <si>
     <t xml:space="preserve">0.935355663299561</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">0.971151411533356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792354106903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913567006587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679680347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89955997467041</t>
+    <t xml:space="preserve">0.947806417942047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792294502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913567066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341659069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679620742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8995600938797</t>
   </si>
   <si>
     <t xml:space="preserve">0.918235957622528</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">0.908898055553436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894890904426575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910454213619232</t>
+    <t xml:space="preserve">0.894890964031219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910454273223877</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">1.05363690853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13767886161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15946745872498</t>
+    <t xml:space="preserve">1.13767874240875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15946757793427</t>
   </si>
   <si>
     <t xml:space="preserve">1.12989723682404</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">1.10032689571381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09877049922943</t>
+    <t xml:space="preserve">1.09877038002014</t>
   </si>
   <si>
     <t xml:space="preserve">1.07231283187866</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">1.12834084033966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12055909633636</t>
+    <t xml:space="preserve">1.12055921554565</t>
   </si>
   <si>
     <t xml:space="preserve">1.11744654178619</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">1.2544037103653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22638976573944</t>
+    <t xml:space="preserve">1.22638988494873</t>
   </si>
   <si>
     <t xml:space="preserve">1.23105871677399</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">1.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25751650333405</t>
+    <t xml:space="preserve">1.25751662254333</t>
   </si>
   <si>
     <t xml:space="preserve">1.26841068267822</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">1.27307987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36023437976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38513565063477</t>
+    <t xml:space="preserve">1.36023426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38513553142548</t>
   </si>
   <si>
     <t xml:space="preserve">1.40069890022278</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112879753113</t>
+    <t xml:space="preserve">1.37112867832184</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">1.49096620082855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51798808574677</t>
+    <t xml:space="preserve">1.51798796653748</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871304512024</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937678337097</t>
+    <t xml:space="preserve">1.48937666416168</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54818868637085</t>
+    <t xml:space="preserve">1.54818880558014</t>
   </si>
   <si>
     <t xml:space="preserve">1.55454683303833</t>
@@ -2831,10 +2831,10 @@
     <t xml:space="preserve">1.57044196128845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56567347049713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56726312637329</t>
+    <t xml:space="preserve">1.56567358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.567263007164</t>
   </si>
   <si>
     <t xml:space="preserve">1.53706228733063</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">1.44328081607819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40672183036804</t>
+    <t xml:space="preserve">1.40672194957733</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374371528625</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">1.39241623878479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744678974152</t>
+    <t xml:space="preserve">1.35744690895081</t>
   </si>
   <si>
     <t xml:space="preserve">1.34949922561646</t>
@@ -2876,16 +2876,16 @@
     <t xml:space="preserve">1.35585737228394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31929838657379</t>
+    <t xml:space="preserve">1.31929850578308</t>
   </si>
   <si>
     <t xml:space="preserve">1.31453001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27638161182404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3018137216568</t>
+    <t xml:space="preserve">1.27638149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30181384086609</t>
   </si>
   <si>
     <t xml:space="preserve">1.30499279499054</t>
@@ -2894,25 +2894,25 @@
     <t xml:space="preserve">1.31135094165802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30340337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479195594788</t>
+    <t xml:space="preserve">1.30340325832367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28432929515839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479207515717</t>
   </si>
   <si>
     <t xml:space="preserve">1.22074854373932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22233784198761</t>
+    <t xml:space="preserve">1.2223379611969</t>
   </si>
   <si>
     <t xml:space="preserve">1.2557178735733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24935984611511</t>
+    <t xml:space="preserve">1.24935972690582</t>
   </si>
   <si>
     <t xml:space="preserve">1.25412821769714</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">1.37652099132538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36698400974274</t>
+    <t xml:space="preserve">1.36698389053345</t>
   </si>
   <si>
     <t xml:space="preserve">1.35267841815948</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">1.3749315738678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37970006465912</t>
+    <t xml:space="preserve">1.37970018386841</t>
   </si>
   <si>
     <t xml:space="preserve">1.38128960132599</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">1.39877426624298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42897498607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40513241291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5338830947876</t>
+    <t xml:space="preserve">1.42897510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40513229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53388321399689</t>
   </si>
   <si>
     <t xml:space="preserve">1.49732434749603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47189211845398</t>
+    <t xml:space="preserve">1.47189199924469</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738556861877</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">1.45917594432831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46076536178589</t>
+    <t xml:space="preserve">1.46076548099518</t>
   </si>
   <si>
     <t xml:space="preserve">1.41943800449371</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">1.33996224403381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3415515422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351936340332</t>
+    <t xml:space="preserve">1.34155166149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33519351482391</t>
   </si>
   <si>
     <t xml:space="preserve">1.37811064720154</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">1.38287913799286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50050342082977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116715908051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49573469161987</t>
+    <t xml:space="preserve">1.50050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116703987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49573481082916</t>
   </si>
   <si>
     <t xml:space="preserve">1.50845086574554</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">1.51321947574615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47507107257843</t>
+    <t xml:space="preserve">1.47507119178772</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010174274445</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">1.47983968257904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45599687099457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301875591278</t>
+    <t xml:space="preserve">1.45599699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301863670349</t>
   </si>
   <si>
     <t xml:space="preserve">1.51004040241241</t>
@@ -3074,19 +3074,19 @@
     <t xml:space="preserve">1.56249439716339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63720178604126</t>
+    <t xml:space="preserve">1.63720166683197</t>
   </si>
   <si>
     <t xml:space="preserve">1.66501832008362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67693960666656</t>
+    <t xml:space="preserve">1.67693948745728</t>
   </si>
   <si>
     <t xml:space="preserve">1.70078253746033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65309679508209</t>
+    <t xml:space="preserve">1.65309691429138</t>
   </si>
   <si>
     <t xml:space="preserve">1.60541141033173</t>
@@ -3098,13 +3098,13 @@
     <t xml:space="preserve">1.57362115383148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43851208686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645977020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440745353699</t>
+    <t xml:space="preserve">1.43851220607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645988941193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4544073343277</t>
   </si>
   <si>
     <t xml:space="preserve">1.45122838020325</t>
@@ -3113,22 +3113,22 @@
     <t xml:space="preserve">1.49414527416229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51639842987061</t>
+    <t xml:space="preserve">1.5163985490799</t>
   </si>
   <si>
     <t xml:space="preserve">1.61335897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61733281612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322806358337</t>
+    <t xml:space="preserve">1.61733293533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322794437408</t>
   </si>
   <si>
     <t xml:space="preserve">1.62130653858185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349024295807</t>
+    <t xml:space="preserve">1.59349012374878</t>
   </si>
   <si>
     <t xml:space="preserve">1.58792674541473</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">1.62925410270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104435920715</t>
+    <t xml:space="preserve">1.66104447841644</t>
   </si>
   <si>
     <t xml:space="preserve">1.53865170478821</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">1.52434611320496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43056464195251</t>
+    <t xml:space="preserve">1.43056452274323</t>
   </si>
   <si>
     <t xml:space="preserve">1.37334203720093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30817198753357</t>
+    <t xml:space="preserve">1.30817186832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.30022442340851</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">1.59746384620667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7484678030014</t>
+    <t xml:space="preserve">1.74846792221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.78423178195953</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">1.77231049537659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78025805950165</t>
+    <t xml:space="preserve">1.78025817871094</t>
   </si>
   <si>
     <t xml:space="preserve">1.74449396133423</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">1.64514923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71667766571045</t>
+    <t xml:space="preserve">1.71667754650116</t>
   </si>
   <si>
     <t xml:space="preserve">1.73654639720917</t>
@@ -3275,22 +3275,22 @@
     <t xml:space="preserve">1.76195001602173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75763154029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490556240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7533130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603892326355</t>
+    <t xml:space="preserve">1.75763165950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75331294536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603904247284</t>
   </si>
   <si>
     <t xml:space="preserve">1.67730736732483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.644486784935</t>
+    <t xml:space="preserve">1.64448666572571</t>
   </si>
   <si>
     <t xml:space="preserve">1.55811655521393</t>
@@ -3311,16 +3311,16 @@
     <t xml:space="preserve">1.50456702709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50283980369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865617275238</t>
+    <t xml:space="preserve">1.50283968448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865605354309</t>
   </si>
   <si>
     <t xml:space="preserve">1.51665902137756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48038339614868</t>
+    <t xml:space="preserve">1.48038351535797</t>
   </si>
   <si>
     <t xml:space="preserve">1.4890204668045</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">1.3819215297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40092289447784</t>
+    <t xml:space="preserve">1.40092301368713</t>
   </si>
   <si>
     <t xml:space="preserve">1.43028879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4061051607132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501204013824</t>
+    <t xml:space="preserve">1.40610527992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501192092896</t>
   </si>
   <si>
     <t xml:space="preserve">1.37328457832336</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">1.34737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52875065803528</t>
+    <t xml:space="preserve">1.52875077724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.59957420825958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54775214195251</t>
+    <t xml:space="preserve">1.5477522611618</t>
   </si>
   <si>
     <t xml:space="preserve">1.55293428897858</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">1.55466175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60648393630981</t>
+    <t xml:space="preserve">1.60648381710052</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475647449493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58230018615723</t>
+    <t xml:space="preserve">1.58230030536652</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057284355164</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">1.4665641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45447242259979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510652542114</t>
+    <t xml:space="preserve">1.45447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510664463043</t>
   </si>
   <si>
     <t xml:space="preserve">1.43547093868256</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">1.33009946346283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3801943063736</t>
+    <t xml:space="preserve">1.38019418716431</t>
   </si>
   <si>
     <t xml:space="preserve">1.35082840919495</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">1.2005443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22300064563751</t>
+    <t xml:space="preserve">1.22300052642822</t>
   </si>
   <si>
     <t xml:space="preserve">1.1884526014328</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">1.35773801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39574074745178</t>
+    <t xml:space="preserve">1.39574086666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.39746820926666</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44929027557373</t>
+    <t xml:space="preserve">1.44929015636444</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992437839508</t>
+    <t xml:space="preserve">1.41992449760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301488876343</t>
+    <t xml:space="preserve">1.41301476955414</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710367679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464762687683</t>
+    <t xml:space="preserve">1.38710379600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464750766754</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33182692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591595172882</t>
+    <t xml:space="preserve">1.331827044487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591583251953</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3569,22 +3569,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564614295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937075614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136790752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345954418182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655017375946</t>
+    <t xml:space="preserve">1.34564602375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937063694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827751636505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136778831482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345966339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655005455017</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036927223206</t>
+    <t xml:space="preserve">1.29036915302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910094738007</t>
+    <t xml:space="preserve">1.34910106658936</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938476085663</t>
+    <t xml:space="preserve">1.49938488006592</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838624477386</t>
+    <t xml:space="preserve">1.51838636398315</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974929332733</t>
+    <t xml:space="preserve">1.50974941253662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41819703578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729312419891</t>
+    <t xml:space="preserve">1.4181969165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729300498962</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302889347076</t>
+    <t xml:space="preserve">1.60302901268005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62894010543823</t>
+    <t xml:space="preserve">1.62893998622894</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63239479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093725681305</t>
+    <t xml:space="preserve">1.6323949098587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093713760376</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548530101776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5719358921051</t>
+    <t xml:space="preserve">1.62548518180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57193577289581</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -13601,7 +13601,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="s">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13627,7 +13627,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G332" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13653,7 +13653,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13705,7 +13705,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G335" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13731,7 +13731,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13783,7 +13783,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13809,7 +13809,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G339" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13861,7 +13861,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13887,7 +13887,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13913,7 +13913,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13939,7 +13939,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13965,7 +13965,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13991,7 +13991,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14017,7 +14017,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G347" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14043,7 +14043,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14069,7 +14069,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14095,7 +14095,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14147,7 +14147,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14173,7 +14173,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14225,7 +14225,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G355" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14251,7 +14251,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14277,7 +14277,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G357" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14303,7 +14303,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14329,7 +14329,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G359" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14355,7 +14355,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14381,7 +14381,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14407,7 +14407,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G362" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14433,7 +14433,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14459,7 +14459,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14485,7 +14485,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14511,7 +14511,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14537,7 +14537,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14563,7 +14563,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14589,7 +14589,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14615,7 +14615,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14641,7 +14641,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G371" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14667,7 +14667,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G372" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14693,7 +14693,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G373" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14719,7 +14719,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G374" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14745,7 +14745,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14771,7 +14771,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G376" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14797,7 +14797,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G377" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14823,7 +14823,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14849,7 +14849,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G379" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14875,7 +14875,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G380" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14901,7 +14901,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G381" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14927,7 +14927,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14953,7 +14953,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14979,7 +14979,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15005,7 +15005,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G385" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15031,7 +15031,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15057,7 +15057,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15083,7 +15083,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G388" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15109,7 +15109,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15135,7 +15135,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G390" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15161,7 +15161,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G391" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15187,7 +15187,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15213,7 +15213,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G393" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15239,7 +15239,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G394" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15265,7 +15265,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15291,7 +15291,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G396" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15317,7 +15317,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G397" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15343,7 +15343,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G398" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15369,7 +15369,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G399" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15395,7 +15395,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15421,7 +15421,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G401" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15447,7 +15447,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15473,7 +15473,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G403" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15499,7 +15499,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15525,7 +15525,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15551,7 +15551,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15577,7 +15577,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G407" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15603,7 +15603,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G408" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15629,7 +15629,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G409" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15655,7 +15655,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G410" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15681,7 +15681,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15707,7 +15707,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15733,7 +15733,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15759,7 +15759,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15785,7 +15785,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15811,7 +15811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15837,7 +15837,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15863,7 +15863,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15889,7 +15889,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15915,7 +15915,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G420" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15941,7 +15941,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15967,7 +15967,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15993,7 +15993,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G423" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16019,7 +16019,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G424" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16045,7 +16045,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G425" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16071,7 +16071,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G426" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16097,7 +16097,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G427" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16123,7 +16123,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G428" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16149,7 +16149,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16175,7 +16175,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16201,7 +16201,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G431" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16227,7 +16227,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16253,7 +16253,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16279,7 +16279,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16305,7 +16305,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16331,7 +16331,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16357,7 +16357,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G437" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16383,7 +16383,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G438" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16409,7 +16409,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16435,7 +16435,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G440" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16461,7 +16461,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16487,7 +16487,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16513,7 +16513,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16539,7 +16539,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16565,7 +16565,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16591,7 +16591,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16617,7 +16617,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16643,7 +16643,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16669,7 +16669,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16695,7 +16695,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16721,7 +16721,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16747,7 +16747,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16773,7 +16773,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16799,7 +16799,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16825,7 +16825,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16851,7 +16851,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G456" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16877,7 +16877,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16903,7 +16903,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G458" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16929,7 +16929,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G459" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16955,7 +16955,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16981,7 +16981,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17007,7 +17007,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G462" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17033,7 +17033,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17059,7 +17059,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17085,7 +17085,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G465" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17111,7 +17111,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17137,7 +17137,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17163,7 +17163,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17189,7 +17189,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17215,7 +17215,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17241,7 +17241,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17267,7 +17267,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17293,7 +17293,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17319,7 +17319,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G474" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17345,7 +17345,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17371,7 +17371,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17397,7 +17397,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17423,7 +17423,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17449,7 +17449,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17475,7 +17475,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17501,7 +17501,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17527,7 +17527,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G482" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17553,7 +17553,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17579,7 +17579,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17605,7 +17605,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G485" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17631,7 +17631,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17657,7 +17657,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G487" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17683,7 +17683,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17709,7 +17709,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17735,7 +17735,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G490" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17761,7 +17761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17787,7 +17787,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17813,7 +17813,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17839,7 +17839,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G494" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17865,7 +17865,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G495" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17891,7 +17891,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G496" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17917,7 +17917,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G497" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17943,7 +17943,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17969,7 +17969,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17995,7 +17995,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18021,7 +18021,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18047,7 +18047,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18073,7 +18073,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18099,7 +18099,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18125,7 +18125,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18151,7 +18151,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18177,7 +18177,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18203,7 +18203,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18229,7 +18229,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18255,7 +18255,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18281,7 +18281,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G511" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18307,7 +18307,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G512" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18333,7 +18333,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18359,7 +18359,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18385,7 +18385,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18411,7 +18411,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18437,7 +18437,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18463,7 +18463,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18489,7 +18489,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18515,7 +18515,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18541,7 +18541,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18567,7 +18567,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G522" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18593,7 +18593,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18619,7 +18619,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18645,7 +18645,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18671,7 +18671,7 @@
         <v>3.875</v>
       </c>
       <c r="G526" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18697,7 +18697,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18723,7 +18723,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G528" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18749,7 +18749,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G529" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18775,7 +18775,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G530" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18801,7 +18801,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G531" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18827,7 +18827,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18853,7 +18853,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18879,7 +18879,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G534" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18905,7 +18905,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18931,7 +18931,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18957,7 +18957,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18983,7 +18983,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19009,7 +19009,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G539" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19035,7 +19035,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19061,7 +19061,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G541" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19087,7 +19087,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19113,7 +19113,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19139,7 +19139,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19165,7 +19165,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19191,7 +19191,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G546" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19217,7 +19217,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19243,7 +19243,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G548" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19269,7 +19269,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19295,7 +19295,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G550" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19321,7 +19321,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G551" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19347,7 +19347,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19373,7 +19373,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G553" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19399,7 +19399,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19425,7 +19425,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G555" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19451,7 +19451,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G556" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19477,7 +19477,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G557" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19503,7 +19503,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G558" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19529,7 +19529,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G559" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19555,7 +19555,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19581,7 +19581,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19607,7 +19607,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19633,7 +19633,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19659,7 +19659,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G564" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19685,7 +19685,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19711,7 +19711,7 @@
         <v>3.5</v>
       </c>
       <c r="G566" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19737,7 +19737,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19763,7 +19763,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19789,7 +19789,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19815,7 +19815,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19841,7 +19841,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19867,7 +19867,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19893,7 +19893,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19919,7 +19919,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19945,7 +19945,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19971,7 +19971,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19997,7 +19997,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20023,7 +20023,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20049,7 +20049,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G579" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20075,7 +20075,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20101,7 +20101,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20127,7 +20127,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20153,7 +20153,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20179,7 +20179,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20205,7 +20205,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20231,7 +20231,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G586" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20257,7 +20257,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20283,7 +20283,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20309,7 +20309,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G589" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20335,7 +20335,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20361,7 +20361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20387,7 +20387,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20413,7 +20413,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G593" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20439,7 +20439,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20465,7 +20465,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20491,7 +20491,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20517,7 +20517,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20543,7 +20543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20569,7 +20569,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20595,7 +20595,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20621,7 +20621,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20647,7 +20647,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20673,7 +20673,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20699,7 +20699,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20725,7 +20725,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20751,7 +20751,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20777,7 +20777,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20803,7 +20803,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20829,7 +20829,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20855,7 +20855,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20881,7 +20881,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20907,7 +20907,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20933,7 +20933,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20959,7 +20959,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20985,7 +20985,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G615" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21011,7 +21011,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21037,7 +21037,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21063,7 +21063,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G618" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21089,7 +21089,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21115,7 +21115,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21141,7 +21141,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21167,7 +21167,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G622" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21193,7 +21193,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21219,7 +21219,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21245,7 +21245,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G625" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21271,7 +21271,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21297,7 +21297,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G627" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21323,7 +21323,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21349,7 +21349,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21375,7 +21375,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G630" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21401,7 +21401,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21427,7 +21427,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21453,7 +21453,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21479,7 +21479,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21505,7 +21505,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G635" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21531,7 +21531,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21557,7 +21557,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G637" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21583,7 +21583,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21609,7 +21609,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G639" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21635,7 +21635,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21661,7 +21661,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21687,7 +21687,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21713,7 +21713,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21739,7 +21739,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21765,7 +21765,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G645" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21791,7 +21791,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21817,7 +21817,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G647" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21843,7 +21843,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21869,7 +21869,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G649" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21895,7 +21895,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21921,7 +21921,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21947,7 +21947,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21973,7 +21973,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21999,7 +21999,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G654" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22025,7 +22025,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22051,7 +22051,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G656" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22077,7 +22077,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22103,7 +22103,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G658" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22129,7 +22129,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22155,7 +22155,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22181,7 +22181,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22207,7 +22207,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22233,7 +22233,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22259,7 +22259,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G664" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22285,7 +22285,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G665" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22311,7 +22311,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22337,7 +22337,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22363,7 +22363,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22389,7 +22389,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G669" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22415,7 +22415,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G670" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22441,7 +22441,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22467,7 +22467,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G672" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22493,7 +22493,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22519,7 +22519,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22545,7 +22545,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22571,7 +22571,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G676" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22597,7 +22597,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G677" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22623,7 +22623,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22649,7 +22649,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22675,7 +22675,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22701,7 +22701,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22727,7 +22727,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G682" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22753,7 +22753,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22779,7 +22779,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22805,7 +22805,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G685" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22831,7 +22831,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22857,7 +22857,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22883,7 +22883,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22909,7 +22909,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G689" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22935,7 +22935,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22961,7 +22961,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22987,7 +22987,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23013,7 +23013,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G693" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23039,7 +23039,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23065,7 +23065,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23091,7 +23091,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23117,7 +23117,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23143,7 +23143,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23169,7 +23169,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G699" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23195,7 +23195,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G700" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23221,7 +23221,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23247,7 +23247,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23273,7 +23273,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23299,7 +23299,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23325,7 +23325,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G705" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23351,7 +23351,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23377,7 +23377,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G707" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23403,7 +23403,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23429,7 +23429,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23455,7 +23455,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23481,7 +23481,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23507,7 +23507,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G712" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23533,7 +23533,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23559,7 +23559,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23585,7 +23585,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G715" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23611,7 +23611,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23637,7 +23637,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23663,7 +23663,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23689,7 +23689,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23715,7 +23715,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23741,7 +23741,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23767,7 +23767,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23793,7 +23793,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23819,7 +23819,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23845,7 +23845,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23871,7 +23871,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23897,7 +23897,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23923,7 +23923,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23949,7 +23949,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23975,7 +23975,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24001,7 +24001,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24027,7 +24027,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G732" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24053,7 +24053,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G733" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24079,7 +24079,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24105,7 +24105,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G735" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24131,7 +24131,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24157,7 +24157,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G737" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24183,7 +24183,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24209,7 +24209,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24235,7 +24235,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24261,7 +24261,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24287,7 +24287,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G742" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24313,7 +24313,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G743" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24339,7 +24339,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G744" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24365,7 +24365,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G745" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24391,7 +24391,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24417,7 +24417,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24443,7 +24443,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24469,7 +24469,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G749" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24495,7 +24495,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24521,7 +24521,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24547,7 +24547,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G752" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24573,7 +24573,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G753" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24599,7 +24599,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24625,7 +24625,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G755" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24651,7 +24651,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24677,7 +24677,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G757" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24703,7 +24703,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24729,7 +24729,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24755,7 +24755,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24781,7 +24781,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24807,7 +24807,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24833,7 +24833,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G763" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24859,7 +24859,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24885,7 +24885,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24911,7 +24911,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G766" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24937,7 +24937,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G767" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24963,7 +24963,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G768" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24989,7 +24989,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25015,7 +25015,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25041,7 +25041,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25067,7 +25067,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25093,7 +25093,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25119,7 +25119,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25145,7 +25145,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25171,7 +25171,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25197,7 +25197,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25223,7 +25223,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25249,7 +25249,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25275,7 +25275,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25301,7 +25301,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25327,7 +25327,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25353,7 +25353,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25379,7 +25379,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25405,7 +25405,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25431,7 +25431,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25457,7 +25457,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25483,7 +25483,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G788" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25509,7 +25509,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25535,7 +25535,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25561,7 +25561,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G791" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25587,7 +25587,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G792" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25613,7 +25613,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25639,7 +25639,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G794" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25665,7 +25665,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25691,7 +25691,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25717,7 +25717,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25743,7 +25743,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25769,7 +25769,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25795,7 +25795,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G800" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25821,7 +25821,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G801" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25847,7 +25847,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25873,7 +25873,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25899,7 +25899,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25925,7 +25925,7 @@
         <v>4</v>
       </c>
       <c r="G805" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25951,7 +25951,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25977,7 +25977,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26003,7 +26003,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G808" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26029,7 +26029,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G809" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26055,7 +26055,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26081,7 +26081,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26107,7 +26107,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26133,7 +26133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26159,7 +26159,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26185,7 +26185,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G815" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26211,7 +26211,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26237,7 +26237,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26263,7 +26263,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26289,7 +26289,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26315,7 +26315,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26341,7 +26341,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G821" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26367,7 +26367,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26393,7 +26393,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26419,7 +26419,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26445,7 +26445,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26471,7 +26471,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26497,7 +26497,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26523,7 +26523,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26549,7 +26549,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26575,7 +26575,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G830" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26601,7 +26601,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G831" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26627,7 +26627,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G832" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26653,7 +26653,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G833" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26679,7 +26679,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26705,7 +26705,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26731,7 +26731,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26757,7 +26757,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26783,7 +26783,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26809,7 +26809,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26835,7 +26835,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26861,7 +26861,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26887,7 +26887,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G842" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26913,7 +26913,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26939,7 +26939,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26965,7 +26965,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26991,7 +26991,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27017,7 +27017,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="s">
-        <v>609</v>
+        <v>43</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27095,7 +27095,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G850" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27225,7 +27225,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G855" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27251,7 +27251,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27277,7 +27277,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27329,7 +27329,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27407,7 +27407,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27485,7 +27485,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27745,7 +27745,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28395,7 +28395,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -70861,7 +70861,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6911805556</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>131288</v>
@@ -70882,6 +70882,32 @@
         <v>1469</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6911805556</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>156739</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>2.64499998092651</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>2.65499997138977</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">3.08614468574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01786732673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690105438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98099708557129</t>
+    <t xml:space="preserve">3.01786756515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690057754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98099732398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.88131165504456</t>
@@ -62,67 +62,67 @@
     <t xml:space="preserve">2.94003105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86082887649536</t>
+    <t xml:space="preserve">2.80620694160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86082863807678</t>
   </si>
   <si>
     <t xml:space="preserve">2.7584125995636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73929500579834</t>
+    <t xml:space="preserve">2.73929476737976</t>
   </si>
   <si>
     <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71744585037231</t>
+    <t xml:space="preserve">2.71744608879089</t>
   </si>
   <si>
     <t xml:space="preserve">2.866290807724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76387453079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7447566986084</t>
+    <t xml:space="preserve">2.76387476921082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74475693702698</t>
   </si>
   <si>
     <t xml:space="preserve">2.75704717636108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.710618019104</t>
+    <t xml:space="preserve">2.71061825752258</t>
   </si>
   <si>
     <t xml:space="preserve">2.73110151290894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76114368438721</t>
+    <t xml:space="preserve">2.76114344596863</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69696283340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72290754318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62868499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935702323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45799112319946</t>
+    <t xml:space="preserve">2.69696259498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72290802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62868475914001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.30095291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38971376419067</t>
+    <t xml:space="preserve">2.38971400260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.53992438316345</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">2.50442004203796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67511391639709</t>
+    <t xml:space="preserve">2.67511367797852</t>
   </si>
   <si>
     <t xml:space="preserve">2.81713104248047</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">2.68467259407043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8621940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83351802825928</t>
+    <t xml:space="preserve">2.86219382286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83351755142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.84717297554016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88404297828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540863990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769864082336</t>
+    <t xml:space="preserve">2.88404321670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769840240479</t>
   </si>
   <si>
     <t xml:space="preserve">2.85126972198486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94685864448547</t>
+    <t xml:space="preserve">2.94685840606689</t>
   </si>
   <si>
     <t xml:space="preserve">2.9495894908905</t>
@@ -176,25 +176,25 @@
     <t xml:space="preserve">3.05883359909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12164926528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1612503528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173313140869</t>
+    <t xml:space="preserve">3.12164878845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16125011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173289299011</t>
   </si>
   <si>
     <t xml:space="preserve">3.20767879486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900252342224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635506629944</t>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217421531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635530471802</t>
   </si>
   <si>
     <t xml:space="preserve">3.25001072883606</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">3.21040987968445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22269940376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089337348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952771186829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895939826965</t>
+    <t xml:space="preserve">3.2226996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089289665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952723503113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076638221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
   </si>
   <si>
     <t xml:space="preserve">3.22543096542358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29234290122986</t>
+    <t xml:space="preserve">3.29234266281128</t>
   </si>
   <si>
     <t xml:space="preserve">3.21587181091309</t>
@@ -230,70 +230,70 @@
     <t xml:space="preserve">3.30463290214539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2773220539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559941291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608195304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704917907715</t>
+    <t xml:space="preserve">3.27732157707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559893608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608266830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
   </si>
   <si>
     <t xml:space="preserve">3.38656568527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33330941200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
+    <t xml:space="preserve">3.33330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833073616028</t>
   </si>
   <si>
     <t xml:space="preserve">3.32511591911316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32375049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780507087708</t>
+    <t xml:space="preserve">3.32375073432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2978048324585</t>
   </si>
   <si>
     <t xml:space="preserve">3.26366662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29097723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182634353638</t>
+    <t xml:space="preserve">3.29097747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022243499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182658195496</t>
   </si>
   <si>
     <t xml:space="preserve">3.1562032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13482975959778</t>
+    <t xml:space="preserve">3.1348295211792</t>
   </si>
   <si>
     <t xml:space="preserve">3.17330241203308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09208250045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291913032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856748580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33431911468506</t>
+    <t xml:space="preserve">3.09208202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3229193687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856796264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3343186378479</t>
   </si>
   <si>
     <t xml:space="preserve">3.31151986122131</t>
@@ -302,82 +302,82 @@
     <t xml:space="preserve">3.38419079780579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44403743743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981434822083</t>
+    <t xml:space="preserve">3.44403767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981410980225</t>
   </si>
   <si>
     <t xml:space="preserve">3.43406319618225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48108553886414</t>
+    <t xml:space="preserve">3.48108601570129</t>
   </si>
   <si>
     <t xml:space="preserve">3.47681093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4383385181427</t>
+    <t xml:space="preserve">3.43833875656128</t>
   </si>
   <si>
     <t xml:space="preserve">3.45116209983826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40841388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796030044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246506690979</t>
+    <t xml:space="preserve">3.40841460227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714293479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796053886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246530532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.8997175693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89686751365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195442199707</t>
+    <t xml:space="preserve">2.89686727523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495759963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195418357849</t>
   </si>
   <si>
     <t xml:space="preserve">3.02938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84984517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500816345215</t>
+    <t xml:space="preserve">2.84984540939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671439170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500887870789</t>
   </si>
   <si>
     <t xml:space="preserve">3.16332793235779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9652636051178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528888702393</t>
+    <t xml:space="preserve">2.96526408195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9552891254425</t>
   </si>
   <si>
     <t xml:space="preserve">2.9923369884491</t>
@@ -389,16 +389,13 @@
     <t xml:space="preserve">3.1704523563385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757725715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13625454902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94958925247192</t>
+    <t xml:space="preserve">3.23599886894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625431060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.83702087402344</t>
@@ -407,28 +404,28 @@
     <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86551928520203</t>
+    <t xml:space="preserve">2.86551904678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.90399217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84129500389099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549328804016</t>
+    <t xml:space="preserve">2.84129524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549376487732</t>
   </si>
   <si>
     <t xml:space="preserve">2.83559584617615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854798316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73442649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77717399597168</t>
+    <t xml:space="preserve">2.79854774475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442625999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771737575531</t>
   </si>
   <si>
     <t xml:space="preserve">2.88546824455261</t>
@@ -440,16 +437,16 @@
     <t xml:space="preserve">2.84272050857544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87834358215332</t>
+    <t xml:space="preserve">2.87834334373474</t>
   </si>
   <si>
     <t xml:space="preserve">2.92821574211121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94103980064392</t>
+    <t xml:space="preserve">2.92109084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94103956222534</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694431304932</t>
@@ -458,22 +455,22 @@
     <t xml:space="preserve">2.85839486122131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86409401893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707191467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007485389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80567240715027</t>
+    <t xml:space="preserve">2.86409425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707215309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007509231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80567264556885</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289938926697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7586498260498</t>
+    <t xml:space="preserve">2.75865006446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.77859902381897</t>
@@ -485,79 +482,79 @@
     <t xml:space="preserve">2.62470722198486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59478378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54776167869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605545043945</t>
+    <t xml:space="preserve">2.59478402137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5477614402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480954170227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605568885803</t>
   </si>
   <si>
     <t xml:space="preserve">2.65463066101074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63610672950745</t>
+    <t xml:space="preserve">2.63610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60333323478699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5719850063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45086646080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44516706466675</t>
+    <t xml:space="preserve">2.57198476791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45086693763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44516682624817</t>
   </si>
   <si>
     <t xml:space="preserve">2.42379331588745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44374203681946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666865348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941615104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900734901428</t>
+    <t xml:space="preserve">2.44374227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41666889190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900758743286</t>
   </si>
   <si>
     <t xml:space="preserve">2.61045837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54918622970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57910990715027</t>
+    <t xml:space="preserve">2.54918646812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57910966873169</t>
   </si>
   <si>
     <t xml:space="preserve">2.5506112575531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52353763580322</t>
+    <t xml:space="preserve">2.52353811264038</t>
   </si>
   <si>
     <t xml:space="preserve">2.57341003417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6931037902832</t>
+    <t xml:space="preserve">2.64465618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69310355186462</t>
   </si>
   <si>
     <t xml:space="preserve">2.64038157463074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63895654678345</t>
+    <t xml:space="preserve">2.63895630836487</t>
   </si>
   <si>
     <t xml:space="preserve">2.62898182868958</t>
@@ -566,7 +563,7 @@
     <t xml:space="preserve">2.63325715065002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67172980308533</t>
+    <t xml:space="preserve">2.67172956466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.74867558479309</t>
@@ -575,37 +572,37 @@
     <t xml:space="preserve">2.73727607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67315435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71447730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735263824463</t>
+    <t xml:space="preserve">2.67315459251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70307779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71447706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735287666321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65178084373474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66887998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65748023986816</t>
+    <t xml:space="preserve">2.66887974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65748047828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.56486034393311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52211284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498794555664</t>
+    <t xml:space="preserve">2.52211260795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498818397522</t>
   </si>
   <si>
     <t xml:space="preserve">2.41524386405945</t>
@@ -617,58 +614,58 @@
     <t xml:space="preserve">2.43661761283875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39386940002441</t>
+    <t xml:space="preserve">2.39386987686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.39244484901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3511221408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236828804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53066253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57768487930298</t>
+    <t xml:space="preserve">2.45799160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35112237930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53066229820251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5776846408844</t>
   </si>
   <si>
     <t xml:space="preserve">2.58908438682556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69595336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68027949333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69167876243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69737815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012565612793</t>
+    <t xml:space="preserve">2.63468194007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6959536075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68027925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69167852401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69737839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012589454651</t>
   </si>
   <si>
     <t xml:space="preserve">2.74297571182251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72445178031921</t>
+    <t xml:space="preserve">2.72445154190063</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7287266254425</t>
+    <t xml:space="preserve">2.72872638702393</t>
   </si>
   <si>
     <t xml:space="preserve">2.76434969902039</t>
@@ -677,16 +674,16 @@
     <t xml:space="preserve">2.75152540206909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75580024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71162748336792</t>
+    <t xml:space="preserve">2.7558000087738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71162724494934</t>
   </si>
   <si>
     <t xml:space="preserve">2.6902539730072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035581588745</t>
+    <t xml:space="preserve">2.65035605430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.60760831832886</t>
@@ -701,43 +698,43 @@
     <t xml:space="preserve">2.5206880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60618305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5449116230011</t>
+    <t xml:space="preserve">2.60618329048157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058573722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54491138458252</t>
   </si>
   <si>
     <t xml:space="preserve">2.54063677787781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501346588135</t>
+    <t xml:space="preserve">2.50501394271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.49788928031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50643873214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53351211547852</t>
+    <t xml:space="preserve">2.50643849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53351235389709</t>
   </si>
   <si>
     <t xml:space="preserve">2.57625985145569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60048365592957</t>
+    <t xml:space="preserve">2.60048413276672</t>
   </si>
   <si>
     <t xml:space="preserve">2.59193396568298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58195996284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5591607093811</t>
+    <t xml:space="preserve">2.58195948600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55916094779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.58623433113098</t>
@@ -749,13 +746,13 @@
     <t xml:space="preserve">2.48506474494934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54348659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6874041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69452857971191</t>
+    <t xml:space="preserve">2.54348707199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68740391731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69452834129333</t>
   </si>
   <si>
     <t xml:space="preserve">2.75722503662109</t>
@@ -764,10 +761,10 @@
     <t xml:space="preserve">2.77147436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79712271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78857374191284</t>
+    <t xml:space="preserve">2.79712295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7885730266571</t>
   </si>
   <si>
     <t xml:space="preserve">2.79997277259827</t>
@@ -776,19 +773,19 @@
     <t xml:space="preserve">2.83132100105286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90541696548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03508520126343</t>
+    <t xml:space="preserve">2.9054172039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03508496284485</t>
   </si>
   <si>
     <t xml:space="preserve">3.06215810775757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15477824211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727077484131</t>
+    <t xml:space="preserve">3.15477848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727053642273</t>
   </si>
   <si>
     <t xml:space="preserve">3.25737309455872</t>
@@ -797,22 +794,22 @@
     <t xml:space="preserve">3.07783246040344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1676025390625</t>
+    <t xml:space="preserve">3.16760277748108</t>
   </si>
   <si>
     <t xml:space="preserve">3.16190314292908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16047811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21889972686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174954414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589654922485</t>
+    <t xml:space="preserve">3.16047835350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21889996528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589702606201</t>
   </si>
   <si>
     <t xml:space="preserve">3.28159642219543</t>
@@ -824,28 +821,31 @@
     <t xml:space="preserve">3.23172426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12912964820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19610142707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19752597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884892463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602486610413</t>
+    <t xml:space="preserve">3.17900204658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12913036346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19610118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10063147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1975257396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602438926697</t>
   </si>
   <si>
     <t xml:space="preserve">3.29157114028931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32576894760132</t>
+    <t xml:space="preserve">3.3257691860199</t>
   </si>
   <si>
     <t xml:space="preserve">3.28302145004272</t>
@@ -857,25 +857,25 @@
     <t xml:space="preserve">3.34001851081848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39559054374695</t>
+    <t xml:space="preserve">3.39559006690979</t>
   </si>
   <si>
     <t xml:space="preserve">3.3556923866272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23457384109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27019715309143</t>
+    <t xml:space="preserve">3.23457407951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27019762992859</t>
   </si>
   <si>
     <t xml:space="preserve">3.08923196792603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06358337402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17489004135132</t>
+    <t xml:space="preserve">3.06358361244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
     <t xml:space="preserve">3.0970664024353</t>
@@ -884,64 +884,64 @@
     <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13886070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462542533875</t>
+    <t xml:space="preserve">3.13886046409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">3.11003732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11868405342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07112598419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03797888755798</t>
+    <t xml:space="preserve">3.1186842918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07112574577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0379786491394</t>
   </si>
   <si>
     <t xml:space="preserve">3.04806733131409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99762630462646</t>
+    <t xml:space="preserve">2.99762606620789</t>
   </si>
   <si>
     <t xml:space="preserve">3.00627303123474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97744989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91836214065552</t>
+    <t xml:space="preserve">2.97744965553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9183623790741</t>
   </si>
   <si>
     <t xml:space="preserve">2.8722448348999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90395069122314</t>
+    <t xml:space="preserve">2.90395045280457</t>
   </si>
   <si>
     <t xml:space="preserve">2.89098024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87512707710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92700910568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90683269500732</t>
+    <t xml:space="preserve">2.87512731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92700886726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9068329334259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86936259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.878009557724</t>
+    <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.85783314704895</t>
@@ -953,43 +953,43 @@
     <t xml:space="preserve">2.87080359458923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82468628883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79298067092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76415729522705</t>
+    <t xml:space="preserve">2.8246865272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79298043251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76415753364563</t>
   </si>
   <si>
     <t xml:space="preserve">2.81027483940125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80018663406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79153943061829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72956943511963</t>
+    <t xml:space="preserve">2.80018639564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79153966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72956919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.75262808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75983381271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74686360359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95439147949219</t>
+    <t xml:space="preserve">2.75983357429504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7468638420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95439100265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.92124462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92845058441162</t>
+    <t xml:space="preserve">2.92845034599304</t>
   </si>
   <si>
     <t xml:space="preserve">2.92556810379028</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">2.83189225196838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84342169761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80450987815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83045125007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82612752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865694999695</t>
+    <t xml:space="preserve">2.843421459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83045101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82612729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865718841553</t>
   </si>
   <si>
     <t xml:space="preserve">2.80739235877991</t>
@@ -1019,34 +1019,34 @@
     <t xml:space="preserve">2.808833360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84053921699524</t>
+    <t xml:space="preserve">2.84053897857666</t>
   </si>
   <si>
     <t xml:space="preserve">2.85495090484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86503911018372</t>
+    <t xml:space="preserve">2.86503934860229</t>
   </si>
   <si>
     <t xml:space="preserve">2.87656855583191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90827369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83909797668457</t>
+    <t xml:space="preserve">2.90827417373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83909821510315</t>
   </si>
   <si>
     <t xml:space="preserve">2.73821640014648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7555103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7684805393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70218729972839</t>
+    <t xml:space="preserve">2.75551009178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76848077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72668719291687</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">2.71371650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7252459526062</t>
+    <t xml:space="preserve">2.72524571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.68056988716125</t>
@@ -1064,34 +1064,34 @@
     <t xml:space="preserve">2.67480492591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67336392402649</t>
+    <t xml:space="preserve">2.67336416244507</t>
   </si>
   <si>
     <t xml:space="preserve">2.65895199775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67624640464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406908988953</t>
+    <t xml:space="preserve">2.67624616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406932830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79874539375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74542212486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78577494621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92268562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02500820159912</t>
+    <t xml:space="preserve">2.79874563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74542188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78577470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92268586158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0250084400177</t>
   </si>
   <si>
     <t xml:space="preserve">3.02644944190979</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">3.10571360588074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12156653404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17056608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14174318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09850788116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05671405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07689023017883</t>
+    <t xml:space="preserve">3.12156629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17056632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14174294471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09850811958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05671429634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07689046859741</t>
   </si>
   <si>
     <t xml:space="preserve">3.08409667015076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07400751113892</t>
+    <t xml:space="preserve">3.07400798797607</t>
   </si>
   <si>
     <t xml:space="preserve">3.04086089134216</t>
@@ -1136,64 +1136,64 @@
     <t xml:space="preserve">3.05383157730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17921328544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589001655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05527305603027</t>
+    <t xml:space="preserve">3.17921352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589025497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05527281761169</t>
   </si>
   <si>
     <t xml:space="preserve">3.07977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14894866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16191935539246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14750742912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0999493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15903663635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15471291542053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1287727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11580228805542</t>
+    <t xml:space="preserve">3.14894843101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16191911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1475076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09994959831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15903687477112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15471315383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12877225875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11580181121826</t>
   </si>
   <si>
     <t xml:space="preserve">3.10427284240723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12012553215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815529823303</t>
+    <t xml:space="preserve">3.12012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815505981445</t>
   </si>
   <si>
     <t xml:space="preserve">3.00483202934265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9716854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82180380821228</t>
+    <t xml:space="preserve">2.97168564796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78433394432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82180404663086</t>
   </si>
   <si>
     <t xml:space="preserve">2.86792135238647</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">2.89674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88233280181885</t>
+    <t xml:space="preserve">2.88233327865601</t>
   </si>
   <si>
     <t xml:space="preserve">2.85062742233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82900977134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82324528694153</t>
+    <t xml:space="preserve">2.82901000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82324504852295</t>
   </si>
   <si>
     <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72236371040344</t>
+    <t xml:space="preserve">2.72236347198486</t>
   </si>
   <si>
     <t xml:space="preserve">2.70506954193115</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">2.71227526664734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65606999397278</t>
+    <t xml:space="preserve">2.65607023239136</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.76703977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78505444526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740769386292</t>
+    <t xml:space="preserve">2.78505420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740745544434</t>
   </si>
   <si>
     <t xml:space="preserve">2.69498133659363</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.72020173072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79225993156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84630393981934</t>
+    <t xml:space="preserve">2.79226040840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84630370140076</t>
   </si>
   <si>
     <t xml:space="preserve">2.77424550056458</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">2.77064275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70939302444458</t>
+    <t xml:space="preserve">2.709392786026</t>
   </si>
   <si>
     <t xml:space="preserve">2.74181938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71299600601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63373160362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652587890625</t>
+    <t xml:space="preserve">2.71299576759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63373184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652611732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.6409375667572</t>
@@ -1289,58 +1289,58 @@
     <t xml:space="preserve">2.65534901618958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64814329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5868935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248210906982</t>
+    <t xml:space="preserve">2.64814352989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689379692078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248258590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.57968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55807065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56167364120483</t>
+    <t xml:space="preserve">2.55807042121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56167340278625</t>
   </si>
   <si>
     <t xml:space="preserve">2.55086445808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56887912750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43557143211365</t>
+    <t xml:space="preserve">2.56887936592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43557167053223</t>
   </si>
   <si>
     <t xml:space="preserve">2.37432169914246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30946946144104</t>
+    <t xml:space="preserve">2.30946922302246</t>
   </si>
   <si>
     <t xml:space="preserve">2.39593935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41755700111389</t>
+    <t xml:space="preserve">2.41755676269531</t>
   </si>
   <si>
     <t xml:space="preserve">2.41395378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991048812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4499831199646</t>
+    <t xml:space="preserve">2.36351323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44998335838318</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">2.52204155921936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42836570739746</t>
+    <t xml:space="preserve">2.42836546897888</t>
   </si>
   <si>
     <t xml:space="preserve">2.44638013839722</t>
@@ -1361,46 +1361,46 @@
     <t xml:space="preserve">2.50762963294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59409976005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56527614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63012886047363</t>
+    <t xml:space="preserve">2.59409952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56527638435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63012933731079</t>
   </si>
   <si>
     <t xml:space="preserve">2.65174627304077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62292289733887</t>
+    <t xml:space="preserve">2.62292313575745</t>
   </si>
   <si>
     <t xml:space="preserve">2.60130524635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60851144790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63733458518982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68417263031006</t>
+    <t xml:space="preserve">2.60851120948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6373348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68417239189148</t>
   </si>
   <si>
     <t xml:space="preserve">2.66615796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69137835502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67696690559387</t>
+    <t xml:space="preserve">2.69137859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67696666717529</t>
   </si>
   <si>
     <t xml:space="preserve">2.73281216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172174453735</t>
+    <t xml:space="preserve">2.62172198295593</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.48841404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40324521064758</t>
+    <t xml:space="preserve">2.403244972229</t>
   </si>
   <si>
     <t xml:space="preserve">2.43657207489014</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">2.29956126213074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21068954467773</t>
+    <t xml:space="preserve">2.21068906784058</t>
   </si>
   <si>
     <t xml:space="preserve">2.32548236846924</t>
@@ -1442,19 +1442,19 @@
     <t xml:space="preserve">2.38843321800232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42916631698608</t>
+    <t xml:space="preserve">2.4291660785675</t>
   </si>
   <si>
     <t xml:space="preserve">2.41805720329285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989917755127</t>
+    <t xml:space="preserve">2.46989941596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.5032262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52174091339111</t>
+    <t xml:space="preserve">2.52174115180969</t>
   </si>
   <si>
     <t xml:space="preserve">2.53285002708435</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5254442691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45508718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58098912239075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395914077759</t>
+    <t xml:space="preserve">2.52544403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45508694648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58098888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395890235901</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
@@ -1487,19 +1487,19 @@
     <t xml:space="preserve">2.4773051738739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51433515548706</t>
+    <t xml:space="preserve">2.51433491706848</t>
   </si>
   <si>
     <t xml:space="preserve">2.48100805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46619582176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39583921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41065144538879</t>
+    <t xml:space="preserve">2.46619606018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39583897590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41065120697021</t>
   </si>
   <si>
     <t xml:space="preserve">2.35140323638916</t>
@@ -1508,34 +1508,34 @@
     <t xml:space="preserve">2.36621499061584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34399747848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35880899429321</t>
+    <t xml:space="preserve">2.34399724006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35880923271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.35510635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36251258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31067037582397</t>
+    <t xml:space="preserve">2.36251211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30696702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3995418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102698326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41435408592224</t>
+    <t xml:space="preserve">2.39954209327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41435432434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.37362122535706</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">2.31807637214661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29585838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104615211487</t>
+    <t xml:space="preserve">2.29585814476013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104591369629</t>
   </si>
   <si>
     <t xml:space="preserve">2.26993727684021</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">2.30326414108276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32918548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27734351158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2662341594696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29215526580811</t>
+    <t xml:space="preserve">2.32918524742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27734303474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26623439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29215550422668</t>
   </si>
   <si>
     <t xml:space="preserve">2.27364015579224</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">2.2884521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28474926948547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38473033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20698618888855</t>
+    <t xml:space="preserve">2.28474950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20698642730713</t>
   </si>
   <si>
     <t xml:space="preserve">2.24031329154968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15514445304871</t>
+    <t xml:space="preserve">2.15514421463013</t>
   </si>
   <si>
     <t xml:space="preserve">2.13292646408081</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10330247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959959983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849048614502</t>
+    <t xml:space="preserve">2.10330200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849024772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10700535774231</t>
@@ -1610,31 +1610,31 @@
     <t xml:space="preserve">2.06256937980652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98850953578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95147967338562</t>
+    <t xml:space="preserve">1.98850929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95147943496704</t>
   </si>
   <si>
     <t xml:space="preserve">2.02553939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06627225875854</t>
+    <t xml:space="preserve">2.06627249717712</t>
   </si>
   <si>
     <t xml:space="preserve">2.04775762557983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06997561454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922334671021</t>
+    <t xml:space="preserve">2.06997537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922310829163</t>
   </si>
   <si>
     <t xml:space="preserve">2.14403557777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13662958145142</t>
+    <t xml:space="preserve">2.13662934303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.18847131729126</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">2.21439218521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23290729522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512528419495</t>
+    <t xml:space="preserve">2.23290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512552261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.20328330993652</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">2.1995804309845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809530258179</t>
+    <t xml:space="preserve">2.21809506416321</t>
   </si>
   <si>
     <t xml:space="preserve">2.11811423301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07367849349976</t>
+    <t xml:space="preserve">2.07367825508118</t>
   </si>
   <si>
     <t xml:space="preserve">2.11070823669434</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">2.65134596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62542486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71800017356873</t>
+    <t xml:space="preserve">2.62542510032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71799993515015</t>
   </si>
   <si>
     <t xml:space="preserve">2.70318794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72910904884338</t>
+    <t xml:space="preserve">2.7291088104248</t>
   </si>
   <si>
     <t xml:space="preserve">2.69207882881165</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">2.84390187263489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87352585792542</t>
+    <t xml:space="preserve">2.87352609634399</t>
   </si>
   <si>
     <t xml:space="preserve">2.86241674423218</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">2.81427788734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79576301574707</t>
+    <t xml:space="preserve">2.79576277732849</t>
   </si>
   <si>
     <t xml:space="preserve">2.75873279571533</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">2.89574384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90685272216797</t>
+    <t xml:space="preserve">2.90685296058655</t>
   </si>
   <si>
     <t xml:space="preserve">2.88833785057068</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">2.98091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91796207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758558273315</t>
+    <t xml:space="preserve">2.91796159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758582115173</t>
   </si>
   <si>
     <t xml:space="preserve">2.95128870010376</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">2.9364767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95499205589294</t>
+    <t xml:space="preserve">2.95499157905579</t>
   </si>
   <si>
     <t xml:space="preserve">2.93277382850647</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">2.91055583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96980381011963</t>
+    <t xml:space="preserve">2.96980404853821</t>
   </si>
   <si>
     <t xml:space="preserve">2.97720980644226</t>
@@ -1808,31 +1808,31 @@
     <t xml:space="preserve">2.89944672584534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81057524681091</t>
+    <t xml:space="preserve">2.81057500839233</t>
   </si>
   <si>
     <t xml:space="preserve">2.8661196231842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80687165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279299736023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85501074790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71059417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70689058303833</t>
+    <t xml:space="preserve">2.80687189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85501098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71059393882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70689105987549</t>
   </si>
   <si>
     <t xml:space="preserve">2.61061310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64023685455322</t>
+    <t xml:space="preserve">2.6402370929718</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">2.61801910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69578218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68837594985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61431622505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56988024711609</t>
+    <t xml:space="preserve">2.69578194618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6883761882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6143159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56988000869751</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211716651917</t>
@@ -1865,31 +1865,31 @@
     <t xml:space="preserve">2.50692915916443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34770011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23661017417908</t>
+    <t xml:space="preserve">2.34770035743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23661041259766</t>
   </si>
   <si>
     <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587707519531</t>
+    <t xml:space="preserve">2.19587731361389</t>
   </si>
   <si>
     <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21777319908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10882997512817</t>
+    <t xml:space="preserve">2.2177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10883021354675</t>
   </si>
   <si>
     <t xml:space="preserve">2.12439346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0893759727478</t>
+    <t xml:space="preserve">2.08937573432922</t>
   </si>
   <si>
     <t xml:space="preserve">2.10104846954346</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326696395874</t>
+    <t xml:space="preserve">2.09326672554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.12050247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13995695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12828397750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770371437073</t>
+    <t xml:space="preserve">2.13995671272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12828421592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770347595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.05046772956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657673835754</t>
+    <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03490447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435872077942</t>
+    <t xml:space="preserve">2.05435848236084</t>
   </si>
   <si>
     <t xml:space="preserve">2.03101325035095</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944593429565</t>
+    <t xml:space="preserve">2.22944569587708</t>
   </si>
   <si>
     <t xml:space="preserve">2.1866466999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9687602519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00377774238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92985188961029</t>
+    <t xml:space="preserve">1.96876013278961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00377750396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.929851770401</t>
   </si>
   <si>
     <t xml:space="preserve">2.02712249755859</t>
@@ -1958,43 +1958,43 @@
     <t xml:space="preserve">1.94152414798737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84425365924835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79367291927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76643705368042</t>
+    <t xml:space="preserve">1.84425354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79367303848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76643693447113</t>
   </si>
   <si>
     <t xml:space="preserve">1.8092360496521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75087380409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74698281288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69251120090485</t>
+    <t xml:space="preserve">1.75087368488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74698269367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69251108169556</t>
   </si>
   <si>
     <t xml:space="preserve">1.78978180885315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82090854644775</t>
+    <t xml:space="preserve">1.82090842723846</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7430921792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69640219211578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71196556091309</t>
+    <t xml:space="preserve">1.74309206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69640207290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7119654417038</t>
   </si>
   <si>
     <t xml:space="preserve">1.7197470664978</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">1.78589117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141956329346</t>
+    <t xml:space="preserve">1.73141932487488</t>
   </si>
   <si>
     <t xml:space="preserve">1.71585619449615</t>
@@ -2015,79 +2015,79 @@
     <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78200042247772</t>
+    <t xml:space="preserve">1.78200018405914</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80145466327667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84036290645599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85592591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83647203445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8792712688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79756379127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032780647278</t>
+    <t xml:space="preserve">1.80145454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403627872467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85592615604401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83647191524506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87927103042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79756367206573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032792568207</t>
   </si>
   <si>
     <t xml:space="preserve">1.82869029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75476467609406</t>
+    <t xml:space="preserve">1.75476455688477</t>
   </si>
   <si>
     <t xml:space="preserve">1.75865530967712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254630088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80534529685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81701791286469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8247994184494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91428875923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93374264240265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89094352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538015842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89483428001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85981714725494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92207038402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01155948638916</t>
+    <t xml:space="preserve">1.76254618167877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80534517765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81701767444611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82479953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91428864002228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93374252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89094376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538027763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650677680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89483439922333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85981702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92207026481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01155924797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.16719269752502</t>
@@ -2102,22 +2102,22 @@
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217496871948</t>
+    <t xml:space="preserve">2.13217520713806</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19053745269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15552020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17108345031738</t>
+    <t xml:space="preserve">2.19053769111633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15551996231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19831919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1710832118988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14384770393372</t>
@@ -2126,55 +2126,55 @@
     <t xml:space="preserve">2.11272072792053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08548521995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01545023918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15941119194031</t>
+    <t xml:space="preserve">2.08548498153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01545000076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821425437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15941095352173</t>
   </si>
   <si>
     <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01934123039246</t>
+    <t xml:space="preserve">2.01934099197388</t>
   </si>
   <si>
     <t xml:space="preserve">1.87148940563202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91039776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872527122498</t>
+    <t xml:space="preserve">1.91039741039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596089839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872539043427</t>
   </si>
   <si>
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988698959351</t>
+    <t xml:space="preserve">1.99988663196564</t>
   </si>
   <si>
     <t xml:space="preserve">1.95708787441254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96486973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72752869129181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862056732178</t>
+    <t xml:space="preserve">1.96486937999725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210500717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72752857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862044811249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
@@ -2192,34 +2192,34 @@
     <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33844566345215</t>
+    <t xml:space="preserve">1.33844578266144</t>
   </si>
   <si>
     <t xml:space="preserve">1.30420637130737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27619242668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09098887443542</t>
+    <t xml:space="preserve">1.27619230747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09098875522614</t>
   </si>
   <si>
     <t xml:space="preserve">1.16102385520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08009457588196</t>
+    <t xml:space="preserve">1.08009445667267</t>
   </si>
   <si>
     <t xml:space="preserve">1.05986213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0847635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10188317298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22483336925507</t>
+    <t xml:space="preserve">1.08476364612579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10188329219818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22483348846436</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
@@ -2231,46 +2231,46 @@
     <t xml:space="preserve">1.35400903224945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26685440540314</t>
+    <t xml:space="preserve">1.26685428619385</t>
   </si>
   <si>
     <t xml:space="preserve">1.27152335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32288253307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28864312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28397417068481</t>
+    <t xml:space="preserve">1.32288241386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28864300251007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28397393226624</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39291739463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36179065704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062893867493</t>
+    <t xml:space="preserve">1.39291727542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36179053783417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062917709351</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798102378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33688950538635</t>
+    <t xml:space="preserve">1.29798114299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31354427337646</t>
+    <t xml:space="preserve">1.31354439258575</t>
   </si>
   <si>
     <t xml:space="preserve">1.29175567626953</t>
@@ -2282,64 +2282,64 @@
     <t xml:space="preserve">1.22950255870819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23884034156799</t>
+    <t xml:space="preserve">1.23884046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.24350941181183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20927023887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17503070831299</t>
+    <t xml:space="preserve">1.20927011966705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17503082752228</t>
   </si>
   <si>
     <t xml:space="preserve">1.13300979137421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10343945026398</t>
+    <t xml:space="preserve">1.10343956947327</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08631980419159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05674970149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06764388084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12211549282074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10655236244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14234793186188</t>
+    <t xml:space="preserve">1.08631992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05674958229065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06764376163483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12211561203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10655224323273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14234781265259</t>
   </si>
   <si>
     <t xml:space="preserve">1.15012955665588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13923513889313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19837582111359</t>
+    <t xml:space="preserve">1.13923525810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1983757019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.2450658082962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2372841835022</t>
+    <t xml:space="preserve">1.23728406429291</t>
   </si>
   <si>
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708672523499</t>
+    <t xml:space="preserve">1.28708684444427</t>
   </si>
   <si>
     <t xml:space="preserve">1.27930510044098</t>
@@ -2348,22 +2348,22 @@
     <t xml:space="preserve">1.17969989776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16413640975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23572790622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20615744590759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20771372318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18748152256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21082651615143</t>
+    <t xml:space="preserve">1.16413652896881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23572778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2061573266983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20771396160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18748164176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21082639694214</t>
   </si>
   <si>
     <t xml:space="preserve">1.17814350128174</t>
@@ -2372,55 +2372,55 @@
     <t xml:space="preserve">1.18592512607574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612258434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15791118144989</t>
+    <t xml:space="preserve">1.13612246513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1579110622406</t>
   </si>
   <si>
     <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18436884880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17036187648773</t>
+    <t xml:space="preserve">1.18436872959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
     <t xml:space="preserve">1.14546048641205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16724920272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17347455024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15168571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17191815376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16569292545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15635478496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1252281665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.16724908351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1734744310379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15168583393097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17191827297211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1656928062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1563549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12522804737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08320724964142</t>
+    <t xml:space="preserve">1.06608760356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08320713043213</t>
   </si>
   <si>
     <t xml:space="preserve">1.06297492980957</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">1.07075667381287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09721410274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0614185333252</t>
+    <t xml:space="preserve">1.09721422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06141865253448</t>
   </si>
   <si>
     <t xml:space="preserve">1.05052423477173</t>
@@ -2453,22 +2453,22 @@
     <t xml:space="preserve">1.04118621349335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03340446949005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03496098518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03651714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02251017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996052622795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01628482341766</t>
+    <t xml:space="preserve">1.03340458869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03496086597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0365172624588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02251029014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996052503585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01628494262695</t>
   </si>
   <si>
     <t xml:space="preserve">1.00850331783295</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">1.01005959510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00072169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991383671760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966482281684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964925944805145</t>
+    <t xml:space="preserve">1.00072157382965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991383612155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96648234128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9649258852005</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954031586647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975820243358612</t>
+    <t xml:space="preserve">0.954031646251678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
     <t xml:space="preserve">0.989827215671539</t>
@@ -2504,52 +2504,52 @@
     <t xml:space="preserve">0.969595015048981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949362635612488</t>
+    <t xml:space="preserve">0.949362695217133</t>
   </si>
   <si>
     <t xml:space="preserve">0.968038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957144379615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489194393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999165296554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06453132629395</t>
+    <t xml:space="preserve">0.957144320011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999165236949921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06453120708466</t>
   </si>
   <si>
     <t xml:space="preserve">1.05830585956573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02406656742096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988270878791809</t>
+    <t xml:space="preserve">1.02406668663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988270998001099</t>
   </si>
   <si>
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941581010818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93379944562912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904229044914246</t>
+    <t xml:space="preserve">0.941580951213837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93379932641983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904228985309601</t>
   </si>
   <si>
     <t xml:space="preserve">0.879327654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887109339237213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888665616512299</t>
+    <t xml:space="preserve">0.887109279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888665676116943</t>
   </si>
   <si>
     <t xml:space="preserve">0.891778409481049</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">0.835750341415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803067326545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787504076957703</t>
+    <t xml:space="preserve">0.80306738615036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787504136562347</t>
   </si>
   <si>
     <t xml:space="preserve">0.829525053501129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831081390380859</t>
+    <t xml:space="preserve">0.831081330776215</t>
   </si>
   <si>
     <t xml:space="preserve">0.840419411659241</t>
@@ -2579,82 +2579,82 @@
     <t xml:space="preserve">0.817074358463287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86687707901001</t>
+    <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
     <t xml:space="preserve">0.89644730091095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902672648429871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915123343467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940024554729462</t>
+    <t xml:space="preserve">0.902672588825226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915123403072357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940024614334106</t>
   </si>
   <si>
     <t xml:space="preserve">0.977376699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983601987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978933036327362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92913031578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961813151836395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946249961853027</t>
+    <t xml:space="preserve">0.963369727134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983601927757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978932917118073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929130375385284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961813271045685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946250021457672</t>
   </si>
   <si>
     <t xml:space="preserve">0.943137288093567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930686771869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952475309371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927573919296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926017701625824</t>
+    <t xml:space="preserve">0.930686712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952475190162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927573978900909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926017582416534</t>
   </si>
   <si>
     <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971151351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947806417942047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913566946983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341659069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679620742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560034275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918236017227173</t>
+    <t xml:space="preserve">0.971151411533356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792354106903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913567006587982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341718673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679680347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89955997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918235957622528</t>
   </si>
   <si>
     <t xml:space="preserve">0.908898055553436</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">0.894890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910454273223877</t>
+    <t xml:space="preserve">0.910454213619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12989711761475</t>
+    <t xml:space="preserve">1.12989723682404</t>
   </si>
   <si>
     <t xml:space="preserve">1.10032689571381</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">1.07231283187866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12834095954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12055921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11744666099548</t>
+    <t xml:space="preserve">1.12834084033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12055909633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11744654178619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15479850769043</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">1.31198811531067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25907289981842</t>
+    <t xml:space="preserve">1.25907266139984</t>
   </si>
   <si>
     <t xml:space="preserve">1.24662208557129</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">1.22638976573944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23105883598328</t>
+    <t xml:space="preserve">1.23105871677399</t>
   </si>
   <si>
     <t xml:space="preserve">1.2699670791626</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307975292206</t>
+    <t xml:space="preserve">1.27307987213135</t>
   </si>
   <si>
     <t xml:space="preserve">1.36023437976837</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069901943207</t>
+    <t xml:space="preserve">1.40069890022278</t>
   </si>
   <si>
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112867832184</t>
+    <t xml:space="preserve">1.37112879753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">1.39447367191315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3898047208786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3975864648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3913608789444</t>
+    <t xml:space="preserve">1.38980460166931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39758634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39136099815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.40536797046661</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">1.4380509853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52053666114807</t>
+    <t xml:space="preserve">1.52053654193878</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
@@ -2786,19 +2786,19 @@
     <t xml:space="preserve">1.58745884895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53765618801117</t>
+    <t xml:space="preserve">1.53765606880188</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431119441986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497317314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49096632003784</t>
+    <t xml:space="preserve">1.50341689586639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497329235077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49096620082855</t>
   </si>
   <si>
     <t xml:space="preserve">1.51798808574677</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937666416168</t>
+    <t xml:space="preserve">1.48937678337097</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54818880558014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55454695224762</t>
+    <t xml:space="preserve">1.54818868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55454683303833</t>
   </si>
   <si>
     <t xml:space="preserve">1.5561363697052</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">1.56567347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.567263007164</t>
+    <t xml:space="preserve">1.56726312637329</t>
   </si>
   <si>
     <t xml:space="preserve">1.53706228733063</t>
@@ -2852,682 +2852,682 @@
     <t xml:space="preserve">1.47030258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4432806968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40672194957733</t>
+    <t xml:space="preserve">1.44328081607819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40672183036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374371528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44487023353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39241623878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35744678974152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949922561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34790980815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33201467990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929838657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31453001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27638161182404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3018137216568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30499279499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31135094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30340337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2843291759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479195594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22074854373932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22233784198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2557178735733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935984611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25412821769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22710657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21121144294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2732025384903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26366543769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37652099132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36698400974274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35267841815948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3749315738678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37970006465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128960132599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34314131736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33678317070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221539974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.363804936409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39877426624298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897498607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40513241291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49732434749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189211845398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738556861877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4146693944931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42420661449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45917594432831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46076536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41943800449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39082670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33996224403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3415515422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37811064720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35426783561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33042514324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37175250053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33837270736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287913799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116715908051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49573469161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50845086574554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51162993907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50209283828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51321947574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47507107257843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010174274445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4877872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47983968257904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45599687099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301875591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51004040241241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249439716339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63720178604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66501832008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67693960666656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70078253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65309679508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60541141033173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55772590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57362115383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43851208686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645977020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440745353699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45122838020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49414527416229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51639842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61335897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733281612396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322806358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62130653858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349024295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58792674541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60143768787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62925410270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66104435920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53865170478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183077812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52911472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53070402145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43056464195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37334203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30817198753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30022442340851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22869610786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23346471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539447307587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36062598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40831136703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59746384620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7484678030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423178195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76038908958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77231049537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025805950165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74449396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81999599933624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81204843521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83191752433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8279435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178625583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589112758636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986508846283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76833665370941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788205742836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72859871387482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64514923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71667766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73654639720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641548633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436293125153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410075187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7403576374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76195001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75763154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490556240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7533130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67730736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.644486784935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55811655521393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4769287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46483683586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45792722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50456702709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50283980369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865617275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51665902137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48038339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4890204668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47001910209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41128730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3819215297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40092289447784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43028879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4061051607132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501204013824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37328457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34737348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52875065803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59957420825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54775214195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55293428897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466175079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60648393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60475647449493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58230018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58057284355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53047811985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5252959728241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51493144035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49420273303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49765753746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45447242259979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43547093868256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44756281375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4285614490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39228594303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35255575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33873653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3214625120163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32318985462189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31973516941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31628036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31282544136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33009946346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3801943063736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35082840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33355438709259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31800770759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555153846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26791310310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2368198633194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25754857063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2247279882431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23854720592499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2005443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22300064563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1884526014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21954572200775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2610034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28691446781158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32664465904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29382407665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2730952501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35773801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39574074745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39746820926666</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44487023353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39241623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35744690895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34790980815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33201456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585725307465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929850578308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31453001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27638149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30181384086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30499279499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31135094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30340337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479207515717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22074842453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22233808040619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2557178735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935984611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25412821769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28273963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2112113237381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2732025384903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26366543769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37652099132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36698389053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35267841815948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970006465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128972053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34314119815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33678317070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221539974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.363804936409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39877438545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40513241291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53388321399689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49732422828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189199924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738556861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4146693944931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42420661449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45917594432831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46076548099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41943800449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39082670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33996224403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34155166149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37811064720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35426783561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33042514324188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37175250053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33837270736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287913799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050342082977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116703987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49573481082916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50845098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51162981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50209283828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51321947574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47507107257843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010174274445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48778712749481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47983956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45599699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301875591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51004040241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249451637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63720166683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66501832008362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67693948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70078253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65309679508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60541141033173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55772590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57362115383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43851220607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645988941193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4544073343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45122826099396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49414539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61335897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733293533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62130665779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58792674541473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60143768787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62925410270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53865170478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183065891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52911460399628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53070414066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43056464195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37334203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30817174911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30022430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22869598865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23346471786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539447307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36062586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40831136703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59746384620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74846792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423190116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76038908958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77231061458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74449396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81999611854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81204855442047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83191764354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82794368267059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178649425507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589136600494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986520767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.823970079422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628433704376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217970371246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76833665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78820586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859883308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71667754650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436305046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410087108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7403576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71012794971466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76195001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75763165950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75331294536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603904247284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67730736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448666572571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55811655521393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46483683586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45792722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42337930202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50456702709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50283968448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865605354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51665902137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48038351535797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4890204668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48211085796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47001910209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41128730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3819215297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40092301368713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43028879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37328457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34737348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52875077724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59957420825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477522611618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55293428897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60648381710052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60475647449493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58230030536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58057284355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53047811985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5252959728241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51493144035339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49420273303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49765753746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510664463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43547093868256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44756281375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4285614490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39228594303131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35255575180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33873653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3214625120163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32318985462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31973516941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31628036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31282544136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33009946346283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38019418716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35082840919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33355438709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31800770759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555153846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26791310310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2368198633194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25754857063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247279882431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23854720592499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2005443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22300052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1884526014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21954572200775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2610034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28691446781158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30418848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32664465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29382407665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2730952501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35773801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39574086666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39746820926666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44929015636444</t>
+    <t xml:space="preserve">1.44929027557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992449760437</t>
+    <t xml:space="preserve">1.41992437839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301476955414</t>
+    <t xml:space="preserve">1.41301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464750766754</t>
+    <t xml:space="preserve">1.38710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464762687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.331827044487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591583251953</t>
+    <t xml:space="preserve">1.33182692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591595172882</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564602375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937063694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827751636505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136778831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655005455017</t>
+    <t xml:space="preserve">1.34564614295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136790752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655017375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036915302277</t>
+    <t xml:space="preserve">1.29036927223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910106658936</t>
+    <t xml:space="preserve">1.34910094738007</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938488006592</t>
+    <t xml:space="preserve">1.49938476085663</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838636398315</t>
+    <t xml:space="preserve">1.51838624477386</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974941253662</t>
+    <t xml:space="preserve">1.50974929332733</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4181969165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729300498962</t>
+    <t xml:space="preserve">1.41819703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729312419891</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302901268005</t>
+    <t xml:space="preserve">1.60302889347076</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62893998622894</t>
+    <t xml:space="preserve">1.62894010543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6323949098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093713760376</t>
+    <t xml:space="preserve">1.63239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093725681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3737,10 +3737,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548518180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57193577289581</t>
+    <t xml:space="preserve">1.62548530101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5719358921051</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -8641,7 +8641,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G140" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8667,7 +8667,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8693,7 +8693,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8719,7 +8719,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8745,7 +8745,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8797,7 +8797,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8823,7 +8823,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8849,7 +8849,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8875,7 +8875,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8901,7 +8901,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8927,7 +8927,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8953,7 +8953,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8979,7 +8979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9005,7 +9005,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9031,7 +9031,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9057,7 +9057,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9083,7 +9083,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9109,7 +9109,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9135,7 +9135,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9161,7 +9161,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9187,7 +9187,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9213,7 +9213,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9291,7 +9291,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9317,7 +9317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9395,7 +9395,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9421,7 +9421,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9473,7 +9473,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9499,7 +9499,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9525,7 +9525,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9551,7 +9551,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9577,7 +9577,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9603,7 +9603,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9629,7 +9629,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9655,7 +9655,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9681,7 +9681,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9707,7 +9707,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9733,7 +9733,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9759,7 +9759,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9785,7 +9785,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9811,7 +9811,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9863,7 +9863,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9889,7 +9889,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9915,7 +9915,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9941,7 +9941,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9967,7 +9967,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9993,7 +9993,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10019,7 +10019,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10045,7 +10045,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10071,7 +10071,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10097,7 +10097,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10123,7 +10123,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10149,7 +10149,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10175,7 +10175,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10201,7 +10201,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10227,7 +10227,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10253,7 +10253,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10279,7 +10279,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10305,7 +10305,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10331,7 +10331,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10357,7 +10357,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10383,7 +10383,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10409,7 +10409,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10435,7 +10435,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10461,7 +10461,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10487,7 +10487,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10513,7 +10513,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10539,7 +10539,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10565,7 +10565,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10591,7 +10591,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10617,7 +10617,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10643,7 +10643,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G217" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10669,7 +10669,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10695,7 +10695,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10721,7 +10721,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10747,7 +10747,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10773,7 +10773,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10799,7 +10799,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10825,7 +10825,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10851,7 +10851,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10877,7 +10877,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10903,7 +10903,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10929,7 +10929,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10955,7 +10955,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10981,7 +10981,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11007,7 +11007,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11033,7 +11033,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11059,7 +11059,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11085,7 +11085,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11111,7 +11111,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11137,7 +11137,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11163,7 +11163,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11189,7 +11189,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11215,7 +11215,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G239" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11241,7 +11241,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11267,7 +11267,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11293,7 +11293,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11319,7 +11319,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G243" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11345,7 +11345,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11371,7 +11371,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11397,7 +11397,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11423,7 +11423,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11449,7 +11449,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11475,7 +11475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11501,7 +11501,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11527,7 +11527,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G251" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11553,7 +11553,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11579,7 +11579,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11605,7 +11605,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11631,7 +11631,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11657,7 +11657,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11683,7 +11683,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11709,7 +11709,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11735,7 +11735,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11761,7 +11761,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11787,7 +11787,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11813,7 +11813,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G262" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11839,7 +11839,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11865,7 +11865,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G264" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11891,7 +11891,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11917,7 +11917,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11943,7 +11943,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11969,7 +11969,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12021,7 +12021,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G270" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12047,7 +12047,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12073,7 +12073,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G272" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12099,7 +12099,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12125,7 +12125,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12151,7 +12151,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12177,7 +12177,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12203,7 +12203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12229,7 +12229,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12255,7 +12255,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12281,7 +12281,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G281" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12333,7 +12333,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G282" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12359,7 +12359,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12385,7 +12385,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12411,7 +12411,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12437,7 +12437,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12463,7 +12463,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12489,7 +12489,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12515,7 +12515,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12541,7 +12541,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12567,7 +12567,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12593,7 +12593,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12619,7 +12619,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12645,7 +12645,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12671,7 +12671,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12697,7 +12697,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12723,7 +12723,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12749,7 +12749,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12775,7 +12775,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12801,7 +12801,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12827,7 +12827,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12853,7 +12853,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12879,7 +12879,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12905,7 +12905,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12931,7 +12931,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12957,7 +12957,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G306" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12983,7 +12983,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13009,7 +13009,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13035,7 +13035,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13061,7 +13061,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13087,7 +13087,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13113,7 +13113,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13139,7 +13139,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13165,7 +13165,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13191,7 +13191,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13217,7 +13217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13243,7 +13243,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13269,7 +13269,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13347,7 +13347,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13373,7 +13373,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13399,7 +13399,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13425,7 +13425,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13451,7 +13451,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13477,7 +13477,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13503,7 +13503,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13529,7 +13529,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G328" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13555,7 +13555,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13581,7 +13581,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13607,7 +13607,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14205,7 +14205,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -47251,7 +47251,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47277,7 +47277,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47303,7 +47303,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47329,7 +47329,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47355,7 +47355,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47381,7 +47381,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47407,7 +47407,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47433,7 +47433,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47459,7 +47459,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47485,7 +47485,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47511,7 +47511,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47537,7 +47537,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47563,7 +47563,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G1637" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47589,7 +47589,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1638" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47615,7 +47615,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47641,7 +47641,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1640" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47667,7 +47667,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47693,7 +47693,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1642" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47719,7 +47719,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47745,7 +47745,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1644" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47771,7 +47771,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1645" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47797,7 +47797,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1646" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47823,7 +47823,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47849,7 +47849,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47875,7 +47875,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47901,7 +47901,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47927,7 +47927,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47953,7 +47953,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47979,7 +47979,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -48005,7 +48005,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -48031,7 +48031,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -48057,7 +48057,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -48083,7 +48083,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1657" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -48109,7 +48109,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -48135,7 +48135,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1659" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -48161,7 +48161,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -48187,7 +48187,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -48213,7 +48213,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -48239,7 +48239,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1663" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48265,7 +48265,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48291,7 +48291,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1665" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48317,7 +48317,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48343,7 +48343,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48369,7 +48369,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48395,7 +48395,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48421,7 +48421,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48447,7 +48447,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48473,7 +48473,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1672" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48499,7 +48499,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48525,7 +48525,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48551,7 +48551,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48577,7 +48577,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1676" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48603,7 +48603,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1677" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48629,7 +48629,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1678" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48655,7 +48655,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48681,7 +48681,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48707,7 +48707,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48733,7 +48733,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48759,7 +48759,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48785,7 +48785,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1684" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48811,7 +48811,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48837,7 +48837,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48863,7 +48863,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1687" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48889,7 +48889,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48915,7 +48915,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48941,7 +48941,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48967,7 +48967,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48993,7 +48993,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -49019,7 +49019,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -49045,7 +49045,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -49071,7 +49071,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -49097,7 +49097,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1696" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -49123,7 +49123,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -49149,7 +49149,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -49175,7 +49175,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -49201,7 +49201,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1700" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -49227,7 +49227,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49253,7 +49253,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49279,7 +49279,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49305,7 +49305,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49331,7 +49331,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49357,7 +49357,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49383,7 +49383,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49409,7 +49409,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49435,7 +49435,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1709" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49461,7 +49461,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49487,7 +49487,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49513,7 +49513,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49539,7 +49539,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49565,7 +49565,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49591,7 +49591,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1715" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49617,7 +49617,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49643,7 +49643,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49669,7 +49669,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49695,7 +49695,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49721,7 +49721,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49747,7 +49747,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1721" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49773,7 +49773,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49799,7 +49799,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49825,7 +49825,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49851,7 +49851,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49877,7 +49877,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49903,7 +49903,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49929,7 +49929,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49955,7 +49955,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49981,7 +49981,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -50007,7 +50007,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -50033,7 +50033,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -50059,7 +50059,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -50085,7 +50085,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -50111,7 +50111,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="s">
-        <v>948</v>
+        <v>1170</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -50267,7 +50267,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50293,7 +50293,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50371,7 +50371,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50423,7 +50423,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50475,7 +50475,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1749" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50683,7 +50683,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1757" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50761,7 +50761,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50787,7 +50787,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50839,7 +50839,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50891,7 +50891,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1765" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50943,7 +50943,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -51021,7 +51021,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -51073,7 +51073,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -51281,7 +51281,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51411,7 +51411,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51515,7 +51515,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51541,7 +51541,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51593,7 +51593,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51645,7 +51645,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51723,7 +51723,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51749,7 +51749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1798" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51775,7 +51775,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51879,7 +51879,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51931,7 +51931,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -52295,7 +52295,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52347,7 +52347,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1821" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52399,7 +52399,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52503,7 +52503,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1827" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52529,7 +52529,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52633,7 +52633,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52659,7 +52659,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52711,7 +52711,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52737,7 +52737,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52763,7 +52763,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52841,7 +52841,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52893,7 +52893,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -53075,7 +53075,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1849" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53257,7 +53257,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53517,7 +53517,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1866" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53777,7 +53777,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1876" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53907,7 +53907,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -70971,7 +70971,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.6909837963</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>565004</v>
@@ -70992,6 +70992,32 @@
         <v>1547</v>
       </c>
       <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.691087963</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>141083</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>2.71499991416931</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>1535</v>
+      </c>
+      <c r="H2539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385468482971</t>
+    <t xml:space="preserve">3.07385444641113</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614468574524</t>
+    <t xml:space="preserve">3.08614444732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.01786661148071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97690081596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98099756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131213188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003057479858</t>
+    <t xml:space="preserve">2.97690033912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98099732398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131189346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94003081321716</t>
   </si>
   <si>
     <t xml:space="preserve">2.80620670318604</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">2.86082863807678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75841212272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73929476737976</t>
+    <t xml:space="preserve">2.75841236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73929500579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.69013500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71744561195374</t>
+    <t xml:space="preserve">2.71744585037231</t>
   </si>
   <si>
     <t xml:space="preserve">2.86629104614258</t>
@@ -92,73 +92,73 @@
     <t xml:space="preserve">2.7570469379425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.710618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110151290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76114368438721</t>
+    <t xml:space="preserve">2.71061825752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110127449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76114344596863</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69696307182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72290825843811</t>
+    <t xml:space="preserve">2.69696283340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72290802001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.62868499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935702323914</t>
+    <t xml:space="preserve">2.45935678482056</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30095291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38971376419067</t>
+    <t xml:space="preserve">2.30095267295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971352577209</t>
   </si>
   <si>
     <t xml:space="preserve">2.53992438316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50442028045654</t>
+    <t xml:space="preserve">2.50442004203796</t>
   </si>
   <si>
     <t xml:space="preserve">2.67511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7488534450531</t>
+    <t xml:space="preserve">2.81713080406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74885368347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.78162670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68467235565186</t>
+    <t xml:space="preserve">2.68467259407043</t>
   </si>
   <si>
     <t xml:space="preserve">2.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8335177898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84717321395874</t>
+    <t xml:space="preserve">2.83351755142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84717297554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.88404321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88540816307068</t>
+    <t xml:space="preserve">2.88540863990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.89769864082336</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">2.9495894908905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05883359909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124987602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173265457153</t>
+    <t xml:space="preserve">3.058833360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164855003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173313140869</t>
   </si>
   <si>
     <t xml:space="preserve">3.20767831802368</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">3.17217445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040964126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269940376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2308931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952723503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076638221741</t>
+    <t xml:space="preserve">3.23635530471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001072883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040987968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2226996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089289665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076662063599</t>
   </si>
   <si>
     <t xml:space="preserve">3.14895987510681</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.29234266281128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21587228775024</t>
+    <t xml:space="preserve">3.21587181091309</t>
   </si>
   <si>
     <t xml:space="preserve">3.30463290214539</t>
@@ -233,64 +233,64 @@
     <t xml:space="preserve">3.27732157707214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34559941291809</t>
+    <t xml:space="preserve">3.34559917449951</t>
   </si>
   <si>
     <t xml:space="preserve">3.36608242988586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40704870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375025749207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780530929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26366686820984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022267341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182658195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13482999801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330288887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907908439636</t>
+    <t xml:space="preserve">3.40704894065857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3865659236908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330893516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780507087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15620350837708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330241203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208226203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
   </si>
   <si>
     <t xml:space="preserve">3.32291913032532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34856796264648</t>
+    <t xml:space="preserve">3.34856772422791</t>
   </si>
   <si>
     <t xml:space="preserve">3.3343186378479</t>
@@ -302,43 +302,43 @@
     <t xml:space="preserve">3.38419103622437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44403743743896</t>
+    <t xml:space="preserve">3.4440381526947</t>
   </si>
   <si>
     <t xml:space="preserve">3.41981410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43406319618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681069374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833804130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841484069824</t>
+    <t xml:space="preserve">3.43406295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108601570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.476811170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4383385181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841460227966</t>
   </si>
   <si>
     <t xml:space="preserve">3.39844012260437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714341163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607566833496</t>
+    <t xml:space="preserve">3.34714269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607614517212</t>
   </si>
   <si>
     <t xml:space="preserve">3.02796030044556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246482849121</t>
+    <t xml:space="preserve">2.94246506690979</t>
   </si>
   <si>
     <t xml:space="preserve">2.8997175693512</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">3.06643319129944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08495688438416</t>
+    <t xml:space="preserve">3.08495736122131</t>
   </si>
   <si>
     <t xml:space="preserve">3.1319797039032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14195418357849</t>
+    <t xml:space="preserve">3.14195394515991</t>
   </si>
   <si>
     <t xml:space="preserve">3.02938508987427</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">2.84984493255615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95671415328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500792503357</t>
+    <t xml:space="preserve">2.95671439170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500816345215</t>
   </si>
   <si>
     <t xml:space="preserve">3.16332793235779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9652636051178</t>
+    <t xml:space="preserve">2.96526384353638</t>
   </si>
   <si>
     <t xml:space="preserve">2.9552891254425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9923369884491</t>
+    <t xml:space="preserve">2.99233746528625</t>
   </si>
   <si>
     <t xml:space="preserve">3.12058043479919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1704523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599910736084</t>
+    <t xml:space="preserve">3.17045259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17757725715637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13625454902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702063560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91966605186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86551928520203</t>
+    <t xml:space="preserve">3.13625431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91966652870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86551904678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.90399241447449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84129524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549352645874</t>
+    <t xml:space="preserve">2.84129548072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549328804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.83559584617615</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73442649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77717423439026</t>
+    <t xml:space="preserve">2.73442625999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771737575531</t>
   </si>
   <si>
     <t xml:space="preserve">2.88546824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87406873703003</t>
+    <t xml:space="preserve">2.87406849861145</t>
   </si>
   <si>
     <t xml:space="preserve">2.84272050857544</t>
@@ -440,28 +440,28 @@
     <t xml:space="preserve">2.87834358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92821550369263</t>
+    <t xml:space="preserve">2.92821574211121</t>
   </si>
   <si>
     <t xml:space="preserve">2.92109107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94103980064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694407463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85839462280273</t>
+    <t xml:space="preserve">2.9410400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85839486122131</t>
   </si>
   <si>
     <t xml:space="preserve">2.86409401893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81707191467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007485389709</t>
+    <t xml:space="preserve">2.81707167625427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007509231567</t>
   </si>
   <si>
     <t xml:space="preserve">2.80567264556885</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">2.77289915084839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7586498260498</t>
+    <t xml:space="preserve">2.75865006446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.77859902381897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68597912788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62470746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478402137756</t>
+    <t xml:space="preserve">2.68597888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62470722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478354454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.54776120185852</t>
@@ -491,73 +491,73 @@
     <t xml:space="preserve">2.58480930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65605545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57198524475098</t>
+    <t xml:space="preserve">2.65605568885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463089942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333323478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5719850063324</t>
   </si>
   <si>
     <t xml:space="preserve">2.45086669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44516658782959</t>
+    <t xml:space="preserve">2.44516706466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.42379307746887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44374203681946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666841506958</t>
+    <t xml:space="preserve">2.44374227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.416668176651</t>
   </si>
   <si>
     <t xml:space="preserve">2.45941615104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61900758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61045813560486</t>
+    <t xml:space="preserve">2.61900782585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61045837402344</t>
   </si>
   <si>
     <t xml:space="preserve">2.54918622970581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57910966873169</t>
+    <t xml:space="preserve">2.57910990715027</t>
   </si>
   <si>
     <t xml:space="preserve">2.55061101913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52353763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57340979576111</t>
+    <t xml:space="preserve">2.52353811264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57341003417969</t>
   </si>
   <si>
     <t xml:space="preserve">2.64465594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6931037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64038157463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898206710815</t>
+    <t xml:space="preserve">2.69310355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64038133621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63895630836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898182868958</t>
   </si>
   <si>
     <t xml:space="preserve">2.63325691223145</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">2.67172980308533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74867558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727607727051</t>
+    <t xml:space="preserve">2.74867582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727583885193</t>
   </si>
   <si>
     <t xml:space="preserve">2.67315483093262</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">2.70307803153992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71447730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735287666321</t>
+    <t xml:space="preserve">2.7144775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735263824463</t>
   </si>
   <si>
     <t xml:space="preserve">2.65178084373474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66887998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65748047828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486058235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211260795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498818397522</t>
+    <t xml:space="preserve">2.66887974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6574809551239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486082077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211308479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498794555664</t>
   </si>
   <si>
     <t xml:space="preserve">2.41524362564087</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">2.39386987686157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39244484901428</t>
+    <t xml:space="preserve">2.39244508743286</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799136161804</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">2.57768487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58908438682556</t>
+    <t xml:space="preserve">2.58908414840698</t>
   </si>
   <si>
     <t xml:space="preserve">2.63468170166016</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">2.69595336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68027949333191</t>
+    <t xml:space="preserve">2.68027925491333</t>
   </si>
   <si>
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297595024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72445154190063</t>
+    <t xml:space="preserve">2.69737839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72445178031921</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7287266254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152516365051</t>
+    <t xml:space="preserve">2.72872638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152540206909</t>
   </si>
   <si>
     <t xml:space="preserve">2.75580024719238</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">2.69025349617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035605430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760831832886</t>
+    <t xml:space="preserve">2.65035581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760807991028</t>
   </si>
   <si>
     <t xml:space="preserve">2.58338451385498</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">2.55346131324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5206880569458</t>
+    <t xml:space="preserve">2.52068781852722</t>
   </si>
   <si>
     <t xml:space="preserve">2.60618329048157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56058597564697</t>
+    <t xml:space="preserve">2.56058573722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5449116230011</t>
@@ -710,31 +710,31 @@
     <t xml:space="preserve">2.54063677787781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501370429993</t>
+    <t xml:space="preserve">2.50501394271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.49788928031921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50643849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53351211547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57626008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048341751099</t>
+    <t xml:space="preserve">2.50643873214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53351235389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57625985145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048389434814</t>
   </si>
   <si>
     <t xml:space="preserve">2.59193396568298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58195972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5591607093811</t>
+    <t xml:space="preserve">2.58195948600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55916094779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.58623433113098</t>
@@ -743,31 +743,31 @@
     <t xml:space="preserve">2.53636193275452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48506498336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54348635673523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6874041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69452857971191</t>
+    <t xml:space="preserve">2.48506474494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54348683357239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68740391731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69452834129333</t>
   </si>
   <si>
     <t xml:space="preserve">2.75722503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77147459983826</t>
+    <t xml:space="preserve">2.77147436141968</t>
   </si>
   <si>
     <t xml:space="preserve">2.79712295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78857326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79997277259827</t>
+    <t xml:space="preserve">2.78857350349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79997301101685</t>
   </si>
   <si>
     <t xml:space="preserve">2.83132100105286</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">2.9054172039032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03508496284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215858459473</t>
+    <t xml:space="preserve">3.03508520126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215810775757</t>
   </si>
   <si>
     <t xml:space="preserve">3.15477824211121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29727029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25737285614014</t>
+    <t xml:space="preserve">3.29727053642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25737309455872</t>
   </si>
   <si>
     <t xml:space="preserve">3.07783269882202</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">3.16190338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16047835350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21889972686768</t>
+    <t xml:space="preserve">3.16047811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21890020370483</t>
   </si>
   <si>
     <t xml:space="preserve">3.22174954414368</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">3.27589678764343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28159642219543</t>
+    <t xml:space="preserve">3.28159666061401</t>
   </si>
   <si>
     <t xml:space="preserve">3.26877188682556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23172402381897</t>
+    <t xml:space="preserve">3.23172426223755</t>
   </si>
   <si>
     <t xml:space="preserve">3.12913012504578</t>
@@ -827,58 +827,58 @@
     <t xml:space="preserve">3.19610118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10063147544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1975257396698</t>
+    <t xml:space="preserve">3.10063171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752597808838</t>
   </si>
   <si>
     <t xml:space="preserve">3.23884892463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22602438926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157090187073</t>
+    <t xml:space="preserve">3.22602462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157137870789</t>
   </si>
   <si>
     <t xml:space="preserve">3.32576966285706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28302121162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864476203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34001874923706</t>
+    <t xml:space="preserve">3.28302145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864428520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3400182723999</t>
   </si>
   <si>
     <t xml:space="preserve">3.39559006690979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3556923866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457407951355</t>
+    <t xml:space="preserve">3.35569262504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457431793213</t>
   </si>
   <si>
     <t xml:space="preserve">3.27019739151001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0892322063446</t>
+    <t xml:space="preserve">3.08923196792603</t>
   </si>
   <si>
     <t xml:space="preserve">3.06358337402344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17489004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11147809028625</t>
+    <t xml:space="preserve">3.17488980293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09706664085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.13886022567749</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">3.14462518692017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11003684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11868405342102</t>
+    <t xml:space="preserve">3.11003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1186842918396</t>
   </si>
   <si>
     <t xml:space="preserve">3.07112598419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03797912597656</t>
+    <t xml:space="preserve">3.03797888755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.04806733131409</t>
@@ -908,28 +908,28 @@
     <t xml:space="preserve">3.00627326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97744965553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9183623790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87224507331848</t>
+    <t xml:space="preserve">2.97744989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91836214065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8722448348999</t>
   </si>
   <si>
     <t xml:space="preserve">2.90395069122314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8909797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87512707710266</t>
+    <t xml:space="preserve">2.89098000526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87512731552124</t>
   </si>
   <si>
     <t xml:space="preserve">2.84918618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92700886726379</t>
+    <t xml:space="preserve">2.92700910568237</t>
   </si>
   <si>
     <t xml:space="preserve">2.90683269500732</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">2.86936259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87800908088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85783338546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85350966453552</t>
+    <t xml:space="preserve">2.878009557724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85783314704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85350942611694</t>
   </si>
   <si>
     <t xml:space="preserve">2.87080359458923</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">2.82468628883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7929801940918</t>
+    <t xml:space="preserve">2.79298067092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.76415705680847</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">2.79153966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72956943511963</t>
+    <t xml:space="preserve">2.72956967353821</t>
   </si>
   <si>
     <t xml:space="preserve">2.75262784957886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75983381271362</t>
+    <t xml:space="preserve">2.75983357429504</t>
   </si>
   <si>
     <t xml:space="preserve">2.74686360359192</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">2.92556810379028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189225196838</t>
+    <t xml:space="preserve">2.83189249038696</t>
   </si>
   <si>
     <t xml:space="preserve">2.84342169761658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83045125007629</t>
+    <t xml:space="preserve">2.80450987815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83045101165771</t>
   </si>
   <si>
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865694999695</t>
+    <t xml:space="preserve">2.78865718841553</t>
   </si>
   <si>
     <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80883359909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84053921699524</t>
+    <t xml:space="preserve">2.80883312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84053897857666</t>
   </si>
   <si>
     <t xml:space="preserve">2.85495066642761</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">2.76848077774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218753814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72668719291687</t>
+    <t xml:space="preserve">2.70218729972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72668695449829</t>
   </si>
   <si>
     <t xml:space="preserve">2.71371650695801</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">2.7252459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68056988716125</t>
+    <t xml:space="preserve">2.68056964874268</t>
   </si>
   <si>
     <t xml:space="preserve">2.6748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67336392402649</t>
+    <t xml:space="preserve">2.67336368560791</t>
   </si>
   <si>
     <t xml:space="preserve">2.65895199775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406908988953</t>
+    <t xml:space="preserve">2.67624640464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406932830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
@@ -1082,22 +1082,22 @@
     <t xml:space="preserve">2.74542212486267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78577470779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92268586158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0250084400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02644944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06968450546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10571360588074</t>
+    <t xml:space="preserve">2.78577494621277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92268562316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02500820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02644968032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06968474388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1057140827179</t>
   </si>
   <si>
     <t xml:space="preserve">3.12156653404236</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">3.17056655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14174318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597822189331</t>
+    <t xml:space="preserve">3.14174294471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597846031189</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850788116455</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">3.07689046859741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08409667015076</t>
+    <t xml:space="preserve">3.08409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">3.07400798797607</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">3.04086089134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05383133888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17921304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12588977813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05527281761169</t>
+    <t xml:space="preserve">3.05383157730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17921376228333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589001655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05527257919312</t>
   </si>
   <si>
     <t xml:space="preserve">3.07977294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14894866943359</t>
+    <t xml:space="preserve">3.14894890785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.16191959381104</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">3.14750742912292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09994912147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15903687477112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15471339225769</t>
+    <t xml:space="preserve">3.09994888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15903663635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15471291542053</t>
   </si>
   <si>
     <t xml:space="preserve">3.12877249717712</t>
@@ -1172,58 +1172,58 @@
     <t xml:space="preserve">3.11580181121826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10427284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815529823303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9716854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86792135238647</t>
+    <t xml:space="preserve">3.10427260398865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815505981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168517112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78433394432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82180380821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86792159080505</t>
   </si>
   <si>
     <t xml:space="preserve">2.89674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88233280181885</t>
+    <t xml:space="preserve">2.88233304023743</t>
   </si>
   <si>
     <t xml:space="preserve">2.85062718391418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82901000976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82324528694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70362854003906</t>
+    <t xml:space="preserve">2.8290102481842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82324504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
     <t xml:space="preserve">2.72236371040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70506978034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71227526664734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6560697555542</t>
+    <t xml:space="preserve">2.70506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71227502822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65606999397278</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">2.76703953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78505396842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69498157501221</t>
+    <t xml:space="preserve">2.78505420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740769386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69498133659363</t>
   </si>
   <si>
     <t xml:space="preserve">2.73461365699768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70579028129578</t>
+    <t xml:space="preserve">2.7057900428772</t>
   </si>
   <si>
     <t xml:space="preserve">2.7310106754303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72020196914673</t>
+    <t xml:space="preserve">2.72020173072815</t>
   </si>
   <si>
     <t xml:space="preserve">2.79225993156433</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.84630393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77424550056458</t>
+    <t xml:space="preserve">2.774245262146</t>
   </si>
   <si>
     <t xml:space="preserve">2.77064251899719</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">2.70939302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74181938171387</t>
+    <t xml:space="preserve">2.74181914329529</t>
   </si>
   <si>
     <t xml:space="preserve">2.71299600601196</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">2.63373160362244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62652611732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6409375667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65534925460815</t>
+    <t xml:space="preserve">2.62652587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65534901618958</t>
   </si>
   <si>
     <t xml:space="preserve">2.64814329147339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58689379692078</t>
+    <t xml:space="preserve">2.58689403533936</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248210906982</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">2.57968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55807065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56167340278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086469650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56887936592102</t>
+    <t xml:space="preserve">2.55807042121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56167364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086493492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56887912750244</t>
   </si>
   <si>
     <t xml:space="preserve">2.43557143211365</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">2.39593935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41755700111389</t>
+    <t xml:space="preserve">2.41755676269531</t>
   </si>
   <si>
     <t xml:space="preserve">2.41395378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36351323127747</t>
+    <t xml:space="preserve">2.36351275444031</t>
   </si>
   <si>
     <t xml:space="preserve">2.35991024971008</t>
@@ -1352,34 +1352,34 @@
     <t xml:space="preserve">2.44638013839722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42115998268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50762963294983</t>
+    <t xml:space="preserve">2.42115950584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50762987136841</t>
   </si>
   <si>
     <t xml:space="preserve">2.59409976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56527614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63012862205505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65174627304077</t>
+    <t xml:space="preserve">2.56527638435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63012886047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65174651145935</t>
   </si>
   <si>
     <t xml:space="preserve">2.62292313575745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60130524635315</t>
+    <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
     <t xml:space="preserve">2.60851144790649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6373348236084</t>
+    <t xml:space="preserve">2.63733458518982</t>
   </si>
   <si>
     <t xml:space="preserve">2.68417239189148</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">2.67696666717529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73281216621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62172174453735</t>
+    <t xml:space="preserve">2.73281192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62172198295593</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">2.48841404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40324521064758</t>
+    <t xml:space="preserve">2.403244972229</t>
   </si>
   <si>
     <t xml:space="preserve">2.43657207489014</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.45879006385803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39213609695435</t>
+    <t xml:space="preserve">2.39213585853577</t>
   </si>
   <si>
     <t xml:space="preserve">2.40694832801819</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.36991810798645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29956126213074</t>
+    <t xml:space="preserve">2.29956150054932</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068930625916</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">2.32548213005066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37732410430908</t>
+    <t xml:space="preserve">2.37732434272766</t>
   </si>
   <si>
     <t xml:space="preserve">2.38843321800232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42916631698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805720329285</t>
+    <t xml:space="preserve">2.4291660785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805744171143</t>
   </si>
   <si>
     <t xml:space="preserve">2.46989917755127</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">2.5032262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52174091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53285002708435</t>
+    <t xml:space="preserve">2.52174115180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53285026550293</t>
   </si>
   <si>
     <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5254442691803</t>
+    <t xml:space="preserve">2.52544403076172</t>
   </si>
   <si>
     <t xml:space="preserve">2.45508718490601</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">2.58098888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395914077759</t>
+    <t xml:space="preserve">2.54395890235901</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44768118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53655314445496</t>
+    <t xml:space="preserve">2.44768095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53655290603638</t>
   </si>
   <si>
     <t xml:space="preserve">2.4773051738739</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">2.39583921432495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41065120697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35140323638916</t>
+    <t xml:space="preserve">2.41065144538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35140347480774</t>
   </si>
   <si>
     <t xml:space="preserve">2.36621522903442</t>
@@ -1511,25 +1511,25 @@
     <t xml:space="preserve">2.35880899429321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35510635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36251258850098</t>
+    <t xml:space="preserve">2.35510659217834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
     <t xml:space="preserve">2.30696749687195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3106701374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32177948951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39954209327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38102722167969</t>
+    <t xml:space="preserve">2.31067037582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32177925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39954233169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38102698326111</t>
   </si>
   <si>
     <t xml:space="preserve">2.41435408592224</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">2.31807637214661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29585814476013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104639053345</t>
+    <t xml:space="preserve">2.29585838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104591369629</t>
   </si>
   <si>
     <t xml:space="preserve">2.26993727684021</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">2.26623439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29215526580811</t>
+    <t xml:space="preserve">2.29215502738953</t>
   </si>
   <si>
     <t xml:space="preserve">2.27364015579224</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">2.28474926948547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38473033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20698642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24031352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15514421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292646408081</t>
+    <t xml:space="preserve">2.38473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20698618888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24031329154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15514469146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292670249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.14773845672607</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.08849048614502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10700535774231</t>
+    <t xml:space="preserve">2.10700559616089</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625696182251</t>
@@ -1613,37 +1613,37 @@
     <t xml:space="preserve">1.95147943496704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02553915977478</t>
+    <t xml:space="preserve">2.02553963661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.06627225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997561454773</t>
+    <t xml:space="preserve">2.04775738716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997537612915</t>
   </si>
   <si>
     <t xml:space="preserve">2.12922310829163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14403533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13662958145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847131729126</t>
+    <t xml:space="preserve">2.14403557777405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13662910461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847155570984</t>
   </si>
   <si>
     <t xml:space="preserve">2.21439242362976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23290753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512528419495</t>
+    <t xml:space="preserve">2.23290729522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512552261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.20328330993652</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">2.19958066940308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809530258179</t>
+    <t xml:space="preserve">2.21809506416321</t>
   </si>
   <si>
     <t xml:space="preserve">2.11811423301697</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">2.51063227653503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65504884719849</t>
+    <t xml:space="preserve">2.65504908561707</t>
   </si>
   <si>
     <t xml:space="preserve">2.68096995353699</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">2.71800017356873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70318794250488</t>
+    <t xml:space="preserve">2.70318818092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.7291088104248</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.75502991676331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80316877365112</t>
+    <t xml:space="preserve">2.8031690120697</t>
   </si>
   <si>
     <t xml:space="preserve">2.81798076629639</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">2.87352585792542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86241698265076</t>
+    <t xml:space="preserve">2.86241674423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.88093185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76243567466736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76984214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7994658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205989837646</t>
+    <t xml:space="preserve">2.76243615150452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76984190940857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205965995789</t>
   </si>
   <si>
     <t xml:space="preserve">2.81427788734436</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">2.75873279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85871362686157</t>
+    <t xml:space="preserve">2.85871386528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.90314984321594</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">2.89574384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90685272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88833808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.962397813797</t>
+    <t xml:space="preserve">2.90685296058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88833785057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96239805221558</t>
   </si>
   <si>
     <t xml:space="preserve">2.98091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91796183586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758558273315</t>
+    <t xml:space="preserve">2.91796207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758582115173</t>
   </si>
   <si>
     <t xml:space="preserve">2.95128893852234</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">2.95499181747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93277382850647</t>
+    <t xml:space="preserve">2.93277359008789</t>
   </si>
   <si>
     <t xml:space="preserve">2.91055583953857</t>
@@ -1796,22 +1796,22 @@
     <t xml:space="preserve">2.96980381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97721004486084</t>
+    <t xml:space="preserve">2.97720956802368</t>
   </si>
   <si>
     <t xml:space="preserve">2.94018006324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89944696426392</t>
+    <t xml:space="preserve">2.89944648742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.81057500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8661196231842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80687165260315</t>
+    <t xml:space="preserve">2.86611986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80687212944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.83279299736023</t>
@@ -1820,22 +1820,22 @@
     <t xml:space="preserve">2.85501098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71059417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70689082145691</t>
+    <t xml:space="preserve">2.71059393882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70689105987549</t>
   </si>
   <si>
     <t xml:space="preserve">2.61061310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6402370929718</t>
+    <t xml:space="preserve">2.64023685455322</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63283109664917</t>
+    <t xml:space="preserve">2.63283085823059</t>
   </si>
   <si>
     <t xml:space="preserve">2.61801910400391</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">2.6143159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56988024711609</t>
+    <t xml:space="preserve">2.56988000869751</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211716651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50692915916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34770035743713</t>
+    <t xml:space="preserve">2.50692939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34770011901855</t>
   </si>
   <si>
     <t xml:space="preserve">2.23661017417908</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587683677673</t>
+    <t xml:space="preserve">2.19587731361389</t>
   </si>
   <si>
     <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21777319908142</t>
+    <t xml:space="preserve">2.2177734375</t>
   </si>
   <si>
     <t xml:space="preserve">2.10882997512817</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">2.13995695114136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12828397750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770371437073</t>
+    <t xml:space="preserve">2.12828421592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770347595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.05046772956848</t>
@@ -1916,19 +1916,19 @@
     <t xml:space="preserve">2.04657673835754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03490447998047</t>
+    <t xml:space="preserve">2.03490424156189</t>
   </si>
   <si>
     <t xml:space="preserve">2.05435872077942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03101325035095</t>
+    <t xml:space="preserve">2.03101348876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0582492351532</t>
+    <t xml:space="preserve">2.05824947357178</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">1.75087380409241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74698281288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69251120090485</t>
+    <t xml:space="preserve">1.74698269367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69251132011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.78978180885315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82090854644775</t>
+    <t xml:space="preserve">1.82090866565704</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7430921792984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69640219211578</t>
+    <t xml:space="preserve">1.74309206008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
     <t xml:space="preserve">1.71196556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7197470664978</t>
+    <t xml:space="preserve">1.71974718570709</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">1.78589117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141956329346</t>
+    <t xml:space="preserve">1.73141944408417</t>
   </si>
   <si>
     <t xml:space="preserve">1.71585619449615</t>
@@ -2018,34 +2018,34 @@
     <t xml:space="preserve">1.8325811624527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80145466327667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84036290645599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85592591762543</t>
+    <t xml:space="preserve">1.80145454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84036302566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85592615604401</t>
   </si>
   <si>
     <t xml:space="preserve">1.83647203445435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8792712688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79756379127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032780647278</t>
+    <t xml:space="preserve">1.87927114963531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79756367206573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032792568207</t>
   </si>
   <si>
     <t xml:space="preserve">1.82869029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75476467609406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75865530967712</t>
+    <t xml:space="preserve">1.75476479530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75865542888641</t>
   </si>
   <si>
     <t xml:space="preserve">1.76254630088806</t>
@@ -2057,19 +2057,19 @@
     <t xml:space="preserve">1.81701791286469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8247994184494</t>
+    <t xml:space="preserve">1.82479953765869</t>
   </si>
   <si>
     <t xml:space="preserve">1.91428875923157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93374264240265</t>
+    <t xml:space="preserve">1.93374240398407</t>
   </si>
   <si>
     <t xml:space="preserve">1.89094352722168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87538015842438</t>
+    <t xml:space="preserve">1.87538039684296</t>
   </si>
   <si>
     <t xml:space="preserve">1.90650701522827</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217496871948</t>
+    <t xml:space="preserve">2.13217520713806</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
@@ -2108,16 +2108,16 @@
     <t xml:space="preserve">2.19053745269775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15552020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19831895828247</t>
+    <t xml:space="preserve">2.15551996231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19831919670105</t>
   </si>
   <si>
     <t xml:space="preserve">2.17108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14384770393372</t>
+    <t xml:space="preserve">2.14384794235229</t>
   </si>
   <si>
     <t xml:space="preserve">2.11272072792053</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">2.01545023918152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821449279785</t>
+    <t xml:space="preserve">1.98821473121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.15941119194031</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01934123039246</t>
+    <t xml:space="preserve">2.01934099197388</t>
   </si>
   <si>
     <t xml:space="preserve">1.87148940563202</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">1.91039776802063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92596101760864</t>
+    <t xml:space="preserve">1.92596113681793</t>
   </si>
   <si>
     <t xml:space="preserve">1.89872527122498</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">1.95708787441254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96486973762512</t>
+    <t xml:space="preserve">1.96486949920654</t>
   </si>
   <si>
     <t xml:space="preserve">1.99210524559021</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">1.62636709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59524047374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.542325258255</t>
+    <t xml:space="preserve">1.59524035453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54232513904572</t>
   </si>
   <si>
     <t xml:space="preserve">1.48941004276276</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">1.27619242668152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09098887443542</t>
+    <t xml:space="preserve">1.09098875522614</t>
   </si>
   <si>
     <t xml:space="preserve">1.16102385520935</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">1.08009457588196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05986213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0847635269165</t>
+    <t xml:space="preserve">1.05986225605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08476364612579</t>
   </si>
   <si>
     <t xml:space="preserve">1.10188317298889</t>
@@ -2234,22 +2234,22 @@
     <t xml:space="preserve">1.27152335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32288253307343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28864312171936</t>
+    <t xml:space="preserve">1.32288241386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28864300251007</t>
   </si>
   <si>
     <t xml:space="preserve">1.28397417068481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29331207275391</t>
+    <t xml:space="preserve">1.29331195354462</t>
   </si>
   <si>
     <t xml:space="preserve">1.39291739463806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36179065704346</t>
+    <t xml:space="preserve">1.36179077625275</t>
   </si>
   <si>
     <t xml:space="preserve">1.26062893867493</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798102378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33688950538635</t>
+    <t xml:space="preserve">1.29798114299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
     <t xml:space="preserve">1.29953730106354</t>
@@ -2273,46 +2273,46 @@
     <t xml:space="preserve">1.29175567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28241765499115</t>
+    <t xml:space="preserve">1.28241777420044</t>
   </si>
   <si>
     <t xml:space="preserve">1.22950255870819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23884034156799</t>
+    <t xml:space="preserve">1.23884046077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.24350941181183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20927023887634</t>
+    <t xml:space="preserve">1.20927011966705</t>
   </si>
   <si>
     <t xml:space="preserve">1.17503070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13300979137421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10343945026398</t>
+    <t xml:space="preserve">1.13300967216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10343956947327</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08631980419159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05674970149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06764388084412</t>
+    <t xml:space="preserve">1.08631992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05674958229065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06764400005341</t>
   </si>
   <si>
     <t xml:space="preserve">1.12211549282074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10655236244202</t>
+    <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
     <t xml:space="preserve">1.14234793186188</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.2450658082962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2372841835022</t>
+    <t xml:space="preserve">1.23728406429291</t>
   </si>
   <si>
     <t xml:space="preserve">1.2217208147049</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">1.28708672523499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27930510044098</t>
+    <t xml:space="preserve">1.27930498123169</t>
   </si>
   <si>
     <t xml:space="preserve">1.17969989776611</t>
@@ -2348,19 +2348,19 @@
     <t xml:space="preserve">1.16413640975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23572790622711</t>
+    <t xml:space="preserve">1.23572778701782</t>
   </si>
   <si>
     <t xml:space="preserve">1.20615744590759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20771372318268</t>
+    <t xml:space="preserve">1.20771384239197</t>
   </si>
   <si>
     <t xml:space="preserve">1.18748152256012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21082651615143</t>
+    <t xml:space="preserve">1.21082639694214</t>
   </si>
   <si>
     <t xml:space="preserve">1.17814350128174</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">1.13612258434296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15791118144989</t>
+    <t xml:space="preserve">1.1579110622406</t>
   </si>
   <si>
     <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18436884880066</t>
+    <t xml:space="preserve">1.18436872959137</t>
   </si>
   <si>
     <t xml:space="preserve">1.17036187648773</t>
@@ -2393,31 +2393,31 @@
     <t xml:space="preserve">1.17347455024719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15168571472168</t>
+    <t xml:space="preserve">1.15168583393097</t>
   </si>
   <si>
     <t xml:space="preserve">1.17191815376282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16569292545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15635478496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1252281665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.1656928062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1563549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12522804737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08320724964142</t>
+    <t xml:space="preserve">1.06608760356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08320713043213</t>
   </si>
   <si>
     <t xml:space="preserve">1.06297492980957</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">1.03962993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04118621349335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03340446949005</t>
+    <t xml:space="preserve">1.04118633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03340458869934</t>
   </si>
   <si>
     <t xml:space="preserve">1.03496098518372</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">0.996052622795105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01628482341766</t>
+    <t xml:space="preserve">1.01628494262695</t>
   </si>
   <si>
     <t xml:space="preserve">1.00850331783295</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.975820243358612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827215671539</t>
+    <t xml:space="preserve">0.989827334880829</t>
   </si>
   <si>
     <t xml:space="preserve">0.969595015048981</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">0.957144379615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980489194393158</t>
+    <t xml:space="preserve">0.980489313602448</t>
   </si>
   <si>
     <t xml:space="preserve">0.999165296554565</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">1.06453132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05830585956573</t>
+    <t xml:space="preserve">1.05830597877502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02406656742096</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">0.941581010818481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93379944562912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904229044914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879327654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887109339237213</t>
+    <t xml:space="preserve">0.93379932641983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904228985309601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879327714443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887109398841858</t>
   </si>
   <si>
     <t xml:space="preserve">0.888665616512299</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.835750341415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803067326545715</t>
+    <t xml:space="preserve">0.80306738615036</t>
   </si>
   <si>
     <t xml:space="preserve">0.787504076957703</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">0.817074358463287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86687707901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89644730091095</t>
+    <t xml:space="preserve">0.866877019405365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896447241306305</t>
   </si>
   <si>
     <t xml:space="preserve">0.902672648429871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915123343467712</t>
+    <t xml:space="preserve">0.915123283863068</t>
   </si>
   <si>
     <t xml:space="preserve">0.940024554729462</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">0.963369607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983601987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978933036327362</t>
+    <t xml:space="preserve">0.983602106571198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978932917118073</t>
   </si>
   <si>
     <t xml:space="preserve">0.92913031578064</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">0.930686771869659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952475309371948</t>
+    <t xml:space="preserve">0.952475190162659</t>
   </si>
   <si>
     <t xml:space="preserve">0.927573919296265</t>
@@ -2639,28 +2639,28 @@
     <t xml:space="preserve">0.919792413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913566946983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341659069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679620742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560034275055</t>
+    <t xml:space="preserve">0.913567006587982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341718673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679680347443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8995600938797</t>
   </si>
   <si>
     <t xml:space="preserve">0.918236017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908898055553436</t>
+    <t xml:space="preserve">0.908897936344147</t>
   </si>
   <si>
     <t xml:space="preserve">0.894890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910454273223877</t>
+    <t xml:space="preserve">0.910454332828522</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">1.05363690853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13767886161804</t>
+    <t xml:space="preserve">1.13767898082733</t>
   </si>
   <si>
     <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12989711761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10032689571381</t>
+    <t xml:space="preserve">1.12989723682404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10032677650452</t>
   </si>
   <si>
     <t xml:space="preserve">1.09877049922943</t>
@@ -2696,19 +2696,19 @@
     <t xml:space="preserve">1.12055921554565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11744666099548</t>
+    <t xml:space="preserve">1.11744654178619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15479850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31198811531067</t>
+    <t xml:space="preserve">1.31198799610138</t>
   </si>
   <si>
     <t xml:space="preserve">1.25907289981842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24662208557129</t>
+    <t xml:space="preserve">1.24662220478058</t>
   </si>
   <si>
     <t xml:space="preserve">1.25284743309021</t>
@@ -2741,13 +2741,13 @@
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069901943207</t>
+    <t xml:space="preserve">1.40069913864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112867832184</t>
+    <t xml:space="preserve">1.37112855911255</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">1.39447367191315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3898047208786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3975864648819</t>
+    <t xml:space="preserve">1.38980460166931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39758634567261</t>
   </si>
   <si>
     <t xml:space="preserve">1.3913608789444</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">1.56022310256958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58745884895325</t>
+    <t xml:space="preserve">1.58745872974396</t>
   </si>
   <si>
     <t xml:space="preserve">1.53765618801117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51431119441986</t>
+    <t xml:space="preserve">1.51431131362915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50341701507568</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">1.50497317314148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49096632003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51798808574677</t>
+    <t xml:space="preserve">1.49096620082855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51798796653748</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871304512024</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">1.54818880558014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55454695224762</t>
+    <t xml:space="preserve">1.55454683303833</t>
   </si>
   <si>
     <t xml:space="preserve">1.5561363697052</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">1.57044196128845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56567347049713</t>
+    <t xml:space="preserve">1.56567358970642</t>
   </si>
   <si>
     <t xml:space="preserve">1.567263007164</t>
@@ -2849,679 +2849,679 @@
     <t xml:space="preserve">1.47030258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4432806968689</t>
+    <t xml:space="preserve">1.44328081607819</t>
   </si>
   <si>
     <t xml:space="preserve">1.40672194957733</t>
   </si>
   <si>
+    <t xml:space="preserve">1.43374371528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44487023353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39241623878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35744690895081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949922561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34790980815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33201467990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929850578308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31453001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27638149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30181384086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30499279499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31135094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30340325832367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28432929515839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479207515717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22074854373932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2223379611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2557178735733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935972690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25412821769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22710657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21121144294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2732025384903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26366543769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37652099132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36698389053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35267841815948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3749315738678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37970018386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128960132599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34314131736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33678317070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221539974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.363804936409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39877426624298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40513229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53388321399689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49732434749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189199924469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738556861877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4146693944931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42420661449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45917594432831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46076548099518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41943800449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39082670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33996224403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34155166149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33519351482391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37811064720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35426783561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33042514324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37175250053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33837270736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287913799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116703987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49573481082916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50845086574554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51162993907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50209283828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51321947574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47507119178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010174274445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4877872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47983968257904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45599699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301863670349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51004040241241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249439716339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63720166683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66501832008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67693948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70078253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65309691429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60541141033173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55772590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57362115383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43851220607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645988941193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4544073343277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45122838020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49414527416229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5163985490799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61335897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733293533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322794437408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62130653858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58792674541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60143768787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62925410270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66104447841644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53865170478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183077812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52911472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53070402145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43056452274323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37334203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30817186832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30022442340851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22869610786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23346471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539447307587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36062598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40831136703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59746384620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74846792221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423178195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76038908958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77231049537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74449396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81999599933624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81204843521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83191752433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8279435634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178625583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589112758636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986508846283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396984100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76833665370941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788205742836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72859871387482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64514923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71667754650116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73654639720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641548633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436293125153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410075187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7403576374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76195001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75763165950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75331294536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603904247284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67730736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64448666572571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55811655521393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4769287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46483683586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45792722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50456702709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50283968448639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865605354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51665902137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48038351535797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4890204668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47001910209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41128730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3819215297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40092301368713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43028879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40610527992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37328457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34737348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52875077724457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59957420825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5477522611618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55293428897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466175079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60648381710052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60475647449493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58230030536652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58057284355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53047811985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5252959728241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51493144035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49420273303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49765753746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510664463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43547093868256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44756281375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4285614490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39228594303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35255575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33873653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3214625120163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32318985462189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31973516941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31628036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31282544136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33009946346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38019418716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35082840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33355438709259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31800770759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555153846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26791310310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2368198633194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25754857063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2247279882431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23854720592499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2005443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22300052642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1884526014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21954572200775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2610034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28691446781158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32664465904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29382407665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2730952501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35773801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39574086666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39746820926666</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.43374359607697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44487023353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39241623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35744690895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34790980815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33201456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585725307465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929850578308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31453001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27638149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30181384086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30499279499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31135094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30340337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479207515717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22074842453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22233808040619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2557178735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935984611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25412821769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28273963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2112113237381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2732025384903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26366543769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37652099132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36698389053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35267841815948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970006465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128972053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34314119815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33678317070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221539974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.363804936409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39877438545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40513241291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53388321399689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49732422828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189199924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738556861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4146693944931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42420661449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45917594432831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46076548099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41943800449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39082670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33996224403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34155166149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37811064720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35426783561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33042514324188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37175250053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33837270736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287913799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050342082977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116703987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49573481082916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50845098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51162981987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50209283828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51321947574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47507107257843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010174274445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48778712749481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47983956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45599699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301875591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51004040241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249451637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63720166683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66501832008362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67693948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70078253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65309679508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60541141033173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55772590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57362115383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43851220607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645988941193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4544073343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45122826099396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49414539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61335897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733293533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62130665779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58792674541473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60143768787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62925410270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53865170478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183065891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52911460399628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53070414066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434611320496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43056464195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37334203720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30817174911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30022430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22869598865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23346471786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539447307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36062586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40831136703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59746384620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74846792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423190116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76038908958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77231061458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74449396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81999611854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81204855442047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83191764354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82794368267059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178649425507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589136600494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986520767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.823970079422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628433704376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217970371246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76833665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78820586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859883308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71667754650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436305046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410087108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7403576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71012794971466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76195001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75763165950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75331294536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603904247284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67730736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448666572571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55811655521393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46483683586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45792722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42337930202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50456702709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50283968448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865605354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51665902137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48038351535797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4890204668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48211085796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47001910209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41128730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3819215297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40092301368713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43028879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37328457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34737348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52875077724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59957420825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477522611618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55293428897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60648381710052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60475647449493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58230030536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58057284355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53047811985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5252959728241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51493144035339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49420273303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49765753746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510664463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43547093868256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44756281375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4285614490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39228594303131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35255575180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33873653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3214625120163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32318985462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31973516941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31628036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31282544136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33009946346283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38019418716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35082840919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33355438709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31800770759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555153846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26791310310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2368198633194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25754857063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247279882431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23854720592499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2005443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22300052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1884526014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21954572200775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2610034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28691446781158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30418848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32664465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29382407665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2730952501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35773801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39574086666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39746820926666</t>
   </si>
   <si>
     <t xml:space="preserve">1.44929015636444</t>
@@ -47248,7 +47248,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47274,7 +47274,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47300,7 +47300,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47326,7 +47326,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47352,7 +47352,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47378,7 +47378,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47404,7 +47404,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47430,7 +47430,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47456,7 +47456,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47482,7 +47482,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47508,7 +47508,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47534,7 +47534,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47560,7 +47560,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G1637" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47586,7 +47586,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1638" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47612,7 +47612,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47638,7 +47638,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1640" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47664,7 +47664,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47690,7 +47690,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1642" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47716,7 +47716,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47742,7 +47742,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1644" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47768,7 +47768,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1645" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47794,7 +47794,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1646" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47820,7 +47820,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47846,7 +47846,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47872,7 +47872,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47898,7 +47898,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47924,7 +47924,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47950,7 +47950,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47976,7 +47976,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -48002,7 +48002,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -48028,7 +48028,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -48054,7 +48054,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -48080,7 +48080,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1657" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -48106,7 +48106,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -48132,7 +48132,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1659" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -48158,7 +48158,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -48184,7 +48184,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -48210,7 +48210,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -48236,7 +48236,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1663" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48262,7 +48262,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48288,7 +48288,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1665" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48314,7 +48314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48340,7 +48340,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48366,7 +48366,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48392,7 +48392,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48418,7 +48418,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48444,7 +48444,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48470,7 +48470,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1672" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48496,7 +48496,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48522,7 +48522,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48548,7 +48548,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48574,7 +48574,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1676" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48600,7 +48600,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1677" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48626,7 +48626,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1678" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48652,7 +48652,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48678,7 +48678,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48704,7 +48704,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48730,7 +48730,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48756,7 +48756,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48782,7 +48782,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1684" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48808,7 +48808,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48834,7 +48834,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48860,7 +48860,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1687" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48886,7 +48886,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48912,7 +48912,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48938,7 +48938,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48964,7 +48964,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48990,7 +48990,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -49016,7 +49016,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -49042,7 +49042,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -49068,7 +49068,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -49094,7 +49094,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1696" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -49120,7 +49120,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -49146,7 +49146,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -49172,7 +49172,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -49198,7 +49198,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1700" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -49224,7 +49224,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49250,7 +49250,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49276,7 +49276,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49302,7 +49302,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49328,7 +49328,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49354,7 +49354,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49380,7 +49380,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49406,7 +49406,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49432,7 +49432,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1709" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49458,7 +49458,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49484,7 +49484,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49510,7 +49510,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49536,7 +49536,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49562,7 +49562,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49588,7 +49588,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1715" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49614,7 +49614,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49640,7 +49640,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49666,7 +49666,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49692,7 +49692,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49718,7 +49718,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49744,7 +49744,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1721" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49770,7 +49770,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49796,7 +49796,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49822,7 +49822,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49848,7 +49848,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49874,7 +49874,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49900,7 +49900,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49926,7 +49926,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49952,7 +49952,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49978,7 +49978,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -50004,7 +50004,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -50030,7 +50030,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -50056,7 +50056,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -50082,7 +50082,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -50108,7 +50108,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="s">
-        <v>947</v>
+        <v>1169</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -50264,7 +50264,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50290,7 +50290,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50368,7 +50368,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50420,7 +50420,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50472,7 +50472,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1749" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50680,7 +50680,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1757" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50758,7 +50758,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50784,7 +50784,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50836,7 +50836,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50888,7 +50888,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1765" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50940,7 +50940,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -51018,7 +51018,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -51070,7 +51070,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -51278,7 +51278,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51408,7 +51408,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51512,7 +51512,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51538,7 +51538,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51590,7 +51590,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51642,7 +51642,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51720,7 +51720,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51746,7 +51746,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1798" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51772,7 +51772,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51876,7 +51876,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51928,7 +51928,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -52292,7 +52292,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52344,7 +52344,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1821" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52396,7 +52396,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52500,7 +52500,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1827" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52526,7 +52526,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52630,7 +52630,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52656,7 +52656,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52708,7 +52708,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52734,7 +52734,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52760,7 +52760,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52838,7 +52838,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52890,7 +52890,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -53072,7 +53072,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1849" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53254,7 +53254,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53514,7 +53514,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1866" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53774,7 +53774,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1876" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53904,7 +53904,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385444641113</t>
+    <t xml:space="preserve">3.07385492324829</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">3.08614444732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01786661148071</t>
+    <t xml:space="preserve">3.01786732673645</t>
   </si>
   <si>
     <t xml:space="preserve">2.97690033912659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98099732398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131189346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003081321716</t>
+    <t xml:space="preserve">2.98099708557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131165504456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94003105163574</t>
   </si>
   <si>
     <t xml:space="preserve">2.80620670318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86082863807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75841236114502</t>
+    <t xml:space="preserve">2.86082911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75841283798218</t>
   </si>
   <si>
     <t xml:space="preserve">2.73929500579834</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.71744585037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86629104614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76387453079224</t>
+    <t xml:space="preserve">2.866290807724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76387476921082</t>
   </si>
   <si>
     <t xml:space="preserve">2.74475693702698</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">2.7570469379425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71061825752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110127449036</t>
+    <t xml:space="preserve">2.710618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110151290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.76114344596863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72563934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69696283340454</t>
+    <t xml:space="preserve">2.72563910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69696259498596</t>
   </si>
   <si>
     <t xml:space="preserve">2.72290802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62868499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45935678482056</t>
+    <t xml:space="preserve">2.62868523597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45935702323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799112319946</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">2.30095267295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38971352577209</t>
+    <t xml:space="preserve">2.38971400260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.53992438316345</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">2.67511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81713080406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74885368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78162670135498</t>
+    <t xml:space="preserve">2.81713104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7816264629364</t>
   </si>
   <si>
     <t xml:space="preserve">2.68467259407043</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83351755142212</t>
+    <t xml:space="preserve">2.8335177898407</t>
   </si>
   <si>
     <t xml:space="preserve">2.84717297554016</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">2.88404321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88540863990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769864082336</t>
+    <t xml:space="preserve">2.88540816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769840240479</t>
   </si>
   <si>
     <t xml:space="preserve">2.85126972198486</t>
@@ -173,31 +173,31 @@
     <t xml:space="preserve">2.9495894908905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164855003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217445373535</t>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1612503528595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173336982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767855644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217421531677</t>
   </si>
   <si>
     <t xml:space="preserve">3.23635530471802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25001072883606</t>
+    <t xml:space="preserve">3.2500102519989</t>
   </si>
   <si>
     <t xml:space="preserve">3.21040987968445</t>
@@ -206,22 +206,22 @@
     <t xml:space="preserve">3.2226996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23089289665222</t>
+    <t xml:space="preserve">3.2308931350708</t>
   </si>
   <si>
     <t xml:space="preserve">3.22952747344971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895987510681</t>
+    <t xml:space="preserve">3.14076614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895963668823</t>
   </si>
   <si>
     <t xml:space="preserve">3.225430727005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29234266281128</t>
+    <t xml:space="preserve">3.29234290122986</t>
   </si>
   <si>
     <t xml:space="preserve">3.21587181091309</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">3.34559917449951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36608242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
+    <t xml:space="preserve">3.36608266830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
   </si>
   <si>
     <t xml:space="preserve">3.3865659236908</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">3.33330893516541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34833002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375049591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780507087708</t>
+    <t xml:space="preserve">3.3483304977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511591911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375073432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780530929565</t>
   </si>
   <si>
     <t xml:space="preserve">3.26366662979126</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">3.29097747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26022291183472</t>
+    <t xml:space="preserve">3.26022267341614</t>
   </si>
   <si>
     <t xml:space="preserve">3.19182634353638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15620350837708</t>
+    <t xml:space="preserve">3.1562032699585</t>
   </si>
   <si>
     <t xml:space="preserve">3.13482975959778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17330241203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208226203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291913032532</t>
+    <t xml:space="preserve">3.1733021736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3229193687439</t>
   </si>
   <si>
     <t xml:space="preserve">3.34856772422791</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">3.31151986122131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38419103622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4440381526947</t>
+    <t xml:space="preserve">3.38419079780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403719902039</t>
   </si>
   <si>
     <t xml:space="preserve">3.41981410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43406295776367</t>
+    <t xml:space="preserve">3.43406343460083</t>
   </si>
   <si>
     <t xml:space="preserve">3.48108601570129</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">3.4383385181427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45116233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841460227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844012260437</t>
+    <t xml:space="preserve">3.45116257667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4084141254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844036102295</t>
   </si>
   <si>
     <t xml:space="preserve">3.34714269638062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20607614517212</t>
+    <t xml:space="preserve">3.20607566833496</t>
   </si>
   <si>
     <t xml:space="preserve">3.02796030044556</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">2.8997175693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89686751365662</t>
+    <t xml:space="preserve">2.89686727523804</t>
   </si>
   <si>
     <t xml:space="preserve">3.06643319129944</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">3.08495736122131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1319797039032</t>
+    <t xml:space="preserve">3.13197946548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.14195394515991</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">3.02938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84984493255615</t>
+    <t xml:space="preserve">2.84984517097473</t>
   </si>
   <si>
     <t xml:space="preserve">2.95671439170837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06500816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332793235779</t>
+    <t xml:space="preserve">3.06500840187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332817077637</t>
   </si>
   <si>
     <t xml:space="preserve">2.96526384353638</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">2.9552891254425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99233746528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058043479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599886894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757725715637</t>
+    <t xml:space="preserve">2.9923369884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1704523563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757701873779</t>
   </si>
   <si>
     <t xml:space="preserve">3.13625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83702087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91966652870178</t>
+    <t xml:space="preserve">2.83702063560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
     <t xml:space="preserve">2.86551904678345</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">2.84129548072815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87549328804016</t>
+    <t xml:space="preserve">2.87549376487732</t>
   </si>
   <si>
     <t xml:space="preserve">2.83559584617615</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">2.73442625999451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7771737575531</t>
+    <t xml:space="preserve">2.77717423439026</t>
   </si>
   <si>
     <t xml:space="preserve">2.88546824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87406849861145</t>
+    <t xml:space="preserve">2.87406873703003</t>
   </si>
   <si>
     <t xml:space="preserve">2.84272050857544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87834358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821574211121</t>
+    <t xml:space="preserve">2.8783438205719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821598052979</t>
   </si>
   <si>
     <t xml:space="preserve">2.92109107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9410400390625</t>
+    <t xml:space="preserve">2.94103980064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694431304932</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">2.85839486122131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86409401893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707167625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76007509231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80567264556885</t>
+    <t xml:space="preserve">2.86409425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707191467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76007485389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80567216873169</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289915084839</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">2.68597888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62470722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478354454041</t>
+    <t xml:space="preserve">2.62470746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478378295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.54776120185852</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">2.58480930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65605568885803</t>
+    <t xml:space="preserve">2.65605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">2.65463089942932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63610672950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333323478699</t>
+    <t xml:space="preserve">2.63610696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333347320557</t>
   </si>
   <si>
     <t xml:space="preserve">2.5719850063324</t>
@@ -512,73 +512,73 @@
     <t xml:space="preserve">2.44516706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42379307746887</t>
+    <t xml:space="preserve">2.42379331588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.44374227523804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.416668176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941615104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900782585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61045837402344</t>
+    <t xml:space="preserve">2.41666865348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61045813560486</t>
   </si>
   <si>
     <t xml:space="preserve">2.54918622970581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57910990715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55061101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52353811264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465594291687</t>
+    <t xml:space="preserve">2.57910966873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5506112575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57340979576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465618133545</t>
   </si>
   <si>
     <t xml:space="preserve">2.69310355186462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64038133621216</t>
+    <t xml:space="preserve">2.64038181304932</t>
   </si>
   <si>
     <t xml:space="preserve">2.63895630836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62898182868958</t>
+    <t xml:space="preserve">2.62898206710815</t>
   </si>
   <si>
     <t xml:space="preserve">2.63325691223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67172980308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727583885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67315483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7144775390625</t>
+    <t xml:space="preserve">2.67172956466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67315459251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70307779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71447730064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.70735263824463</t>
@@ -587,34 +587,34 @@
     <t xml:space="preserve">2.65178084373474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66887974739075</t>
+    <t xml:space="preserve">2.66888022422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.63753151893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6574809551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486082077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211308479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41524362564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43234276771545</t>
+    <t xml:space="preserve">2.65748071670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486058235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498818397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41524386405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43234300613403</t>
   </si>
   <si>
     <t xml:space="preserve">2.43661761283875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39386987686157</t>
+    <t xml:space="preserve">2.39386963844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.39244508743286</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3511221408844</t>
+    <t xml:space="preserve">2.35112237930298</t>
   </si>
   <si>
     <t xml:space="preserve">2.42236828804016</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">2.57768487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58908414840698</t>
+    <t xml:space="preserve">2.58908438682556</t>
   </si>
   <si>
     <t xml:space="preserve">2.63468170166016</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012613296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297571182251</t>
+    <t xml:space="preserve">2.69737815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012589454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297595024109</t>
   </si>
   <si>
     <t xml:space="preserve">2.72445178031921</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72872638702393</t>
+    <t xml:space="preserve">2.72872614860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.76434969902039</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">2.75580024719238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7116277217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025349617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65035581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760807991028</t>
+    <t xml:space="preserve">2.71162748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6902539730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65035605430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760831832886</t>
   </si>
   <si>
     <t xml:space="preserve">2.58338451385498</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">2.55346131324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52068781852722</t>
+    <t xml:space="preserve">2.5206880569458</t>
   </si>
   <si>
     <t xml:space="preserve">2.60618329048157</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">2.54063677787781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501394271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49788928031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50643873214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53351235389709</t>
+    <t xml:space="preserve">2.50501370429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49788951873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50643849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53351259231567</t>
   </si>
   <si>
     <t xml:space="preserve">2.57625985145569</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">2.60048389434814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59193396568298</t>
+    <t xml:space="preserve">2.59193420410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.58195948600769</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">2.55916094779968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58623433113098</t>
+    <t xml:space="preserve">2.58623456954956</t>
   </si>
   <si>
     <t xml:space="preserve">2.53636193275452</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">2.68740391731262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69452834129333</t>
+    <t xml:space="preserve">2.69452857971191</t>
   </si>
   <si>
     <t xml:space="preserve">2.75722503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77147436141968</t>
+    <t xml:space="preserve">2.77147459983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.79712295532227</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">2.78857350349426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79997301101685</t>
+    <t xml:space="preserve">2.79997277259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.83132100105286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9054172039032</t>
+    <t xml:space="preserve">2.90541696548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.03508520126343</t>
@@ -794,34 +794,34 @@
     <t xml:space="preserve">3.07783269882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16190338134766</t>
+    <t xml:space="preserve">3.16760277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16190314292908</t>
   </si>
   <si>
     <t xml:space="preserve">3.16047811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21890020370483</t>
+    <t xml:space="preserve">3.21889996528625</t>
   </si>
   <si>
     <t xml:space="preserve">3.22174954414368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27589678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159666061401</t>
+    <t xml:space="preserve">3.27589726448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159642219543</t>
   </si>
   <si>
     <t xml:space="preserve">3.26877188682556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23172426223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12913012504578</t>
+    <t xml:space="preserve">3.23172402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12913036346436</t>
   </si>
   <si>
     <t xml:space="preserve">3.19610118865967</t>
@@ -830,25 +830,25 @@
     <t xml:space="preserve">3.10063171386719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19752597808838</t>
+    <t xml:space="preserve">3.1975257396698</t>
   </si>
   <si>
     <t xml:space="preserve">3.23884892463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22602462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157137870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32576966285706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864428520203</t>
+    <t xml:space="preserve">3.22602438926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157114028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32576942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302121162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864476203918</t>
   </si>
   <si>
     <t xml:space="preserve">3.3400182723999</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">3.39559006690979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35569262504578</t>
+    <t xml:space="preserve">3.3556923866272</t>
   </si>
   <si>
     <t xml:space="preserve">3.23457431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27019739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08923196792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06358337402344</t>
+    <t xml:space="preserve">3.27019762992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0892322063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06358361244202</t>
   </si>
   <si>
     <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706664085388</t>
+    <t xml:space="preserve">3.09706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13886022567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003732681274</t>
+    <t xml:space="preserve">3.13886046409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462542533875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003708839417</t>
   </si>
   <si>
     <t xml:space="preserve">3.1186842918396</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">3.04806733131409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99762630462646</t>
+    <t xml:space="preserve">2.99762582778931</t>
   </si>
   <si>
     <t xml:space="preserve">3.00627326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97744989395142</t>
+    <t xml:space="preserve">2.97744965553284</t>
   </si>
   <si>
     <t xml:space="preserve">2.91836214065552</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">2.84918618202209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92700910568237</t>
+    <t xml:space="preserve">2.92700886726379</t>
   </si>
   <si>
     <t xml:space="preserve">2.90683269500732</t>
@@ -938,46 +938,46 @@
     <t xml:space="preserve">2.86936259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.878009557724</t>
+    <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85350942611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87080359458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82468628883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79298067092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76415705680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81027483940125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80018663406372</t>
+    <t xml:space="preserve">2.85350966453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87080383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8246865272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79298043251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76415753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81027460098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80018639564514</t>
   </si>
   <si>
     <t xml:space="preserve">2.79153966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72956967353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75262784957886</t>
+    <t xml:space="preserve">2.72956943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75262808799744</t>
   </si>
   <si>
     <t xml:space="preserve">2.75983357429504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74686360359192</t>
+    <t xml:space="preserve">2.7468638420105</t>
   </si>
   <si>
     <t xml:space="preserve">2.95439124107361</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">2.92124462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92845058441162</t>
+    <t xml:space="preserve">2.92845034599304</t>
   </si>
   <si>
     <t xml:space="preserve">2.92556810379028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342169761658</t>
+    <t xml:space="preserve">2.83189225196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.843421459198</t>
   </si>
   <si>
     <t xml:space="preserve">2.80450987815857</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865718841553</t>
+    <t xml:space="preserve">2.78865694999695</t>
   </si>
   <si>
     <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80883312225342</t>
+    <t xml:space="preserve">2.80883359909058</t>
   </si>
   <si>
     <t xml:space="preserve">2.84053897857666</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">2.85495066642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86503911018372</t>
+    <t xml:space="preserve">2.86503934860229</t>
   </si>
   <si>
     <t xml:space="preserve">2.87656855583191</t>
@@ -1043,34 +1043,34 @@
     <t xml:space="preserve">2.76848077774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218729972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72668695449829</t>
+    <t xml:space="preserve">2.70218706130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72668719291687</t>
   </si>
   <si>
     <t xml:space="preserve">2.71371650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7252459526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68056964874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336368560791</t>
+    <t xml:space="preserve">2.72524571418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68056988716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480492591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336416244507</t>
   </si>
   <si>
     <t xml:space="preserve">2.65895199775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67624640464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406932830811</t>
+    <t xml:space="preserve">2.67624616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406908988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
@@ -1079,37 +1079,37 @@
     <t xml:space="preserve">2.79874539375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74542212486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78577494621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92268562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02500820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02644968032837</t>
+    <t xml:space="preserve">2.74542188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78577470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92268586158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02500796318054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02644944190979</t>
   </si>
   <si>
     <t xml:space="preserve">3.06968474388123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1057140827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12156653404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17056655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14174294471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597846031189</t>
+    <t xml:space="preserve">3.10571360588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12156629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17056632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14174318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850788116455</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">3.07689046859741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08409690856934</t>
+    <t xml:space="preserve">3.08409667015076</t>
   </si>
   <si>
     <t xml:space="preserve">3.07400798797607</t>
@@ -1133,37 +1133,37 @@
     <t xml:space="preserve">3.05383157730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17921376228333</t>
+    <t xml:space="preserve">3.17921328544617</t>
   </si>
   <si>
     <t xml:space="preserve">3.12589001655579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05527257919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07977294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14894890785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16191959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14750742912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09994888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453722000122</t>
+    <t xml:space="preserve">3.05527281761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07977342605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14894866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16191911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1475076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0999493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.15903663635254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15471291542053</t>
+    <t xml:space="preserve">3.15471339225769</t>
   </si>
   <si>
     <t xml:space="preserve">3.12877249717712</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">3.11580181121826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10427260398865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012553215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815505981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168517112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78433394432068</t>
+    <t xml:space="preserve">3.10427284240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815529823303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483202934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9716854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7843337059021</t>
   </si>
   <si>
     <t xml:space="preserve">2.82180380821228</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">2.88233304023743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85062718391418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8290102481842</t>
+    <t xml:space="preserve">2.85062742233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82900977134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324504852295</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">2.70506954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71227502822876</t>
+    <t xml:space="preserve">2.71227526664734</t>
   </si>
   <si>
     <t xml:space="preserve">2.65606999397278</t>
@@ -1229,46 +1229,46 @@
     <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76703953742981</t>
+    <t xml:space="preserve">2.76704001426697</t>
   </si>
   <si>
     <t xml:space="preserve">2.78505420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72740769386292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69498133659363</t>
+    <t xml:space="preserve">2.72740745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69498109817505</t>
   </si>
   <si>
     <t xml:space="preserve">2.73461365699768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7057900428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7310106754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72020173072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79225993156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84630393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.774245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77064251899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70939302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74181914329529</t>
+    <t xml:space="preserve">2.70579028129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73101043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72020196914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79226016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84630370140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77424550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77064275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.709392786026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74181938171387</t>
   </si>
   <si>
     <t xml:space="preserve">2.71299600601196</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">2.63373160362244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64093780517578</t>
+    <t xml:space="preserve">2.62652564048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6409375667572</t>
   </si>
   <si>
     <t xml:space="preserve">2.65534901618958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64814329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58689403533936</t>
+    <t xml:space="preserve">2.64814376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689379692078</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248210906982</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">2.56167364120483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55086493492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56887912750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43557143211365</t>
+    <t xml:space="preserve">2.55086445808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56887936592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43557167053223</t>
   </si>
   <si>
     <t xml:space="preserve">2.37432169914246</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">2.41395378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36351275444031</t>
+    <t xml:space="preserve">2.36351299285889</t>
   </si>
   <si>
     <t xml:space="preserve">2.35991024971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29505777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4499831199646</t>
+    <t xml:space="preserve">2.29505753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44998335838318</t>
   </si>
   <si>
     <t xml:space="preserve">2.3527045249939</t>
@@ -1355,31 +1355,31 @@
     <t xml:space="preserve">2.42115950584412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50762987136841</t>
+    <t xml:space="preserve">2.50762963294983</t>
   </si>
   <si>
     <t xml:space="preserve">2.59409976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56527638435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63012886047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65174651145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62292313575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60130548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60851144790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63733458518982</t>
+    <t xml:space="preserve">2.56527614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63012909889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65174627304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62292289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60130524635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60851120948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6373348236084</t>
   </si>
   <si>
     <t xml:space="preserve">2.68417239189148</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">2.66615796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69137811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67696666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73281192779541</t>
+    <t xml:space="preserve">2.69137835502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67696642875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73281216621399</t>
   </si>
   <si>
     <t xml:space="preserve">2.62172198295593</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">2.48841404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.403244972229</t>
+    <t xml:space="preserve">2.40324473381042</t>
   </si>
   <si>
     <t xml:space="preserve">2.43657207489014</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">2.45879006385803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39213585853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40694832801819</t>
+    <t xml:space="preserve">2.39213609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40694808959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.36991810798645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29956150054932</t>
+    <t xml:space="preserve">2.29956126213074</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068930625916</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">2.37732434272766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38843321800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4291660785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805744171143</t>
+    <t xml:space="preserve">2.38843297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42916631698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805720329285</t>
   </si>
   <si>
     <t xml:space="preserve">2.46989917755127</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">2.5032262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52174115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53285026550293</t>
+    <t xml:space="preserve">2.52174091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53285002708435</t>
   </si>
   <si>
     <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52544403076172</t>
+    <t xml:space="preserve">2.5254442691803</t>
   </si>
   <si>
     <t xml:space="preserve">2.45508718490601</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">2.44768095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53655290603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4773051738739</t>
+    <t xml:space="preserve">2.53655314445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47730493545532</t>
   </si>
   <si>
     <t xml:space="preserve">2.51433515548706</t>
@@ -1490,43 +1490,43 @@
     <t xml:space="preserve">2.48100805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46619606018066</t>
+    <t xml:space="preserve">2.46619582176208</t>
   </si>
   <si>
     <t xml:space="preserve">2.39583921432495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41065144538879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35140347480774</t>
+    <t xml:space="preserve">2.41065120697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35140323638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.36621522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34399724006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35880899429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35510659217834</t>
+    <t xml:space="preserve">2.34399700164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35880923271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35510635375977</t>
   </si>
   <si>
     <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31067037582397</t>
+    <t xml:space="preserve">2.30696725845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39954233169556</t>
+    <t xml:space="preserve">2.39954209327698</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102698326111</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">2.29585838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26993727684021</t>
+    <t xml:space="preserve">2.28104615211487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26993703842163</t>
   </si>
   <si>
     <t xml:space="preserve">2.30326414108276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32918548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27734327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26623439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29215502738953</t>
+    <t xml:space="preserve">2.32918524742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27734351158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2662341594696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29215526580811</t>
   </si>
   <si>
     <t xml:space="preserve">2.27364015579224</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">2.38473010063171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698618888855</t>
+    <t xml:space="preserve">2.20698642730713</t>
   </si>
   <si>
     <t xml:space="preserve">2.24031329154968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15514469146729</t>
+    <t xml:space="preserve">2.15514445304871</t>
   </si>
   <si>
     <t xml:space="preserve">2.13292670249939</t>
@@ -1595,55 +1595,55 @@
     <t xml:space="preserve">2.1033022403717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09959959983826</t>
+    <t xml:space="preserve">2.09959936141968</t>
   </si>
   <si>
     <t xml:space="preserve">2.08849048614502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10700559616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0625696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98850929737091</t>
+    <t xml:space="preserve">2.10700535774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06256937980652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98850953578949</t>
   </si>
   <si>
     <t xml:space="preserve">1.95147943496704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02553963661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06627225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04775738716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922310829163</t>
+    <t xml:space="preserve">2.02553939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06627249717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04775762557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997561454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922334671021</t>
   </si>
   <si>
     <t xml:space="preserve">2.14403557777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13662910461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18847155570984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439242362976</t>
+    <t xml:space="preserve">2.13662934303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439218521118</t>
   </si>
   <si>
     <t xml:space="preserve">2.23290729522705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25512552261353</t>
+    <t xml:space="preserve">2.25512528419495</t>
   </si>
   <si>
     <t xml:space="preserve">2.20328330993652</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">2.19958066940308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809506416321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811423301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070847511292</t>
+    <t xml:space="preserve">2.21809530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811399459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367825508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070823669434</t>
   </si>
   <si>
     <t xml:space="preserve">2.24771928787231</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">2.51063227653503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65504908561707</t>
+    <t xml:space="preserve">2.65504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">2.68096995353699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60320711135864</t>
+    <t xml:space="preserve">2.60320734977722</t>
   </si>
   <si>
     <t xml:space="preserve">2.62912797927856</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">2.62542510032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71800017356873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70318818092346</t>
+    <t xml:space="preserve">2.71799993515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70318794250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.7291088104248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69207906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71429705619812</t>
+    <t xml:space="preserve">2.69207882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71429681777954</t>
   </si>
   <si>
     <t xml:space="preserve">2.75502991676331</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">2.8031690120697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81798076629639</t>
+    <t xml:space="preserve">2.81798100471497</t>
   </si>
   <si>
     <t xml:space="preserve">2.84390163421631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87352585792542</t>
+    <t xml:space="preserve">2.87352609634399</t>
   </si>
   <si>
     <t xml:space="preserve">2.86241674423218</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">2.88093185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76243615150452</t>
+    <t xml:space="preserve">2.76243591308594</t>
   </si>
   <si>
     <t xml:space="preserve">2.76984190940857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79946565628052</t>
+    <t xml:space="preserve">2.79946613311768</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205965995789</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">2.75873279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85871386528015</t>
+    <t xml:space="preserve">2.85871362686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.90314984321594</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">2.89574384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90685296058655</t>
+    <t xml:space="preserve">2.90685272216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.88833785057068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96239805221558</t>
+    <t xml:space="preserve">2.962397813797</t>
   </si>
   <si>
     <t xml:space="preserve">2.98091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91796207427979</t>
+    <t xml:space="preserve">2.91796183586121</t>
   </si>
   <si>
     <t xml:space="preserve">2.94758582115173</t>
@@ -1781,37 +1781,37 @@
     <t xml:space="preserve">2.95128893852234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9364767074585</t>
+    <t xml:space="preserve">2.93647646903992</t>
   </si>
   <si>
     <t xml:space="preserve">2.95499181747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93277359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91055583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720956802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94018006324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89944648742676</t>
+    <t xml:space="preserve">2.93277382850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91055607795715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96980404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720980644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9401798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89944672584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.81057500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86611986160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80687212944031</t>
+    <t xml:space="preserve">2.8661196231842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80687189102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.83279299736023</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">2.71059393882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70689105987549</t>
+    <t xml:space="preserve">2.70689082145691</t>
   </si>
   <si>
     <t xml:space="preserve">2.61061310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64023685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6365339756012</t>
+    <t xml:space="preserve">2.6402370929718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63653373718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.63283085823059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61801910400391</t>
+    <t xml:space="preserve">2.61801886558533</t>
   </si>
   <si>
     <t xml:space="preserve">2.69578194618225</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">2.6143159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56988000869751</t>
+    <t xml:space="preserve">2.56988024711609</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211716651917</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587731361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.299480676651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2177734375</t>
+    <t xml:space="preserve">2.19587707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29948091506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21777319908142</t>
   </si>
   <si>
     <t xml:space="preserve">2.10882997512817</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326696395874</t>
+    <t xml:space="preserve">2.09326672554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.12050247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13995695114136</t>
+    <t xml:space="preserve">2.13995671272278</t>
   </si>
   <si>
     <t xml:space="preserve">2.12828421592712</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">2.05046772956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04657673835754</t>
+    <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03490424156189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435872077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03101348876953</t>
+    <t xml:space="preserve">2.05435848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03101325035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05824947357178</t>
+    <t xml:space="preserve">2.0582492351532</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
@@ -1937,49 +1937,49 @@
     <t xml:space="preserve">2.22944593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1866466999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9687602519989</t>
+    <t xml:space="preserve">2.18664646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96876001358032</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92985188961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02712249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94152414798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84425365924835</t>
+    <t xml:space="preserve">1.92985165119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02712273597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94152438640594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84425342082977</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76643705368042</t>
+    <t xml:space="preserve">1.76643693447113</t>
   </si>
   <si>
     <t xml:space="preserve">1.8092360496521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75087380409241</t>
+    <t xml:space="preserve">1.75087368488312</t>
   </si>
   <si>
     <t xml:space="preserve">1.74698269367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69251132011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78978180885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82090866565704</t>
+    <t xml:space="preserve">1.69251108169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78978192806244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82090854644775</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71974718570709</t>
+    <t xml:space="preserve">1.7119654417038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7197470664978</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">1.78589117527008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73141944408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585619449615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7353104352951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78200042247772</t>
+    <t xml:space="preserve">1.73141932487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71585607528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73531031608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78200030326843</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
@@ -2021,31 +2021,31 @@
     <t xml:space="preserve">1.80145454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84036302566528</t>
+    <t xml:space="preserve">1.84036290645599</t>
   </si>
   <si>
     <t xml:space="preserve">1.85592615604401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83647203445435</t>
+    <t xml:space="preserve">1.83647191524506</t>
   </si>
   <si>
     <t xml:space="preserve">1.87927114963531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79756367206573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77032792568207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75476479530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75865542888641</t>
+    <t xml:space="preserve">1.79756355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77032780647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869017124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75476455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75865530967712</t>
   </si>
   <si>
     <t xml:space="preserve">1.76254630088806</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">1.80534529685974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81701791286469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82479953765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91428875923157</t>
+    <t xml:space="preserve">1.8170177936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8247994184494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91428852081299</t>
   </si>
   <si>
     <t xml:space="preserve">1.93374240398407</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">1.87538039684296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90650701522827</t>
+    <t xml:space="preserve">1.90650677680969</t>
   </si>
   <si>
     <t xml:space="preserve">1.89483428001404</t>
@@ -2081,10 +2081,10 @@
     <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92207038402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01155948638916</t>
+    <t xml:space="preserve">1.92207026481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01155924797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.16719269752502</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">2.15551996231079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19831919670105</t>
+    <t xml:space="preserve">2.19831895828247</t>
   </si>
   <si>
     <t xml:space="preserve">2.17108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14384794235229</t>
+    <t xml:space="preserve">2.14384770393372</t>
   </si>
   <si>
     <t xml:space="preserve">2.11272072792053</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">2.08548521995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01545023918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15941119194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13606595993042</t>
+    <t xml:space="preserve">2.01545000076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821425437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15941095352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13606572151184</t>
   </si>
   <si>
     <t xml:space="preserve">2.01934099197388</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">1.87148940563202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91039776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596113681793</t>
+    <t xml:space="preserve">1.91039752960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596101760864</t>
   </si>
   <si>
     <t xml:space="preserve">1.89872527122498</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988698959351</t>
+    <t xml:space="preserve">1.99988675117493</t>
   </si>
   <si>
     <t xml:space="preserve">1.95708787441254</t>
@@ -2165,25 +2165,25 @@
     <t xml:space="preserve">1.96486949920654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99210524559021</t>
+    <t xml:space="preserve">1.99210500717163</t>
   </si>
   <si>
     <t xml:space="preserve">1.72752869129181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68862056732178</t>
+    <t xml:space="preserve">1.68862044811249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59524035453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54232513904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48941004276276</t>
+    <t xml:space="preserve">1.59524047374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.542325258255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940992355347</t>
   </si>
   <si>
     <t xml:space="preserve">1.45361435413361</t>
@@ -2192,31 +2192,31 @@
     <t xml:space="preserve">1.33844566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30420637130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27619242668152</t>
+    <t xml:space="preserve">1.30420649051666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27619230747223</t>
   </si>
   <si>
     <t xml:space="preserve">1.09098875522614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16102385520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08009457588196</t>
+    <t xml:space="preserve">1.16102373600006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08009445667267</t>
   </si>
   <si>
     <t xml:space="preserve">1.05986225605011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08476364612579</t>
+    <t xml:space="preserve">1.0847635269165</t>
   </si>
   <si>
     <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22483336925507</t>
+    <t xml:space="preserve">1.22483348846436</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">1.32288241386414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28864300251007</t>
+    <t xml:space="preserve">1.28864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">1.28397417068481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29331195354462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39291739463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36179077625275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062893867493</t>
+    <t xml:space="preserve">1.29331207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39291727542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36179065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062905788422</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">1.29175567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28241777420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22950255870819</t>
+    <t xml:space="preserve">1.28241765499115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2295024394989</t>
   </si>
   <si>
     <t xml:space="preserve">1.23884046077728</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">1.17503070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13300967216492</t>
+    <t xml:space="preserve">1.1330099105835</t>
   </si>
   <si>
     <t xml:space="preserve">1.10343956947327</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">1.05674958229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06764400005341</t>
+    <t xml:space="preserve">1.06764388084412</t>
   </si>
   <si>
     <t xml:space="preserve">1.12211549282074</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14234793186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15012955665588</t>
+    <t xml:space="preserve">1.14234781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15012943744659</t>
   </si>
   <si>
     <t xml:space="preserve">1.13923513889313</t>
@@ -2336,10 +2336,10 @@
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708672523499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27930498123169</t>
+    <t xml:space="preserve">1.28708684444427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27930521965027</t>
   </si>
   <si>
     <t xml:space="preserve">1.17969989776611</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">1.16413640975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23572778701782</t>
+    <t xml:space="preserve">1.23572766780853</t>
   </si>
   <si>
     <t xml:space="preserve">1.20615744590759</t>
@@ -2366,49 +2366,49 @@
     <t xml:space="preserve">1.17814350128174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18592512607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612258434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1579110622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14079141616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18436872959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17036187648773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14546048641205</t>
+    <t xml:space="preserve">1.18592524528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612246513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15791118144989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1407915353775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18436884880066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17036175727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14546060562134</t>
   </si>
   <si>
     <t xml:space="preserve">1.16724920272827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17347455024719</t>
+    <t xml:space="preserve">1.1734744310379</t>
   </si>
   <si>
     <t xml:space="preserve">1.15168583393097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17191815376282</t>
+    <t xml:space="preserve">1.17191827297211</t>
   </si>
   <si>
     <t xml:space="preserve">1.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1563549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12522804737091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565782546997</t>
+    <t xml:space="preserve">1.15635478496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1252281665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565794467926</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">1.06297492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04896795749664</t>
+    <t xml:space="preserve">1.04896783828735</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410154819489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07075667381287</t>
+    <t xml:space="preserve">1.07075655460358</t>
   </si>
   <si>
     <t xml:space="preserve">1.09721410274506</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">1.04585528373718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03962993621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04118633270264</t>
+    <t xml:space="preserve">1.03963005542755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04118621349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
@@ -2462,13 +2462,13 @@
     <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996052622795105</t>
+    <t xml:space="preserve">0.996052503585815</t>
   </si>
   <si>
     <t xml:space="preserve">1.01628494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00850331783295</t>
+    <t xml:space="preserve">1.00850319862366</t>
   </si>
   <si>
     <t xml:space="preserve">1.01005959510803</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">1.00072169303894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991383671760559</t>
+    <t xml:space="preserve">0.99138355255127</t>
   </si>
   <si>
     <t xml:space="preserve">0.966482281684875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964925944805145</t>
+    <t xml:space="preserve">0.964925825595856</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954031586647034</t>
+    <t xml:space="preserve">0.954031646251678</t>
   </si>
   <si>
     <t xml:space="preserve">0.975820243358612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827334880829</t>
+    <t xml:space="preserve">0.989827215671539</t>
   </si>
   <si>
     <t xml:space="preserve">0.969595015048981</t>
@@ -2504,22 +2504,22 @@
     <t xml:space="preserve">0.949362635612488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968038558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957144379615784</t>
+    <t xml:space="preserve">0.96803867816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957144260406494</t>
   </si>
   <si>
     <t xml:space="preserve">0.980489313602448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999165296554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05830597877502</t>
+    <t xml:space="preserve">0.999165415763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06453120708466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05830585956573</t>
   </si>
   <si>
     <t xml:space="preserve">1.02406656742096</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">0.904228985309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879327714443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887109398841858</t>
+    <t xml:space="preserve">0.879327654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887109279632568</t>
   </si>
   <si>
     <t xml:space="preserve">0.888665616512299</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">0.891778409481049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835750341415405</t>
+    <t xml:space="preserve">0.83575040102005</t>
   </si>
   <si>
     <t xml:space="preserve">0.80306738615036</t>
@@ -2588,25 +2588,25 @@
     <t xml:space="preserve">0.915123283863068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940024554729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983602106571198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978932917118073</t>
+    <t xml:space="preserve">0.940024673938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977376580238342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963369727134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983601987361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978933036327362</t>
   </si>
   <si>
     <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961813151836395</t>
+    <t xml:space="preserve">0.961813271045685</t>
   </si>
   <si>
     <t xml:space="preserve">0.946249961853027</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">0.943137288093567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930686771869659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952475190162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927573919296265</t>
+    <t xml:space="preserve">0.93068665266037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952475309371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927574038505554</t>
   </si>
   <si>
     <t xml:space="preserve">0.926017701625824</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">0.947806417942047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919792413711548</t>
+    <t xml:space="preserve">0.919792294502258</t>
   </si>
   <si>
     <t xml:space="preserve">0.913567006587982</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">0.916679680347443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8995600938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918236017227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908897936344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894890904426575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910454332828522</t>
+    <t xml:space="preserve">0.899560034275055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918235957622528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908898055553436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894890964031219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910454273223877</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">1.05363690853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13767898082733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15946745872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12989723682404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10032677650452</t>
+    <t xml:space="preserve">1.13767874240875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15946757793427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12989711761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10032689571381</t>
   </si>
   <si>
     <t xml:space="preserve">1.09877049922943</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">1.15479850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31198799610138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24662220478058</t>
+    <t xml:space="preserve">1.31198811531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907278060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24662208557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.25284743309021</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">1.2544037103653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22638976573944</t>
+    <t xml:space="preserve">1.22638988494873</t>
   </si>
   <si>
     <t xml:space="preserve">1.23105883598328</t>
@@ -2726,28 +2726,28 @@
     <t xml:space="preserve">1.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25751650333405</t>
+    <t xml:space="preserve">1.25751662254333</t>
   </si>
   <si>
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307975292206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36023437976837</t>
+    <t xml:space="preserve">1.27307987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36023426055908</t>
   </si>
   <si>
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40381169319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37112855911255</t>
+    <t xml:space="preserve">1.40069890022278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40381181240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37112867832184</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">1.39758634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3913608789444</t>
+    <t xml:space="preserve">1.39136099815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.40536797046661</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">1.4380509853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52053666114807</t>
+    <t xml:space="preserve">1.52053654193878</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022310256958</t>
+    <t xml:space="preserve">1.56022322177887</t>
   </si>
   <si>
     <t xml:space="preserve">1.58745872974396</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">1.53765618801117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51431131362915</t>
+    <t xml:space="preserve">1.51431119441986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50341701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497317314148</t>
+    <t xml:space="preserve">1.50497329235077</t>
   </si>
   <si>
     <t xml:space="preserve">1.49096620082855</t>
@@ -71018,6 +71018,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6913078704</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>248463</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>2.76500010490417</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>2.71499991416931</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>2.76500010490417</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1550</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -44,43 +44,43 @@
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614468574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01786684989929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690057754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98099756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131165504456</t>
+    <t xml:space="preserve">3.08614444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01786708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690033912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98099732398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131189346313</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003081321716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620694160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86082887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7584125995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73929476737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69013476371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71744608879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86629104614258</t>
+    <t xml:space="preserve">2.80620670318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86082863807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75841212272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73929452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69013500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71744585037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86629128456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.76387476921082</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">2.75704741477966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71061825752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110127449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76114368438721</t>
+    <t xml:space="preserve">2.71061849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76114344596863</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563910484314</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">2.69696259498596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290825843811</t>
+    <t xml:space="preserve">2.72290778160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.62868523597717</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">2.45935702323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799112319946</t>
+    <t xml:space="preserve">2.45799136161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.30095291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38971376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50442028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67511391639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74885368347168</t>
+    <t xml:space="preserve">2.38971352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50441980361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67511415481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81713080406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
   </si>
   <si>
     <t xml:space="preserve">2.78162670135498</t>
@@ -146,109 +146,109 @@
     <t xml:space="preserve">2.68467259407043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86219453811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83351755142212</t>
+    <t xml:space="preserve">2.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8335177898407</t>
   </si>
   <si>
     <t xml:space="preserve">2.84717345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88404273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769864082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85126972198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94685840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94958972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124987602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173289299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767903327942</t>
+    <t xml:space="preserve">2.88404321670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540863990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85126996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685864448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9495894908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767879486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.17900228500366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17217397689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635530471802</t>
+    <t xml:space="preserve">3.17217421531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2363555431366</t>
   </si>
   <si>
     <t xml:space="preserve">3.25001096725464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21040964126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269940376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089289665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952723503113</t>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2308931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
   </si>
   <si>
     <t xml:space="preserve">3.14076638221741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14895963668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543048858643</t>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22543096542358</t>
   </si>
   <si>
     <t xml:space="preserve">3.29234290122986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21587204933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463242530823</t>
+    <t xml:space="preserve">3.21587181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463314056396</t>
   </si>
   <si>
     <t xml:space="preserve">3.27732157707214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34559941291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608266830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
+    <t xml:space="preserve">3.34559965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608242988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
   </si>
   <si>
     <t xml:space="preserve">3.38656568527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833002090454</t>
+    <t xml:space="preserve">3.33330941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833025932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.32511568069458</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">3.32375049591064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29780507087708</t>
+    <t xml:space="preserve">3.29780530929565</t>
   </si>
   <si>
     <t xml:space="preserve">3.26366639137268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29097723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022291183472</t>
+    <t xml:space="preserve">3.29097771644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022267341614</t>
   </si>
   <si>
     <t xml:space="preserve">3.19182634353638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15620350837708</t>
+    <t xml:space="preserve">3.15620303153992</t>
   </si>
   <si>
     <t xml:space="preserve">3.13482975959778</t>
@@ -281,70 +281,70 @@
     <t xml:space="preserve">3.17330265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09208154678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1490786075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291913032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856772422791</t>
+    <t xml:space="preserve">3.09208202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32291960716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856748580933</t>
   </si>
   <si>
     <t xml:space="preserve">3.33431839942932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31152009963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419079780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44403767585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406319618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.476811170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4383385181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841436386108</t>
+    <t xml:space="preserve">3.31151986122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403791427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981387138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406367301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108553886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681021690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833804130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841484069824</t>
   </si>
   <si>
     <t xml:space="preserve">3.39844012260437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714341163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607590675354</t>
+    <t xml:space="preserve">3.34714317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607566833496</t>
   </si>
   <si>
     <t xml:space="preserve">3.02796030044556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246482849121</t>
+    <t xml:space="preserve">2.94246506690979</t>
   </si>
   <si>
     <t xml:space="preserve">2.8997175693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89686727523804</t>
+    <t xml:space="preserve">2.89686751365662</t>
   </si>
   <si>
     <t xml:space="preserve">3.06643319129944</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">3.08495712280273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1319797039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195370674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938532829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984493255615</t>
+    <t xml:space="preserve">3.13197946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984517097473</t>
   </si>
   <si>
     <t xml:space="preserve">2.95671415328979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06500816345215</t>
+    <t xml:space="preserve">3.06500840187073</t>
   </si>
   <si>
     <t xml:space="preserve">3.16332793235779</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">2.99233722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12058043479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599863052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757701873779</t>
+    <t xml:space="preserve">3.12058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1704523563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757749557495</t>
   </si>
   <si>
     <t xml:space="preserve">3.13625431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9495894908905</t>
+    <t xml:space="preserve">2.94958925247192</t>
   </si>
   <si>
     <t xml:space="preserve">2.83702111244202</t>
@@ -407,115 +407,115 @@
     <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86551904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90399241447449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84129548072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83559608459473</t>
+    <t xml:space="preserve">2.86551928520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90399217605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549376487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83559560775757</t>
   </si>
   <si>
     <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73442625999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77717399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88546824455261</t>
+    <t xml:space="preserve">2.73442649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771737575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88546848297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.87406849861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84272027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94103980064392</t>
+    <t xml:space="preserve">2.84272050857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92109084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9410400390625</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85839462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409401893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707167625427</t>
+    <t xml:space="preserve">2.85839438438416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409425735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707191467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.76007485389709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80567240715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289938926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75865030288696</t>
+    <t xml:space="preserve">2.80567216873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75865006446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.77859902381897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68597912788391</t>
+    <t xml:space="preserve">2.68597888946533</t>
   </si>
   <si>
     <t xml:space="preserve">2.62470746040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59478354454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5477614402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480954170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605568885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463089942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60333323478699</t>
+    <t xml:space="preserve">2.59478402137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54776167869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605521202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60333347320557</t>
   </si>
   <si>
     <t xml:space="preserve">2.5719850063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45086669921875</t>
+    <t xml:space="preserve">2.45086693763733</t>
   </si>
   <si>
     <t xml:space="preserve">2.44516682624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42379307746887</t>
+    <t xml:space="preserve">2.42379331588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.44374203681946</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">2.41666841506958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45941591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900782585144</t>
+    <t xml:space="preserve">2.45941615104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900758743286</t>
   </si>
   <si>
     <t xml:space="preserve">2.61045813560486</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">2.5506112575531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5235378742218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57341003417969</t>
+    <t xml:space="preserve">2.52353763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57341027259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.64465618133545</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">2.64038157463074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63895630836487</t>
+    <t xml:space="preserve">2.63895654678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.62898206710815</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">2.63325691223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67172956466675</t>
+    <t xml:space="preserve">2.67172980308533</t>
   </si>
   <si>
     <t xml:space="preserve">2.74867558479309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73727631568909</t>
+    <t xml:space="preserve">2.73727583885193</t>
   </si>
   <si>
     <t xml:space="preserve">2.67315459251404</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">2.70307779312134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71447730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735263824463</t>
+    <t xml:space="preserve">2.7144775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735287666321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65178060531616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66887998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753128051758</t>
+    <t xml:space="preserve">2.66887974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
   </si>
   <si>
     <t xml:space="preserve">2.65748071670532</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">2.56486058235168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52211260795593</t>
+    <t xml:space="preserve">2.52211284637451</t>
   </si>
   <si>
     <t xml:space="preserve">2.51498818397522</t>
@@ -611,34 +611,31 @@
     <t xml:space="preserve">2.41524362564087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43234300613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43661761283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39386963844299</t>
+    <t xml:space="preserve">2.43234276771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43661737442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39386987686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.39244484901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799136161804</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.3511221408844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42236828804016</t>
+    <t xml:space="preserve">2.42236852645874</t>
   </si>
   <si>
     <t xml:space="preserve">2.53066253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57768535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58908414840698</t>
+    <t xml:space="preserve">2.57768487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58908438682556</t>
   </si>
   <si>
     <t xml:space="preserve">2.63468170166016</t>
@@ -647,37 +644,37 @@
     <t xml:space="preserve">2.69595336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68027925491333</t>
+    <t xml:space="preserve">2.68027949333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012589454651</t>
+    <t xml:space="preserve">2.69737863540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012613296509</t>
   </si>
   <si>
     <t xml:space="preserve">2.74297595024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72445154190063</t>
+    <t xml:space="preserve">2.72445178031921</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434969902039</t>
+    <t xml:space="preserve">2.7287266254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434993743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.75152540206909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75580024719238</t>
+    <t xml:space="preserve">2.7558000087738</t>
   </si>
   <si>
     <t xml:space="preserve">2.71162748336792</t>
@@ -689,7 +686,7 @@
     <t xml:space="preserve">2.65035605430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60760807991028</t>
+    <t xml:space="preserve">2.60760831832886</t>
   </si>
   <si>
     <t xml:space="preserve">2.58338451385498</t>
@@ -698,13 +695,13 @@
     <t xml:space="preserve">2.5534610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52068829536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60618329048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058573722839</t>
+    <t xml:space="preserve">2.5206880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60618352890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058597564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.54491138458252</t>
@@ -713,34 +710,34 @@
     <t xml:space="preserve">2.54063677787781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501394271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49788951873779</t>
+    <t xml:space="preserve">2.50501370429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49788928031921</t>
   </si>
   <si>
     <t xml:space="preserve">2.50643849372864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53351235389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57625985145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048365592957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193420410156</t>
+    <t xml:space="preserve">2.53351211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57626008987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193396568298</t>
   </si>
   <si>
     <t xml:space="preserve">2.58195972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5591607093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58623433113098</t>
+    <t xml:space="preserve">2.55916094779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58623480796814</t>
   </si>
   <si>
     <t xml:space="preserve">2.5363621711731</t>
@@ -752,43 +749,43 @@
     <t xml:space="preserve">2.54348659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68740391731262</t>
+    <t xml:space="preserve">2.6874041557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.69452834129333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75722503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79712271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78857350349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79997301101685</t>
+    <t xml:space="preserve">2.75722479820251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77147459983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79712295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78857326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79997277259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.83132100105286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90541696548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03508543968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215810775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477824211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727077484131</t>
+    <t xml:space="preserve">2.9054172039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03508496284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477871894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727053642273</t>
   </si>
   <si>
     <t xml:space="preserve">3.25737285614014</t>
@@ -800,7 +797,7 @@
     <t xml:space="preserve">3.16760301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16190361976624</t>
+    <t xml:space="preserve">3.1619029045105</t>
   </si>
   <si>
     <t xml:space="preserve">3.16047811508179</t>
@@ -809,100 +806,103 @@
     <t xml:space="preserve">3.21889996528625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22174954414368</t>
+    <t xml:space="preserve">3.2217493057251</t>
   </si>
   <si>
     <t xml:space="preserve">3.27589678764343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28159666061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877212524414</t>
+    <t xml:space="preserve">3.28159689903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877236366272</t>
   </si>
   <si>
     <t xml:space="preserve">3.23172402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12913036346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19610118865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19752597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884892463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602486610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157090187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32576942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302121162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864428520203</t>
+    <t xml:space="preserve">3.17900204658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1291298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19610142707825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10063147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752621650696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602438926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157114028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3257691860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864452362061</t>
   </si>
   <si>
     <t xml:space="preserve">3.34001874923706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39559006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35569262504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27019762992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0892322063446</t>
+    <t xml:space="preserve">3.39559054374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3556923866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27019739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08923196792603</t>
   </si>
   <si>
     <t xml:space="preserve">3.06358337402344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17488956451416</t>
+    <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11147856712341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13886022567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462494850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003708839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1186842918396</t>
+    <t xml:space="preserve">3.11147832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13886070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11868405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.07112598419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03797888755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04806709289551</t>
+    <t xml:space="preserve">3.03797912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04806733131409</t>
   </si>
   <si>
     <t xml:space="preserve">2.99762606620789</t>
@@ -914,40 +914,40 @@
     <t xml:space="preserve">2.97744989395142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91836214065552</t>
+    <t xml:space="preserve">2.9183623790741</t>
   </si>
   <si>
     <t xml:space="preserve">2.8722448348999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90395069122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8909797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87512707710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92700910568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90683269500732</t>
+    <t xml:space="preserve">2.90395045280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89098024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87512731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92700886726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9068329334259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86936283111572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87800931930542</t>
+    <t xml:space="preserve">2.878009557724</t>
   </si>
   <si>
     <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85350966453552</t>
+    <t xml:space="preserve">2.85351014137268</t>
   </si>
   <si>
     <t xml:space="preserve">2.87080359458923</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">2.82468628883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79298043251038</t>
+    <t xml:space="preserve">2.79298067092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.76415729522705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81027460098267</t>
+    <t xml:space="preserve">2.81027483940125</t>
   </si>
   <si>
     <t xml:space="preserve">2.80018639564514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79153966903687</t>
+    <t xml:space="preserve">2.79153943061829</t>
   </si>
   <si>
     <t xml:space="preserve">2.72956943511963</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">2.75262808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75983357429504</t>
+    <t xml:space="preserve">2.75983381271362</t>
   </si>
   <si>
     <t xml:space="preserve">2.74686360359192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95439147949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92124462127686</t>
+    <t xml:space="preserve">2.95439124107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92124438285828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92845034599304</t>
@@ -995,46 +995,46 @@
     <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342193603516</t>
+    <t xml:space="preserve">2.83189225196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342169761658</t>
   </si>
   <si>
     <t xml:space="preserve">2.80450987815857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83045101165771</t>
+    <t xml:space="preserve">2.83045077323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80739212036133</t>
+    <t xml:space="preserve">2.78865718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
     <t xml:space="preserve">2.80883359909058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84053897857666</t>
+    <t xml:space="preserve">2.84053921699524</t>
   </si>
   <si>
     <t xml:space="preserve">2.85495066642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86503911018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87656855583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90827393531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83909797668457</t>
+    <t xml:space="preserve">2.86503934860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87656831741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90827369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83909821510315</t>
   </si>
   <si>
     <t xml:space="preserve">2.73821663856506</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">2.75551009178162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76848077774048</t>
+    <t xml:space="preserve">2.76848101615906</t>
   </si>
   <si>
     <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72668719291687</t>
+    <t xml:space="preserve">2.72668695449829</t>
   </si>
   <si>
     <t xml:space="preserve">2.71371650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72524571418762</t>
+    <t xml:space="preserve">2.7252459526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.68056964874268</t>
@@ -1064,22 +1064,22 @@
     <t xml:space="preserve">2.6748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67336416244507</t>
+    <t xml:space="preserve">2.67336392402649</t>
   </si>
   <si>
     <t xml:space="preserve">2.65895223617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67624592781067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406908988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79442167282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79874539375305</t>
+    <t xml:space="preserve">2.67624616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79442191123962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79874515533447</t>
   </si>
   <si>
     <t xml:space="preserve">2.74542212486267</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">3.0250084400177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02644944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0696849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10571384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12156653404236</t>
+    <t xml:space="preserve">3.02644920349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06968450546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10571360588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12156629562378</t>
   </si>
   <si>
     <t xml:space="preserve">3.17056655883789</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">3.14174318313599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13597846031189</t>
+    <t xml:space="preserve">3.13597869873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850811958313</t>
@@ -1121,28 +1121,28 @@
     <t xml:space="preserve">3.05671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07689023017883</t>
+    <t xml:space="preserve">3.07689046859741</t>
   </si>
   <si>
     <t xml:space="preserve">3.08409667015076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07400798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04086112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05383157730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17921328544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589025497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05527257919312</t>
+    <t xml:space="preserve">3.07400822639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04086089134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05383133888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17921352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589001655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05527305603027</t>
   </si>
   <si>
     <t xml:space="preserve">3.07977294921875</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">3.14894866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16191959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14750742912292</t>
+    <t xml:space="preserve">3.16191935539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14750790596008</t>
   </si>
   <si>
     <t xml:space="preserve">3.09994912147522</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">3.15903687477112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15471315383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12877249717712</t>
+    <t xml:space="preserve">3.15471339225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12877225875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.11580181121826</t>
@@ -1178,55 +1178,55 @@
     <t xml:space="preserve">3.10427284240723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12012577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815529823303</t>
+    <t xml:space="preserve">3.12012529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815553665161</t>
   </si>
   <si>
     <t xml:space="preserve">3.00483226776123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97168517112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7843337059021</t>
+    <t xml:space="preserve">2.97168564796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78433394432068</t>
   </si>
   <si>
     <t xml:space="preserve">2.82180404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86792159080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8967444896698</t>
+    <t xml:space="preserve">2.8679211139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.88233304023743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85062718391418</t>
+    <t xml:space="preserve">2.85062766075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.82901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324528694153</t>
+    <t xml:space="preserve">2.82324504852295</t>
   </si>
   <si>
     <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72236371040344</t>
+    <t xml:space="preserve">2.72236347198486</t>
   </si>
   <si>
     <t xml:space="preserve">2.70506954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71227550506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65606999397278</t>
+    <t xml:space="preserve">2.71227526664734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65607023239136</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.76703953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78505396842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740769386292</t>
+    <t xml:space="preserve">2.78505444526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740745544434</t>
   </si>
   <si>
     <t xml:space="preserve">2.69498133659363</t>
@@ -1250,37 +1250,37 @@
     <t xml:space="preserve">2.7057900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7310106754303</t>
+    <t xml:space="preserve">2.73101043701172</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020196914673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79225993156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84630370140076</t>
+    <t xml:space="preserve">2.79226016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84630393981934</t>
   </si>
   <si>
     <t xml:space="preserve">2.77424550056458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77064275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.709392786026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74181914329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71299600601196</t>
+    <t xml:space="preserve">2.77064251899719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70939302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74181938171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71299624443054</t>
   </si>
   <si>
     <t xml:space="preserve">2.63373160362244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62652564048767</t>
+    <t xml:space="preserve">2.62652611732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.6409375667572</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">2.64814352989197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58689403533936</t>
+    <t xml:space="preserve">2.58689379692078</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248210906982</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.57968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55807042121887</t>
+    <t xml:space="preserve">2.55807065963745</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167340278625</t>
@@ -1313,46 +1313,46 @@
     <t xml:space="preserve">2.56887912750244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43557167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37432193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30946922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39593935012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41755676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991024971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44998335838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3527045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52204155921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42836546897888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44638013839722</t>
+    <t xml:space="preserve">2.43557143211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37432169914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30946946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39593958854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41755700111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41395354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36351323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4499831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35270428657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5220410823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4283652305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4463803768158</t>
   </si>
   <si>
     <t xml:space="preserve">2.4211597442627</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">2.50762987136841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59409976005554</t>
+    <t xml:space="preserve">2.59409952163696</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527638435364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63012862205505</t>
+    <t xml:space="preserve">2.63012886047363</t>
   </si>
   <si>
     <t xml:space="preserve">2.65174651145935</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">2.6373348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68417239189148</t>
+    <t xml:space="preserve">2.68417263031006</t>
   </si>
   <si>
     <t xml:space="preserve">2.66615796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69137811660767</t>
+    <t xml:space="preserve">2.69137835502625</t>
   </si>
   <si>
     <t xml:space="preserve">2.67696666717529</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.73281216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172198295593</t>
+    <t xml:space="preserve">2.62172222137451</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">2.48841404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40324473381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43657207489014</t>
+    <t xml:space="preserve">2.40324521064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43657231330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.45879006385803</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.39213609695435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40694808959961</t>
+    <t xml:space="preserve">2.40694856643677</t>
   </si>
   <si>
     <t xml:space="preserve">2.36991810798645</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">2.29956150054932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21068930625916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32548213005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732434272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38843297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42916631698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46989917755127</t>
+    <t xml:space="preserve">2.21068906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32548236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732410430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38843321800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4291660785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46989941596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.5032262802124</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">2.53285026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57728624343872</t>
+    <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
     <t xml:space="preserve">2.5254442691803</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">2.45508718490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58098888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395890235901</t>
+    <t xml:space="preserve">2.58098912239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395914077759</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">2.44768095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53655314445496</t>
+    <t xml:space="preserve">2.53655290603638</t>
   </si>
   <si>
     <t xml:space="preserve">2.4773051738739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51433539390564</t>
+    <t xml:space="preserve">2.51433515548706</t>
   </si>
   <si>
     <t xml:space="preserve">2.48100805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46619582176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39583921432495</t>
+    <t xml:space="preserve">2.46619629859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39583897590637</t>
   </si>
   <si>
     <t xml:space="preserve">2.41065120697021</t>
@@ -1505,22 +1505,22 @@
     <t xml:space="preserve">2.35140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36621499061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34399700164795</t>
+    <t xml:space="preserve">2.36621522903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34399724006653</t>
   </si>
   <si>
     <t xml:space="preserve">2.35880923271179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35510659217834</t>
+    <t xml:space="preserve">2.35510611534119</t>
   </si>
   <si>
     <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30696725845337</t>
+    <t xml:space="preserve">2.30696702003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.3106701374054</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39954233169556</t>
+    <t xml:space="preserve">2.39954209327698</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102722167969</t>
@@ -1547,61 +1547,61 @@
     <t xml:space="preserve">2.29585838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26993703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30326414108276</t>
+    <t xml:space="preserve">2.28104615211487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26993727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30326437950134</t>
   </si>
   <si>
     <t xml:space="preserve">2.32918524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27734351158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2662341594696</t>
+    <t xml:space="preserve">2.27734303474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26623439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.29215526580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27364015579224</t>
+    <t xml:space="preserve">2.27363991737366</t>
   </si>
   <si>
     <t xml:space="preserve">2.2884521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28474926948547</t>
+    <t xml:space="preserve">2.28474950790405</t>
   </si>
   <si>
     <t xml:space="preserve">2.38473010063171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698618888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24031352996826</t>
+    <t xml:space="preserve">2.20698642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24031329154968</t>
   </si>
   <si>
     <t xml:space="preserve">2.15514445304871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13292670249939</t>
+    <t xml:space="preserve">2.13292622566223</t>
   </si>
   <si>
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10330247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959959983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849048614502</t>
+    <t xml:space="preserve">2.1033022403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849024772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10700535774231</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">1.98850953578949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95147943496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553939819336</t>
+    <t xml:space="preserve">1.95147967338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553915977478</t>
   </si>
   <si>
     <t xml:space="preserve">2.06627225875854</t>
@@ -1625,13 +1625,13 @@
     <t xml:space="preserve">2.04775762557983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06997561454773</t>
+    <t xml:space="preserve">2.06997537612915</t>
   </si>
   <si>
     <t xml:space="preserve">2.12922334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14403557777405</t>
+    <t xml:space="preserve">2.14403533935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.13662934303284</t>
@@ -1640,37 +1640,37 @@
     <t xml:space="preserve">2.18847131729126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23290729522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25512528419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2032835483551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19958066940308</t>
+    <t xml:space="preserve">2.21439218521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25512552261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20328330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1995804309845</t>
   </si>
   <si>
     <t xml:space="preserve">2.21809530258179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11811399459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070823669434</t>
+    <t xml:space="preserve">2.11811447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367825508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070847511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.24771928787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3365912437439</t>
+    <t xml:space="preserve">2.33659100532532</t>
   </si>
   <si>
     <t xml:space="preserve">2.51063227653503</t>
@@ -1679,82 +1679,82 @@
     <t xml:space="preserve">2.65504908561707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68096995353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60320734977722</t>
+    <t xml:space="preserve">2.68096971511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60320687294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65875196456909</t>
+    <t xml:space="preserve">2.65875172615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.65134596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62542510032654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71799993515015</t>
+    <t xml:space="preserve">2.62542486190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71800017356873</t>
   </si>
   <si>
     <t xml:space="preserve">2.70318794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7291088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69207906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71429681777954</t>
+    <t xml:space="preserve">2.72910904884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69207882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71429705619812</t>
   </si>
   <si>
     <t xml:space="preserve">2.75502991676331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8031690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81798076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84390163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87352609634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86241674423218</t>
+    <t xml:space="preserve">2.80316877365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81798100471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84390187263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87352585792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86241698265076</t>
   </si>
   <si>
     <t xml:space="preserve">2.88093185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76243591308594</t>
+    <t xml:space="preserve">2.76243615150452</t>
   </si>
   <si>
     <t xml:space="preserve">2.76984190940857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7994658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205965995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81427812576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79576301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75873279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85871362686157</t>
+    <t xml:space="preserve">2.79946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81427788734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79576325416565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75873303413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85871386528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.90314984321594</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">2.962397813797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98091268539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91796183586121</t>
+    <t xml:space="preserve">2.98091292381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91796207427979</t>
   </si>
   <si>
     <t xml:space="preserve">2.94758582115173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95128893852234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93647646903992</t>
+    <t xml:space="preserve">2.95128846168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93647694587708</t>
   </si>
   <si>
     <t xml:space="preserve">2.95499181747437</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">2.93277382850647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91055607795715</t>
+    <t xml:space="preserve">2.91055583953857</t>
   </si>
   <si>
     <t xml:space="preserve">2.96980404853821</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">2.8661196231842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80687189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279323577881</t>
+    <t xml:space="preserve">2.80687165260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279275894165</t>
   </si>
   <si>
     <t xml:space="preserve">2.85501098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71059393882751</t>
+    <t xml:space="preserve">2.71059417724609</t>
   </si>
   <si>
     <t xml:space="preserve">2.70689082145691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61061310768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64023685455322</t>
+    <t xml:space="preserve">2.61061334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6402370929718</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">2.69578194618225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68467283248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68837594985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6143159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56988024711609</t>
+    <t xml:space="preserve">2.68467307090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6883761882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61431622505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56988000869751</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211716651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50692939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34770011901855</t>
+    <t xml:space="preserve">2.50692915916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34770035743713</t>
   </si>
   <si>
     <t xml:space="preserve">2.23661017417908</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587707519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29948091506958</t>
+    <t xml:space="preserve">2.19587731361389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
     <t xml:space="preserve">2.21777319908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10882997512817</t>
+    <t xml:space="preserve">2.10883021354675</t>
   </si>
   <si>
     <t xml:space="preserve">2.12439346313477</t>
@@ -1898,34 +1898,34 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326672554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12050247192383</t>
+    <t xml:space="preserve">2.09326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12050271034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.13995671272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12828421592712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05046772956848</t>
+    <t xml:space="preserve">2.12828397750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770371437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05046796798706</t>
   </si>
   <si>
     <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03490424156189</t>
+    <t xml:space="preserve">2.03490447998047</t>
   </si>
   <si>
     <t xml:space="preserve">2.05435848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03101325035095</t>
+    <t xml:space="preserve">2.03101348876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.02323174476624</t>
@@ -1940,25 +1940,25 @@
     <t xml:space="preserve">2.22944593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18664646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96876001358032</t>
+    <t xml:space="preserve">2.1866466999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96876037120819</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92985165119171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02712273597717</t>
+    <t xml:space="preserve">1.92985200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02712249755859</t>
   </si>
   <si>
     <t xml:space="preserve">1.94152438640594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84425342082977</t>
+    <t xml:space="preserve">1.84425354003906</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">1.8092360496521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75087368488312</t>
+    <t xml:space="preserve">1.7508739233017</t>
   </si>
   <si>
     <t xml:space="preserve">1.74698269367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69251108169556</t>
+    <t xml:space="preserve">1.69251120090485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78978192806244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82090854644775</t>
+    <t xml:space="preserve">1.82090866565704</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">1.7119654417038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7197470664978</t>
+    <t xml:space="preserve">1.71974694728851</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78589117527008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73141932487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585607528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73531031608582</t>
+    <t xml:space="preserve">1.78589129447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73141944408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71585619449615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
     <t xml:space="preserve">1.78200030326843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8325811624527</t>
+    <t xml:space="preserve">1.83258104324341</t>
   </si>
   <si>
     <t xml:space="preserve">1.80145454406738</t>
@@ -2030,19 +2030,19 @@
     <t xml:space="preserve">1.85592615604401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83647191524506</t>
+    <t xml:space="preserve">1.83647203445435</t>
   </si>
   <si>
     <t xml:space="preserve">1.87927114963531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79756355285645</t>
+    <t xml:space="preserve">1.79756367206573</t>
   </si>
   <si>
     <t xml:space="preserve">1.77032780647278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82869017124176</t>
+    <t xml:space="preserve">1.82869040966034</t>
   </si>
   <si>
     <t xml:space="preserve">1.75476455688477</t>
@@ -2051,43 +2051,43 @@
     <t xml:space="preserve">1.75865530967712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254630088806</t>
+    <t xml:space="preserve">1.76254618167877</t>
   </si>
   <si>
     <t xml:space="preserve">1.80534529685974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8170177936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8247994184494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91428852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93374240398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89094352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538039684296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650677680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89483428001404</t>
+    <t xml:space="preserve">1.81701791286469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82479953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91428864002228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93374276161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89094376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538027763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89483439922333</t>
   </si>
   <si>
     <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92207026481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01155924797058</t>
+    <t xml:space="preserve">1.92207038402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01155948638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.16719269752502</t>
@@ -2096,28 +2096,28 @@
     <t xml:space="preserve">2.16330170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08159422874451</t>
+    <t xml:space="preserve">2.08159446716309</t>
   </si>
   <si>
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217520713806</t>
+    <t xml:space="preserve">2.13217496871948</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19053745269775</t>
+    <t xml:space="preserve">2.19053769111633</t>
   </si>
   <si>
     <t xml:space="preserve">2.15551996231079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17108345031738</t>
+    <t xml:space="preserve">2.19831919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1710832118988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14384770393372</t>
@@ -2129,16 +2129,16 @@
     <t xml:space="preserve">2.08548521995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01545000076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821425437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15941095352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13606572151184</t>
+    <t xml:space="preserve">2.01545023918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15941119194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
     <t xml:space="preserve">2.01934099197388</t>
@@ -2147,34 +2147,34 @@
     <t xml:space="preserve">1.87148940563202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91039752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872527122498</t>
+    <t xml:space="preserve">1.91039764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596113681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872539043427</t>
   </si>
   <si>
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988675117493</t>
+    <t xml:space="preserve">1.99988687038422</t>
   </si>
   <si>
     <t xml:space="preserve">1.95708787441254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96486949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99210500717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72752869129181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862044811249</t>
+    <t xml:space="preserve">1.96486961841583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99210524559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72752857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862056732178</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
@@ -2183,49 +2183,49 @@
     <t xml:space="preserve">1.59524047374725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.542325258255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940992355347</t>
+    <t xml:space="preserve">1.54232513904572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48941004276276</t>
   </si>
   <si>
     <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33844566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30420649051666</t>
+    <t xml:space="preserve">1.33844578266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30420637130737</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619230747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09098875522614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16102373600006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08009445667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05986225605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0847635269165</t>
+    <t xml:space="preserve">1.09098887443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16102385520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08009457588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05986213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08476364612579</t>
   </si>
   <si>
     <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22483348846436</t>
+    <t xml:space="preserve">1.22483336925507</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910764217377</t>
+    <t xml:space="preserve">1.32910752296448</t>
   </si>
   <si>
     <t xml:space="preserve">1.35400903224945</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">1.28864312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28397417068481</t>
+    <t xml:space="preserve">1.28397405147552</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39291727542877</t>
+    <t xml:space="preserve">1.39291739463806</t>
   </si>
   <si>
     <t xml:space="preserve">1.36179065704346</t>
@@ -2261,22 +2261,22 @@
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798114299774</t>
+    <t xml:space="preserve">1.29798102378845</t>
   </si>
   <si>
     <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29953730106354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31354427337646</t>
+    <t xml:space="preserve">1.29953742027283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31354439258575</t>
   </si>
   <si>
     <t xml:space="preserve">1.29175567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28241765499115</t>
+    <t xml:space="preserve">1.28241777420044</t>
   </si>
   <si>
     <t xml:space="preserve">1.2295024394989</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">1.17503070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1330099105835</t>
+    <t xml:space="preserve">1.13300967216492</t>
   </si>
   <si>
     <t xml:space="preserve">1.10343956947327</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">1.08631992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05674958229065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06764388084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12211549282074</t>
+    <t xml:space="preserve">1.05674970149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06764376163483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12211561203003</t>
   </si>
   <si>
     <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15012943744659</t>
+    <t xml:space="preserve">1.14234793186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15012955665588</t>
   </si>
   <si>
     <t xml:space="preserve">1.13923513889313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19837582111359</t>
+    <t xml:space="preserve">1.1983757019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.2450658082962</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708684444427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27930521965027</t>
+    <t xml:space="preserve">1.28708672523499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27930498123169</t>
   </si>
   <si>
     <t xml:space="preserve">1.17969989776611</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">1.16413640975952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23572766780853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20615744590759</t>
+    <t xml:space="preserve">1.23572778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2061573266983</t>
   </si>
   <si>
     <t xml:space="preserve">1.20771384239197</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">1.17814350128174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18592524528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13612246513367</t>
+    <t xml:space="preserve">1.18592512607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13612258434296</t>
   </si>
   <si>
     <t xml:space="preserve">1.15791118144989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1407915353775</t>
+    <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
     <t xml:space="preserve">1.18436884880066</t>
@@ -2387,19 +2387,19 @@
     <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546060562134</t>
+    <t xml:space="preserve">1.14546048641205</t>
   </si>
   <si>
     <t xml:space="preserve">1.16724920272827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1734744310379</t>
+    <t xml:space="preserve">1.17347455024719</t>
   </si>
   <si>
     <t xml:space="preserve">1.15168583393097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17191827297211</t>
+    <t xml:space="preserve">1.17191815376282</t>
   </si>
   <si>
     <t xml:space="preserve">1.1656928062439</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">1.1252281665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608760356903</t>
+    <t xml:space="preserve">1.06608748435974</t>
   </si>
   <si>
     <t xml:space="preserve">1.08320713043213</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">1.06297492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04896783828735</t>
+    <t xml:space="preserve">1.04896795749664</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410154819489</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">1.07075655460358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09721410274506</t>
+    <t xml:space="preserve">1.09721422195435</t>
   </si>
   <si>
     <t xml:space="preserve">1.0614185333252</t>
@@ -2447,46 +2447,46 @@
     <t xml:space="preserve">1.04585528373718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03963005542755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04118621349335</t>
+    <t xml:space="preserve">1.03962993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04118633270264</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03496098518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03651714324951</t>
+    <t xml:space="preserve">1.03496086597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0365172624588</t>
   </si>
   <si>
     <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996052503585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01628494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00850319862366</t>
+    <t xml:space="preserve">0.996052622795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01628482341766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00850331783295</t>
   </si>
   <si>
     <t xml:space="preserve">1.01005959510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00072169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99138355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966482281684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964925825595856</t>
+    <t xml:space="preserve">1.00072157382965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991383731365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96648234128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96492600440979</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.954031646251678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975820243358612</t>
+    <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
     <t xml:space="preserve">0.989827215671539</t>
@@ -2504,37 +2504,37 @@
     <t xml:space="preserve">0.969595015048981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949362635612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96803867816925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957144260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489313602448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999165415763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06453120708466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05830585956573</t>
+    <t xml:space="preserve">0.949362695217133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968038558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957144320011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99916535615921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06453132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05830597877502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02406656742096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988270878791809</t>
+    <t xml:space="preserve">0.988270998001099</t>
   </si>
   <si>
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941581010818481</t>
+    <t xml:space="preserve">0.941581070423126</t>
   </si>
   <si>
     <t xml:space="preserve">0.93379932641983</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">0.879327654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887109279632568</t>
+    <t xml:space="preserve">0.887109339237213</t>
   </si>
   <si>
     <t xml:space="preserve">0.888665616512299</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">0.83575040102005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80306738615036</t>
+    <t xml:space="preserve">0.803067326545715</t>
   </si>
   <si>
     <t xml:space="preserve">0.787504076957703</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">0.831081390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840419411659241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826412439346313</t>
+    <t xml:space="preserve">0.840419352054596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826412498950958</t>
   </si>
   <si>
     <t xml:space="preserve">0.817074358463287</t>
@@ -2588,37 +2588,37 @@
     <t xml:space="preserve">0.902672648429871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915123283863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940024673938751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977376580238342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963369727134705</t>
+    <t xml:space="preserve">0.915123343467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940024495124817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977376639842987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963369607925415</t>
   </si>
   <si>
     <t xml:space="preserve">0.983601987361908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978933036327362</t>
+    <t xml:space="preserve">0.978932917118073</t>
   </si>
   <si>
     <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961813271045685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946249961853027</t>
+    <t xml:space="preserve">0.961813151836395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946249902248383</t>
   </si>
   <si>
     <t xml:space="preserve">0.943137288093567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93068665266037</t>
+    <t xml:space="preserve">0.930686712265015</t>
   </si>
   <si>
     <t xml:space="preserve">0.952475309371948</t>
@@ -2633,40 +2633,40 @@
     <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971151351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947806417942047</t>
+    <t xml:space="preserve">0.971151292324066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">0.919792294502258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913567006587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679680347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899560034275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918235957622528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908898055553436</t>
+    <t xml:space="preserve">0.913566946983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341599464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8995600938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918236017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908897995948792</t>
   </si>
   <si>
     <t xml:space="preserve">0.894890964031219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910454273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944693624973297</t>
+    <t xml:space="preserve">0.910454332828522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944693684577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.01784121990204</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">1.05363690853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13767874240875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15946757793427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12989711761475</t>
+    <t xml:space="preserve">1.13767886161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15946745872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12989735603333</t>
   </si>
   <si>
     <t xml:space="preserve">1.10032689571381</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">1.07231283187866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12834095954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12055921554565</t>
+    <t xml:space="preserve">1.12834084033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12055909633636</t>
   </si>
   <si>
     <t xml:space="preserve">1.11744654178619</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">1.15479850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31198811531067</t>
+    <t xml:space="preserve">1.31198799610138</t>
   </si>
   <si>
     <t xml:space="preserve">1.25907278060913</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">1.2544037103653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22638988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23105883598328</t>
+    <t xml:space="preserve">1.22638976573944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23105871677399</t>
   </si>
   <si>
     <t xml:space="preserve">1.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25751662254333</t>
+    <t xml:space="preserve">1.25751650333405</t>
   </si>
   <si>
     <t xml:space="preserve">1.26841068267822</t>
@@ -2738,16 +2738,16 @@
     <t xml:space="preserve">1.27307987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36023426055908</t>
+    <t xml:space="preserve">1.36023437976837</t>
   </si>
   <si>
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069890022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40381181240082</t>
+    <t xml:space="preserve">1.40069901943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
     <t xml:space="preserve">1.37112867832184</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">1.40536797046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4380509853363</t>
+    <t xml:space="preserve">1.43805086612701</t>
   </si>
   <si>
     <t xml:space="preserve">1.52053654193878</t>
@@ -2780,37 +2780,37 @@
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022322177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58745872974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53765618801117</t>
+    <t xml:space="preserve">1.56022310256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58745884895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53765606880188</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431119441986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50341701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50497329235077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49096620082855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51798796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871304512024</t>
+    <t xml:space="preserve">1.50341689586639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50497317314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49096632003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51798808574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871316432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.45281779766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46712350845337</t>
+    <t xml:space="preserve">1.46712338924408</t>
   </si>
   <si>
     <t xml:space="preserve">1.47348153591156</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937666416168</t>
+    <t xml:space="preserve">1.48937678337097</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
@@ -2831,31 +2831,31 @@
     <t xml:space="preserve">1.55454683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5561363697052</t>
+    <t xml:space="preserve">1.55613648891449</t>
   </si>
   <si>
     <t xml:space="preserve">1.57044196128845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56567358970642</t>
+    <t xml:space="preserve">1.56567347049713</t>
   </si>
   <si>
     <t xml:space="preserve">1.567263007164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53706228733063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5275251865387</t>
+    <t xml:space="preserve">1.53706216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52752506732941</t>
   </si>
   <si>
     <t xml:space="preserve">1.47030258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44328081607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40672194957733</t>
+    <t xml:space="preserve">1.4432806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40672183036804</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374371528625</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">1.34790980815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33201467990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585737228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929850578308</t>
+    <t xml:space="preserve">1.33201456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585725307465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929838657379</t>
   </si>
   <si>
     <t xml:space="preserve">1.31453001499176</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">1.27638149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30181384086609</t>
+    <t xml:space="preserve">1.3018137216568</t>
   </si>
   <si>
     <t xml:space="preserve">1.30499279499054</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">1.31135094165802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30340325832367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28432929515839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479207515717</t>
+    <t xml:space="preserve">1.30340337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2843291759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479195594788</t>
   </si>
   <si>
     <t xml:space="preserve">1.22074854373932</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">1.2557178735733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24935972690582</t>
+    <t xml:space="preserve">1.24935984611511</t>
   </si>
   <si>
     <t xml:space="preserve">1.25412821769714</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">1.28273963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21121144294739</t>
+    <t xml:space="preserve">1.2271066904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2112113237381</t>
   </si>
   <si>
     <t xml:space="preserve">1.2732025384903</t>
@@ -2942,19 +2942,19 @@
     <t xml:space="preserve">1.37652099132538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36698389053345</t>
+    <t xml:space="preserve">1.36698400974274</t>
   </si>
   <si>
     <t xml:space="preserve">1.35267841815948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970018386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128960132599</t>
+    <t xml:space="preserve">1.37493169307709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37969994544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128972053528</t>
   </si>
   <si>
     <t xml:space="preserve">1.34314131736755</t>
@@ -2963,28 +2963,28 @@
     <t xml:space="preserve">1.33678317070007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221539974213</t>
+    <t xml:space="preserve">1.36221528053284</t>
   </si>
   <si>
     <t xml:space="preserve">1.363804936409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39877426624298</t>
+    <t xml:space="preserve">1.39877438545227</t>
   </si>
   <si>
     <t xml:space="preserve">1.42897510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40513229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53388321399689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49732434749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189199924469</t>
+    <t xml:space="preserve">1.40513241291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49732422828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189211845398</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738556861877</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">1.34155166149139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33519351482391</t>
+    <t xml:space="preserve">1.3351936340332</t>
   </si>
   <si>
     <t xml:space="preserve">1.37811064720154</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">1.38287913799286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50050330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116703987122</t>
+    <t xml:space="preserve">1.50050342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116715908051</t>
   </si>
   <si>
     <t xml:space="preserve">1.49573481082916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50845086574554</t>
+    <t xml:space="preserve">1.50845098495483</t>
   </si>
   <si>
     <t xml:space="preserve">1.51162993907928</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">1.51321947574615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47507119178772</t>
+    <t xml:space="preserve">1.47507095336914</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010174274445</t>
@@ -3065,34 +3065,34 @@
     <t xml:space="preserve">1.4877872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47983968257904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45599699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301863670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51004040241241</t>
+    <t xml:space="preserve">1.47983956336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45599687099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301875591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51004028320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.56249439716339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63720166683197</t>
+    <t xml:space="preserve">1.63720178604126</t>
   </si>
   <si>
     <t xml:space="preserve">1.66501832008362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67693948745728</t>
+    <t xml:space="preserve">1.67693960666656</t>
   </si>
   <si>
     <t xml:space="preserve">1.70078253746033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65309691429138</t>
+    <t xml:space="preserve">1.65309679508209</t>
   </si>
   <si>
     <t xml:space="preserve">1.60541141033173</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">1.43851220607758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44645988941193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4544073343277</t>
+    <t xml:space="preserve">1.44645977020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440745353699</t>
   </si>
   <si>
     <t xml:space="preserve">1.45122838020325</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">1.49414527416229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61335897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733293533325</t>
+    <t xml:space="preserve">1.51639842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61335909366608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733281612396</t>
   </si>
   <si>
     <t xml:space="preserve">1.63322794437408</t>
@@ -3134,22 +3134,22 @@
     <t xml:space="preserve">1.62130653858185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349012374878</t>
+    <t xml:space="preserve">1.59349024295807</t>
   </si>
   <si>
     <t xml:space="preserve">1.58792674541473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60143768787384</t>
+    <t xml:space="preserve">1.60143780708313</t>
   </si>
   <si>
     <t xml:space="preserve">1.62925410270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104447841644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53865170478821</t>
+    <t xml:space="preserve">1.66104435920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5386518239975</t>
   </si>
   <si>
     <t xml:space="preserve">1.51957750320435</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">1.52911472320557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53070402145386</t>
+    <t xml:space="preserve">1.53070414066315</t>
   </si>
   <si>
     <t xml:space="preserve">1.52434611320496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43056452274323</t>
+    <t xml:space="preserve">1.43056464195251</t>
   </si>
   <si>
     <t xml:space="preserve">1.37334203720093</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">1.30022442340851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22869610786438</t>
+    <t xml:space="preserve">1.22869598865509</t>
   </si>
   <si>
     <t xml:space="preserve">1.23346471786499</t>
@@ -3194,82 +3194,82 @@
     <t xml:space="preserve">1.40831136703491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59746384620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74846792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423178195953</t>
+    <t xml:space="preserve">1.59746372699738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7484678030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423190116882</t>
   </si>
   <si>
     <t xml:space="preserve">1.76038908958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77231049537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74449396133423</t>
+    <t xml:space="preserve">1.77231061458588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025805950165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74449408054352</t>
   </si>
   <si>
     <t xml:space="preserve">1.81999599933624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81204843521118</t>
+    <t xml:space="preserve">1.81204855442047</t>
   </si>
   <si>
     <t xml:space="preserve">1.83191752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8279435634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178625583649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589112758636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986508846283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82396984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628421783447</t>
+    <t xml:space="preserve">1.82794368267059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178649425507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986520767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396996021271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628433704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.79217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76833665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.788205742836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859871387482</t>
+    <t xml:space="preserve">1.76833689212799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78820586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7285989522934</t>
   </si>
   <si>
     <t xml:space="preserve">1.64514923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71667754650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436293125153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410075187683</t>
+    <t xml:space="preserve">1.71667766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73654651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641560554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436305046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410087108612</t>
   </si>
   <si>
     <t xml:space="preserve">1.7403576374054</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">1.76195001602173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75763165950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75331294536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603904247284</t>
+    <t xml:space="preserve">1.75763154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490556240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7533130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603892326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.67730736732483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64448666572571</t>
+    <t xml:space="preserve">1.644486784935</t>
   </si>
   <si>
     <t xml:space="preserve">1.55811655521393</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">1.50456702709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50283968448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865605354309</t>
+    <t xml:space="preserve">1.50283980369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865617275238</t>
   </si>
   <si>
     <t xml:space="preserve">1.51665902137756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48038351535797</t>
+    <t xml:space="preserve">1.48038339614868</t>
   </si>
   <si>
     <t xml:space="preserve">1.4890204668045</t>
@@ -3344,16 +3344,16 @@
     <t xml:space="preserve">1.3819215297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40092301368713</t>
+    <t xml:space="preserve">1.40092289447784</t>
   </si>
   <si>
     <t xml:space="preserve">1.43028879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501192092896</t>
+    <t xml:space="preserve">1.4061051607132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501204013824</t>
   </si>
   <si>
     <t xml:space="preserve">1.37328457832336</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">1.34737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52875077724457</t>
+    <t xml:space="preserve">1.52875065803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.59957420825958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5477522611618</t>
+    <t xml:space="preserve">1.54775214195251</t>
   </si>
   <si>
     <t xml:space="preserve">1.55293428897858</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">1.55466175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60648381710052</t>
+    <t xml:space="preserve">1.60648393630981</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475647449493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58230030536652</t>
+    <t xml:space="preserve">1.58230018615723</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057284355164</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">1.4665641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510664463043</t>
+    <t xml:space="preserve">1.45447242259979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510652542114</t>
   </si>
   <si>
     <t xml:space="preserve">1.43547093868256</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">1.33009946346283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38019418716431</t>
+    <t xml:space="preserve">1.3801943063736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35082840919495</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">1.2005443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22300052642822</t>
+    <t xml:space="preserve">1.22300064563751</t>
   </si>
   <si>
     <t xml:space="preserve">1.1884526014328</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">1.35773801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39574086666107</t>
+    <t xml:space="preserve">1.39574074745178</t>
   </si>
   <si>
     <t xml:space="preserve">1.39746820926666</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44929015636444</t>
+    <t xml:space="preserve">1.44929027557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992449760437</t>
+    <t xml:space="preserve">1.41992437839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301476955414</t>
+    <t xml:space="preserve">1.41301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464750766754</t>
+    <t xml:space="preserve">1.38710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464762687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.331827044487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591583251953</t>
+    <t xml:space="preserve">1.33182692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591595172882</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564602375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937063694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827751636505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136778831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655005455017</t>
+    <t xml:space="preserve">1.34564614295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136790752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655017375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036915302277</t>
+    <t xml:space="preserve">1.29036927223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910106658936</t>
+    <t xml:space="preserve">1.34910094738007</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938488006592</t>
+    <t xml:space="preserve">1.49938476085663</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838636398315</t>
+    <t xml:space="preserve">1.51838624477386</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974941253662</t>
+    <t xml:space="preserve">1.50974929332733</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4181969165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729300498962</t>
+    <t xml:space="preserve">1.41819703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729312419891</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302901268005</t>
+    <t xml:space="preserve">1.60302889347076</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62893998622894</t>
+    <t xml:space="preserve">1.62894010543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6323949098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093713760376</t>
+    <t xml:space="preserve">1.63239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093725681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3737,10 +3737,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548518180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57193577289581</t>
+    <t xml:space="preserve">1.62548530101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5719358921051</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -11163,7 +11163,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11189,7 +11189,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11215,7 +11215,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G239" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11241,7 +11241,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11293,7 +11293,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11319,7 +11319,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G243" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11397,7 +11397,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11527,7 +11527,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G251" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11553,7 +11553,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11605,7 +11605,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11631,7 +11631,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11709,7 +11709,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11735,7 +11735,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11761,7 +11761,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11787,7 +11787,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11813,7 +11813,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G262" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11917,7 +11917,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11969,7 +11969,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11995,7 +11995,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12021,7 +12021,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G270" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12047,7 +12047,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12073,7 +12073,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G272" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12099,7 +12099,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12125,7 +12125,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12151,7 +12151,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12203,7 +12203,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12229,7 +12229,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12281,7 +12281,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12307,7 +12307,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G281" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12333,7 +12333,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G282" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12359,7 +12359,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12385,7 +12385,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12411,7 +12411,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12437,7 +12437,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12463,7 +12463,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12489,7 +12489,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12515,7 +12515,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12541,7 +12541,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12567,7 +12567,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12593,7 +12593,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12619,7 +12619,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12645,7 +12645,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12671,7 +12671,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12697,7 +12697,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12723,7 +12723,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12775,7 +12775,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12801,7 +12801,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12827,7 +12827,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12853,7 +12853,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12905,7 +12905,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12931,7 +12931,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12957,7 +12957,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G306" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12983,7 +12983,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13009,7 +13009,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13035,7 +13035,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13061,7 +13061,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13087,7 +13087,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13113,7 +13113,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13165,7 +13165,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13191,7 +13191,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13217,7 +13217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13243,7 +13243,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13269,7 +13269,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13347,7 +13347,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13373,7 +13373,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13399,7 +13399,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13425,7 +13425,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13451,7 +13451,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13477,7 +13477,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13503,7 +13503,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13529,7 +13529,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G328" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13555,7 +13555,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13581,7 +13581,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13607,7 +13607,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14205,7 +14205,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -71075,7 +71075,7 @@
     </row>
     <row r="2542">
       <c r="A2542" s="1" t="n">
-        <v>46024.6913078704</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2542" t="n">
         <v>85470</v>
@@ -71096,6 +71096,32 @@
         <v>1530</v>
       </c>
       <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.6910532407</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>254946</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>1529</v>
+      </c>
+      <c r="H2543" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385468482971</t>
+    <t xml:space="preserve">3.07385444641113</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">3.08614492416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01786756515503</t>
+    <t xml:space="preserve">3.01786732673645</t>
   </si>
   <si>
     <t xml:space="preserve">2.97690057754517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98099756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131189346313</t>
+    <t xml:space="preserve">2.98099732398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131165504456</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003081321716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620646476746</t>
+    <t xml:space="preserve">2.80620670318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.86082887649536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75841236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73929452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69013524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71744561195374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.866290807724</t>
+    <t xml:space="preserve">2.7584125995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73929476737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69013500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71744608879089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86629128456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.76387476921082</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">2.74475693702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7570469379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.710618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110127449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76114368438721</t>
+    <t xml:space="preserve">2.75704741477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71061825752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76114344596863</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563910484314</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">2.69696283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290778160095</t>
+    <t xml:space="preserve">2.72290802001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.62868499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935702323914</t>
+    <t xml:space="preserve">2.45935678482056</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799136161804</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">2.30095267295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38971376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992438316345</t>
+    <t xml:space="preserve">2.38971400260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992462158203</t>
   </si>
   <si>
     <t xml:space="preserve">2.50442004203796</t>
@@ -134,172 +134,172 @@
     <t xml:space="preserve">2.67511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81713080406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74885368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78162670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68467259407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8621940612793</t>
+    <t xml:space="preserve">2.81713104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7816264629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86219429969788</t>
   </si>
   <si>
     <t xml:space="preserve">2.8335177898407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84717297554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88404321670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88540863990784</t>
+    <t xml:space="preserve">2.84717345237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88404297828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540887832642</t>
   </si>
   <si>
     <t xml:space="preserve">2.89769864082336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85126972198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94685840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94958972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05883383750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1612503528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173289299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767903327942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217421531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635458946228</t>
+    <t xml:space="preserve">2.85126996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685816764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.058833360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16125011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217373847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635530471802</t>
   </si>
   <si>
     <t xml:space="preserve">3.25001072883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22270011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089265823364</t>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269940376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2308931350708</t>
   </si>
   <si>
     <t xml:space="preserve">3.22952747344971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14076638221741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895987510681</t>
+    <t xml:space="preserve">3.14076614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895963668823</t>
   </si>
   <si>
     <t xml:space="preserve">3.225430727005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29234266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587204933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463290214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27732157707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608290672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330893516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511591911316</t>
+    <t xml:space="preserve">3.29234290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732181549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559941291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3865659236908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34832978248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.325115442276</t>
   </si>
   <si>
     <t xml:space="preserve">3.32375049591064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29780507087708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26366662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182658195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1348295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330241203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208226203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907908439636</t>
+    <t xml:space="preserve">3.29780530929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366686820984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15620303153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208178520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
   </si>
   <si>
     <t xml:space="preserve">3.32291960716248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34856772422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33431911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31152009963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419079780579</t>
+    <t xml:space="preserve">3.34856796264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33431887626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151938438416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419103622437</t>
   </si>
   <si>
     <t xml:space="preserve">3.44403743743896</t>
@@ -308,118 +308,118 @@
     <t xml:space="preserve">3.41981387138367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43406391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4383385181427</t>
+    <t xml:space="preserve">3.43406343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108601570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681069374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833804130554</t>
   </si>
   <si>
     <t xml:space="preserve">3.45116233825684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40841460227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844036102295</t>
+    <t xml:space="preserve">3.40841484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844012260437</t>
   </si>
   <si>
     <t xml:space="preserve">3.34714317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20607566833496</t>
+    <t xml:space="preserve">3.20607590675354</t>
   </si>
   <si>
     <t xml:space="preserve">3.02796030044556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89971733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89686727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495759963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195370674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938532829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671439170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500864028931</t>
+    <t xml:space="preserve">2.94246530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8997175693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8968677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643319129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495688438416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195418357849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671391487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500816345215</t>
   </si>
   <si>
     <t xml:space="preserve">3.16332793235779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96526408195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9552891254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99233675003052</t>
+    <t xml:space="preserve">2.96526384353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233722686768</t>
   </si>
   <si>
     <t xml:space="preserve">3.12058019638062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1704523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599934577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757701873779</t>
+    <t xml:space="preserve">3.17045259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757749557495</t>
   </si>
   <si>
     <t xml:space="preserve">3.13625454902649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83702087402344</t>
+    <t xml:space="preserve">2.83702111244202</t>
   </si>
   <si>
     <t xml:space="preserve">2.91966605186462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86551904678345</t>
+    <t xml:space="preserve">2.86551928520203</t>
   </si>
   <si>
     <t xml:space="preserve">2.90399241447449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84129524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87549328804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83559560775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.84129548072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549376487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83559584617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.73442625999451</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">2.77717399597168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88546824455261</t>
+    <t xml:space="preserve">2.88546848297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.87406873703003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84272050857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87834358215332</t>
+    <t xml:space="preserve">2.84272027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87834334373474</t>
   </si>
   <si>
     <t xml:space="preserve">2.92821574211121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92109107971191</t>
+    <t xml:space="preserve">2.92109084129333</t>
   </si>
   <si>
     <t xml:space="preserve">2.94103980064392</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">2.86694431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85839486122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409401893616</t>
+    <t xml:space="preserve">2.85839462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409425735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.81707191467285</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">2.80567240715027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77289915084839</t>
+    <t xml:space="preserve">2.77289938926697</t>
   </si>
   <si>
     <t xml:space="preserve">2.75865006446838</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">2.62470746040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59478378295898</t>
+    <t xml:space="preserve">2.59478402137756</t>
   </si>
   <si>
     <t xml:space="preserve">2.5477614402771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58480954170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65605568885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610649108887</t>
+    <t xml:space="preserve">2.58480930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65605521202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65463042259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610672950745</t>
   </si>
   <si>
     <t xml:space="preserve">2.60333347320557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5719850063324</t>
+    <t xml:space="preserve">2.57198524475098</t>
   </si>
   <si>
     <t xml:space="preserve">2.45086669921875</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">2.44516706466675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42379307746887</t>
+    <t xml:space="preserve">2.42379331588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.44374203681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41666889190674</t>
+    <t xml:space="preserve">2.41666865348816</t>
   </si>
   <si>
     <t xml:space="preserve">2.45941615104675</t>
@@ -527,43 +527,43 @@
     <t xml:space="preserve">2.61900758743286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61045813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54918622970581</t>
+    <t xml:space="preserve">2.61045789718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54918646812439</t>
   </si>
   <si>
     <t xml:space="preserve">2.57910966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55061101913452</t>
+    <t xml:space="preserve">2.5506112575531</t>
   </si>
   <si>
     <t xml:space="preserve">2.52353763580322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57340979576111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6931037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64038157463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63895606994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898206710815</t>
+    <t xml:space="preserve">2.57341027259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69310355186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64038133621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898230552673</t>
   </si>
   <si>
     <t xml:space="preserve">2.63325691223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67173004150391</t>
+    <t xml:space="preserve">2.67172980308533</t>
   </si>
   <si>
     <t xml:space="preserve">2.74867558479309</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">2.73727607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67315459251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71447730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70735263824463</t>
+    <t xml:space="preserve">2.67315483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7030782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71447706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70735287666321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65178060531616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66887974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65748023986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486082077026</t>
+    <t xml:space="preserve">2.66887998580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753151893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65748047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486058235168</t>
   </si>
   <si>
     <t xml:space="preserve">2.52211260795593</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">2.51498818397522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41524386405945</t>
+    <t xml:space="preserve">2.41524362564087</t>
   </si>
   <si>
     <t xml:space="preserve">2.43234276771545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43661785125732</t>
+    <t xml:space="preserve">2.43661761283875</t>
   </si>
   <si>
     <t xml:space="preserve">2.39386987686157</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">2.39244484901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3511221408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42236828804016</t>
+    <t xml:space="preserve">2.35112190246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42236852645874</t>
   </si>
   <si>
     <t xml:space="preserve">2.53066253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57768487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58908414840698</t>
+    <t xml:space="preserve">2.5776846408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58908438682556</t>
   </si>
   <si>
     <t xml:space="preserve">2.63468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6959536075592</t>
+    <t xml:space="preserve">2.69595336914062</t>
   </si>
   <si>
     <t xml:space="preserve">2.68027925491333</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737863540649</t>
+    <t xml:space="preserve">2.69737839698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.74012613296509</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">2.74297595024109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72445154190063</t>
+    <t xml:space="preserve">2.72445178031921</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">2.72872638702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76434946060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152564048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75580024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71162748336792</t>
+    <t xml:space="preserve">2.76434969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7558000087738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71162724494934</t>
   </si>
   <si>
     <t xml:space="preserve">2.69025373458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035605430603</t>
+    <t xml:space="preserve">2.65035581588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.60760831832886</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">2.52068781852722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60618329048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5449116230011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54063677787781</t>
+    <t xml:space="preserve">2.60618352890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058573722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54491114616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54063701629639</t>
   </si>
   <si>
     <t xml:space="preserve">2.50501394271851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49788904190063</t>
+    <t xml:space="preserve">2.49788928031921</t>
   </si>
   <si>
     <t xml:space="preserve">2.50643849372864</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">2.57625985145569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60048389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5919337272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58195948600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55916118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58623433113098</t>
+    <t xml:space="preserve">2.60048365592957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59193420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58195972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5591607093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58623480796814</t>
   </si>
   <si>
     <t xml:space="preserve">2.5363621711731</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.48506474494934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54348683357239</t>
+    <t xml:space="preserve">2.54348635673523</t>
   </si>
   <si>
     <t xml:space="preserve">2.6874041557312</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">2.69452857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75722503662109</t>
+    <t xml:space="preserve">2.75722455978394</t>
   </si>
   <si>
     <t xml:space="preserve">2.77147459983826</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">2.9054172039032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03508472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215834617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727053642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25737261772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07783246040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16760277748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16190338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16047835350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21890020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22174954414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589726448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159618377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877188682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23172450065613</t>
+    <t xml:space="preserve">3.03508496284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727029800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25737285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07783269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16760301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16190314292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16047811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21889996528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22174978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23172378540039</t>
   </si>
   <si>
     <t xml:space="preserve">3.12913012504578</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">3.19610142707825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10063195228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1975257396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884844779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602438926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29157114028931</t>
+    <t xml:space="preserve">3.10063147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884892463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29157090187073</t>
   </si>
   <si>
     <t xml:space="preserve">3.3257691860199</t>
@@ -845,52 +845,52 @@
     <t xml:space="preserve">3.28302121162415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31864500045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34001851081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559006690979</t>
+    <t xml:space="preserve">3.31864452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34001922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559030532837</t>
   </si>
   <si>
     <t xml:space="preserve">3.35569262504578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23457431793213</t>
+    <t xml:space="preserve">3.23457384109497</t>
   </si>
   <si>
     <t xml:space="preserve">3.27019715309143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0892322063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06358361244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17488980293274</t>
+    <t xml:space="preserve">3.08923172950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06358337402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17489004135132</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11147856712341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13886070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11868453025818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07112598419189</t>
+    <t xml:space="preserve">3.11147809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13886022567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462494850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003708839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11868405342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07112574577332</t>
   </si>
   <si>
     <t xml:space="preserve">3.03797912597656</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">3.04806733131409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99762582778931</t>
+    <t xml:space="preserve">2.99762630462646</t>
   </si>
   <si>
     <t xml:space="preserve">3.00627326965332</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">2.89098024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87512731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918618202209</t>
+    <t xml:space="preserve">2.87512707710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918642044067</t>
   </si>
   <si>
     <t xml:space="preserve">2.92700886726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9068329334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86936259269714</t>
+    <t xml:space="preserve">2.90683317184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86936283111572</t>
   </si>
   <si>
     <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85783314704895</t>
+    <t xml:space="preserve">2.85783290863037</t>
   </si>
   <si>
     <t xml:space="preserve">2.8535099029541</t>
@@ -950,31 +950,31 @@
     <t xml:space="preserve">2.8246865272522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79298067092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76415705680847</t>
+    <t xml:space="preserve">2.79298043251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76415729522705</t>
   </si>
   <si>
     <t xml:space="preserve">2.81027483940125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80018639564514</t>
+    <t xml:space="preserve">2.80018663406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.79153943061829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72956919670105</t>
+    <t xml:space="preserve">2.72956943511963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75262808799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75983357429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74686360359192</t>
+    <t xml:space="preserve">2.75983381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74686336517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.95439124107361</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">2.92124462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92845010757446</t>
+    <t xml:space="preserve">2.92845058441162</t>
   </si>
   <si>
     <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189225196838</t>
+    <t xml:space="preserve">2.8318920135498</t>
   </si>
   <si>
     <t xml:space="preserve">2.84342169761658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80450987815857</t>
+    <t xml:space="preserve">2.80451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">2.83045101165771</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80739212036133</t>
+    <t xml:space="preserve">2.78865694999695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
     <t xml:space="preserve">2.80883359909058</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">2.84053921699524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85495090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86503911018372</t>
+    <t xml:space="preserve">2.85495066642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86503934860229</t>
   </si>
   <si>
     <t xml:space="preserve">2.87656831741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90827369689941</t>
+    <t xml:space="preserve">2.90827417373657</t>
   </si>
   <si>
     <t xml:space="preserve">2.83909821510315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73821616172791</t>
+    <t xml:space="preserve">2.73821663856506</t>
   </si>
   <si>
     <t xml:space="preserve">2.75551009178162</t>
@@ -1040,34 +1040,34 @@
     <t xml:space="preserve">2.76848077774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218753814697</t>
+    <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72668719291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71371650695801</t>
+    <t xml:space="preserve">2.71371674537659</t>
   </si>
   <si>
     <t xml:space="preserve">2.7252459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68056988716125</t>
+    <t xml:space="preserve">2.6805694103241</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480492591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67336368560791</t>
+    <t xml:space="preserve">2.67336392402649</t>
   </si>
   <si>
     <t xml:space="preserve">2.65895223617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67624640464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406932830811</t>
+    <t xml:space="preserve">2.67624592781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406908988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.79442191123962</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">2.79874539375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74542212486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78577470779419</t>
+    <t xml:space="preserve">2.74542188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78577494621277</t>
   </si>
   <si>
     <t xml:space="preserve">2.92268586158752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02500820159912</t>
+    <t xml:space="preserve">3.0250084400177</t>
   </si>
   <si>
     <t xml:space="preserve">3.02644920349121</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">3.10571360588074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12156653404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17056632041931</t>
+    <t xml:space="preserve">3.12156629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17056655883789</t>
   </si>
   <si>
     <t xml:space="preserve">3.14174318313599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13597893714905</t>
+    <t xml:space="preserve">3.13597822189331</t>
   </si>
   <si>
     <t xml:space="preserve">3.09850811958313</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">3.08409667015076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07400798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04086112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05383157730103</t>
+    <t xml:space="preserve">3.07400822639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04086089134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05383133888245</t>
   </si>
   <si>
     <t xml:space="preserve">3.17921352386475</t>
@@ -1136,49 +1136,49 @@
     <t xml:space="preserve">3.12589001655579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05527305603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07977318763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14894890785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1619188785553</t>
+    <t xml:space="preserve">3.05527281761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07977271080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14894843101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16191935539246</t>
   </si>
   <si>
     <t xml:space="preserve">3.1475076675415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0999493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13453722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15903663635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15471315383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12877297401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11580228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10427308082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815505981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483202934265</t>
+    <t xml:space="preserve">3.09994912147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13453674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15903687477112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15471339225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12877249717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11580181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10427284240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012505531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815553665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483250617981</t>
   </si>
   <si>
     <t xml:space="preserve">2.97168564796448</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.82180404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8679211139679</t>
+    <t xml:space="preserve">2.86792135238647</t>
   </si>
   <si>
     <t xml:space="preserve">2.8967444896698</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">2.88233304023743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85062766075134</t>
+    <t xml:space="preserve">2.85062742233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.82901000976562</t>
@@ -1211,52 +1211,52 @@
     <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72236371040344</t>
+    <t xml:space="preserve">2.72236347198486</t>
   </si>
   <si>
     <t xml:space="preserve">2.70506954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71227526664734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65606999397278</t>
+    <t xml:space="preserve">2.71227550506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65607023239136</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76703977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505444526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740745544434</t>
+    <t xml:space="preserve">2.76703929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740769386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.69498133659363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73461365699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7057900428772</t>
+    <t xml:space="preserve">2.7346134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70579028129578</t>
   </si>
   <si>
     <t xml:space="preserve">2.73101043701172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72020196914673</t>
+    <t xml:space="preserve">2.72020173072815</t>
   </si>
   <si>
     <t xml:space="preserve">2.79226016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84630393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77424573898315</t>
+    <t xml:space="preserve">2.84630370140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77424550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.77064275741577</t>
@@ -1268,28 +1268,28 @@
     <t xml:space="preserve">2.74181938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71299624443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63373184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6409375667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65534925460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64814352989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5868935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5724823474884</t>
+    <t xml:space="preserve">2.71299600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63373160362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65534949302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64814329147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689379692078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248210906982</t>
   </si>
   <si>
     <t xml:space="preserve">2.57968783378601</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">2.55807065963745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56167364120483</t>
+    <t xml:space="preserve">2.56167340278625</t>
   </si>
   <si>
     <t xml:space="preserve">2.55086445808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56887936592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43557143211365</t>
+    <t xml:space="preserve">2.56887912750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43557167053223</t>
   </si>
   <si>
     <t xml:space="preserve">2.37432169914246</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">2.39593935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41755676269531</t>
+    <t xml:space="preserve">2.41755700111389</t>
   </si>
   <si>
     <t xml:space="preserve">2.41395378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991048812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505777359009</t>
+    <t xml:space="preserve">2.36351323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505753517151</t>
   </si>
   <si>
     <t xml:space="preserve">2.4499831199646</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">2.52204132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4283652305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44637989997864</t>
+    <t xml:space="preserve">2.42836546897888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4463803768158</t>
   </si>
   <si>
     <t xml:space="preserve">2.4211597442627</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">2.50762963294983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59409999847412</t>
+    <t xml:space="preserve">2.59409976005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527638435364</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">2.65174627304077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62292289733887</t>
+    <t xml:space="preserve">2.62292313575745</t>
   </si>
   <si>
     <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60851120948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6373348236084</t>
+    <t xml:space="preserve">2.60851144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63733458518982</t>
   </si>
   <si>
     <t xml:space="preserve">2.68417239189148</t>
@@ -1385,70 +1385,70 @@
     <t xml:space="preserve">2.66615796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69137835502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67696642875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73281192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62172198295593</t>
+    <t xml:space="preserve">2.69137811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67696666717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73281216621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62172222137451</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48841428756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.403244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43657207489014</t>
+    <t xml:space="preserve">2.48841404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40324521064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43657231330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.45879006385803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39213633537292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40694808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36991834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29956126213074</t>
+    <t xml:space="preserve">2.39213609695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40694856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36991810798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29956150054932</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32548213005066</t>
+    <t xml:space="preserve">2.32548236846924</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732410430908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38843297958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42916631698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41805744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46989917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50322604179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52174115180969</t>
+    <t xml:space="preserve">2.38843321800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4291660785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41805696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46989941596985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5032262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52174091339111</t>
   </si>
   <si>
     <t xml:space="preserve">2.53285026550293</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45508694648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58098888397217</t>
+    <t xml:space="preserve">2.5254442691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45508718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58098912239075</t>
   </si>
   <si>
     <t xml:space="preserve">2.54395914077759</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">2.4736020565033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44768118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53655314445496</t>
+    <t xml:space="preserve">2.44768095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53655290603638</t>
   </si>
   <si>
     <t xml:space="preserve">2.4773051738739</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">2.51433515548706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48100781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46619606018066</t>
+    <t xml:space="preserve">2.48100805282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46619629859924</t>
   </si>
   <si>
     <t xml:space="preserve">2.39583897590637</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">2.36621522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34399747848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35880899429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35510635375977</t>
+    <t xml:space="preserve">2.34399724006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35880923271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35510611534119</t>
   </si>
   <si>
     <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30696725845337</t>
+    <t xml:space="preserve">2.30696702003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.3106701374054</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">2.32177925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39954233169556</t>
+    <t xml:space="preserve">2.39954209327698</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41435432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37362122535706</t>
+    <t xml:space="preserve">2.41435408592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37362146377563</t>
   </si>
   <si>
     <t xml:space="preserve">2.31807637214661</t>
@@ -1553,49 +1553,49 @@
     <t xml:space="preserve">2.32918524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27734327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2662341594696</t>
+    <t xml:space="preserve">2.27734303474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26623439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.29215526580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27364039421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28845191001892</t>
+    <t xml:space="preserve">2.27363991737366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2884521484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.28474950790405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38472986221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20698618888855</t>
+    <t xml:space="preserve">2.38473010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20698642730713</t>
   </si>
   <si>
     <t xml:space="preserve">2.24031329154968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15514421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1477382183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10330247879028</t>
+    <t xml:space="preserve">2.15514445304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292622566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14773845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1033022403717</t>
   </si>
   <si>
     <t xml:space="preserve">2.09959936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08849048614502</t>
+    <t xml:space="preserve">2.08849024772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10700535774231</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">1.98850953578949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95147931575775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553939819336</t>
+    <t xml:space="preserve">1.95147967338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553915977478</t>
   </si>
   <si>
     <t xml:space="preserve">2.06627225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04775738716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997561454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12922358512878</t>
+    <t xml:space="preserve">2.04775762557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12922334671021</t>
   </si>
   <si>
     <t xml:space="preserve">2.14403533935547</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">2.13662934303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18847155570984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23290729522705</t>
+    <t xml:space="preserve">2.18847131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439218521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23290753364563</t>
   </si>
   <si>
     <t xml:space="preserve">2.25512552261353</t>
@@ -1646,22 +1646,22 @@
     <t xml:space="preserve">2.20328330993652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19958066940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21809506416321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811423301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11070823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24771976470947</t>
+    <t xml:space="preserve">2.1995804309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21809530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367825508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11070847511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24771928787231</t>
   </si>
   <si>
     <t xml:space="preserve">2.33659100532532</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">2.51063227653503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65504932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68096995353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60320711135864</t>
+    <t xml:space="preserve">2.65504908561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68096971511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60320687294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65875196456909</t>
+    <t xml:space="preserve">2.65875172615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.65134596824646</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">2.62542486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71799993515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70318818092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7291088104248</t>
+    <t xml:space="preserve">2.71800017356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70318794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72910904884338</t>
   </si>
   <si>
     <t xml:space="preserve">2.69207882881165</t>
@@ -1709,22 +1709,22 @@
     <t xml:space="preserve">2.75502991676331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8031690120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81798076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84390163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87352609634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86241674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88093209266663</t>
+    <t xml:space="preserve">2.80316877365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81798100471497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84390187263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87352585792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86241698265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88093185424805</t>
   </si>
   <si>
     <t xml:space="preserve">2.76243615150452</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">2.76984190940857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7994658946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205965995789</t>
+    <t xml:space="preserve">2.79946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205989837646</t>
   </si>
   <si>
     <t xml:space="preserve">2.81427788734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79576301574707</t>
+    <t xml:space="preserve">2.79576325416565</t>
   </si>
   <si>
     <t xml:space="preserve">2.75873303413391</t>
@@ -1763,28 +1763,28 @@
     <t xml:space="preserve">2.88833785057068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96239757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98091268539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91796183586121</t>
+    <t xml:space="preserve">2.962397813797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98091292381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91796207427979</t>
   </si>
   <si>
     <t xml:space="preserve">2.94758582115173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95128870010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9364767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95499157905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93277359008789</t>
+    <t xml:space="preserve">2.95128846168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93647694587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95499181747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93277382850647</t>
   </si>
   <si>
     <t xml:space="preserve">2.91055583953857</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">2.96980404853821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97720980644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94018006324768</t>
+    <t xml:space="preserve">2.97720956802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9401798248291</t>
   </si>
   <si>
     <t xml:space="preserve">2.89944672584534</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">2.8661196231842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80687212944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279299736023</t>
+    <t xml:space="preserve">2.80687165260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279275894165</t>
   </si>
   <si>
     <t xml:space="preserve">2.85501098632812</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">2.71059417724609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70689105987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61061310768127</t>
+    <t xml:space="preserve">2.70689082145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61061334609985</t>
   </si>
   <si>
     <t xml:space="preserve">2.6402370929718</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">2.6365339756012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63283109664917</t>
+    <t xml:space="preserve">2.63283085823059</t>
   </si>
   <si>
     <t xml:space="preserve">2.61801910400391</t>
@@ -1841,31 +1841,31 @@
     <t xml:space="preserve">2.69578194618225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68467283248901</t>
+    <t xml:space="preserve">2.68467307090759</t>
   </si>
   <si>
     <t xml:space="preserve">2.6883761882782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6143159866333</t>
+    <t xml:space="preserve">2.61431622505188</t>
   </si>
   <si>
     <t xml:space="preserve">2.56988000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211692810059</t>
+    <t xml:space="preserve">2.49211716651917</t>
   </si>
   <si>
     <t xml:space="preserve">2.50692915916443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34770011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23661041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18476843833923</t>
+    <t xml:space="preserve">2.34770035743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23661017417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
     <t xml:space="preserve">2.19587731361389</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">2.10493922233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09326672554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12050247192383</t>
+    <t xml:space="preserve">2.09326696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12050271034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.13995671272278</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">2.07770371437073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0504674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04657673835754</t>
+    <t xml:space="preserve">2.05046796798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04657697677612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03490447998047</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">2.05435848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03101372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02323198318481</t>
+    <t xml:space="preserve">2.03101348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
     <t xml:space="preserve">2.0582492351532</t>
@@ -1931,49 +1931,49 @@
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944569587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18664693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9687602519989</t>
+    <t xml:space="preserve">2.22944593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1866466999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96876037120819</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92985188961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02712273597717</t>
+    <t xml:space="preserve">1.92985200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02712249755859</t>
   </si>
   <si>
     <t xml:space="preserve">1.94152438640594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84425377845764</t>
+    <t xml:space="preserve">1.84425354003906</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76643705368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80923628807068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75087380409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74698281288147</t>
+    <t xml:space="preserve">1.76643693447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8092360496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7508739233017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74698269367218</t>
   </si>
   <si>
     <t xml:space="preserve">1.69251120090485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78978204727173</t>
+    <t xml:space="preserve">1.78978192806244</t>
   </si>
   <si>
     <t xml:space="preserve">1.82090866565704</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">1.73920106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7430921792984</t>
+    <t xml:space="preserve">1.74309206008911</t>
   </si>
   <si>
     <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196532249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7197470664978</t>
+    <t xml:space="preserve">1.7119654417038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71974694728851</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78589117527008</t>
+    <t xml:space="preserve">1.78589129447937</t>
   </si>
   <si>
     <t xml:space="preserve">1.73141944408417</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78200042247772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83258140087128</t>
+    <t xml:space="preserve">1.78200030326843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83258104324341</t>
   </si>
   <si>
     <t xml:space="preserve">1.80145454406738</t>
@@ -2021,82 +2021,82 @@
     <t xml:space="preserve">1.84036290645599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85592603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83647191524506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87927103042603</t>
+    <t xml:space="preserve">1.85592615604401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83647203445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87927114963531</t>
   </si>
   <si>
     <t xml:space="preserve">1.79756367206573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77032804489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75476467609406</t>
+    <t xml:space="preserve">1.77032780647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869040966034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75476455688477</t>
   </si>
   <si>
     <t xml:space="preserve">1.75865530967712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76254630088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80534541606903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81701803207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82479965686798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91428875923157</t>
+    <t xml:space="preserve">1.76254618167877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80534529685974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81701791286469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82479953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91428864002228</t>
   </si>
   <si>
     <t xml:space="preserve">1.93374276161194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89094352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538015842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650689601898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89483416080475</t>
+    <t xml:space="preserve">1.89094376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538027763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89483439922333</t>
   </si>
   <si>
     <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92207026481628</t>
+    <t xml:space="preserve">1.92207038402557</t>
   </si>
   <si>
     <t xml:space="preserve">2.01155948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1671929359436</t>
+    <t xml:space="preserve">2.16719269752502</t>
   </si>
   <si>
     <t xml:space="preserve">2.16330170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08159422874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06213998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13217520713806</t>
+    <t xml:space="preserve">2.08159446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06214022636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13217496871948</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
@@ -2105,19 +2105,19 @@
     <t xml:space="preserve">2.19053769111633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15552020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19831943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17108345031738</t>
+    <t xml:space="preserve">2.15551996231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19831919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1710832118988</t>
   </si>
   <si>
     <t xml:space="preserve">2.14384770393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11272096633911</t>
+    <t xml:space="preserve">2.11272072792053</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548521995544</t>
@@ -2132,43 +2132,43 @@
     <t xml:space="preserve">2.15941119194031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13606572151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01934123039246</t>
+    <t xml:space="preserve">2.13606595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01934099197388</t>
   </si>
   <si>
     <t xml:space="preserve">1.87148940563202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91039776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872527122498</t>
+    <t xml:space="preserve">1.91039764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596113681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872539043427</t>
   </si>
   <si>
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988698959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95708775520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96486937999725</t>
+    <t xml:space="preserve">1.99988687038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95708787441254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96486961841583</t>
   </si>
   <si>
     <t xml:space="preserve">1.99210524559021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7275288105011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862044811249</t>
+    <t xml:space="preserve">1.72752857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862056732178</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">1.54232513904572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48940992355347</t>
+    <t xml:space="preserve">1.48941004276276</t>
   </si>
   <si>
     <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33844566345215</t>
+    <t xml:space="preserve">1.33844578266144</t>
   </si>
   <si>
     <t xml:space="preserve">1.30420637130737</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">1.27619230747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09098875522614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16102373600006</t>
+    <t xml:space="preserve">1.09098887443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16102385520935</t>
   </si>
   <si>
     <t xml:space="preserve">1.08009457588196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05986225605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0847635269165</t>
+    <t xml:space="preserve">1.05986213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08476364612579</t>
   </si>
   <si>
     <t xml:space="preserve">1.10188317298889</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">1.31976974010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910764217377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35400891304016</t>
+    <t xml:space="preserve">1.32910752296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35400903224945</t>
   </si>
   <si>
     <t xml:space="preserve">1.26685440540314</t>
@@ -2234,25 +2234,25 @@
     <t xml:space="preserve">1.32288241386414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28864300251007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28397417068481</t>
+    <t xml:space="preserve">1.28864312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28397405147552</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39291727542877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36179077625275</t>
+    <t xml:space="preserve">1.39291739463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36179065704346</t>
   </si>
   <si>
     <t xml:space="preserve">1.26062905788422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29642462730408</t>
+    <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
     <t xml:space="preserve">1.29798102378845</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29953730106354</t>
+    <t xml:space="preserve">1.29953742027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.31354439258575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29175579547882</t>
+    <t xml:space="preserve">1.29175567626953</t>
   </si>
   <si>
     <t xml:space="preserve">1.28241777420044</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">1.24350941181183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20927023887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17503082752228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13300979137421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10343945026398</t>
+    <t xml:space="preserve">1.20927011966705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17503070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13300967216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10343956947327</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">1.05674970149994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06764388084412</t>
+    <t xml:space="preserve">1.06764376163483</t>
   </si>
   <si>
     <t xml:space="preserve">1.12211561203003</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">1.13923513889313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19837582111359</t>
+    <t xml:space="preserve">1.1983757019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.2450658082962</t>
@@ -2333,28 +2333,28 @@
     <t xml:space="preserve">1.2217208147049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28708684444427</t>
+    <t xml:space="preserve">1.28708672523499</t>
   </si>
   <si>
     <t xml:space="preserve">1.27930498123169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17969977855682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1641366481781</t>
+    <t xml:space="preserve">1.17969989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16413640975952</t>
   </si>
   <si>
     <t xml:space="preserve">1.23572778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20615756511688</t>
+    <t xml:space="preserve">1.2061573266983</t>
   </si>
   <si>
     <t xml:space="preserve">1.20771384239197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18748140335083</t>
+    <t xml:space="preserve">1.18748152256012</t>
   </si>
   <si>
     <t xml:space="preserve">1.21082639694214</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">1.18592512607574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612246513367</t>
+    <t xml:space="preserve">1.13612258434296</t>
   </si>
   <si>
     <t xml:space="preserve">1.15791118144989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1407915353775</t>
+    <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
     <t xml:space="preserve">1.18436884880066</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">1.1252281665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09565794467926</t>
+    <t xml:space="preserve">1.09565782546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608760356903</t>
+    <t xml:space="preserve">1.06608748435974</t>
   </si>
   <si>
     <t xml:space="preserve">1.08320713043213</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">1.06297492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04896783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0941014289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07075667381287</t>
+    <t xml:space="preserve">1.04896795749664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410154819489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07075655460358</t>
   </si>
   <si>
     <t xml:space="preserve">1.09721422195435</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">1.03962993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04118621349335</t>
+    <t xml:space="preserve">1.04118633270264</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">1.03496086597443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03651738166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02251029014587</t>
+    <t xml:space="preserve">1.0365172624588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
     <t xml:space="preserve">0.996052622795105</t>
@@ -2465,22 +2465,22 @@
     <t xml:space="preserve">1.01628482341766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00850319862366</t>
+    <t xml:space="preserve">1.00850331783295</t>
   </si>
   <si>
     <t xml:space="preserve">1.01005959510803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00072169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991383612155914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966482162475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964925944805145</t>
+    <t xml:space="preserve">1.00072157382965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991383731365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96648234128952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96492600440979</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
@@ -2489,49 +2489,49 @@
     <t xml:space="preserve">0.954031646251678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975820183753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989827275276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969595074653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949362635612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968038618564606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957144379615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489313602448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999165177345276</t>
+    <t xml:space="preserve">0.975820302963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989827215671539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969595015048981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949362695217133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968038558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957144320011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99916535615921</t>
   </si>
   <si>
     <t xml:space="preserve">1.06453132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05830585956573</t>
+    <t xml:space="preserve">1.05830597877502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02406656742096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988270878791809</t>
+    <t xml:space="preserve">0.988270998001099</t>
   </si>
   <si>
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941580951213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933799266815186</t>
+    <t xml:space="preserve">0.941581070423126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93379932641983</t>
   </si>
   <si>
     <t xml:space="preserve">0.904228985309601</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">0.888665616512299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891778349876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835750460624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80306738615036</t>
+    <t xml:space="preserve">0.891778409481049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83575040102005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803067326545715</t>
   </si>
   <si>
     <t xml:space="preserve">0.787504076957703</t>
@@ -2564,28 +2564,28 @@
     <t xml:space="preserve">0.831081390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840419411659241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826412439346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817074298858643</t>
+    <t xml:space="preserve">0.840419352054596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826412498950958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817074358463287</t>
   </si>
   <si>
     <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89644730091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902672708034515</t>
+    <t xml:space="preserve">0.896447241306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902672648429871</t>
   </si>
   <si>
     <t xml:space="preserve">0.915123343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940024614334106</t>
+    <t xml:space="preserve">0.940024495124817</t>
   </si>
   <si>
     <t xml:space="preserve">0.977376639842987</t>
@@ -2597,22 +2597,22 @@
     <t xml:space="preserve">0.983601987361908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978933095932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929130375385284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961813271045685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946249961853027</t>
+    <t xml:space="preserve">0.978932917118073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92913031578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961813151836395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946249902248383</t>
   </si>
   <si>
     <t xml:space="preserve">0.943137288093567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930686593055725</t>
+    <t xml:space="preserve">0.930686712265015</t>
   </si>
   <si>
     <t xml:space="preserve">0.952475309371948</t>
@@ -2624,58 +2624,58 @@
     <t xml:space="preserve">0.926017701625824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935355722904205</t>
+    <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
     <t xml:space="preserve">0.971151292324066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947806417942047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792354106903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913567066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341659069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679620742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89955997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918235957622528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908897936344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894891023635864</t>
+    <t xml:space="preserve">0.947806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792294502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913566946983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341599464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8995600938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918236017227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908897995948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894890964031219</t>
   </si>
   <si>
     <t xml:space="preserve">0.910454332828522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944693624973297</t>
+    <t xml:space="preserve">0.944693684577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.01784121990204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05363702774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13767874240875</t>
+    <t xml:space="preserve">1.05363690853119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13767886161804</t>
   </si>
   <si>
     <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12989723682404</t>
+    <t xml:space="preserve">1.12989735603333</t>
   </si>
   <si>
     <t xml:space="preserve">1.10032689571381</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">1.09877049922943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07231295108795</t>
+    <t xml:space="preserve">1.07231283187866</t>
   </si>
   <si>
     <t xml:space="preserve">1.12834084033966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12055921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1174464225769</t>
+    <t xml:space="preserve">1.12055909633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11744654178619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15479850769043</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">1.31198799610138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25907289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.246621966362</t>
+    <t xml:space="preserve">1.25907278060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24662208557129</t>
   </si>
   <si>
     <t xml:space="preserve">1.25284743309021</t>
@@ -2717,19 +2717,19 @@
     <t xml:space="preserve">1.22638976573944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23105883598328</t>
+    <t xml:space="preserve">1.23105871677399</t>
   </si>
   <si>
     <t xml:space="preserve">1.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25751638412476</t>
+    <t xml:space="preserve">1.25751650333405</t>
   </si>
   <si>
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307975292206</t>
+    <t xml:space="preserve">1.27307987213135</t>
   </si>
   <si>
     <t xml:space="preserve">1.36023437976837</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">1.40069901943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381157398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37112855911255</t>
+    <t xml:space="preserve">1.40381169319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37112867832184</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39447379112244</t>
+    <t xml:space="preserve">1.39447367191315</t>
   </si>
   <si>
     <t xml:space="preserve">1.38980460166931</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">1.39758634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39136111736298</t>
+    <t xml:space="preserve">1.39136099815369</t>
   </si>
   <si>
     <t xml:space="preserve">1.40536797046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4380509853363</t>
+    <t xml:space="preserve">1.43805086612701</t>
   </si>
   <si>
     <t xml:space="preserve">1.52053654193878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57189559936523</t>
+    <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
     <t xml:space="preserve">1.56022310256958</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">1.58745884895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53765618801117</t>
+    <t xml:space="preserve">1.53765606880188</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431119441986</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">1.50341689586639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50497329235077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49096620082855</t>
+    <t xml:space="preserve">1.50497317314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49096632003784</t>
   </si>
   <si>
     <t xml:space="preserve">1.51798808574677</t>
@@ -2807,43 +2807,40 @@
     <t xml:space="preserve">1.46712338924408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47348165512085</t>
+    <t xml:space="preserve">1.47348153591156</t>
   </si>
   <si>
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937666416168</t>
+    <t xml:space="preserve">1.48937678337097</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49096632003784</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.54818880558014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55454695224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5561363697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57044208049774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56567358970642</t>
+    <t xml:space="preserve">1.55454683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55613648891449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57044196128845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56567347049713</t>
   </si>
   <si>
     <t xml:space="preserve">1.567263007164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53706228733063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5275251865387</t>
+    <t xml:space="preserve">1.53706216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52752506732941</t>
   </si>
   <si>
     <t xml:space="preserve">1.47030258178711</t>
@@ -2852,676 +2849,679 @@
     <t xml:space="preserve">1.4432806968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40672194957733</t>
+    <t xml:space="preserve">1.40672183036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374371528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44487023353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39241623878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35744690895081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34949922561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34790980815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33201456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585725307465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929838657379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31453001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27638149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3018137216568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30499279499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31135094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30340337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2843291759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479195594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22074854373932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2223379611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2557178735733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24935984611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25412821769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28273963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2271066904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2112113237381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2732025384903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26366543769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37652099132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36698400974274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35267841815948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37493169307709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37969994544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128972053528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34314131736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33678317070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36221528053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.363804936409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39877438545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40513241291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49732422828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189211845398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42738556861877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4146693944931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42420661449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45917594432831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46076548099518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41943800449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39082670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33996224403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34155166149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37811064720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35426783561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33042514324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37175250053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33837270736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38287913799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116715908051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49573481082916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50845098495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51162993907928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50209283828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51321947574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47507095336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010174274445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4877872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47983956336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45599687099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301875591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51004028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56249439716339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63720178604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66501832008362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67693960666656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70078253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65309679508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60541141033173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55772590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57362115383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43851220607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44645977020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440745353699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45122838020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49414527416229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51639842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61335909366608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733281612396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63322794437408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62130653858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59349024295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58792674541473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60143780708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62925410270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66104435920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5386518239975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54183077812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52911472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53070414066315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434611320496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43056464195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37334203720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30817186832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30022442340851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22869598865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23346471786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36539447307587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36062598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40831136703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59746372699738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7484678030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423190116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76038908958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77231061458588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025805950165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74449408054352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81999599933624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81204855442047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83191752433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82794368267059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178649425507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986520767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396996021271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628433704376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76833689212799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78820586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7285989522934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64514923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71667766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73654651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641560554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436305046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410087108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7403576374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76195001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75763154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490556240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7533130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67730736732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.644486784935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55811655521393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4769287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46483683586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45792722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42337930202484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50456702709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50283980369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865617275238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51665902137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48038339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4890204668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47001910209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41128730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3819215297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40092289447784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43028879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4061051607132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501204013824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37328457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34737348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52875065803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59957420825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54775214195251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55293428897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55466175079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60648393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60475647449493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58230018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58057284355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53047811985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5252959728241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51493144035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49420273303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49765753746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45447242259979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43547093868256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44756281375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4285614490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39228594303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35255575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33873653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3214625120163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32318985462189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31973516941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31628036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31282544136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33009946346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3801943063736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35082840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33355438709259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31800770759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29555153846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26791310310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2368198633194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25754857063293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2247279882431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23854720592499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2005443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22300064563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1884526014328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21954572200775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2610034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28691446781158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32664465904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29382407665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2730952501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35773801803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39574074745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39746820926666</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44487023353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39241623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35744690895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34949922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34790980815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33201456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585737228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929850578308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31453001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27638161182404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30181384086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30499279499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31135094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30340325832367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2843291759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479207515717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22074842453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2223379611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25571775436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24935984611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25412821769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28273963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21121144294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2732025384903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26366543769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37652099132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36698389053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3526782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970006465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128960132599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34314119815826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33678317070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36221539974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.363804936409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39877426624298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897498607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40513241291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53388321399689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49732422828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189199924469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42738556861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4146693944931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42420661449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45917594432831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46076548099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41943800449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39082670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33996224403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34155166149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37811064720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35426783561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33042514324188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37175250053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33837270736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38287913799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116715908051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49573469161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50845098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51162993907928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50209295749664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51321947574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47507107257843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010186195374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4877872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47983956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45599699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301875591278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51004040241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56249439716339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63720178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66501832008362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67693948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70078253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65309679508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60541141033173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55772590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57362103462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43851220607758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44645977020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440745353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45122826099396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49414527416229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61335897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733293533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62130653858185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59349012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58792674541473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60143780708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62925410270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53865170478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54183077812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52911460399628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53070414066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434599399567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43056464195251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37334215641022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30817186832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30022430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22869610786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23346471786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36539447307587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36062586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40831136703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59746384620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74846792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423190116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76038920879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77231061458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74449408054352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81999611854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81204855442047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83191764354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82794368267059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178637504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986508846283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82396996021271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628433704376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7683367729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.788205742836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859883308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71667754650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436305046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410087108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7403576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71012794971466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76195001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75763165950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75331294536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603904247284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67730736732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64448666572571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55811655521393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46483683586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45792722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42337930202484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50456702709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50283968448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865605354309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51665902137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48038351535797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4890204668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48211085796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47001910209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41128730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3819215297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40092301368713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43028879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37328457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34737348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52875077724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59957420825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477522611618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55293428897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55466175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60648381710052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60475647449493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58230030536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58057284355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53047811985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5252959728241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51493144035339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49420273303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49765753746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510664463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43547093868256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44756281375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4285614490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39228594303131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35255575180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33873653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3214625120163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32318985462189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31973516941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31628036499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31282544136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33009946346283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38019418716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35082840919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33355438709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31800770759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29555153846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26791310310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2368198633194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25754857063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247279882431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23854720592499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2005443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22300052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1884526014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21954572200775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2610034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28691446781158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30418848991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32664465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29382407665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2730952501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35773801803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39574086666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39746820926666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44929015636444</t>
+    <t xml:space="preserve">1.44929027557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992449760437</t>
+    <t xml:space="preserve">1.41992437839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301476955414</t>
+    <t xml:space="preserve">1.41301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464750766754</t>
+    <t xml:space="preserve">1.38710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464762687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.331827044487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591583251953</t>
+    <t xml:space="preserve">1.33182692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591595172882</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3569,22 +3569,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564602375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937063694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827751636505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136778831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655005455017</t>
+    <t xml:space="preserve">1.34564614295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136790752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655017375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036915302277</t>
+    <t xml:space="preserve">1.29036927223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910106658936</t>
+    <t xml:space="preserve">1.34910094738007</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938488006592</t>
+    <t xml:space="preserve">1.49938476085663</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838636398315</t>
+    <t xml:space="preserve">1.51838624477386</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974941253662</t>
+    <t xml:space="preserve">1.50974929332733</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4181969165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729300498962</t>
+    <t xml:space="preserve">1.41819703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729312419891</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302901268005</t>
+    <t xml:space="preserve">1.60302889347076</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62893998622894</t>
+    <t xml:space="preserve">1.62894010543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6323949098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093713760376</t>
+    <t xml:space="preserve">1.63239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093725681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548518180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57193577289581</t>
+    <t xml:space="preserve">1.62548530101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5719358921051</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -40797,7 +40797,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1377" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -40849,7 +40849,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1379" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -40875,7 +40875,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1380" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -40901,7 +40901,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40927,7 +40927,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40953,7 +40953,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40979,7 +40979,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G1384" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -41005,7 +41005,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -41031,7 +41031,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1386" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -41057,7 +41057,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1387" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -41083,7 +41083,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -41135,7 +41135,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1390" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -41161,7 +41161,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1391" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -41187,7 +41187,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1392" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -41213,7 +41213,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1393" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -41239,7 +41239,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -41265,7 +41265,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1395" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -41291,7 +41291,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1396" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -41317,7 +41317,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -41343,7 +41343,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -41369,7 +41369,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1399" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -41395,7 +41395,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -41421,7 +41421,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1401" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -41447,7 +41447,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -41473,7 +41473,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1403" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -41499,7 +41499,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1404" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41525,7 +41525,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41551,7 +41551,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1406" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41577,7 +41577,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -41603,7 +41603,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -41629,7 +41629,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1409" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -41655,7 +41655,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1410" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -41681,7 +41681,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1411" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -41707,7 +41707,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1412" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -41733,7 +41733,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1413" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -41759,7 +41759,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1414" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -41785,7 +41785,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1415" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41811,7 +41811,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1416" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41837,7 +41837,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1417" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41863,7 +41863,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1418" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41889,7 +41889,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1419" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41915,7 +41915,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1420" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41941,7 +41941,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1421" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41967,7 +41967,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41993,7 +41993,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1423" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -42019,7 +42019,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1424" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -42045,7 +42045,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1425" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -42071,7 +42071,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1426" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -42097,7 +42097,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1427" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -42123,7 +42123,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1428" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -42149,7 +42149,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1429" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -42175,7 +42175,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1430" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -42201,7 +42201,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1431" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -42227,7 +42227,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1432" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -42253,7 +42253,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1433" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -42279,7 +42279,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1434" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -42305,7 +42305,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1435" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42331,7 +42331,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -42357,7 +42357,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1437" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -42383,7 +42383,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1438" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -42409,7 +42409,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1439" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -42435,7 +42435,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1440" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -42487,7 +42487,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1442" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -42513,7 +42513,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42565,7 +42565,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1445" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -42591,7 +42591,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1446" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -42617,7 +42617,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1447" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -42643,7 +42643,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1448" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -42669,7 +42669,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1449" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -42695,7 +42695,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1450" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -42721,7 +42721,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1451" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -42747,7 +42747,7 @@
         <v>1.75</v>
       </c>
       <c r="G1452" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -42773,7 +42773,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1453" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42799,7 +42799,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1454" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42825,7 +42825,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1455" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42851,7 +42851,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1456" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42877,7 +42877,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1457" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42903,7 +42903,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1458" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42929,7 +42929,7 @@
         <v>1.75</v>
       </c>
       <c r="G1459" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42955,7 +42955,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G1460" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42981,7 +42981,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1461" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -43007,7 +43007,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1462" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -43033,7 +43033,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1463" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -43059,7 +43059,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1464" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -43085,7 +43085,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1465" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -43111,7 +43111,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1466" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -43137,7 +43137,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1467" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -43163,7 +43163,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1468" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -43189,7 +43189,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1469" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -43215,7 +43215,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1470" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -43241,7 +43241,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1471" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -43267,7 +43267,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1472" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -43319,7 +43319,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1474" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -43345,7 +43345,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1475" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -43397,7 +43397,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1477" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -43423,7 +43423,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1478" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43449,7 +43449,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1479" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43475,7 +43475,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1480" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43501,7 +43501,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1481" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43527,7 +43527,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1482" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43553,7 +43553,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1483" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43579,7 +43579,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1484" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -43605,7 +43605,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1485" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43631,7 +43631,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1486" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43657,7 +43657,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1487" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43683,7 +43683,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1488" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -43709,7 +43709,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1489" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43735,7 +43735,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1490" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -43761,7 +43761,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1491" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43787,7 +43787,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1492" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43813,7 +43813,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1493" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43839,7 +43839,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1494" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43865,7 +43865,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1495" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43891,7 +43891,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1496" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43917,7 +43917,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1497" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43943,7 +43943,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43969,7 +43969,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1499" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43995,7 +43995,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -44021,7 +44021,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1501" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -44047,7 +44047,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1502" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -44099,7 +44099,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1504" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -44125,7 +44125,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1505" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -44203,7 +44203,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1508" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -44229,7 +44229,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1509" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -44255,7 +44255,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1510" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -44281,7 +44281,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1511" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -44307,7 +44307,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1512" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -44333,7 +44333,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1513" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -44359,7 +44359,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1514" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44385,7 +44385,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1515" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -44411,7 +44411,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1516" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44437,7 +44437,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1517" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -44463,7 +44463,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1518" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44489,7 +44489,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1519" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44541,7 +44541,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1521" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44567,7 +44567,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44593,7 +44593,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1523" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -44619,7 +44619,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1524" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -44645,7 +44645,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -44671,7 +44671,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -44697,7 +44697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1527" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -44723,7 +44723,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1528" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -44749,7 +44749,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1529" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -44775,7 +44775,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1530" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44801,7 +44801,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44827,7 +44827,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1532" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44853,7 +44853,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1533" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44879,7 +44879,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44905,7 +44905,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1535" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44931,7 +44931,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1536" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44957,7 +44957,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44983,7 +44983,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1538" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -45009,7 +45009,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1539" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -45035,7 +45035,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1540" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -45061,7 +45061,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1541" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -45087,7 +45087,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1542" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -45139,7 +45139,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1544" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -45165,7 +45165,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1545" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -45191,7 +45191,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1546" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -45217,7 +45217,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1547" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -45243,7 +45243,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1548" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -45269,7 +45269,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1549" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -45295,7 +45295,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1550" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -45321,7 +45321,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1551" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45347,7 +45347,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1552" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -45373,7 +45373,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1553" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -45399,7 +45399,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1554" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45425,7 +45425,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1555" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45451,7 +45451,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G1556" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45477,7 +45477,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1557" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45503,7 +45503,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45529,7 +45529,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1559" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45555,7 +45555,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1560" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45581,7 +45581,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1561" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45607,7 +45607,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1562" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45633,7 +45633,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1563" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45659,7 +45659,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1564" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45685,7 +45685,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45711,7 +45711,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1566" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45737,7 +45737,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1567" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45763,7 +45763,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1568" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45789,7 +45789,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1569" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45815,7 +45815,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45841,7 +45841,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G1571" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45867,7 +45867,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1572" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45893,7 +45893,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1573" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45919,7 +45919,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1574" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45945,7 +45945,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45971,7 +45971,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1576" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45997,7 +45997,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1577" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -46023,7 +46023,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1578" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -46049,7 +46049,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1579" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -46075,7 +46075,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1580" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -46101,7 +46101,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1581" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -46127,7 +46127,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1582" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -46153,7 +46153,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1583" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -46179,7 +46179,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1584" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -46205,7 +46205,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1585" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -46231,7 +46231,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1586" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -46257,7 +46257,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1587" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -46283,7 +46283,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1588" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -46309,7 +46309,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1589" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -46335,7 +46335,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46361,7 +46361,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1591" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -46387,7 +46387,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46413,7 +46413,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46439,7 +46439,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1594" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46465,7 +46465,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1595" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46491,7 +46491,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1596" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46517,7 +46517,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46543,7 +46543,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46569,7 +46569,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46595,7 +46595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1600" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46621,7 +46621,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46647,7 +46647,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46673,7 +46673,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46699,7 +46699,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46725,7 +46725,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46751,7 +46751,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46777,7 +46777,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46803,7 +46803,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1608" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46829,7 +46829,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46855,7 +46855,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46881,7 +46881,7 @@
         <v>2.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46907,7 +46907,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46933,7 +46933,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1613" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46959,7 +46959,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1614" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46985,7 +46985,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -47011,7 +47011,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1616" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -47037,7 +47037,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1617" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -47063,7 +47063,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -47089,7 +47089,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1619" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -47115,7 +47115,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1620" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -47141,7 +47141,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -47167,7 +47167,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -47193,7 +47193,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -47219,7 +47219,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1624" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -47245,7 +47245,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47271,7 +47271,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47297,7 +47297,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47323,7 +47323,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47349,7 +47349,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47375,7 +47375,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47401,7 +47401,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47427,7 +47427,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47453,7 +47453,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47479,7 +47479,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47505,7 +47505,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47531,7 +47531,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47557,7 +47557,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G1637" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47583,7 +47583,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1638" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47609,7 +47609,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47635,7 +47635,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1640" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47661,7 +47661,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47687,7 +47687,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1642" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47713,7 +47713,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47739,7 +47739,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1644" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47765,7 +47765,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1645" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47791,7 +47791,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1646" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47817,7 +47817,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47843,7 +47843,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47869,7 +47869,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47895,7 +47895,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47921,7 +47921,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47947,7 +47947,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47973,7 +47973,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47999,7 +47999,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -48025,7 +48025,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -48051,7 +48051,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -48077,7 +48077,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1657" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -48103,7 +48103,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -48129,7 +48129,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1659" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -48155,7 +48155,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -48181,7 +48181,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -48207,7 +48207,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -48233,7 +48233,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1663" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48259,7 +48259,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48285,7 +48285,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1665" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48311,7 +48311,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48337,7 +48337,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48363,7 +48363,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48389,7 +48389,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48415,7 +48415,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48441,7 +48441,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48467,7 +48467,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1672" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48493,7 +48493,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48519,7 +48519,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48545,7 +48545,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48571,7 +48571,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1676" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48597,7 +48597,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1677" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48623,7 +48623,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G1678" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48649,7 +48649,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48675,7 +48675,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48701,7 +48701,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48727,7 +48727,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48753,7 +48753,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48779,7 +48779,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1684" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48805,7 +48805,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48831,7 +48831,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48857,7 +48857,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1687" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48883,7 +48883,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48909,7 +48909,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48935,7 +48935,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48961,7 +48961,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48987,7 +48987,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -49013,7 +49013,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -49039,7 +49039,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -49065,7 +49065,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -49091,7 +49091,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1696" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -49117,7 +49117,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -49143,7 +49143,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -49169,7 +49169,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -49195,7 +49195,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1700" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -49221,7 +49221,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49247,7 +49247,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -49273,7 +49273,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49299,7 +49299,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49325,7 +49325,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49351,7 +49351,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49377,7 +49377,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49403,7 +49403,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49429,7 +49429,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1709" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49455,7 +49455,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49481,7 +49481,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49507,7 +49507,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49533,7 +49533,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49559,7 +49559,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49585,7 +49585,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1715" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49611,7 +49611,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49637,7 +49637,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49663,7 +49663,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49689,7 +49689,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49715,7 +49715,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49741,7 +49741,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1721" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49767,7 +49767,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49793,7 +49793,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49819,7 +49819,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49845,7 +49845,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49871,7 +49871,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49897,7 +49897,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49923,7 +49923,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49949,7 +49949,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49975,7 +49975,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -50001,7 +50001,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -50027,7 +50027,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -50053,7 +50053,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -50079,7 +50079,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -50105,7 +50105,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="s">
-        <v>947</v>
+        <v>1168</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -50261,7 +50261,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -50287,7 +50287,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -50365,7 +50365,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50417,7 +50417,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50469,7 +50469,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1749" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50677,7 +50677,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1757" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50755,7 +50755,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50781,7 +50781,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50833,7 +50833,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50885,7 +50885,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1765" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50937,7 +50937,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -51015,7 +51015,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -51067,7 +51067,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -51275,7 +51275,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51405,7 +51405,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51509,7 +51509,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51535,7 +51535,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51587,7 +51587,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51639,7 +51639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51717,7 +51717,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51743,7 +51743,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1798" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51769,7 +51769,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51873,7 +51873,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51925,7 +51925,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -52289,7 +52289,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -52341,7 +52341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1821" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52393,7 +52393,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52497,7 +52497,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1827" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52523,7 +52523,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52627,7 +52627,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52653,7 +52653,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52705,7 +52705,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52731,7 +52731,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52757,7 +52757,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52835,7 +52835,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52887,7 +52887,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -53069,7 +53069,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1849" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53251,7 +53251,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -53511,7 +53511,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1866" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53771,7 +53771,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1876" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53901,7 +53901,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -71615,7 +71615,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6910532407</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>80401</v>
@@ -71636,6 +71636,32 @@
         <v>1532</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6910648148</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>235809</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>2.78500008583069</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>2.74499988555908</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385468482971</t>
+    <t xml:space="preserve">3.07385420799255</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614444732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01786661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690057754517</t>
+    <t xml:space="preserve">3.0861451625824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01786732673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690033912659</t>
   </si>
   <si>
     <t xml:space="preserve">2.98099732398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88131237030029</t>
+    <t xml:space="preserve">2.88131189346313</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003081321716</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">2.86082863807678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75841236114502</t>
+    <t xml:space="preserve">2.7584125995636</t>
   </si>
   <si>
     <t xml:space="preserve">2.73929476737976</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">2.866290807724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76387453079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74475717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7570469379425</t>
+    <t xml:space="preserve">2.76387476921082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7447566986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75704717636108</t>
   </si>
   <si>
     <t xml:space="preserve">2.71061825752258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73110151290894</t>
+    <t xml:space="preserve">2.73110103607178</t>
   </si>
   <si>
     <t xml:space="preserve">2.76114344596863</t>
@@ -113,31 +113,31 @@
     <t xml:space="preserve">2.62868499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935654640198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30095291137695</t>
+    <t xml:space="preserve">2.45935678482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45799088478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30095314979553</t>
   </si>
   <si>
     <t xml:space="preserve">2.38971400260925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53992438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50442028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74885368347168</t>
+    <t xml:space="preserve">2.53992414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50442004203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67511391639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81713080406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
   </si>
   <si>
     <t xml:space="preserve">2.78162670135498</t>
@@ -152,115 +152,115 @@
     <t xml:space="preserve">2.8335177898407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84717321395874</t>
+    <t xml:space="preserve">2.84717297554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.88404321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88540840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89769864082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85126972198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94685864448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9495894908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164926528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124987602234</t>
+    <t xml:space="preserve">2.88540887832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85126996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16125011444092</t>
   </si>
   <si>
     <t xml:space="preserve">3.18173313140869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217421531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635506629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001120567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22269988059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089289665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952771186829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076685905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587252616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463314056396</t>
+    <t xml:space="preserve">3.20767855644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900252342224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217397689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21041011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269940376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089337348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076638221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14896059036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225430727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2923424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463290214539</t>
   </si>
   <si>
     <t xml:space="preserve">3.27732157707214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34559941291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704846382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330941200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511591911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32374978065491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29780530929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26366686820984</t>
+    <t xml:space="preserve">3.34559893608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608171463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3865659236908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330893516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833073616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375073432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780507087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366662979126</t>
   </si>
   <si>
     <t xml:space="preserve">3.29097747802734</t>
@@ -269,31 +269,31 @@
     <t xml:space="preserve">3.26022291183472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1918261051178</t>
+    <t xml:space="preserve">3.19182634353638</t>
   </si>
   <si>
     <t xml:space="preserve">3.1562032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13482999801636</t>
+    <t xml:space="preserve">3.1348295211792</t>
   </si>
   <si>
     <t xml:space="preserve">3.17330265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09208226203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291913032532</t>
+    <t xml:space="preserve">3.09208250045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3229193687439</t>
   </si>
   <si>
     <t xml:space="preserve">3.34856772422791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3343186378479</t>
+    <t xml:space="preserve">3.33431839942932</t>
   </si>
   <si>
     <t xml:space="preserve">3.31151986122131</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">3.38419103622437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44403767585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981410980225</t>
+    <t xml:space="preserve">3.4440381526947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981434822083</t>
   </si>
   <si>
     <t xml:space="preserve">3.43406319618225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48108601570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47681069374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833875656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116257667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841460227966</t>
+    <t xml:space="preserve">3.48108553886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43833804130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116209983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4084141254425</t>
   </si>
   <si>
     <t xml:space="preserve">3.39843988418579</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">3.02796030044556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8997175693512</t>
+    <t xml:space="preserve">2.94246530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89971733093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.89686751365662</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">3.08495712280273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13197946548462</t>
+    <t xml:space="preserve">3.13197922706604</t>
   </si>
   <si>
     <t xml:space="preserve">3.14195394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02938485145569</t>
+    <t xml:space="preserve">3.02938532829285</t>
   </si>
   <si>
     <t xml:space="preserve">2.84984493255615</t>
@@ -368,28 +368,28 @@
     <t xml:space="preserve">2.95671439170837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06500816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332769393921</t>
+    <t xml:space="preserve">3.06500840187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332793235779</t>
   </si>
   <si>
     <t xml:space="preserve">2.96526384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95528936386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99233746528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058019638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599886894226</t>
+    <t xml:space="preserve">2.9552891254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9923369884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058043479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17045211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599910736084</t>
   </si>
   <si>
     <t xml:space="preserve">3.17757725715637</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">2.83702087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91966652870178</t>
+    <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
     <t xml:space="preserve">2.86551928520203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90399217605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84129524230957</t>
+    <t xml:space="preserve">2.90399241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129548072815</t>
   </si>
   <si>
     <t xml:space="preserve">2.87549352645874</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">2.73442625999451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77717399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88546824455261</t>
+    <t xml:space="preserve">2.7771737575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88546848297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.87406873703003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84272027015686</t>
+    <t xml:space="preserve">2.84272050857544</t>
   </si>
   <si>
     <t xml:space="preserve">2.87834358215332</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">2.92821574211121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94103956222534</t>
+    <t xml:space="preserve">2.92109131813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9410400390625</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694407463074</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">2.86409425735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81707191467285</t>
+    <t xml:space="preserve">2.81707215309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.76007509231567</t>
@@ -467,40 +467,40 @@
     <t xml:space="preserve">2.80567240715027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77289938926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75865006446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77859902381897</t>
+    <t xml:space="preserve">2.77289915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7586498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77859926223755</t>
   </si>
   <si>
     <t xml:space="preserve">2.68597888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62470746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59478402137756</t>
+    <t xml:space="preserve">2.62470722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59478378295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.5477614402771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58480954170227</t>
+    <t xml:space="preserve">2.58480930328369</t>
   </si>
   <si>
     <t xml:space="preserve">2.65605545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65463042259216</t>
+    <t xml:space="preserve">2.65463066101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.63610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60333347320557</t>
+    <t xml:space="preserve">2.60333323478699</t>
   </si>
   <si>
     <t xml:space="preserve">2.5719850063324</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">2.45086693763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44516706466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42379307746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44374203681946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941591262817</t>
+    <t xml:space="preserve">2.44516682624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42379331588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44374227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41666865348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941615104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.61900758743286</t>
@@ -530,37 +530,37 @@
     <t xml:space="preserve">2.61045813560486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54918622970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57910966873169</t>
+    <t xml:space="preserve">2.54918646812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57910990715027</t>
   </si>
   <si>
     <t xml:space="preserve">2.5506112575531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52353763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57340979576111</t>
+    <t xml:space="preserve">2.5235378742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57341003417969</t>
   </si>
   <si>
     <t xml:space="preserve">2.64465594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69310355186462</t>
+    <t xml:space="preserve">2.6931037902832</t>
   </si>
   <si>
     <t xml:space="preserve">2.64038133621216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63895654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898182868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63325667381287</t>
+    <t xml:space="preserve">2.63895678520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898206710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63325691223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.67172956466675</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">2.74867558479309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73727607727051</t>
+    <t xml:space="preserve">2.73727631568909</t>
   </si>
   <si>
     <t xml:space="preserve">2.67315483093262</t>
@@ -578,46 +578,46 @@
     <t xml:space="preserve">2.70307803153992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7144775390625</t>
+    <t xml:space="preserve">2.71447706222534</t>
   </si>
   <si>
     <t xml:space="preserve">2.70735239982605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65178084373474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66887974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63753151893616</t>
+    <t xml:space="preserve">2.65178060531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66887998580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63753128051758</t>
   </si>
   <si>
     <t xml:space="preserve">2.65748047828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56486058235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211260795593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51498818397522</t>
+    <t xml:space="preserve">2.56486034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51498794555664</t>
   </si>
   <si>
     <t xml:space="preserve">2.41524386405945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43234252929688</t>
+    <t xml:space="preserve">2.43234276771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.43661761283875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39386987686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39244508743286</t>
+    <t xml:space="preserve">2.39386963844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39244484901428</t>
   </si>
   <si>
     <t xml:space="preserve">2.45799136161804</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">2.42236828804016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53066253662109</t>
+    <t xml:space="preserve">2.53066277503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.57768487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58908438682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63468146324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69595313072205</t>
+    <t xml:space="preserve">2.58908414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63468194007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6959536075592</t>
   </si>
   <si>
     <t xml:space="preserve">2.68027925491333</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">2.69167876243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69737839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74012589454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74297595024109</t>
+    <t xml:space="preserve">2.69737815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74012613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74297547340393</t>
   </si>
   <si>
     <t xml:space="preserve">2.72445178031921</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">2.7230269908905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76434993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75152516365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75580024719238</t>
+    <t xml:space="preserve">2.7287266254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76434969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75152540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7558000087738</t>
   </si>
   <si>
     <t xml:space="preserve">2.7116277217865</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">2.69025373458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035605430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60760807991028</t>
+    <t xml:space="preserve">2.65035581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60760855674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.58338451385498</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">2.55346131324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52068781852722</t>
+    <t xml:space="preserve">2.5206880569458</t>
   </si>
   <si>
     <t xml:space="preserve">2.60618352890015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56058549880981</t>
+    <t xml:space="preserve">2.56058573722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5449116230011</t>
@@ -710,34 +710,34 @@
     <t xml:space="preserve">2.54063677787781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50501394271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49788928031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50643849372864</t>
+    <t xml:space="preserve">2.50501346588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49788904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50643873214722</t>
   </si>
   <si>
     <t xml:space="preserve">2.53351211547852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57625961303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60048389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59193396568298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58195948600769</t>
+    <t xml:space="preserve">2.57626008987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60048365592957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5919337272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58195972442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.55916094779968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58623433113098</t>
+    <t xml:space="preserve">2.58623456954956</t>
   </si>
   <si>
     <t xml:space="preserve">2.53636193275452</t>
@@ -749,118 +749,118 @@
     <t xml:space="preserve">2.54348659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6874041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69452834129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75722479820251</t>
+    <t xml:space="preserve">2.68740391731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69452857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75722503662109</t>
   </si>
   <si>
     <t xml:space="preserve">2.77147436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79712295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78857326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79997301101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83132100105286</t>
+    <t xml:space="preserve">2.79712271690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78857374191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79997277259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83132123947144</t>
   </si>
   <si>
     <t xml:space="preserve">2.90541696548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03508496284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727005958557</t>
+    <t xml:space="preserve">3.03508543968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215810775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477824211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727077484131</t>
   </si>
   <si>
     <t xml:space="preserve">3.25737285614014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07783269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16190338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16047811508179</t>
+    <t xml:space="preserve">3.07783246040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1676025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16190314292908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16047787666321</t>
   </si>
   <si>
     <t xml:space="preserve">3.21889996528625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22174954414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23172378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12913036346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19610142707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10063171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19752597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602462768555</t>
+    <t xml:space="preserve">3.22175002098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589702606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159689903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877188682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23172450065613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12912964820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19610118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10063147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19752621650696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602438926697</t>
   </si>
   <si>
     <t xml:space="preserve">3.29157090187073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32576942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302121162415</t>
+    <t xml:space="preserve">3.3257691860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302145004272</t>
   </si>
   <si>
     <t xml:space="preserve">3.31864476203918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34001874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559054374695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35569214820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457407951355</t>
+    <t xml:space="preserve">3.34001851081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559030532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35569262504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457360267639</t>
   </si>
   <si>
     <t xml:space="preserve">3.27019739151001</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">3.0892322063446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06358337402344</t>
+    <t xml:space="preserve">3.06358361244202</t>
   </si>
   <si>
     <t xml:space="preserve">3.17488980293274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11147856712341</t>
+    <t xml:space="preserve">3.09706664085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.13886046409607</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">3.14462518692017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11003684997559</t>
+    <t xml:space="preserve">3.11003732681274</t>
   </si>
   <si>
     <t xml:space="preserve">3.1186842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07112622261047</t>
+    <t xml:space="preserve">3.07112574577332</t>
   </si>
   <si>
     <t xml:space="preserve">3.03797888755798</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">3.04806733131409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99762606620789</t>
+    <t xml:space="preserve">2.99762630462646</t>
   </si>
   <si>
     <t xml:space="preserve">3.00627326965332</t>
@@ -917,40 +917,40 @@
     <t xml:space="preserve">2.8722448348999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90395045280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89098000526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87512707710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84918618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92700910568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90683269500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86936259269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87800908088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85783338546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85350966453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87080383300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82468628883362</t>
+    <t xml:space="preserve">2.90395069122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89098024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87512755393982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84918642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92700886726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90683317184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86936235427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87800931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85783290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8535099029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87080359458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8246865272522</t>
   </si>
   <si>
     <t xml:space="preserve">2.79298043251038</t>
@@ -965,52 +965,52 @@
     <t xml:space="preserve">2.80018663406372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79153966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72956943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75262784957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75983357429504</t>
+    <t xml:space="preserve">2.79153943061829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72956895828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75262808799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75983381271362</t>
   </si>
   <si>
     <t xml:space="preserve">2.74686360359192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95439124107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92124462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92845034599304</t>
+    <t xml:space="preserve">2.95439147949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92124438285828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92845058441162</t>
   </si>
   <si>
     <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342169761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83045101165771</t>
+    <t xml:space="preserve">2.83189225196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.843421459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80450987815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83045077323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80739235877991</t>
+    <t xml:space="preserve">2.78865718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80739212036133</t>
   </si>
   <si>
     <t xml:space="preserve">2.808833360672</t>
@@ -1025,31 +1025,31 @@
     <t xml:space="preserve">2.86503911018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87656879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90827417373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83909821510315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73821616172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7555103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76848077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70218729972839</t>
+    <t xml:space="preserve">2.87656855583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90827369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83909845352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73821640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75551009178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76848101615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72668695449829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71371650695801</t>
+    <t xml:space="preserve">2.71371626853943</t>
   </si>
   <si>
     <t xml:space="preserve">2.7252459526062</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">2.68056988716125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336392402649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65895199775696</t>
+    <t xml:space="preserve">2.67480492591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65895223617554</t>
   </si>
   <si>
     <t xml:space="preserve">2.67624616622925</t>
@@ -1082,64 +1082,64 @@
     <t xml:space="preserve">2.74542212486267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78577494621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92268562316895</t>
+    <t xml:space="preserve">2.78577470779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92268586158752</t>
   </si>
   <si>
     <t xml:space="preserve">3.0250084400177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02644968032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06968450546265</t>
+    <t xml:space="preserve">3.02644944190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06968474388123</t>
   </si>
   <si>
     <t xml:space="preserve">3.10571360588074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12156653404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17056655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14174318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597846031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09850788116455</t>
+    <t xml:space="preserve">3.12156629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17056632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14174294471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09850835800171</t>
   </si>
   <si>
     <t xml:space="preserve">3.05671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07400846481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04086089134216</t>
+    <t xml:space="preserve">3.07689023017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08409667015076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07400798797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04086112976074</t>
   </si>
   <si>
     <t xml:space="preserve">3.05383133888245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17921328544617</t>
+    <t xml:space="preserve">3.17921352386475</t>
   </si>
   <si>
     <t xml:space="preserve">3.12589001655579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05527281761169</t>
+    <t xml:space="preserve">3.05527305603027</t>
   </si>
   <si>
     <t xml:space="preserve">3.07977294921875</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">3.16191911697388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14750790596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09994912147522</t>
+    <t xml:space="preserve">3.1475076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09994959831238</t>
   </si>
   <si>
     <t xml:space="preserve">3.13453698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15903663635254</t>
+    <t xml:space="preserve">3.15903687477112</t>
   </si>
   <si>
     <t xml:space="preserve">3.15471315383911</t>
@@ -1172,43 +1172,43 @@
     <t xml:space="preserve">3.11580181121826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10427260398865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12012529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9716854095459</t>
+    <t xml:space="preserve">3.10427284240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12012577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05815505981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483202934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168564796448</t>
   </si>
   <si>
     <t xml:space="preserve">2.78433394432068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8218035697937</t>
+    <t xml:space="preserve">2.82180380821228</t>
   </si>
   <si>
     <t xml:space="preserve">2.86792135238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89674496650696</t>
+    <t xml:space="preserve">2.89674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.88233280181885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85062718391418</t>
+    <t xml:space="preserve">2.85062742233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.82901000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324528694153</t>
+    <t xml:space="preserve">2.82324504852295</t>
   </si>
   <si>
     <t xml:space="preserve">2.70362830162048</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">2.72236371040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70506978034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71227502822876</t>
+    <t xml:space="preserve">2.70506930351257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71227550506592</t>
   </si>
   <si>
     <t xml:space="preserve">2.65606999397278</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76703953742981</t>
+    <t xml:space="preserve">2.76703977584839</t>
   </si>
   <si>
     <t xml:space="preserve">2.78505420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72740769386292</t>
+    <t xml:space="preserve">2.72740745544434</t>
   </si>
   <si>
     <t xml:space="preserve">2.69498133659363</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">2.73461365699768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70579028129578</t>
+    <t xml:space="preserve">2.7057900428772</t>
   </si>
   <si>
     <t xml:space="preserve">2.7310106754303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72020173072815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79225993156433</t>
+    <t xml:space="preserve">2.72020196914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79226016998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.84630370140076</t>
@@ -1265,34 +1265,34 @@
     <t xml:space="preserve">2.77064275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70939302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74181938171387</t>
+    <t xml:space="preserve">2.70939326286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74181914329529</t>
   </si>
   <si>
     <t xml:space="preserve">2.71299600601196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63373160362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65534925460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64814352989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58689403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248210906982</t>
+    <t xml:space="preserve">2.63373184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64093732833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65534901618958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64814376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58689379692078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5724823474884</t>
   </si>
   <si>
     <t xml:space="preserve">2.57968807220459</t>
@@ -1301,46 +1301,46 @@
     <t xml:space="preserve">2.55807042121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56167364120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086445808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56887912750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43557167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37432193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30946922302246</t>
+    <t xml:space="preserve">2.56167340278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086469650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56887936592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43557143211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37432169914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30946946144104</t>
   </si>
   <si>
     <t xml:space="preserve">2.39593935012817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41755700111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41395378112793</t>
+    <t xml:space="preserve">2.41755676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41395401954651</t>
   </si>
   <si>
     <t xml:space="preserve">2.36351299285889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35991048812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4499831199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35270428657532</t>
+    <t xml:space="preserve">2.35991024971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44998335838318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35270404815674</t>
   </si>
   <si>
     <t xml:space="preserve">2.52204132080078</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">2.42836546897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44638013839722</t>
+    <t xml:space="preserve">2.44637989997864</t>
   </si>
   <si>
     <t xml:space="preserve">2.4211597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50762963294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59409952163696</t>
+    <t xml:space="preserve">2.50762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59409976005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527638435364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63012886047363</t>
+    <t xml:space="preserve">2.63012909889221</t>
   </si>
   <si>
     <t xml:space="preserve">2.65174651145935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62292313575745</t>
+    <t xml:space="preserve">2.62292289733887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60851120948792</t>
+    <t xml:space="preserve">2.60851168632507</t>
   </si>
   <si>
     <t xml:space="preserve">2.6373348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68417239189148</t>
+    <t xml:space="preserve">2.68417263031006</t>
   </si>
   <si>
     <t xml:space="preserve">2.66615796089172</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">2.69137811660767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67696690559387</t>
+    <t xml:space="preserve">2.67696642875671</t>
   </si>
   <si>
     <t xml:space="preserve">2.73281192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62172198295593</t>
+    <t xml:space="preserve">2.62172222137451</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.40324521064758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43657207489014</t>
+    <t xml:space="preserve">2.43657231330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.45879006385803</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">2.39213585853577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40694832801819</t>
+    <t xml:space="preserve">2.40694808959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.36991810798645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29956150054932</t>
+    <t xml:space="preserve">2.29956126213074</t>
   </si>
   <si>
     <t xml:space="preserve">2.21068930625916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32548213005066</t>
+    <t xml:space="preserve">2.32548236846924</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732434272766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38843321800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42916631698608</t>
+    <t xml:space="preserve">2.38843297958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4291660785675</t>
   </si>
   <si>
     <t xml:space="preserve">2.41805720329285</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">2.46989917755127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5032262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52174115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53285026550293</t>
+    <t xml:space="preserve">2.50322604179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52174091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53285002708435</t>
   </si>
   <si>
     <t xml:space="preserve">2.57728600502014</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">2.5254442691803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45508742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58098888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395914077759</t>
+    <t xml:space="preserve">2.45508718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58098912239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395890235901</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">2.44768095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53655290603638</t>
+    <t xml:space="preserve">2.53655314445496</t>
   </si>
   <si>
     <t xml:space="preserve">2.4773051738739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51433515548706</t>
+    <t xml:space="preserve">2.51433491706848</t>
   </si>
   <si>
     <t xml:space="preserve">2.48100805282593</t>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">2.46619629859924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39583921432495</t>
+    <t xml:space="preserve">2.39583897590637</t>
   </si>
   <si>
     <t xml:space="preserve">2.41065144538879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35140347480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36621522903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34399724006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35880899429321</t>
+    <t xml:space="preserve">2.35140323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36621499061584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34399747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35880923271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.35510635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36251258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31067037582397</t>
+    <t xml:space="preserve">2.36251211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30696702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3106701374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.32177948951721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39954233169556</t>
+    <t xml:space="preserve">2.39954209327698</t>
   </si>
   <si>
     <t xml:space="preserve">2.38102698326111</t>
@@ -1556,34 +1556,34 @@
     <t xml:space="preserve">2.32918524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27734327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26623439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29215502738953</t>
+    <t xml:space="preserve">2.27734303474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2662341594696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29215526580811</t>
   </si>
   <si>
     <t xml:space="preserve">2.27364015579224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2884521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28474926948547</t>
+    <t xml:space="preserve">2.28845238685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28474950790405</t>
   </si>
   <si>
     <t xml:space="preserve">2.38473033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20698642730713</t>
+    <t xml:space="preserve">2.20698666572571</t>
   </si>
   <si>
     <t xml:space="preserve">2.24031329154968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15514445304871</t>
+    <t xml:space="preserve">2.15514421463013</t>
   </si>
   <si>
     <t xml:space="preserve">2.13292646408081</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1033022403717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09959959983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08849048614502</t>
+    <t xml:space="preserve">2.10330200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09959936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08849024772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10700535774231</t>
@@ -1610,34 +1610,34 @@
     <t xml:space="preserve">1.98850929737091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95147967338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02553939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06627225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06997537612915</t>
+    <t xml:space="preserve">1.95147931575775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02553963661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06627249717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04775738716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06997561454773</t>
   </si>
   <si>
     <t xml:space="preserve">2.12922310829163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14403533935547</t>
+    <t xml:space="preserve">2.14403557777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.13662934303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18847131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21439218521118</t>
+    <t xml:space="preserve">2.18847107887268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21439242362976</t>
   </si>
   <si>
     <t xml:space="preserve">2.23290753364563</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">2.19958066940308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21809530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811423301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07367849349976</t>
+    <t xml:space="preserve">2.21809506416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07367825508118</t>
   </si>
   <si>
     <t xml:space="preserve">2.11070847511292</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">2.24771928787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33659100532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51063227653503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65504884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68096971511841</t>
+    <t xml:space="preserve">2.3365912437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65504908561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68096995353699</t>
   </si>
   <si>
     <t xml:space="preserve">2.60320711135864</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65875196456909</t>
+    <t xml:space="preserve">2.65875172615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.65134596824646</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">2.62542510032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71800017356873</t>
+    <t xml:space="preserve">2.71799993515015</t>
   </si>
   <si>
     <t xml:space="preserve">2.70318818092346</t>
@@ -1706,31 +1706,31 @@
     <t xml:space="preserve">2.69207882881165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71429705619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75503015518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8031690120697</t>
+    <t xml:space="preserve">2.71429681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75502991676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80316877365112</t>
   </si>
   <si>
     <t xml:space="preserve">2.81798100471497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84390163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87352609634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86241698265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88093185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76243591308594</t>
+    <t xml:space="preserve">2.84390187263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87352585792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86241674423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88093209266663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76243615150452</t>
   </si>
   <si>
     <t xml:space="preserve">2.76984214782715</t>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">2.79946565628052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79205989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81427788734436</t>
+    <t xml:space="preserve">2.79206013679504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81427764892578</t>
   </si>
   <si>
     <t xml:space="preserve">2.79576301574707</t>
@@ -1760,82 +1760,82 @@
     <t xml:space="preserve">2.89574384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90685296058655</t>
+    <t xml:space="preserve">2.90685319900513</t>
   </si>
   <si>
     <t xml:space="preserve">2.88833785057068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96239805221558</t>
+    <t xml:space="preserve">2.962397813797</t>
   </si>
   <si>
     <t xml:space="preserve">2.98091268539429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91796207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94758558273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95128893852234</t>
+    <t xml:space="preserve">2.91796183586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94758582115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95128846168518</t>
   </si>
   <si>
     <t xml:space="preserve">2.9364767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95499181747437</t>
+    <t xml:space="preserve">2.95499157905579</t>
   </si>
   <si>
     <t xml:space="preserve">2.93277382850647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91055583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720980644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94018006324768</t>
+    <t xml:space="preserve">2.91055607795715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96980404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720956802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9401798248291</t>
   </si>
   <si>
     <t xml:space="preserve">2.89944672584534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81057500839233</t>
+    <t xml:space="preserve">2.81057476997375</t>
   </si>
   <si>
     <t xml:space="preserve">2.8661196231842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80687189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83279299736023</t>
+    <t xml:space="preserve">2.80687165260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83279275894165</t>
   </si>
   <si>
     <t xml:space="preserve">2.85501098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71059417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70689082145691</t>
+    <t xml:space="preserve">2.71059393882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70689105987549</t>
   </si>
   <si>
     <t xml:space="preserve">2.61061310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64023685455322</t>
+    <t xml:space="preserve">2.64023733139038</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63283085823059</t>
+    <t xml:space="preserve">2.63283109664917</t>
   </si>
   <si>
     <t xml:space="preserve">2.61801910400391</t>
@@ -1850,37 +1850,37 @@
     <t xml:space="preserve">2.68837594985962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6143159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56988024711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49211716651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50692939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34770011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2366099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18476819992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19587707519531</t>
+    <t xml:space="preserve">2.61431622505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56988000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49211740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50692915916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34770059585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23661017417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18476843833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19587731361389</t>
   </si>
   <si>
     <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10882997512817</t>
+    <t xml:space="preserve">2.21777319908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10883045196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.12439346313477</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">2.09326696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12050247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13995695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12828421592712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770347595215</t>
+    <t xml:space="preserve">2.12050271034241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13995671272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12828397750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770371437073</t>
   </si>
   <si>
     <t xml:space="preserve">2.05046772956848</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05824947357178</t>
+    <t xml:space="preserve">2.0582492351532</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
@@ -1940,28 +1940,28 @@
     <t xml:space="preserve">2.1866466999054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9687602519989</t>
+    <t xml:space="preserve">1.96876013278961</t>
   </si>
   <si>
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92985188961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02712249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94152414798737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84425365924835</t>
+    <t xml:space="preserve">1.92985200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02712273597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94152438640594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84425354003906</t>
   </si>
   <si>
     <t xml:space="preserve">1.79367291927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76643705368042</t>
+    <t xml:space="preserve">1.76643693447113</t>
   </si>
   <si>
     <t xml:space="preserve">1.8092360496521</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">1.75087380409241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74698269367218</t>
+    <t xml:space="preserve">1.74698281288147</t>
   </si>
   <si>
     <t xml:space="preserve">1.69251132011414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78978180885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82090866565704</t>
+    <t xml:space="preserve">1.78978204727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82090854644775</t>
   </si>
   <si>
     <t xml:space="preserve">1.73920106887817</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196556091309</t>
+    <t xml:space="preserve">1.71196532249451</t>
   </si>
   <si>
     <t xml:space="preserve">1.71974718570709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7041836977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78589117527008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73141944408417</t>
+    <t xml:space="preserve">1.70418393611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78589129447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73141956329346</t>
   </si>
   <si>
     <t xml:space="preserve">1.71585619449615</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78200042247772</t>
+    <t xml:space="preserve">1.78200018405914</t>
   </si>
   <si>
     <t xml:space="preserve">1.8325811624527</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">1.80145454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84036302566528</t>
+    <t xml:space="preserve">1.8403627872467</t>
   </si>
   <si>
     <t xml:space="preserve">1.85592615604401</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">1.79756367206573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77032792568207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75476479530334</t>
+    <t xml:space="preserve">1.77032780647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869017124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75476455688477</t>
   </si>
   <si>
     <t xml:space="preserve">1.75865542888641</t>
@@ -2060,31 +2060,31 @@
     <t xml:space="preserve">1.82479953765869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91428875923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93374240398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89094352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538039684296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89483428001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85981714725494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92207038402557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01155948638916</t>
+    <t xml:space="preserve">1.91428864002228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93374276161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89094376564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538027763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90650725364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89483439922333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85981702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92207026481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01155924797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.16719269752502</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">2.16330170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08159422874451</t>
+    <t xml:space="preserve">2.08159446716309</t>
   </si>
   <si>
     <t xml:space="preserve">2.06214022636414</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">2.2099916934967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19053745269775</t>
+    <t xml:space="preserve">2.19053769111633</t>
   </si>
   <si>
     <t xml:space="preserve">2.15551996231079</t>
@@ -2117,70 +2117,70 @@
     <t xml:space="preserve">2.17108345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14384794235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11272072792053</t>
+    <t xml:space="preserve">2.14384770393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11272096633911</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548521995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01545023918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15941119194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13606595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01934099197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87148940563202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91039776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92596113681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89872527122498</t>
+    <t xml:space="preserve">2.01545000076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821425437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15941095352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13606572151184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01934123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8714896440506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91039764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92596089839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89872515201569</t>
   </si>
   <si>
     <t xml:space="preserve">1.9531968832016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99988698959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95708787441254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96486949920654</t>
+    <t xml:space="preserve">1.99988687038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95708763599396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96486937999725</t>
   </si>
   <si>
     <t xml:space="preserve">1.99210524559021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72752869129181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68862056732178</t>
+    <t xml:space="preserve">1.7275288105011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68862044811249</t>
   </si>
   <si>
     <t xml:space="preserve">1.62636709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59524035453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54232513904572</t>
+    <t xml:space="preserve">1.59524047374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.542325258255</t>
   </si>
   <si>
     <t xml:space="preserve">1.48941004276276</t>
@@ -2189,25 +2189,25 @@
     <t xml:space="preserve">1.45361435413361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33844566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30420637130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27619242668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09098875522614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16102385520935</t>
+    <t xml:space="preserve">1.33844578266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30420625209808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27619230747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09098887443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16102373600006</t>
   </si>
   <si>
     <t xml:space="preserve">1.08009457588196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05986225605011</t>
+    <t xml:space="preserve">1.05986213684082</t>
   </si>
   <si>
     <t xml:space="preserve">1.08476364612579</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22483336925507</t>
+    <t xml:space="preserve">1.22483348846436</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">1.26685440540314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27152335643768</t>
+    <t xml:space="preserve">1.27152323722839</t>
   </si>
   <si>
     <t xml:space="preserve">1.32288241386414</t>
@@ -2240,61 +2240,61 @@
     <t xml:space="preserve">1.28864300251007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28397417068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29331195354462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39291739463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36179077625275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26062893867493</t>
+    <t xml:space="preserve">1.28397405147552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29331207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39291727542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36179065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26062917709351</t>
   </si>
   <si>
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798114299774</t>
+    <t xml:space="preserve">1.29798102378845</t>
   </si>
   <si>
     <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29953730106354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31354427337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29175567626953</t>
+    <t xml:space="preserve">1.29953742027283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31354439258575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29175555706024</t>
   </si>
   <si>
     <t xml:space="preserve">1.28241777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22950255870819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23884046077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24350941181183</t>
+    <t xml:space="preserve">1.2295024394989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23884034156799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24350953102112</t>
   </si>
   <si>
     <t xml:space="preserve">1.20927011966705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13300967216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10343956947327</t>
+    <t xml:space="preserve">1.17503094673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13300979137421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10343945026398</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">1.08631992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05674958229065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06764400005341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12211549282074</t>
+    <t xml:space="preserve">1.05674970149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06764376163483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12211561203003</t>
   </si>
   <si>
     <t xml:space="preserve">1.10655224323273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14234793186188</t>
+    <t xml:space="preserve">1.14234805107117</t>
   </si>
   <si>
     <t xml:space="preserve">1.15012955665588</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">1.13923513889313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19837582111359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2450658082962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23728406429291</t>
+    <t xml:space="preserve">1.1983757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24506568908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2372841835022</t>
   </si>
   <si>
     <t xml:space="preserve">1.2217208147049</t>
@@ -2339,13 +2339,13 @@
     <t xml:space="preserve">1.28708672523499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27930498123169</t>
+    <t xml:space="preserve">1.27930510044098</t>
   </si>
   <si>
     <t xml:space="preserve">1.17969989776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16413640975952</t>
+    <t xml:space="preserve">1.16413652896881</t>
   </si>
   <si>
     <t xml:space="preserve">1.23572778701782</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">1.18592512607574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13612258434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1579110622406</t>
+    <t xml:space="preserve">1.13612246513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15791118144989</t>
   </si>
   <si>
     <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18436872959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17036187648773</t>
+    <t xml:space="preserve">1.18436884880066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
     <t xml:space="preserve">1.14546048641205</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">1.16724920272827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17347455024719</t>
+    <t xml:space="preserve">1.1734744310379</t>
   </si>
   <si>
     <t xml:space="preserve">1.15168583393097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17191815376282</t>
+    <t xml:space="preserve">1.17191827297211</t>
   </si>
   <si>
     <t xml:space="preserve">1.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1563549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12522804737091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09565782546997</t>
+    <t xml:space="preserve">1.15635466575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1252281665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09565794467926</t>
   </si>
   <si>
     <t xml:space="preserve">1.08165085315704</t>
@@ -2417,19 +2417,19 @@
     <t xml:space="preserve">1.06608760356903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08320713043213</t>
+    <t xml:space="preserve">1.08320724964142</t>
   </si>
   <si>
     <t xml:space="preserve">1.06297492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04896795749664</t>
+    <t xml:space="preserve">1.04896807670593</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410154819489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07075667381287</t>
+    <t xml:space="preserve">1.07075643539429</t>
   </si>
   <si>
     <t xml:space="preserve">1.09721410274506</t>
@@ -2441,25 +2441,25 @@
     <t xml:space="preserve">1.05052423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04585528373718</t>
+    <t xml:space="preserve">1.04585516452789</t>
   </si>
   <si>
     <t xml:space="preserve">1.03962993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04118633270264</t>
+    <t xml:space="preserve">1.04118621349335</t>
   </si>
   <si>
     <t xml:space="preserve">1.03340458869934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03496098518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03651714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02251017093658</t>
+    <t xml:space="preserve">1.03496086597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03651738166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02251029014587</t>
   </si>
   <si>
     <t xml:space="preserve">0.996052622795105</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">1.01628494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00850331783295</t>
+    <t xml:space="preserve">1.00850319862366</t>
   </si>
   <si>
     <t xml:space="preserve">1.01005959510803</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">1.00072169303894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991383671760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966482281684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964925944805145</t>
+    <t xml:space="preserve">0.991383612155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966482222080231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96492600440979</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954031586647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975820243358612</t>
+    <t xml:space="preserve">0.954031646251678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975820183753967</t>
   </si>
   <si>
     <t xml:space="preserve">0.989827334880829</t>
@@ -2501,28 +2501,28 @@
     <t xml:space="preserve">0.969595015048981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949362635612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968038558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957144379615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980489313602448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999165296554565</t>
+    <t xml:space="preserve">0.949362576007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96803867816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957144320011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980489373207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999165236949921</t>
   </si>
   <si>
     <t xml:space="preserve">1.06453132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05830597877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02406656742096</t>
+    <t xml:space="preserve">1.05830585956573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02406668663025</t>
   </si>
   <si>
     <t xml:space="preserve">0.988270878791809</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.985158324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941581010818481</t>
+    <t xml:space="preserve">0.941581070423126</t>
   </si>
   <si>
     <t xml:space="preserve">0.93379932641983</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">0.879327714443207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887109398841858</t>
+    <t xml:space="preserve">0.887109339237213</t>
   </si>
   <si>
     <t xml:space="preserve">0.888665616512299</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">0.891778409481049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835750341415405</t>
+    <t xml:space="preserve">0.83575040102005</t>
   </si>
   <si>
     <t xml:space="preserve">0.80306738615036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787504076957703</t>
+    <t xml:space="preserve">0.787504136562347</t>
   </si>
   <si>
     <t xml:space="preserve">0.829525053501129</t>
@@ -2579,25 +2579,25 @@
     <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896447241306305</t>
+    <t xml:space="preserve">0.896447360515594</t>
   </si>
   <si>
     <t xml:space="preserve">0.902672648429871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915123283863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940024554729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983602106571198</t>
+    <t xml:space="preserve">0.915123343467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940024495124817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977376639842987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963369727134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983601987361908</t>
   </si>
   <si>
     <t xml:space="preserve">0.978932917118073</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961813151836395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946249961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943137288093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930686771869659</t>
+    <t xml:space="preserve">0.961813271045685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946249902248383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943137407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930686712265015</t>
   </si>
   <si>
     <t xml:space="preserve">0.952475190162659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927573919296265</t>
+    <t xml:space="preserve">0.927573978900909</t>
   </si>
   <si>
     <t xml:space="preserve">0.926017701625824</t>
@@ -2630,58 +2630,58 @@
     <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971151351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947806417942047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919792413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913567006587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679680347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8995600938797</t>
+    <t xml:space="preserve">0.971151292324066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919792294502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913567066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341659069061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679620742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899560034275055</t>
   </si>
   <si>
     <t xml:space="preserve">0.918236017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908897936344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894890904426575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910454332828522</t>
+    <t xml:space="preserve">0.908897995948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894891023635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910454273223877</t>
   </si>
   <si>
     <t xml:space="preserve">0.944693624973297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01784121990204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05363690853119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13767898082733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15946745872498</t>
+    <t xml:space="preserve">1.01784110069275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13767886161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15946757793427</t>
   </si>
   <si>
     <t xml:space="preserve">1.12989723682404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10032677650452</t>
+    <t xml:space="preserve">1.10032689571381</t>
   </si>
   <si>
     <t xml:space="preserve">1.09877049922943</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">1.07231283187866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12834095954895</t>
+    <t xml:space="preserve">1.12834084033966</t>
   </si>
   <si>
     <t xml:space="preserve">1.12055921554565</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">1.15479850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31198799610138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24662220478058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25284743309021</t>
+    <t xml:space="preserve">1.31198811531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907278060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24662208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2528475522995</t>
   </si>
   <si>
     <t xml:space="preserve">1.2544037103653</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">1.23105883598328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2699670791626</t>
+    <t xml:space="preserve">1.26996719837189</t>
   </si>
   <si>
     <t xml:space="preserve">1.25751650333405</t>
@@ -2732,22 +2732,22 @@
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307975292206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36023437976837</t>
+    <t xml:space="preserve">1.27307987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36023426055908</t>
   </si>
   <si>
     <t xml:space="preserve">1.38513565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40069913864136</t>
+    <t xml:space="preserve">1.40069901943207</t>
   </si>
   <si>
     <t xml:space="preserve">1.40381169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37112855911255</t>
+    <t xml:space="preserve">1.37112867832184</t>
   </si>
   <si>
     <t xml:space="preserve">1.39914262294769</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">1.38980460166931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39758634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3913608789444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40536797046661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4380509853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52053666114807</t>
+    <t xml:space="preserve">1.39758622646332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39136099815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4053680896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43805110454559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52053654193878</t>
   </si>
   <si>
     <t xml:space="preserve">1.57189548015594</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">1.56022310256958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58745872974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53765618801117</t>
+    <t xml:space="preserve">1.58745884895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53765606880188</t>
   </si>
   <si>
     <t xml:space="preserve">1.51431131362915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50341701507568</t>
+    <t xml:space="preserve">1.50341689586639</t>
   </si>
   <si>
     <t xml:space="preserve">1.50497317314148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49096620082855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51798796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871304512024</t>
+    <t xml:space="preserve">1.49096632003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51798808574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871316432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.45281779766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46712350845337</t>
+    <t xml:space="preserve">1.46712338924408</t>
   </si>
   <si>
     <t xml:space="preserve">1.47348153591156</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">1.48619771003723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48937666416168</t>
+    <t xml:space="preserve">1.48937678337097</t>
   </si>
   <si>
     <t xml:space="preserve">1.48142910003662</t>
@@ -2828,31 +2828,31 @@
     <t xml:space="preserve">1.55454683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5561363697052</t>
+    <t xml:space="preserve">1.55613648891449</t>
   </si>
   <si>
     <t xml:space="preserve">1.57044196128845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56567358970642</t>
+    <t xml:space="preserve">1.56567347049713</t>
   </si>
   <si>
     <t xml:space="preserve">1.567263007164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53706228733063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5275251865387</t>
+    <t xml:space="preserve">1.53706216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52752506732941</t>
   </si>
   <si>
     <t xml:space="preserve">1.47030258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44328081607819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40672194957733</t>
+    <t xml:space="preserve">1.4432806968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40672183036804</t>
   </si>
   <si>
     <t xml:space="preserve">1.43374371528625</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">1.34790980815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33201467990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585737228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31929850578308</t>
+    <t xml:space="preserve">1.33201456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585725307465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31929838657379</t>
   </si>
   <si>
     <t xml:space="preserve">1.31453001499176</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">1.27638149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30181384086609</t>
+    <t xml:space="preserve">1.3018137216568</t>
   </si>
   <si>
     <t xml:space="preserve">1.30499279499054</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">1.31135094165802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30340325832367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28432929515839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27479207515717</t>
+    <t xml:space="preserve">1.30340337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2843291759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27479195594788</t>
   </si>
   <si>
     <t xml:space="preserve">1.22074854373932</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">1.2557178735733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24935972690582</t>
+    <t xml:space="preserve">1.24935984611511</t>
   </si>
   <si>
     <t xml:space="preserve">1.25412821769714</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">1.28273963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21121144294739</t>
+    <t xml:space="preserve">1.2271066904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2112113237381</t>
   </si>
   <si>
     <t xml:space="preserve">1.2732025384903</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">1.37652099132538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36698389053345</t>
+    <t xml:space="preserve">1.36698400974274</t>
   </si>
   <si>
     <t xml:space="preserve">1.35267841815948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970018386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128960132599</t>
+    <t xml:space="preserve">1.37493169307709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37969994544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128972053528</t>
   </si>
   <si>
     <t xml:space="preserve">1.34314131736755</t>
@@ -2960,28 +2960,28 @@
     <t xml:space="preserve">1.33678317070007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221539974213</t>
+    <t xml:space="preserve">1.36221528053284</t>
   </si>
   <si>
     <t xml:space="preserve">1.363804936409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39877426624298</t>
+    <t xml:space="preserve">1.39877438545227</t>
   </si>
   <si>
     <t xml:space="preserve">1.42897510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40513229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53388321399689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49732434749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47189199924469</t>
+    <t xml:space="preserve">1.40513241291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49732422828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47189211845398</t>
   </si>
   <si>
     <t xml:space="preserve">1.42738556861877</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">1.34155166149139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33519351482391</t>
+    <t xml:space="preserve">1.3351936340332</t>
   </si>
   <si>
     <t xml:space="preserve">1.37811064720154</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">1.38287913799286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50050330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52116703987122</t>
+    <t xml:space="preserve">1.50050342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52116715908051</t>
   </si>
   <si>
     <t xml:space="preserve">1.49573481082916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50845086574554</t>
+    <t xml:space="preserve">1.50845098495483</t>
   </si>
   <si>
     <t xml:space="preserve">1.51162993907928</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">1.51321947574615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47507119178772</t>
+    <t xml:space="preserve">1.47507095336914</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010174274445</t>
@@ -3062,34 +3062,34 @@
     <t xml:space="preserve">1.4877872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47983968257904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45599699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48301863670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51004040241241</t>
+    <t xml:space="preserve">1.47983956336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45599687099457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48301875591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51004028320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.56249439716339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63720166683197</t>
+    <t xml:space="preserve">1.63720178604126</t>
   </si>
   <si>
     <t xml:space="preserve">1.66501832008362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67693948745728</t>
+    <t xml:space="preserve">1.67693960666656</t>
   </si>
   <si>
     <t xml:space="preserve">1.70078253746033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65309691429138</t>
+    <t xml:space="preserve">1.65309679508209</t>
   </si>
   <si>
     <t xml:space="preserve">1.60541141033173</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">1.43851220607758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44645988941193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4544073343277</t>
+    <t xml:space="preserve">1.44645977020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440745353699</t>
   </si>
   <si>
     <t xml:space="preserve">1.45122838020325</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">1.49414527416229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5163985490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61335897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61733293533325</t>
+    <t xml:space="preserve">1.51639842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61335909366608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61733281612396</t>
   </si>
   <si>
     <t xml:space="preserve">1.63322794437408</t>
@@ -3131,22 +3131,22 @@
     <t xml:space="preserve">1.62130653858185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59349012374878</t>
+    <t xml:space="preserve">1.59349024295807</t>
   </si>
   <si>
     <t xml:space="preserve">1.58792674541473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60143768787384</t>
+    <t xml:space="preserve">1.60143780708313</t>
   </si>
   <si>
     <t xml:space="preserve">1.62925410270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104447841644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53865170478821</t>
+    <t xml:space="preserve">1.66104435920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5386518239975</t>
   </si>
   <si>
     <t xml:space="preserve">1.51957750320435</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">1.52911472320557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53070402145386</t>
+    <t xml:space="preserve">1.53070414066315</t>
   </si>
   <si>
     <t xml:space="preserve">1.52434611320496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43056452274323</t>
+    <t xml:space="preserve">1.43056464195251</t>
   </si>
   <si>
     <t xml:space="preserve">1.37334203720093</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">1.30022442340851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22869610786438</t>
+    <t xml:space="preserve">1.22869598865509</t>
   </si>
   <si>
     <t xml:space="preserve">1.23346471786499</t>
@@ -3191,82 +3191,82 @@
     <t xml:space="preserve">1.40831136703491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59746384620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74846792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78423178195953</t>
+    <t xml:space="preserve">1.59746372699738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7484678030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78423190116882</t>
   </si>
   <si>
     <t xml:space="preserve">1.76038908958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77231049537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74449396133423</t>
+    <t xml:space="preserve">1.77231061458588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78025805950165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74449408054352</t>
   </si>
   <si>
     <t xml:space="preserve">1.81999599933624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81204843521118</t>
+    <t xml:space="preserve">1.81204855442047</t>
   </si>
   <si>
     <t xml:space="preserve">1.83191752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8279435634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178625583649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589112758636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986508846283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82396984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628421783447</t>
+    <t xml:space="preserve">1.82794368267059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178649425507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986520767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396996021271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628433704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.79217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76833665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.788205742836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859871387482</t>
+    <t xml:space="preserve">1.76833689212799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78820586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7285989522934</t>
   </si>
   <si>
     <t xml:space="preserve">1.64514923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71667754650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436293125153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410075187683</t>
+    <t xml:space="preserve">1.71667766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73654651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641560554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436305046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410087108612</t>
   </si>
   <si>
     <t xml:space="preserve">1.7403576374054</t>
@@ -3278,22 +3278,22 @@
     <t xml:space="preserve">1.76195001602173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75763165950775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75331294536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73603904247284</t>
+    <t xml:space="preserve">1.75763154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77490556240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7533130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73603892326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.67730736732483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64448666572571</t>
+    <t xml:space="preserve">1.644486784935</t>
   </si>
   <si>
     <t xml:space="preserve">1.55811655521393</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">1.50456702709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50283968448639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47865605354309</t>
+    <t xml:space="preserve">1.50283980369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47865617275238</t>
   </si>
   <si>
     <t xml:space="preserve">1.51665902137756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48038351535797</t>
+    <t xml:space="preserve">1.48038339614868</t>
   </si>
   <si>
     <t xml:space="preserve">1.4890204668045</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">1.3819215297699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40092301368713</t>
+    <t xml:space="preserve">1.40092289447784</t>
   </si>
   <si>
     <t xml:space="preserve">1.43028879165649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37501192092896</t>
+    <t xml:space="preserve">1.4061051607132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37501204013824</t>
   </si>
   <si>
     <t xml:space="preserve">1.37328457832336</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">1.34737348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52875077724457</t>
+    <t xml:space="preserve">1.52875065803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.59957420825958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5477522611618</t>
+    <t xml:space="preserve">1.54775214195251</t>
   </si>
   <si>
     <t xml:space="preserve">1.55293428897858</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">1.55466175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60648381710052</t>
+    <t xml:space="preserve">1.60648393630981</t>
   </si>
   <si>
     <t xml:space="preserve">1.60475647449493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58230030536652</t>
+    <t xml:space="preserve">1.58230018615723</t>
   </si>
   <si>
     <t xml:space="preserve">1.58057284355164</t>
@@ -3404,10 +3404,10 @@
     <t xml:space="preserve">1.4665641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45447254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42510664463043</t>
+    <t xml:space="preserve">1.45447242259979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42510652542114</t>
   </si>
   <si>
     <t xml:space="preserve">1.43547093868256</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">1.33009946346283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38019418716431</t>
+    <t xml:space="preserve">1.3801943063736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35082840919495</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">1.2005443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22300052642822</t>
+    <t xml:space="preserve">1.22300064563751</t>
   </si>
   <si>
     <t xml:space="preserve">1.1884526014328</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">1.35773801803589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39574086666107</t>
+    <t xml:space="preserve">1.39574074745178</t>
   </si>
   <si>
     <t xml:space="preserve">1.39746820926666</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">1.43374359607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44929015636444</t>
+    <t xml:space="preserve">1.44929027557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.44065320491791</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">1.43719851970673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41992449760437</t>
+    <t xml:space="preserve">1.41992437839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.40265035629272</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">1.40437793731689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41301476955414</t>
+    <t xml:space="preserve">1.41301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">1.42165184020996</t>
@@ -3551,19 +3551,19 @@
     <t xml:space="preserve">1.45101761817932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38710379600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36464750766754</t>
+    <t xml:space="preserve">1.38710367679596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36464762687683</t>
   </si>
   <si>
     <t xml:space="preserve">1.32837212085724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.331827044487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591583251953</t>
+    <t xml:space="preserve">1.33182692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591595172882</t>
   </si>
   <si>
     <t xml:space="preserve">1.31455290317535</t>
@@ -3572,22 +3572,22 @@
     <t xml:space="preserve">1.31109809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34564602375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30937063694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27827751636505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27136778831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28345966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27655005455017</t>
+    <t xml:space="preserve">1.34564614295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30937075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27827739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27136790752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28345954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27655017375946</t>
   </si>
   <si>
     <t xml:space="preserve">1.29900622367859</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">1.28518712520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036915302277</t>
+    <t xml:space="preserve">1.29036927223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.30764329433441</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">1.33528172969818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34910106658936</t>
+    <t xml:space="preserve">1.34910094738007</t>
   </si>
   <si>
     <t xml:space="preserve">1.36982977390289</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">1.51147675514221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49938488006592</t>
+    <t xml:space="preserve">1.49938476085663</t>
   </si>
   <si>
     <t xml:space="preserve">1.53393292427063</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">1.52011370658875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51838636398315</t>
+    <t xml:space="preserve">1.51838624477386</t>
   </si>
   <si>
     <t xml:space="preserve">1.5373877286911</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">1.47520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50974941253662</t>
+    <t xml:space="preserve">1.50974929332733</t>
   </si>
   <si>
     <t xml:space="preserve">1.49593007564545</t>
@@ -3665,10 +3665,10 @@
     <t xml:space="preserve">1.48383831977844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4181969165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729300498962</t>
+    <t xml:space="preserve">1.41819703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729312419891</t>
   </si>
   <si>
     <t xml:space="preserve">1.54256999492645</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">1.5857549905777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60302901268005</t>
+    <t xml:space="preserve">1.60302889347076</t>
   </si>
   <si>
     <t xml:space="preserve">1.6203031539917</t>
@@ -3704,16 +3704,16 @@
     <t xml:space="preserve">1.64966893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62893998622894</t>
+    <t xml:space="preserve">1.62894010543823</t>
   </si>
   <si>
     <t xml:space="preserve">1.63757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6323949098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59093713760376</t>
+    <t xml:space="preserve">1.63239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59093725681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.61684823036194</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">1.63412225246429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62548518180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57193577289581</t>
+    <t xml:space="preserve">1.62548530101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5719358921051</t>
   </si>
   <si>
     <t xml:space="preserve">1.57020831108093</t>
@@ -71670,7 +71670,7 @@
     </row>
     <row r="2565">
       <c r="A2565" s="1" t="n">
-        <v>46057.6909722222</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2565" t="n">
         <v>232570</v>
@@ -71691,6 +71691,32 @@
         <v>1533</v>
       </c>
       <c r="H2565" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="1" t="n">
+        <v>46058.6920601852</v>
+      </c>
+      <c r="B2566" t="n">
+        <v>147948</v>
+      </c>
+      <c r="C2566" t="n">
+        <v>2.82500004768372</v>
+      </c>
+      <c r="D2566" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="E2566" t="n">
+        <v>2.82500004768372</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H2566" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385444641113</t>
+    <t xml:space="preserve">3.07385492324829</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08614444732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01786661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690033912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98099708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131189346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003105163574</t>
+    <t xml:space="preserve">3.08614468574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01786708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690057754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98099732398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131165504456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94003081321716</t>
   </si>
   <si>
     <t xml:space="preserve">2.80620646476746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86082863807678</t>
+    <t xml:space="preserve">2.86082887649536</t>
   </si>
   <si>
     <t xml:space="preserve">2.75841236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73929500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69013500213623</t>
+    <t xml:space="preserve">2.73929452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69013476371765</t>
   </si>
   <si>
     <t xml:space="preserve">2.71744585037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.866290807724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76387429237366</t>
+    <t xml:space="preserve">2.86629104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76387453079224</t>
   </si>
   <si>
     <t xml:space="preserve">2.74475717544556</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">2.7570469379425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.710618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110127449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76114344596863</t>
+    <t xml:space="preserve">2.71061825752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76114368438721</t>
   </si>
   <si>
     <t xml:space="preserve">2.72563934326172</t>
@@ -107,37 +107,37 @@
     <t xml:space="preserve">2.69696283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72290802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62868475914001</t>
+    <t xml:space="preserve">2.72290825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62868499755859</t>
   </si>
   <si>
     <t xml:space="preserve">2.45935678482056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30095291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38971352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53992414474487</t>
+    <t xml:space="preserve">2.45799136161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30095267295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971400260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992438316345</t>
   </si>
   <si>
     <t xml:space="preserve">2.50441980361938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67511367797852</t>
+    <t xml:space="preserve">2.67511391639709</t>
   </si>
   <si>
     <t xml:space="preserve">2.81713104248047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74885392189026</t>
+    <t xml:space="preserve">2.7488534450531</t>
   </si>
   <si>
     <t xml:space="preserve">2.78162670135498</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">2.83351755142212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84717297554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88404321670532</t>
+    <t xml:space="preserve">2.84717321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88404297828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.88540863990784</t>
@@ -164,301 +164,304 @@
     <t xml:space="preserve">2.89769864082336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85126972198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94685840606689</t>
+    <t xml:space="preserve">2.85126996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685816764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94958972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.058833360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16125011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173241615295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767855644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217373847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635506629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040987968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22270011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089265823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076638221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22543048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463266372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27732157707214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559941291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608266830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704846382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38656568527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3483304977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780507087708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15620303153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13482975959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208178520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14907884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32291913032532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856724739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33431887626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151986122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419103622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44403767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681069374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4383385181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841460227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39843988418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714293479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796053886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89971733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89686727523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643342971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495736122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13197946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500840187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96526408195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528936386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9923369884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12057995796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1704523563385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625431060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.9495894908905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.058833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12164878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16124963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18173313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20767855644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900204658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17217421531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23635530471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25001096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21040987968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2226996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23089289665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22952747344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895987510681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22543048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21587181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30463290214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27732157707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34559917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36608242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40704894065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38656616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34833025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32511591911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32375025749207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2978048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26366662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29097747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26022291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19182634353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15620350837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13482975959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09208226203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14907884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32291913032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34856796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3343186378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31151986122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38419103622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4440381526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41981410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43406295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48108601570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.476811170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43833827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45116257667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40841460227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39844012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714269638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20607590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02796006202698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8997175693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8968677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06643319129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08495736122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13197994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14195394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02938532829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84984493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95671415328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06500816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96526384353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9552891254425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99233746528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12058043479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23599886894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17757725715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13625407218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83702063560486</t>
+    <t xml:space="preserve">2.83702087402344</t>
   </si>
   <si>
     <t xml:space="preserve">2.9196662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86551880836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90399217605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84129548072815</t>
+    <t xml:space="preserve">2.86551904678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90399241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129524230957</t>
   </si>
   <si>
     <t xml:space="preserve">2.87549352645874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83559584617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79854798316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73442602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7771737575531</t>
+    <t xml:space="preserve">2.83559560775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7985475063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442625999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77717399597168</t>
   </si>
   <si>
     <t xml:space="preserve">2.88546824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87406849861145</t>
+    <t xml:space="preserve">2.87406873703003</t>
   </si>
   <si>
     <t xml:space="preserve">2.84272050857544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87834358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92821574211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9410400390625</t>
+    <t xml:space="preserve">2.87834334373474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92821598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92109084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94103980064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85839462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86409425735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81707167625427</t>
+    <t xml:space="preserve">2.85839486122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86409449577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81707215309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.76007485389709</t>
@@ -470,34 +473,34 @@
     <t xml:space="preserve">2.77289915084839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75865006446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77859878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68597865104675</t>
+    <t xml:space="preserve">2.7586498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77859902381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68597912788391</t>
   </si>
   <si>
     <t xml:space="preserve">2.62470722198486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59478354454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54776120185852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58480930328369</t>
+    <t xml:space="preserve">2.59478378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54776167869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58480954170227</t>
   </si>
   <si>
     <t xml:space="preserve">2.65605568885803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65463066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63610672950745</t>
+    <t xml:space="preserve">2.65463089942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60333347320557</t>
@@ -506,25 +509,25 @@
     <t xml:space="preserve">2.5719850063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45086669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44516706466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42379331588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44374227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41666841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45941591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61900806427002</t>
+    <t xml:space="preserve">2.45086693763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44516682624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42379307746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44374203681946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41666865348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45941615104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61900758743286</t>
   </si>
   <si>
     <t xml:space="preserve">2.61045813560486</t>
@@ -536,13 +539,13 @@
     <t xml:space="preserve">2.57910966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55061101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52353811264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57340979576111</t>
+    <t xml:space="preserve">2.5506112575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52353763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57341003417969</t>
   </si>
   <si>
     <t xml:space="preserve">2.64465594291687</t>
@@ -554,31 +557,31 @@
     <t xml:space="preserve">2.64038157463074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63895630836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62898230552673</t>
+    <t xml:space="preserve">2.63895654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62898206710815</t>
   </si>
   <si>
     <t xml:space="preserve">2.63325691223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67172980308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74867582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73727583885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67315483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70307803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7144775390625</t>
+    <t xml:space="preserve">2.67172956466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74867558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73727607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67315459251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70307779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71447730064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.70735287666321</t>
@@ -593,36 +596,33 @@
     <t xml:space="preserve">2.63753151893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65748071670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56486058235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52211308479309</t>
+    <t xml:space="preserve">2.65748047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56486034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52211284637451</t>
   </si>
   <si>
     <t xml:space="preserve">2.51498818397522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41524362564087</t>
+    <t xml:space="preserve">2.41524386405945</t>
   </si>
   <si>
     <t xml:space="preserve">2.43234276771545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43661761283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39386963844299</t>
+    <t xml:space="preserve">2.43661785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39386987686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.39244508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45799136161804</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.3511221408844</t>
   </si>
   <si>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">2.53066253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5776846408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58908414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63468194007874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6959536075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68027925491333</t>
+    <t xml:space="preserve">2.57768487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58908438682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63468146324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69595336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68027949333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.69167876243591</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.74297571182251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72445178031921</t>
+    <t xml:space="preserve">2.72445154190063</t>
   </si>
   <si>
     <t xml:space="preserve">2.7230269908905</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">2.7287266254425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76434969902039</t>
+    <t xml:space="preserve">2.76434993743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.75152540206909</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">2.7558000087738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7116277217865</t>
+    <t xml:space="preserve">2.71162748336792</t>
   </si>
   <si>
     <t xml:space="preserve">2.69025349617004</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">2.65035581588745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60760831832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58338451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55346131324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5206880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60618305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56058597564697</t>
+    <t xml:space="preserve">2.60760807991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5833842754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55346155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52068781852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60618329048157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56058573722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.5449116230011</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.53351211547852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57625985145569</t>
+    <t xml:space="preserve">2.57625961303711</t>
   </si>
   <si>
     <t xml:space="preserve">2.60048389434814</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">2.59193396568298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58195972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5591607093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58623433113098</t>
+    <t xml:space="preserve">2.58195948600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55916118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58623456954956</t>
   </si>
   <si>
     <t xml:space="preserve">2.5363621711731</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">2.48506474494934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54348683357239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68740367889404</t>
+    <t xml:space="preserve">2.54348659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68740391731262</t>
   </si>
   <si>
     <t xml:space="preserve">2.69452857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75722503662109</t>
+    <t xml:space="preserve">2.75722479820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.77147436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79712319374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78857350349426</t>
+    <t xml:space="preserve">2.79712295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7885730266571</t>
   </si>
   <si>
     <t xml:space="preserve">2.79997277259827</t>
@@ -773,136 +773,136 @@
     <t xml:space="preserve">2.83132100105286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90541744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03508520126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06215834617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15477848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29727053642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25737309455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07783269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16760301589966</t>
+    <t xml:space="preserve">2.90541696548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03508472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06215858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15477824211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29727029800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25737285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07783246040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16760277748108</t>
   </si>
   <si>
     <t xml:space="preserve">3.16190338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16047835350037</t>
+    <t xml:space="preserve">3.16047811508179</t>
   </si>
   <si>
     <t xml:space="preserve">3.21889996528625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2217493057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27589678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28159666061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26877188682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23172426223755</t>
+    <t xml:space="preserve">3.22174954414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27589702606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28159642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26877236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23172378540039</t>
   </si>
   <si>
     <t xml:space="preserve">3.12913012504578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19610095024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10063147544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19752597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23884868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22602438926697</t>
+    <t xml:space="preserve">3.19610166549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10063171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1975257396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23884916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22602462768555</t>
   </si>
   <si>
     <t xml:space="preserve">3.29157114028931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32576942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31864428520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34001851081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39559006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35569286346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23457431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27019739151001</t>
+    <t xml:space="preserve">3.32576894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28302097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31864500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34001874923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35569262504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23457407951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27019715309143</t>
   </si>
   <si>
     <t xml:space="preserve">3.08923196792603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06358337402344</t>
+    <t xml:space="preserve">3.06358361244202</t>
   </si>
   <si>
     <t xml:space="preserve">3.17489004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706664085388</t>
+    <t xml:space="preserve">3.09706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">3.11147832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13886022567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14462518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11003732681274</t>
+    <t xml:space="preserve">3.13886046409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14462494850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11003684997559</t>
   </si>
   <si>
     <t xml:space="preserve">3.1186842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07112574577332</t>
+    <t xml:space="preserve">3.07112598419189</t>
   </si>
   <si>
     <t xml:space="preserve">3.03797912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04806709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762630462646</t>
+    <t xml:space="preserve">3.04806733131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762606620789</t>
   </si>
   <si>
     <t xml:space="preserve">3.00627326965332</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">2.97744989395142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91836214065552</t>
+    <t xml:space="preserve">2.9183623790741</t>
   </si>
   <si>
     <t xml:space="preserve">2.8722448348999</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">2.87512731552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84918618202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92700910568237</t>
+    <t xml:space="preserve">2.84918642044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92700886726379</t>
   </si>
   <si>
     <t xml:space="preserve">2.9068329334259</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">2.86936259269714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87800979614258</t>
+    <t xml:space="preserve">2.87800931930542</t>
   </si>
   <si>
     <t xml:space="preserve">2.85783314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85350966453552</t>
+    <t xml:space="preserve">2.8535099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.87080359458923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82468628883362</t>
+    <t xml:space="preserve">2.8246865272522</t>
   </si>
   <si>
     <t xml:space="preserve">2.79298067092896</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">2.76415729522705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81027460098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80018639564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79153966903687</t>
+    <t xml:space="preserve">2.81027483940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80018663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79153943061829</t>
   </si>
   <si>
     <t xml:space="preserve">2.72956943511963</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">2.75262784957886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75983357429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74686336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95439124107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92124438285828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92845058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92556810379028</t>
+    <t xml:space="preserve">2.75983381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74686360359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95439100265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92124462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92845034599304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9255678653717</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189225196838</t>
@@ -1001,31 +1001,31 @@
     <t xml:space="preserve">2.80450987815857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83045125007629</t>
+    <t xml:space="preserve">2.83045077323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.82612752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865718841553</t>
+    <t xml:space="preserve">2.78865694999695</t>
   </si>
   <si>
     <t xml:space="preserve">2.80739235877991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.808833360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84053897857666</t>
+    <t xml:space="preserve">2.80883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84053921699524</t>
   </si>
   <si>
     <t xml:space="preserve">2.85495066642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86503911018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87656855583191</t>
+    <t xml:space="preserve">2.86503934860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87656831741333</t>
   </si>
   <si>
     <t xml:space="preserve">2.90827393531799</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">2.73821640014648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7555103302002</t>
+    <t xml:space="preserve">2.75551009178162</t>
   </si>
   <si>
     <t xml:space="preserve">2.76848077774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70218729972839</t>
+    <t xml:space="preserve">2.70218706130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72668695449829</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">2.71371650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72524571418762</t>
+    <t xml:space="preserve">2.7252459526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.68056964874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67480492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67336368560791</t>
+    <t xml:space="preserve">2.6748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67336392402649</t>
   </si>
   <si>
     <t xml:space="preserve">2.65895223617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75406908988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79442167282104</t>
+    <t xml:space="preserve">2.67624592781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75406932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79442191123962</t>
   </si>
   <si>
     <t xml:space="preserve">2.79874539375305</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">2.92268586158752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0250084400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02644968032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06968474388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10571384429932</t>
+    <t xml:space="preserve">3.02500867843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02644944190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06968450546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10571360588074</t>
   </si>
   <si>
     <t xml:space="preserve">3.12156629562378</t>
@@ -1106,55 +1106,55 @@
     <t xml:space="preserve">3.17056655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14174294471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13597846031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09850788116455</t>
+    <t xml:space="preserve">3.14174318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13597869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09850811958313</t>
   </si>
   <si>
     <t xml:space="preserve">3.05671405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07689046859741</t>
+    <t xml:space="preserve">3.07689070701599</t>
   </si>
   <si>
     <t xml:space="preserve">3.08409667015076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07400798797607</t>
+    <t xml:space="preserve">3.07400846481323</t>
   </si>
   <si>
     <t xml:space="preserve">3.04086089134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0538318157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17921376228333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12589025497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05527257919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07977318763733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14894890785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16191959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14750742912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09994888305664</t>
+    <t xml:space="preserve">3.05383133888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17921328544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12589001655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05527281761169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07977294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14894843101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16191935539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14750790596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09994912147522</t>
   </si>
   <si>
     <t xml:space="preserve">3.13453698158264</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.15471315383911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12877249717712</t>
+    <t xml:space="preserve">3.12877225875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.11580181121826</t>
@@ -1178,25 +1178,25 @@
     <t xml:space="preserve">3.12012553215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05815505981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00483250617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9716854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78433394432068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82180380821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86792135238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8967444896698</t>
+    <t xml:space="preserve">3.05815553665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00483226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168564796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82180404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8679211139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.88233304023743</t>
@@ -1205,40 +1205,40 @@
     <t xml:space="preserve">2.85062742233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8290102481842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82324481010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70362854003906</t>
+    <t xml:space="preserve">2.82901000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82324528694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70362830162048</t>
   </si>
   <si>
     <t xml:space="preserve">2.72236371040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70506978034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71227502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65607023239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76703977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72740769386292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69498133659363</t>
+    <t xml:space="preserve">2.70506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71227526664734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65606999397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858431816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76703953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505444526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72740745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69498157501221</t>
   </si>
   <si>
     <t xml:space="preserve">2.73461365699768</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">2.7057900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7310106754303</t>
+    <t xml:space="preserve">2.73101043701172</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020196914673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79225993156433</t>
+    <t xml:space="preserve">2.79226016998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.84630393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.774245262146</t>
+    <t xml:space="preserve">2.77424550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.77064275741577</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">2.71299600601196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63373184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65534925460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64814329147339</t>
+    <t xml:space="preserve">2.63373160362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62652611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6409375667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65534949302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64814352989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.58689379692078</t>
@@ -1298,22 +1298,22 @@
     <t xml:space="preserve">2.57968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55807042121887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56167364120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55086493492126</t>
+    <t xml:space="preserve">2.55807065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56167340278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55086469650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.56887912750244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43557167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37432193756104</t>
+    <t xml:space="preserve">2.43557143211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37432169914246</t>
   </si>
   <si>
     <t xml:space="preserve">2.30946922302246</t>
@@ -1322,25 +1322,25 @@
     <t xml:space="preserve">2.39593958854675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41755652427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35991024971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29505777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44998288154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3527045249939</t>
+    <t xml:space="preserve">2.41755700111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41395354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36351323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3599100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29505753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4499831199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
     <t xml:space="preserve">2.52204132080078</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">2.42836546897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44637989997864</t>
+    <t xml:space="preserve">2.4463803768158</t>
   </si>
   <si>
     <t xml:space="preserve">2.4211597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50762963294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59409976005554</t>
+    <t xml:space="preserve">2.50762987136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59409952163696</t>
   </si>
   <si>
     <t xml:space="preserve">2.56527638435364</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">2.60130548477173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60851144790649</t>
+    <t xml:space="preserve">2.60851120948792</t>
   </si>
   <si>
     <t xml:space="preserve">2.63733458518982</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">2.67696666717529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73281192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62172222137451</t>
+    <t xml:space="preserve">2.73281216621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62172198295593</t>
   </si>
   <si>
     <t xml:space="preserve">2.49582004547119</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.40324521064758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43657207489014</t>
+    <t xml:space="preserve">2.43657231330872</t>
   </si>
   <si>
     <t xml:space="preserve">2.45879006385803</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">2.4291660785675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41805744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46989941596985</t>
+    <t xml:space="preserve">2.41805696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46989917755127</t>
   </si>
   <si>
     <t xml:space="preserve">2.5032262802124</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">2.57728600502014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45508694648743</t>
+    <t xml:space="preserve">2.5254442691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45508718490601</t>
   </si>
   <si>
     <t xml:space="preserve">2.58098888397217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395890235901</t>
+    <t xml:space="preserve">2.54395914077759</t>
   </si>
   <si>
     <t xml:space="preserve">2.4736020565033</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">2.53655290603638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4773051738739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51433491706848</t>
+    <t xml:space="preserve">2.47730493545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51433515548706</t>
   </si>
   <si>
     <t xml:space="preserve">2.48100805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46619606018066</t>
+    <t xml:space="preserve">2.46619629859924</t>
   </si>
   <si>
     <t xml:space="preserve">2.39583897590637</t>
@@ -1499,22 +1499,22 @@
     <t xml:space="preserve">2.41065144538879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35140347480774</t>
+    <t xml:space="preserve">2.35140323638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.36621499061584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34399724006653</t>
+    <t xml:space="preserve">2.34399747848511</t>
   </si>
   <si>
     <t xml:space="preserve">2.35880923271179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35510659217834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36251211166382</t>
+    <t xml:space="preserve">2.35510611534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3625123500824</t>
   </si>
   <si>
     <t xml:space="preserve">2.30696725845337</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">2.38102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41435432434082</t>
+    <t xml:space="preserve">2.41435408592224</t>
   </si>
   <si>
     <t xml:space="preserve">2.37362122535706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31807661056519</t>
+    <t xml:space="preserve">2.31807637214661</t>
   </si>
   <si>
     <t xml:space="preserve">2.29585838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104591369629</t>
+    <t xml:space="preserve">2.28104639053345</t>
   </si>
   <si>
     <t xml:space="preserve">2.26993727684021</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">2.29215526580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27364015579224</t>
+    <t xml:space="preserve">2.27363991737366</t>
   </si>
   <si>
     <t xml:space="preserve">2.2884521484375</t>
@@ -1574,34 +1574,34 @@
     <t xml:space="preserve">2.28474950790405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38473010063171</t>
+    <t xml:space="preserve">2.38473033905029</t>
   </si>
   <si>
     <t xml:space="preserve">2.20698642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24031329154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15514445304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13292646408081</t>
+    <t xml:space="preserve">2.24031352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15514421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13292622566223</t>
   </si>
   <si>
     <t xml:space="preserve">2.14773845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1033022403717</t>
+    <t xml:space="preserve">2.10330200195312</t>
   </si>
   <si>
     <t xml:space="preserve">2.09959959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08849024772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10700559616089</t>
+    <t xml:space="preserve">2.08849048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10700535774231</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625696182251</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">1.95147943496704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02553963661194</t>
+    <t xml:space="preserve">2.02553915977478</t>
   </si>
   <si>
     <t xml:space="preserve">2.06627225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04775738716125</t>
+    <t xml:space="preserve">2.04775762557983</t>
   </si>
   <si>
     <t xml:space="preserve">2.06997537612915</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">2.12922310829163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14403557777405</t>
+    <t xml:space="preserve">2.14403533935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.13662934303284</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">2.18847131729126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23290729522705</t>
+    <t xml:space="preserve">2.21439218521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23290753364563</t>
   </si>
   <si>
     <t xml:space="preserve">2.25512552261353</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">2.2032835483551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19958066940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21809506416321</t>
+    <t xml:space="preserve">2.1995804309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21809530258179</t>
   </si>
   <si>
     <t xml:space="preserve">2.11811423301697</t>
@@ -1670,22 +1670,22 @@
     <t xml:space="preserve">2.33659100532532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51063227653503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65504932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68096995353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60320711135864</t>
+    <t xml:space="preserve">2.51063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65504908561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68096971511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60320687294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.62912797927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65875196456909</t>
+    <t xml:space="preserve">2.65875172615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.65134596824646</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">2.70318818092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7291088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69207906723022</t>
+    <t xml:space="preserve">2.72910904884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69207882881165</t>
   </si>
   <si>
     <t xml:space="preserve">2.71429705619812</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.75502991676331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8031690120697</t>
+    <t xml:space="preserve">2.80316877365112</t>
   </si>
   <si>
     <t xml:space="preserve">2.81798100471497</t>
@@ -1721,31 +1721,31 @@
     <t xml:space="preserve">2.84390187263489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87352585792542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86241674423218</t>
+    <t xml:space="preserve">2.87352609634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86241698265076</t>
   </si>
   <si>
     <t xml:space="preserve">2.88093185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76243615150452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76984190940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79946565628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205965995789</t>
+    <t xml:space="preserve">2.76243591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76984214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7994658946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205989837646</t>
   </si>
   <si>
     <t xml:space="preserve">2.81427788734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79576301574707</t>
+    <t xml:space="preserve">2.79576325416565</t>
   </si>
   <si>
     <t xml:space="preserve">2.75873279571533</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">2.89574384689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90685296058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88833785057068</t>
+    <t xml:space="preserve">2.90685272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88833808898926</t>
   </si>
   <si>
     <t xml:space="preserve">2.962397813797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98091268539429</t>
+    <t xml:space="preserve">2.98091292381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.91796183586121</t>
@@ -1796,22 +1796,22 @@
     <t xml:space="preserve">2.96980381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97720956802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9401798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89944648742676</t>
+    <t xml:space="preserve">2.97720980644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94018006324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89944672584534</t>
   </si>
   <si>
     <t xml:space="preserve">2.81057500839233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86611986160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80687212944031</t>
+    <t xml:space="preserve">2.86611938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80687165260315</t>
   </si>
   <si>
     <t xml:space="preserve">2.83279299736023</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">2.71059393882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70689105987549</t>
+    <t xml:space="preserve">2.70689082145691</t>
   </si>
   <si>
     <t xml:space="preserve">2.61061334609985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64023685455322</t>
+    <t xml:space="preserve">2.6402370929718</t>
   </si>
   <si>
     <t xml:space="preserve">2.6365339756012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63283109664917</t>
+    <t xml:space="preserve">2.63283085823059</t>
   </si>
   <si>
     <t xml:space="preserve">2.61801910400391</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">2.68467283248901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68837594985962</t>
+    <t xml:space="preserve">2.6883761882782</t>
   </si>
   <si>
     <t xml:space="preserve">2.6143159866333</t>
@@ -1859,25 +1859,25 @@
     <t xml:space="preserve">2.49211716651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50692939758301</t>
+    <t xml:space="preserve">2.50692915916443</t>
   </si>
   <si>
     <t xml:space="preserve">2.34770035743713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23661041259766</t>
+    <t xml:space="preserve">2.23661017417908</t>
   </si>
   <si>
     <t xml:space="preserve">2.18476819992065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587731361389</t>
+    <t xml:space="preserve">2.19587707519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.299480676651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2177734375</t>
+    <t xml:space="preserve">2.21777319908142</t>
   </si>
   <si>
     <t xml:space="preserve">2.10883021354675</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">2.12439346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08937573432922</t>
+    <t xml:space="preserve">2.0893759727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.10104846954346</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">2.12050271034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13995695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12828421592712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07770347595215</t>
+    <t xml:space="preserve">2.13995671272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12828397750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07770371437073</t>
   </si>
   <si>
     <t xml:space="preserve">2.05046796798706</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">2.03490447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435872077942</t>
+    <t xml:space="preserve">2.05435848236084</t>
   </si>
   <si>
     <t xml:space="preserve">2.03101348876953</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">2.02323174476624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05824947357178</t>
+    <t xml:space="preserve">2.0582492351532</t>
   </si>
   <si>
     <t xml:space="preserve">2.04268598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22944569587708</t>
+    <t xml:space="preserve">2.22944593429565</t>
   </si>
   <si>
     <t xml:space="preserve">2.1866466999054</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">2.00377774238586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.929851770401</t>
+    <t xml:space="preserve">1.92985200881958</t>
   </si>
   <si>
     <t xml:space="preserve">2.02712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94152414798737</t>
+    <t xml:space="preserve">1.94152438640594</t>
   </si>
   <si>
     <t xml:space="preserve">1.84425354003906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79367303848267</t>
+    <t xml:space="preserve">1.79367291927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.76643693447113</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.74698269367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69251132011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78978180885315</t>
+    <t xml:space="preserve">1.69251120090485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78978192806244</t>
   </si>
   <si>
     <t xml:space="preserve">1.82090866565704</t>
@@ -1991,31 +1991,31 @@
     <t xml:space="preserve">1.69640207290649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7197470664978</t>
+    <t xml:space="preserve">1.7119654417038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71974694728851</t>
   </si>
   <si>
     <t xml:space="preserve">1.7041836977005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78589117527008</t>
+    <t xml:space="preserve">1.78589129447937</t>
   </si>
   <si>
     <t xml:space="preserve">1.73141944408417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71585631370544</t>
+    <t xml:space="preserve">1.71585619449615</t>
   </si>
   <si>
     <t xml:space="preserve">1.7353104352951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78200042247772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8325811624527</t>
+    <t xml:space="preserve">1.78200030326843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83258104324341</t>
   </si>
   <si>
     <t xml:space="preserve">1.80145454406738</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">1.79756367206573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77032792568207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82869029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75476479530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75865542888641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76254630088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80534517765045</t>
+    <t xml:space="preserve">1.77032780647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82869040966034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75476455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75865530967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76254618167877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80534529685974</t>
   </si>
   <si>
     <t xml:space="preserve">1.81701791286469</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">1.91428864002228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93374252319336</t>
+    <t xml:space="preserve">1.93374276161194</t>
   </si>
   <si>
     <t xml:space="preserve">1.89094376564026</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">1.89483439922333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85981702804565</t>
+    <t xml:space="preserve">1.85981714725494</t>
   </si>
   <si>
     <t xml:space="preserve">1.92207038402557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01155924797058</t>
+    <t xml:space="preserve">2.01155948638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.16719269752502</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">2.16330170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08159422874451</t>
+    <t xml:space="preserve">2.08159446716309</t>
   </si>
   <si>
     <t xml:space="preserve">2.06214022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13217520713806</t>
+    <t xml:space="preserve">2.13217496871948</t>
   </si>
   <si>
     <t xml:space="preserve">2.2099916934967</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">2.19053769111633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15551972389221</t>
+    <t xml:space="preserve">2.15551996231079</t>
   </si>
   <si>
     <t xml:space="preserve">2.19831919670105</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">2.11272072792053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08548498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01545000076294</t>
+    <t xml:space="preserve">2.08548521995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01545023918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15941095352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.136066198349</t>
+    <t xml:space="preserve">2.15941119194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13606595993042</t>
   </si>
   <si>
     <t xml:space="preserve">2.01934099197388</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">1.27619230747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09098875522614</t>
+    <t xml:space="preserve">1.09098887443542</t>
   </si>
   <si>
     <t xml:space="preserve">1.16102385520935</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">1.10188317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22483348846436</t>
+    <t xml:space="preserve">1.22483336925507</t>
   </si>
   <si>
     <t xml:space="preserve">1.31976974010468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910764217377</t>
+    <t xml:space="preserve">1.32910752296448</t>
   </si>
   <si>
     <t xml:space="preserve">1.35400903224945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26685428619385</t>
+    <t xml:space="preserve">1.26685440540314</t>
   </si>
   <si>
     <t xml:space="preserve">1.27152335643768</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">1.32288241386414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28864300251007</t>
+    <t xml:space="preserve">1.28864312171936</t>
   </si>
   <si>
     <t xml:space="preserve">1.28397405147552</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">1.29642474651337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29798114299774</t>
+    <t xml:space="preserve">1.29798102378845</t>
   </si>
   <si>
     <t xml:space="preserve">1.33688938617706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29953730106354</t>
+    <t xml:space="preserve">1.29953742027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.31354439258575</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">1.28241777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22950255870819</t>
+    <t xml:space="preserve">1.2295024394989</t>
   </si>
   <si>
     <t xml:space="preserve">1.23884046077728</t>
@@ -2288,13 +2288,13 @@
     <t xml:space="preserve">1.20927011966705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503082752228</t>
+    <t xml:space="preserve">1.17503070831299</t>
   </si>
   <si>
     <t xml:space="preserve">1.13300967216492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10343945026398</t>
+    <t xml:space="preserve">1.10343956947327</t>
   </si>
   <si>
     <t xml:space="preserve">1.10499584674835</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">1.08631992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05674958229065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06764388084412</t>
+    <t xml:space="preserve">1.05674970149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06764376163483</t>
   </si>
   <si>
     <t xml:space="preserve">1.12211561203003</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">1.2061573266983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20771396160126</t>
+    <t xml:space="preserve">1.20771384239197</t>
   </si>
   <si>
     <t xml:space="preserve">1.18748152256012</t>
@@ -2372,19 +2372,19 @@
     <t xml:space="preserve">1.13612258434296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1579110622406</t>
+    <t xml:space="preserve">1.15791118144989</t>
   </si>
   <si>
     <t xml:space="preserve">1.14079141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18436872959137</t>
+    <t xml:space="preserve">1.18436884880066</t>
   </si>
   <si>
     <t xml:space="preserve">1.17036175727844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14546036720276</t>
+    <t xml:space="preserve">1.14546048641205</t>
   </si>
   <si>
     <t xml:space="preserve">1.16724920272827</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">1.1656928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1563549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12522804737091</t>
+    <t xml:space="preserve">1.15635478496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1252281665802</t>
   </si>
   <si>
     <t xml:space="preserve">1.09565782546997</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">1.08165085315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608760356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08320724964142</t>
+    <t xml:space="preserve">1.06608748435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08320713043213</t>
   </si>
   <si>
     <t xml:space="preserve">1.06297492980957</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">1.09410154819489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07075667381287</t>
+    <t xml:space="preserve">1.07075655460358</t>
   </si>
   <si>
     <t xml:space="preserve">1.09721422195435</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">1.0365172624588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02251029014587</t>
+    <t xml:space="preserve">1.02251017093658</t>
   </si>
   <si>
     <t xml:space="preserve">0.996052622795105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01628494262695</t>
+    <t xml:space="preserve">1.01628482341766</t>
   </si>
   <si>
     <t xml:space="preserve">1.00850331783295</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">1.00072157382965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991383612155914</t>
+    <t xml:space="preserve">0.991383731365204</t>
   </si>
   <si>
     <t xml:space="preserve">0.96648234128952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9649258852005</t>
+    <t xml:space="preserve">0.96492600440979</t>
   </si>
   <si>
     <t xml:space="preserve">0.958700597286224</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.975820302963257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989827334880829</t>
+    <t xml:space="preserve">0.989827215671539</t>
   </si>
   <si>
     <t xml:space="preserve">0.969595015048981</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">0.980489253997803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999165236949921</t>
+    <t xml:space="preserve">0.99916535615921</t>
   </si>
   <si>
     <t xml:space="preserve">1.06453132629395</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">0.904228985309601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879327714443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887109398841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888665556907654</t>
+    <t xml:space="preserve">0.879327654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887109339237213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888665616512299</t>
   </si>
   <si>
     <t xml:space="preserve">0.891778409481049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835750341415405</t>
+    <t xml:space="preserve">0.83575040102005</t>
   </si>
   <si>
     <t xml:space="preserve">0.803067326545715</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">0.787504076957703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829524993896484</t>
+    <t xml:space="preserve">0.829525053501129</t>
   </si>
   <si>
     <t xml:space="preserve">0.831081390380859</t>
@@ -2579,22 +2579,22 @@
     <t xml:space="preserve">0.866877019405365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89644730091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902672588825226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915123283863068</t>
+    <t xml:space="preserve">0.896447241306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902672648429871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915123343467712</t>
   </si>
   <si>
     <t xml:space="preserve">0.940024495124817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963369727134705</t>
+    <t xml:space="preserve">0.977376639842987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963369607925415</t>
   </si>
   <si>
     <t xml:space="preserve">0.983601987361908</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">0.978932917118073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929130375385284</t>
+    <t xml:space="preserve">0.92913031578064</t>
   </si>
   <si>
     <t xml:space="preserve">0.961813151836395</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">0.930686712265015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952475190162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927573978900909</t>
+    <t xml:space="preserve">0.952475309371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927574038505554</t>
   </si>
   <si>
     <t xml:space="preserve">0.926017701625824</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">0.935355663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971151411533356</t>
+    <t xml:space="preserve">0.971151292324066</t>
   </si>
   <si>
     <t xml:space="preserve">0.947806358337402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919792354106903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913567006587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.907341718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.916679680347443</t>
+    <t xml:space="preserve">0.919792294502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913566946983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907341599464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916679739952087</t>
   </si>
   <si>
     <t xml:space="preserve">0.8995600938797</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">0.918236017227173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908897936344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894890904426575</t>
+    <t xml:space="preserve">0.908897995948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894890964031219</t>
   </si>
   <si>
     <t xml:space="preserve">0.910454332828522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944693624973297</t>
+    <t xml:space="preserve">0.944693684577942</t>
   </si>
   <si>
     <t xml:space="preserve">1.01784121990204</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">1.15946745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12989723682404</t>
+    <t xml:space="preserve">1.12989735603333</t>
   </si>
   <si>
     <t xml:space="preserve">1.10032689571381</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">1.25907278060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24662220478058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2528475522995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25440359115601</t>
+    <t xml:space="preserve">1.24662208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25284743309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2544037103653</t>
   </si>
   <si>
     <t xml:space="preserve">1.22638976573944</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">1.26841068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27307975292206</t>
+    <t xml:space="preserve">1.27307987213135</t>
   </si>
   <si>
     <t xml:space="preserve">1.36023437976837</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">1.40536797046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4380509853363</t>
+    <t xml:space="preserve">1.43805086612701</t>
   </si>
   <si>
     <t xml:space="preserve">1.52053654193878</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">1.57189548015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56022298336029</t>
+    <t xml:space="preserve">1.56022310256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.58745884895325</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">1.53765606880188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51431131362915</t>
+    <t xml:space="preserve">1.51431119441986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50341689586639</t>
@@ -2795,19 +2795,19 @@
     <t xml:space="preserve">1.50497317314148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49096620082855</t>
+    <t xml:space="preserve">1.49096632003784</t>
   </si>
   <si>
     <t xml:space="preserve">1.51798808574677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46871304512024</t>
+    <t xml:space="preserve">1.46871316432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.45281779766083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46712350845337</t>
+    <t xml:space="preserve">1.46712338924408</t>
   </si>
   <si>
     <t xml:space="preserve">1.47348153591156</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">1.48142910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54818868637085</t>
+    <t xml:space="preserve">1.54818880558014</t>
   </si>
   <si>
     <t xml:space="preserve">1.55454683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5561363697052</t>
+    <t xml:space="preserve">1.55613648891449</t>
   </si>
   <si>
     <t xml:space="preserve">1.57044196128845</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">1.56567347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56726312637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53706228733063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5275251865387</t>
+    <t xml:space="preserve">1.567263007164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53706216812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52752506732941</t>
   </si>
   <si>
     <t xml:space="preserve">1.47030258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44328081607819</t>
+    <t xml:space="preserve">1.4432806968689</t>
   </si>
   <si>
     <t xml:space="preserve">1.40672183036804</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">1.39241623878479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35744678974152</t>
+    <t xml:space="preserve">1.35744690895081</t>
   </si>
   <si>
     <t xml:space="preserve">1.34949922561646</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">1.34790980815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33201467990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35585737228394</t>
+    <t xml:space="preserve">1.33201456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35585725307465</t>
   </si>
   <si>
     <t xml:space="preserve">1.31929838657379</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">1.31453001499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27638161182404</t>
+    <t xml:space="preserve">1.27638149261475</t>
   </si>
   <si>
     <t xml:space="preserve">1.3018137216568</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">1.22074854373932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22233784198761</t>
+    <t xml:space="preserve">1.2223379611969</t>
   </si>
   <si>
     <t xml:space="preserve">1.2557178735733</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">1.28273963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21121144294739</t>
+    <t xml:space="preserve">1.2271066904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2112113237381</t>
   </si>
   <si>
     <t xml:space="preserve">1.2732025384903</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">1.35267841815948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3749315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37970006465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38128960132599</t>
+    <t xml:space="preserve">1.37493169307709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37969994544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38128972053528</t>
   </si>
   <si>
     <t xml:space="preserve">1.34314131736755</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">1.33678317070007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36221539974213</t>
+    <t xml:space="preserve">1.36221528053284</t>
   </si>
   <si>
     <t xml:space="preserve">1.363804936409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39877426624298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42897498607635</t>
+    <t xml:space="preserve">1.39877438545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42897510528564</t>
   </si>
   <si>
     <t xml:space="preserve">1.40513241291046</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">1.5338830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49732434749603</t>
+    <t xml:space="preserve">1.49732422828674</t>
   </si>
   <si>
     <t xml:space="preserve">1.47189211845398</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">1.45917594432831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46076536178589</t>
+    <t xml:space="preserve">1.46076548099518</t>
   </si>
   <si>
     <t xml:space="preserve">1.41943800449371</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">1.33996224403381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3415515422821</t>
+    <t xml:space="preserve">1.34155166149139</t>
   </si>
   <si>
     <t xml:space="preserve">1.3351936340332</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">1.52116715908051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49573469161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50845086574554</t>
+    <t xml:space="preserve">1.49573481082916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50845098495483</t>
   </si>
   <si>
     <t xml:space="preserve">1.51162993907928</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">1.51321947574615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47507107257843</t>
+    <t xml:space="preserve">1.47507095336914</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010174274445</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">1.4877872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47983968257904</t>
+    <t xml:space="preserve">1.47983956336975</t>
   </si>
   <si>
     <t xml:space="preserve">1.45599687099457</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">1.48301875591278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51004040241241</t>
+    <t xml:space="preserve">1.51004028320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.56249439716339</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">1.57362115383148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43851208686829</t>
+    <t xml:space="preserve">1.43851220607758</t>
   </si>
   <si>
     <t xml:space="preserve">1.44645977020264</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">1.51639842987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61335897445679</t>
+    <t xml:space="preserve">1.61335909366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.61733281612396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63322806358337</t>
+    <t xml:space="preserve">1.63322794437408</t>
   </si>
   <si>
     <t xml:space="preserve">1.62130653858185</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">1.58792674541473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60143768787384</t>
+    <t xml:space="preserve">1.60143780708313</t>
   </si>
   <si>
     <t xml:space="preserve">1.62925410270691</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">1.66104435920715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53865170478821</t>
+    <t xml:space="preserve">1.5386518239975</t>
   </si>
   <si>
     <t xml:space="preserve">1.51957750320435</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">1.52911472320557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53070402145386</t>
+    <t xml:space="preserve">1.53070414066315</t>
   </si>
   <si>
     <t xml:space="preserve">1.52434611320496</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">1.37334203720093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30817198753357</t>
+    <t xml:space="preserve">1.30817186832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.30022442340851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22869610786438</t>
+    <t xml:space="preserve">1.22869598865509</t>
   </si>
   <si>
     <t xml:space="preserve">1.23346471786499</t>
@@ -3191,64 +3191,64 @@
     <t xml:space="preserve">1.40831136703491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59746384620667</t>
+    <t xml:space="preserve">1.59746372699738</t>
   </si>
   <si>
     <t xml:space="preserve">1.7484678030014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78423178195953</t>
+    <t xml:space="preserve">1.78423190116882</t>
   </si>
   <si>
     <t xml:space="preserve">1.76038908958435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77231049537659</t>
+    <t xml:space="preserve">1.77231061458588</t>
   </si>
   <si>
     <t xml:space="preserve">1.78025805950165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74449396133423</t>
+    <t xml:space="preserve">1.74449408054352</t>
   </si>
   <si>
     <t xml:space="preserve">1.81999599933624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81204843521118</t>
+    <t xml:space="preserve">1.81204855442047</t>
   </si>
   <si>
     <t xml:space="preserve">1.83191752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8279435634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85178625583649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83589112758636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83986508846283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82396984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77628421783447</t>
+    <t xml:space="preserve">1.82794368267059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85178649425507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83589124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83986520767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82396996021271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77628433704376</t>
   </si>
   <si>
     <t xml:space="preserve">1.79217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76833665370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.788205742836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72859871387482</t>
+    <t xml:space="preserve">1.76833689212799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78820586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7285989522934</t>
   </si>
   <si>
     <t xml:space="preserve">1.64514923095703</t>
@@ -3257,16 +3257,16 @@
     <t xml:space="preserve">1.71667766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73654639720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75641548633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76436293125153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80410075187683</t>
+    <t xml:space="preserve">1.73654651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75641560554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76436305046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80410087108612</t>
   </si>
   <si>
     <t xml:space="preserve">1.7403576374054</t>
@@ -8638,7 +8638,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G140" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8664,7 +8664,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8690,7 +8690,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8716,7 +8716,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8742,7 +8742,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8794,7 +8794,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8820,7 +8820,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8846,7 +8846,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8872,7 +8872,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8898,7 +8898,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8924,7 +8924,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8950,7 +8950,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -8976,7 +8976,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G153" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9002,7 +9002,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9028,7 +9028,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9054,7 +9054,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9080,7 +9080,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9106,7 +9106,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9132,7 +9132,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9158,7 +9158,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9184,7 +9184,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9210,7 +9210,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9288,7 +9288,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9314,7 +9314,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9392,7 +9392,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9418,7 +9418,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9470,7 +9470,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9496,7 +9496,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9522,7 +9522,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9548,7 +9548,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9574,7 +9574,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9600,7 +9600,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9626,7 +9626,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9652,7 +9652,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9678,7 +9678,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9704,7 +9704,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9730,7 +9730,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9756,7 +9756,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9782,7 +9782,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9808,7 +9808,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9834,7 +9834,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9860,7 +9860,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9886,7 +9886,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9912,7 +9912,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9938,7 +9938,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9964,7 +9964,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9990,7 +9990,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10016,7 +10016,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10042,7 +10042,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10068,7 +10068,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10094,7 +10094,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10120,7 +10120,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10146,7 +10146,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10172,7 +10172,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10198,7 +10198,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10224,7 +10224,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10250,7 +10250,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10276,7 +10276,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10302,7 +10302,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10328,7 +10328,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10354,7 +10354,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10380,7 +10380,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10406,7 +10406,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10432,7 +10432,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10458,7 +10458,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10484,7 +10484,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10510,7 +10510,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10536,7 +10536,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10562,7 +10562,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10588,7 +10588,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10614,7 +10614,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10640,7 +10640,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G217" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10666,7 +10666,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10692,7 +10692,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10718,7 +10718,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10744,7 +10744,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10770,7 +10770,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10796,7 +10796,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10822,7 +10822,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10848,7 +10848,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10874,7 +10874,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10900,7 +10900,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10926,7 +10926,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10952,7 +10952,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10978,7 +10978,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11004,7 +11004,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11030,7 +11030,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11056,7 +11056,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11082,7 +11082,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11108,7 +11108,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11134,7 +11134,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11160,7 +11160,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="s">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11264,7 +11264,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11342,7 +11342,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11368,7 +11368,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11420,7 +11420,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11446,7 +11446,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11472,7 +11472,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11498,7 +11498,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11576,7 +11576,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11654,7 +11654,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11680,7 +11680,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11836,7 +11836,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11862,7 +11862,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G264" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11888,7 +11888,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11940,7 +11940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12174,7 +12174,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12252,7 +12252,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12746,7 +12746,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12876,7 +12876,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13136,7 +13136,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -72060,13 +72060,13 @@
     </row>
     <row r="2580">
       <c r="A2580" s="1" t="n">
-        <v>46078.6912847222</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2580" t="n">
         <v>108024</v>
       </c>
       <c r="C2580" t="n">
-        <v>2.68499994277954</v>
+        <v>2.6949999332428</v>
       </c>
       <c r="D2580" t="n">
         <v>2.63499999046326</v>
@@ -72081,6 +72081,32 @@
         <v>1537</v>
       </c>
       <c r="H2580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46079.6910185185</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>163751</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>2.6949999332428</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>2.71499991416931</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>1547</v>
+      </c>
+      <c r="H2581" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07385444641113</t>
+    <t xml:space="preserve">3.07385468482971</t>
   </si>
   <si>
     <t xml:space="preserve">CAI.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">3.08614468574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01786756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97690081596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98099732398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88131189346313</t>
+    <t xml:space="preserve">3.01786708831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97690033912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98099708557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88131165504456</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003057479858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80620646476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8608283996582</t>
+    <t xml:space="preserve">2.80620670318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86082863807678</t>
   </si>
   <si>
     <t xml:space="preserve">2.75841236114502</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">2.73929476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69013524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71744608879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86629104614258</t>
+    <t xml:space="preserve">2.69013500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71744585037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.866290807724</t>
   </si>
   <si>
     <t xml:space="preserve">2.76387429237366</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">2.7447566986084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7570469379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71061849594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73110151290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76114392280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72563910484314</t>
+    <t xml:space="preserve">2.75704717636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71061825752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73110175132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76114368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72563934326172</t>
   </si>
   <si>
     <t xml:space="preserve">2.69696259498596</t>
@@ -113,529 +113,532 @@
     <t xml:space="preserve">2.62868499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45935654640198</t>
+    <t xml:space="preserve">2.45935726165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45799112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30095291137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38971376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53992462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50442004203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67511391639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81713104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7488534450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78162693977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68467259407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83351755142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84717321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88404297828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88540887832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89769840240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85127019882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94685840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9495894908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05883359909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12164926528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16124963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18173265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17217397689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23635530471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25001120567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21040987968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22269940376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23089241981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14076662063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895987510681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225430727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21587204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30463314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2773220539093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34559917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36608290672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40704894065857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38656568527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33330941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34833025932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32511591911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32375073432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29780459403992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26366662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29097771644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26022291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19182634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1562032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1348295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17330288887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09208202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1490786075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32291913032532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34856748580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33431839942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38419079780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4440381526947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41981434822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43406367301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48108553886414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47681140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4383385181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45116233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40841507911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39844012260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714293479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02796030044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8997175693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8968677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06643319129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08495736122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1319797039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14195394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02938556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84984517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95671415328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06500816345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96526408195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9552891254425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99233722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12058019638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17045283317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23599886894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17757725715637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13625407218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83702087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9196662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86551880836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90399241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84129548072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87549352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83559560775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79854798316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73442602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771737575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88546800613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87406849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272050857544</t>
+  </